--- a/Kho_Can_Cu_Phap_Ly.xlsx
+++ b/Kho_Can_Cu_Phap_Ly.xlsx
@@ -1778,7 +1778,7 @@
       </c>
       <c r="J16" s="20" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 24/2024/NĐ-CP</t>
+          <t>Bị thay thế bởi 24/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="K16" s="20" t="inlineStr">
@@ -5835,132 +5835,132 @@
       </c>
     </row>
     <row r="79" ht="26" customHeight="1">
-      <c r="A79" s="34" t="n">
+      <c r="A79" s="26" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="35" t="inlineStr">
+      <c r="B79" s="27" t="inlineStr">
         <is>
           <t>Xây dựng &amp; Quản lý dự án</t>
         </is>
       </c>
-      <c r="C79" s="36" t="inlineStr">
+      <c r="C79" s="28" t="inlineStr">
         <is>
           <t>Nghị định</t>
         </is>
       </c>
-      <c r="D79" s="37" t="inlineStr">
+      <c r="D79" s="29" t="inlineStr">
         <is>
           <t>05/2025/NĐ-CP</t>
         </is>
       </c>
-      <c r="E79" s="35" t="inlineStr">
+      <c r="E79" s="27" t="inlineStr">
         <is>
           <t>Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP ngày 10 tháng 01 năm 2022 của Chính phủ quy định chi tiết một số điều của Luật Bảo vệ môi trường</t>
         </is>
       </c>
-      <c r="F79" s="38" t="inlineStr">
+      <c r="F79" s="30" t="inlineStr">
         <is>
           <t>Chính phủ</t>
         </is>
       </c>
-      <c r="G79" s="36" t="inlineStr">
+      <c r="G79" s="28" t="inlineStr">
         <is>
           <t>06/01/2025</t>
         </is>
       </c>
-      <c r="H79" s="36" t="inlineStr">
+      <c r="H79" s="28" t="inlineStr">
         <is>
           <t>06/01/2025</t>
         </is>
       </c>
-      <c r="I79" s="34" t="inlineStr">
+      <c r="I79" s="31" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
-      <c r="J79" s="35" t="inlineStr">
+      <c r="J79" s="27" t="inlineStr">
         <is>
           <t>Sửa đổi, bổ sung Nghị định số 08/2022/NĐ-CP; được sửa đổi bởi Nghị định 48/2026/NĐ-CP</t>
         </is>
       </c>
-      <c r="K79" s="35" t="inlineStr">
+      <c r="K79" s="27" t="inlineStr">
         <is>
           <t>Quy định phân quyền và cắt giảm thủ tục cấp Giấy phép môi trường, Đăng ký môi trường</t>
         </is>
       </c>
-      <c r="L79" s="35" t="inlineStr">
+      <c r="L79" s="27" t="inlineStr">
         <is>
           <t>MOI_TRUONG, TV-04, XD-01</t>
         </is>
       </c>
-      <c r="M79" s="39" t="inlineStr"/>
-      <c r="N79" s="36" t="inlineStr">
+      <c r="M79" s="32" t="inlineStr"/>
+      <c r="N79" s="28" t="inlineStr">
         <is>
           <t>2026-08-21 11:07</t>
         </is>
       </c>
     </row>
     <row r="80" ht="26" customHeight="1">
-      <c r="A80" s="34" t="n">
+      <c r="A80" s="19" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="35" t="inlineStr">
+      <c r="B80" s="20" t="inlineStr">
         <is>
           <t>Xây dựng &amp; Quản lý dự án</t>
         </is>
       </c>
-      <c r="C80" s="36" t="inlineStr">
+      <c r="C80" s="21" t="inlineStr">
         <is>
           <t>Nghị định</t>
         </is>
       </c>
-      <c r="D80" s="37" t="inlineStr">
+      <c r="D80" s="22" t="inlineStr">
         <is>
           <t>48/2026/NĐ-CP</t>
         </is>
       </c>
-      <c r="E80" s="35" t="inlineStr">
+      <c r="E80" s="20" t="inlineStr">
         <is>
           <t>Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP ngày 10 tháng 01 năm 2022 của Chính phủ quy định chi tiết một số điều của Luật Bảo vệ môi trường được sửa đổi, bổ sung bởi Nghị định số 05/2025/NĐ-CP ngày 06 tháng 01 năm 2025</t>
         </is>
       </c>
-      <c r="F80" s="38" t="inlineStr">
+      <c r="F80" s="23" t="inlineStr">
         <is>
           <t>Chính phủ</t>
         </is>
       </c>
-      <c r="G80" s="36" t="inlineStr">
+      <c r="G80" s="21" t="inlineStr">
         <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="H80" s="36" t="inlineStr">
+      <c r="H80" s="21" t="inlineStr">
         <is>
           <t>01/07/2026</t>
         </is>
       </c>
-      <c r="I80" s="34" t="inlineStr">
+      <c r="I80" s="31" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
-      <c r="J80" s="35" t="inlineStr">
+      <c r="J80" s="20" t="inlineStr">
         <is>
           <t>Sửa đổi, bổ sung Nghị định số 08/2022/NĐ-CP và Nghị định số 05/2025/NĐ-CP</t>
         </is>
       </c>
-      <c r="K80" s="35" t="inlineStr">
+      <c r="K80" s="20" t="inlineStr">
         <is>
           <t>Đơn giản hóa tối đa thủ tục môi trường cho các công trình xây dựng và dự án đầu tư công hiện hành</t>
         </is>
       </c>
-      <c r="L80" s="35" t="inlineStr">
+      <c r="L80" s="20" t="inlineStr">
         <is>
           <t>ALL, MOI_TRUONG, TV-04, XD-01</t>
         </is>
       </c>
-      <c r="M80" s="39" t="inlineStr"/>
-      <c r="N80" s="36" t="inlineStr">
+      <c r="M80" s="25" t="inlineStr"/>
+      <c r="N80" s="21" t="inlineStr">
         <is>
           <t>2026-08-21 11:07</t>
         </is>

--- a/Kho_Can_Cu_Phap_Ly.xlsx
+++ b/Kho_Can_Cu_Phap_Ly.xlsx
@@ -45,13 +45,13 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00991B1B"/>
+      <color rgb="00065F46"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00065F46"/>
+      <color rgb="00991B1B"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -76,8 +76,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
-        <bgColor rgb="00FEE2E2"/>
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -88,8 +88,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D1FAE5"/>
-        <bgColor rgb="00D1FAE5"/>
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -174,11 +174,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N80"/>
+  <dimension ref="A1:N87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -642,7 +642,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Xây dựng &amp; Quản lý dự án</t>
+          <t>Quy hoạch Xây dựng</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -652,12 +652,12 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>50/2014/QH13</t>
+          <t>30/2009/QH12</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Luật Xây dựng năm 2014</t>
+          <t>Luật Quy hoạch đô thị năm 2009 (sửa đổi, bổ sung bởi Luật số 35/2018/QH14)</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
@@ -667,38 +667,38 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>18/06/2014</t>
+          <t>17/06/2009</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>01/01/2015</t>
+          <t>01/01/2010</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Luật Xây dựng số 135/2025/QH15</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Dự án đã phê duyệt trước thời điểm luật mới thực hiện theo quy định chuyển tiếp</t>
+          <t>Căn cứ pháp lý nền tảng cho việc lập, thẩm định và phê duyệt điều chỉnh Quy hoạch Tổng mặt bằng 1/500 doanh trại và khu chức năng</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>ALL, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+          <t>ALL, QUY_HOACH, TV-01, TV-02, BQP</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr"/>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -708,63 +708,63 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Xây dựng &amp; Quản lý dự án</t>
+          <t>Quy hoạch Xây dựng</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>135/2025/QH15</t>
+          <t>44/2015/NĐ-CP</t>
         </is>
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>Luật Xây dựng năm 2025</t>
+          <t>Quy định chi tiết một số nội dung về quy hoạch xây dựng</t>
         </is>
       </c>
       <c r="F3" s="13" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>06/05/2015</t>
         </is>
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="I3" s="14" t="inlineStr">
+          <t>30/06/2015</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J3" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Luật Xây dựng 50/2014/QH13 và Luật sửa đổi 62/2020/QH14</t>
+          <t>Được sửa đổi, bổ sung bởi Nghị định số 35/2023/NĐ-CP và Nghị định số 72/2019/NĐ-CP</t>
         </is>
       </c>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng toàn diện cho các dự án đầu tư xây dựng mới</t>
+          <t>Quy định trình tự, thủ tục lập và phê duyệt Quy hoạch chi tiết và Quy hoạch Tổng mặt bằng công trình</t>
         </is>
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <t>ALL, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
-        </is>
-      </c>
-      <c r="M3" s="15" t="inlineStr"/>
+          <t>ALL, QUY_HOACH, TV-01, TV-02, QLDA</t>
+        </is>
+      </c>
+      <c r="M3" s="14" t="inlineStr"/>
       <c r="N3" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -774,63 +774,63 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Xây dựng &amp; Quản lý dự án</t>
+          <t>Quy hoạch Xây dựng</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>62/2020/QH14</t>
+          <t>04/2022/TT-BXD</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Luật sửa đổi, bổ sung một số điều của Luật Xây dựng</t>
+          <t>Quy định về hồ sơ nhiệm vụ và hồ sơ đồ án quy hoạch xây dựng vùng liên huyện, quy hoạch xây dựng vùng huyện, quy hoạch đô thị, quy hoạch xây dựng khu chức năng và quy hoạch nông thôn</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>17/06/2020</t>
+          <t>24/10/2022</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Luật Xây dựng số 135/2025/QH15</t>
+          <t>Thay thế Thông tư 12/2016/TT-BXD và Thông tư 02/2017/TT-BXD</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Quy định chuyển tiếp thẩm định thiết kế, cấp phép</t>
+          <t>Quy định thành phần hồ sơ bản vẽ, thuyết minh và quy cách đồ án quy hoạch Tổng mặt bằng tỷ lệ 1/500 gói TV-01</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>ALL, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+          <t>QUY_HOACH, TV-01, HO_SO_QUY_HOACH</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -840,63 +840,63 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Xây dựng &amp; Quản lý dự án</t>
+          <t>Quy hoạch Xây dựng</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>15/2021/NĐ-CP</t>
+          <t>20/2019/TT-BXD</t>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số nội dung về quản lý dự án đầu tư xây dựng</t>
+          <t>Hướng dẫn xác định, quản lý chi phí quy hoạch xây dựng và quy hoạch đô thị</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>03/03/2021</t>
+          <t>31/12/2019</t>
         </is>
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>03/03/2021</t>
+          <t>15/02/2020</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 175/2024/NĐ-CP và Nghị định 217/2026/NĐ-CP</t>
+          <t>Thay thế Thông tư 01/2013/TT-BXD</t>
         </is>
       </c>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng cho các dự án đã trình thẩm định giai đoạn 2021-2024</t>
+          <t>Căn cứ lập dự toán chi phí gói thầu TV-01 Tư vấn lập quy hoạch Tổng mặt bằng tỷ lệ 1/500</t>
         </is>
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
-          <t>ALL, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
-        </is>
-      </c>
-      <c r="M5" s="15" t="inlineStr"/>
+          <t>QUY_HOACH, CHI_PHI_QUY_HOACH, DU_TOAN, TV-01</t>
+        </is>
+      </c>
+      <c r="M5" s="14" t="inlineStr"/>
       <c r="N5" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -906,63 +906,63 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Xây dựng &amp; Quản lý dự án</t>
+          <t>Quy chuẩn Xây dựng</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>175/2024/NĐ-CP</t>
+          <t>01/2021/TT-BXD</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Xây dựng về quản lý hoạt động xây dựng</t>
+          <t>Ban hành Quy chuẩn kỹ thuật quốc gia về Quy hoạch xây dựng (Mã số: QCVN 01:2021/BXD)</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>30/12/2024</t>
+          <t>19/05/2021</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>15/02/2025</t>
+          <t>05/07/2021</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 217/2026/NĐ-CP</t>
+          <t>Thay thế QCVN 01:2019/BXD ban hành kèm Thông tư 22/2019/TT-BXD</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng giai đoạn chuyển tiếp 2025</t>
+          <t>Quy chuẩn bắt buộc áp dụng cho gói TV-01 về mật độ xây dựng, khoảng lùi công trình, khoảng cách an toàn PCCC, chỉ giới đường đỏ</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>ALL, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+          <t>QCVN, QUY_HOACH, TV-01, TV-02, TV-04, XD-01</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr"/>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -972,63 +972,63 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Xây dựng &amp; Quản lý dự án</t>
+          <t>Khảo sát &amp; Đo đạc</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>217/2026/NĐ-CP</t>
+          <t>27/2018/QH14</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Xây dựng về quản lý hoạt động xây dựng</t>
+          <t>Luật Đo đạc và bản đồ năm 2018</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2018</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
+          <t>01/01/2019</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J7" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 15/2021/NĐ-CP và Nghị định 175/2024/NĐ-CP</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K7" s="10" t="inlineStr">
         <is>
-          <t>Căn cứ pháp lý then chốt về quản lý dự án đầu tư xây dựng hiện hành</t>
+          <t>Căn cứ pháp lý cho công tác đo đạc khảo sát địa hình, trắc địa công trình phục vụ lập quy hoạch TV-01 và khảo sát TV-02</t>
         </is>
       </c>
       <c r="L7" s="10" t="inlineStr">
         <is>
-          <t>ALL, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
-        </is>
-      </c>
-      <c r="M7" s="15" t="inlineStr"/>
+          <t>KHAO_SAT, DO_DAC, TV-01, TV-02, XD-01</t>
+        </is>
+      </c>
+      <c r="M7" s="14" t="inlineStr"/>
       <c r="N7" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Xây dựng &amp; Quản lý dự án</t>
+          <t>Khảo sát &amp; Đo đạc</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -1048,12 +1048,12 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>35/2023/NĐ-CP</t>
+          <t>27/2019/NĐ-CP</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của các Nghị định thuộc lĩnh vực quản lý nhà nước của Bộ Xây dựng</t>
+          <t>Quy định chi tiết một số điều của Luật Đo đạc và bản đồ</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -1063,38 +1063,38 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>20/06/2023</t>
+          <t>13/03/2019</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>20/06/2023</t>
-        </is>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
+          <t>01/05/2019</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Được sửa đổi, bổ sung bởi Nghị định 136/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Phân cấp thẩm quyền thẩm định Báo cáo KT-KT và thiết kế dự toán</t>
+          <t>Quy định quy chuẩn đo đạc bản đồ địa hình tỷ lệ 1/500 phục vụ lập quy hoạch TMB và thiết kế xây dựng</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>ALL, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+          <t>KHAO_SAT, DO_DAC, TV-01, TV-02, XD-01</t>
         </is>
       </c>
       <c r="M8" s="8" t="inlineStr"/>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -1109,58 +1109,58 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Nghị quyết</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>66.19/2026/NQ-CP</t>
+          <t>50/2014/QH13</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>Về cắt giảm, phân quyền, đơn giản hóa thủ tục hành chính và cắt giảm, đơn giản hóa điều kiện kinh doanh thuộc phạm vi quản lý của Bộ Nông nghiệp và Môi trường</t>
+          <t>Luật Xây dựng năm 2014</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>18/06/2014</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>28/02/2027</t>
-        </is>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>01/01/2015</t>
+        </is>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J9" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bị thay thế bởi Luật Xây dựng số 135/2025/QH15</t>
         </is>
       </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
-          <t>Cắt giảm, phân quyền thủ tục môi trường và thủ tục hành chính</t>
+          <t>Dự án đã phê duyệt trước thời điểm luật mới thực hiện theo quy định chuyển tiếp</t>
         </is>
       </c>
       <c r="L9" s="10" t="inlineStr">
         <is>
-          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
-        </is>
-      </c>
-      <c r="M9" s="15" t="inlineStr"/>
+          <t>ALL, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+        </is>
+      </c>
+      <c r="M9" s="14" t="inlineStr"/>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Đấu thầu qua mạng</t>
+          <t>Xây dựng &amp; Quản lý dự án</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>22/2023/QH15</t>
+          <t>135/2025/QH15</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Luật Đấu thầu năm 2023</t>
+          <t>Luật Xây dựng năm 2025</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -1195,38 +1195,38 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>23/06/2023</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
-        </is>
-      </c>
-      <c r="I10" s="14" t="inlineStr">
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Luật Đấu thầu 43/2013/QH13</t>
+          <t>Thay thế Luật Xây dựng 50/2014/QH13 và Luật sửa đổi 62/2020/QH14</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Gói thầu phát hành HSMT từ 01/01/2024 áp dụng Luật 22</t>
+          <t>Áp dụng toàn diện cho các dự án đầu tư xây dựng mới</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
+          <t>ALL, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M10" s="8" t="inlineStr"/>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Đấu thầu qua mạng</t>
+          <t>Xây dựng &amp; Quản lý dự án</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>57/2024/QH15</t>
+          <t>62/2020/QH14</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>Luật sửa đổi, bổ sung một số điều của Luật Quy hoạch, Luật Đầu tư, Luật Đầu tư theo phương thức đối tác công tư và Luật Đấu thầu</t>
+          <t>Luật sửa đổi, bổ sung một số điều của Luật Xây dựng</t>
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr">
@@ -1261,38 +1261,38 @@
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>29/11/2024</t>
+          <t>17/06/2020</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>15/01/2025</t>
-        </is>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>01/01/2021</t>
+        </is>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bị thay thế bởi Luật Xây dựng số 135/2025/QH15</t>
         </is>
       </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>Nâng hạn mức chỉ định thầu và đơn giản hóa thủ tục đầu tư</t>
+          <t>Quy định chuyển tiếp thẩm định thiết kế, cấp phép</t>
         </is>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
-        </is>
-      </c>
-      <c r="M11" s="15" t="inlineStr"/>
+          <t>ALL, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+        </is>
+      </c>
+      <c r="M11" s="14" t="inlineStr"/>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -1302,63 +1302,63 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Đấu thầu qua mạng</t>
+          <t>Xây dựng &amp; Quản lý dự án</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>90/2025/QH15</t>
+          <t>15/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Luật sửa đổi bổ sung Luật Đấu thầu</t>
+          <t>Quy định chi tiết một số nội dung về quản lý dự án đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>25/06/2025</t>
+          <t>03/03/2021</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>01/08/2025</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
+          <t>03/03/2021</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Luật Đấu thầu số 22/2023/QH15</t>
+          <t>Bị thay thế bởi Nghị định 175/2024/NĐ-CP và Nghị định 217/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi bổ sung cơ chế đấu thầu thuốc, vật tư và mua sắm công</t>
+          <t>Áp dụng cho các dự án đã trình thẩm định giai đoạn 2021-2024</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, KHLCNT</t>
+          <t>ALL, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr"/>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -1368,63 +1368,63 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Đấu thầu qua mạng</t>
+          <t>Xây dựng &amp; Quản lý dự án</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>43/2013/QH13</t>
+          <t>175/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>Luật Đấu thầu năm 2013</t>
+          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Xây dựng về quản lý hoạt động xây dựng</t>
         </is>
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>26/11/2013</t>
+          <t>30/12/2024</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>01/07/2014</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
+          <t>15/02/2025</t>
+        </is>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Luật Đấu thầu 22/2023/QH15</t>
+          <t>Bị thay thế bởi Nghị định 217/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng cho các gói thầu mở trước 2024</t>
+          <t>Áp dụng giai đoạn chuyển tiếp 2025</t>
         </is>
       </c>
       <c r="L13" s="10" t="inlineStr">
         <is>
-          <t>DAU_THAU, LICHSU</t>
-        </is>
-      </c>
-      <c r="M13" s="15" t="inlineStr"/>
+          <t>ALL, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+        </is>
+      </c>
+      <c r="M13" s="14" t="inlineStr"/>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Đấu thầu qua mạng</t>
+          <t>Xây dựng &amp; Quản lý dự án</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1444,12 +1444,12 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>24/2024/NĐ-CP</t>
+          <t>217/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Đấu thầu về lựa chọn nhà thầu</t>
+          <t>Quy định chi tiết một số điều của Luật Xây dựng về quản lý hoạt động xây dựng</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -1459,38 +1459,38 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>27/02/2024</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>27/02/2024</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 214/2025/NĐ-CP</t>
+          <t>Thay thế Nghị định 15/2021/NĐ-CP và Nghị định 175/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng cho các gói thầu phát hành E-HSMT giai đoạn 2024-2025</t>
+          <t>Căn cứ pháp lý then chốt về quản lý dự án đầu tư xây dựng hiện hành</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
+          <t>ALL, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr"/>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Đấu thầu qua mạng</t>
+          <t>Xây dựng &amp; Quản lý dự án</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -1510,12 +1510,12 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>214/2025/NĐ-CP</t>
+          <t>35/2023/NĐ-CP</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Đấu thầu về lựa chọn nhà thầu</t>
+          <t>Sửa đổi, bổ sung một số điều của các Nghị định thuộc lĩnh vực quản lý nhà nước của Bộ Xây dựng</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
@@ -1525,38 +1525,38 @@
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>15/12/2025</t>
+          <t>20/06/2023</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-      <c r="I15" s="14" t="inlineStr">
+          <t>20/06/2023</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J15" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 24/2024/NĐ-CP</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K15" s="10" t="inlineStr">
         <is>
-          <t>Quy định toàn diện về lựa chọn nhà thầu qua mạng trên Hệ thống e-GP mới</t>
+          <t>Phân cấp thẩm quyền thẩm định Báo cáo KT-KT và thiết kế dự toán</t>
         </is>
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
-        </is>
-      </c>
-      <c r="M15" s="15" t="inlineStr"/>
+          <t>ALL, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+        </is>
+      </c>
+      <c r="M15" s="14" t="inlineStr"/>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -1566,22 +1566,22 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Đấu thầu qua mạng</t>
+          <t>Xây dựng &amp; Quản lý dự án</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Nghị quyết</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>63/2014/NĐ-CP</t>
+          <t>66.19/2026/NQ-CP</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết thi hành một số điều của Luật Đấu thầu về lựa chọn nhà thầu</t>
+          <t>Về cắt giảm, phân quyền, đơn giản hóa thủ tục hành chính và cắt giảm, đơn giản hóa điều kiện kinh doanh thuộc phạm vi quản lý của Bộ Nông nghiệp và Môi trường</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -1591,38 +1591,38 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>26/06/2014</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>15/08/2014</t>
+          <t>28/02/2027</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 24/2024/NĐ-CP</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng cho gói thầu mở trước 27/02/2024</t>
+          <t>Cắt giảm, phân quyền thủ tục môi trường và thủ tục hành chính</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>DAU_THAU, LICHSU</t>
+          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr"/>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -1637,58 +1637,58 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>06/2024/TT-BKHĐT</t>
+          <t>22/2023/QH15</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>Hướng dẫn việc cung cấp, đăng tải thông tin về lựa chọn nhà thầu và mẫu hồ sơ đấu thầu trên Hệ thống mạng đấu thầu quốc gia</t>
+          <t>Luật Đấu thầu năm 2023</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>Bộ Kế hoạch và Đầu tư</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>23/06/2023</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J17" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 22/2024/TT-BKHĐT và Thông tư 79/2025/TT-BTC</t>
+          <t>Luật Đấu thầu 43/2013/QH13</t>
         </is>
       </c>
       <c r="K17" s="10" t="inlineStr">
         <is>
-          <t>Mẫu E-HSMT giai đoạn đầu 2024</t>
+          <t>Gói thầu phát hành HSMT từ 01/01/2024 áp dụng Luật 22</t>
         </is>
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
-        </is>
-      </c>
-      <c r="M17" s="15" t="inlineStr"/>
+          <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
+        </is>
+      </c>
+      <c r="M17" s="14" t="inlineStr"/>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -1703,58 +1703,58 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>22/2024/TT-BKHĐT</t>
+          <t>57/2024/QH15</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Hướng dẫn việc cung cấp, đăng tải thông tin về lựa chọn nhà thầu và mẫu hồ sơ đấu thầu trên Hệ thống mạng đấu thầu quốc gia</t>
+          <t>Luật sửa đổi, bổ sung một số điều của Luật Quy hoạch, Luật Đầu tư, Luật Đầu tư theo phương thức đối tác công tư và Luật Đấu thầu</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>Bộ Kế hoạch và Đầu tư</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>15/11/2024</t>
+          <t>29/11/2024</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>15/01/2025</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 79/2025/TT-BTC</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng giai đoạn chuyển giao 2024-2025</t>
+          <t>Nâng hạn mức chỉ định thầu và đơn giản hóa thủ tục đầu tư</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
+          <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
         </is>
       </c>
       <c r="M18" s="8" t="inlineStr"/>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -1769,58 +1769,58 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>79/2025/TT-BTC</t>
+          <t>90/2025/QH15</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>Hướng dẫn việc cung cấp, đăng tải thông tin về đấu thầu và mẫu hồ sơ đấu thầu trên Hệ thống mạng đấu thầu quốc gia</t>
+          <t>Luật sửa đổi bổ sung Luật Đấu thầu</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>Bộ Tài chính</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>25/06/2025</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-      <c r="I19" s="14" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>01/08/2025</t>
+        </is>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J19" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 06/2024/TT-BKHĐT và Thông tư 22/2024/TT-BKHĐT</t>
+          <t>Sửa đổi, bổ sung một số điều của Luật Đấu thầu số 22/2023/QH15</t>
         </is>
       </c>
       <c r="K19" s="10" t="inlineStr">
         <is>
-          <t>Bộ mẫu E-HSMT chuẩn áp dụng bắt buộc hiện hành</t>
+          <t>Sửa đổi bổ sung cơ chế đấu thầu thuốc, vật tư và mua sắm công</t>
         </is>
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
-        </is>
-      </c>
-      <c r="M19" s="15" t="inlineStr"/>
+          <t>ALL, DAU_THAU, KHLCNT</t>
+        </is>
+      </c>
+      <c r="M19" s="14" t="inlineStr"/>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -1835,58 +1835,58 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>07/2024/TT-BKHĐT</t>
+          <t>43/2013/QH13</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết mẫu hồ sơ yêu cầu, báo cáo đánh giá, báo cáo thẩm định, kiểm tra, giám sát hoạt động đấu thầu</t>
+          <t>Luật Đấu thầu năm 2013</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>Bộ Kế hoạch và Đầu tư</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>26/11/2013</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>15/06/2024</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
+          <t>01/07/2014</t>
+        </is>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 23/2024/TT-BKHĐT và Thông tư 80/2025/TT-BTC</t>
+          <t>Bị thay thế bởi Luật Đấu thầu 22/2023/QH15</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng giai đoạn đầu 2024</t>
+          <t>Áp dụng cho các gói thầu mở trước 2024</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
+          <t>DAU_THAU, LICHSU</t>
         </is>
       </c>
       <c r="M20" s="8" t="inlineStr"/>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -1901,58 +1901,58 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>23/2024/TT-BKHĐT</t>
+          <t>24/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết mẫu hồ sơ yêu cầu, báo cáo đánh giá, báo cáo thẩm định, kiểm tra, báo cáo tình hình thực hiện hoạt động đấu thầu</t>
+          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Đấu thầu về lựa chọn nhà thầu</t>
         </is>
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>Bộ Kế hoạch và Đầu tư</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>18/11/2024</t>
+          <t>27/02/2024</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
+          <t>27/02/2024</t>
+        </is>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J21" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 80/2025/TT-BTC</t>
+          <t>Bị thay thế bởi Nghị định 214/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng giai đoạn cuối 2024</t>
+          <t>Áp dụng cho các gói thầu phát hành E-HSMT giai đoạn 2024-2025</t>
         </is>
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
-        </is>
-      </c>
-      <c r="M21" s="15" t="inlineStr"/>
+          <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
+        </is>
+      </c>
+      <c r="M21" s="14" t="inlineStr"/>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -1967,27 +1967,27 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>80/2025/TT-BTC</t>
+          <t>214/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết mẫu hồ sơ yêu cầu, báo cáo đánh giá, báo cáo thẩm định, kiểm tra, báo cáo tình hình thực hiện hoạt động đấu thầu</t>
+          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Đấu thầu về lựa chọn nhà thầu</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>Bộ Tài chính</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>15/12/2025</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1995,30 +1995,30 @@
           <t>01/01/2026</t>
         </is>
       </c>
-      <c r="I22" s="14" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 07/2024/TT-BKHĐT và Thông tư 23/2024/TT-BKHĐT</t>
+          <t>Thay thế Nghị định 24/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Bộ mẫu HSYC, Báo cáo đánh giá, Thẩm định chỉ định thầu hiện hành</t>
+          <t>Quy định toàn diện về lựa chọn nhà thầu qua mạng trên Hệ thống e-GP mới</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
+          <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
         </is>
       </c>
       <c r="M22" s="8" t="inlineStr"/>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -2033,58 +2033,58 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>15/2024/TT-BKHĐT</t>
+          <t>63/2014/NĐ-CP</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>Quy định mẫu hồ sơ đấu thầu lựa chọn nhà đầu tư thực hiện dự án PPP, dự án đầu tư kinh doanh; cung cấp, đăng tải thông tin trên Hệ thống mạng đấu thầu quốc gia</t>
+          <t>Quy định chi tiết thi hành một số điều của Luật Đấu thầu về lựa chọn nhà thầu</t>
         </is>
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>Bộ Kế hoạch và Đầu tư</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>30/09/2024</t>
+          <t>26/06/2014</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>30/09/2024</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
+          <t>15/08/2014</t>
+        </is>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 98/2025/TT-BTC</t>
+          <t>Bị thay thế bởi Nghị định 24/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng giai đoạn 2024</t>
+          <t>Áp dụng cho gói thầu mở trước 27/02/2024</t>
         </is>
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>DAU_THAU, DAU_TU_KINH_DOANH, PPP</t>
-        </is>
-      </c>
-      <c r="M23" s="15" t="inlineStr"/>
+          <t>DAU_THAU, LICHSU</t>
+        </is>
+      </c>
+      <c r="M23" s="14" t="inlineStr"/>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -2104,53 +2104,53 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>98/2025/TT-BTC</t>
+          <t>06/2024/TT-BKHĐT</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Quy định mẫu hồ sơ đấu thầu lựa chọn nhà đầu tư thực hiện dự án đầu tư theo phương thức đối tác công tư, dự án đầu tư kinh doanh; cung cấp, đăng tải thông tin về đầu tư theo phương thức đối tác công tư, đấu thầu lựa chọn nhà đầu tư trên Hệ thống mạng đấu thầu quốc gia</t>
+          <t>Hướng dẫn việc cung cấp, đăng tải thông tin về lựa chọn nhà thầu và mẫu hồ sơ đấu thầu trên Hệ thống mạng đấu thầu quốc gia</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>Bộ Tài chính</t>
+          <t>Bộ Kế hoạch và Đầu tư</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>15/11/2025</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-      <c r="I24" s="14" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>26/04/2024</t>
+        </is>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 15/2024/TT-BKHĐT</t>
+          <t>Bị thay thế bởi Thông tư 22/2024/TT-BKHĐT và Thông tư 79/2025/TT-BTC</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>Quy định mẫu đấu thầu dự án PPP và kinh doanh hiện hành</t>
+          <t>Mẫu E-HSMT giai đoạn đầu 2024</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>DAU_THAU, DAU_TU_KINH_DOANH, PPP</t>
+          <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
         </is>
       </c>
       <c r="M24" s="8" t="inlineStr"/>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -2160,63 +2160,63 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Quản lý Chi phí &amp; Dự toán</t>
+          <t>Đấu thầu qua mạng</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>10/2021/NĐ-CP</t>
+          <t>22/2024/TT-BKHĐT</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>Về quản lý chi phí đầu tư xây dựng</t>
+          <t>Hướng dẫn việc cung cấp, đăng tải thông tin về lựa chọn nhà thầu và mẫu hồ sơ đấu thầu trên Hệ thống mạng đấu thầu quốc gia</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Kế hoạch và Đầu tư</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>09/02/2021</t>
+          <t>15/11/2024</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>09/02/2021</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 206/2026/NĐ-CP</t>
+          <t>Bị thay thế bởi Thông tư 79/2025/TT-BTC</t>
         </is>
       </c>
       <c r="K25" s="10" t="inlineStr">
         <is>
-          <t>Dự toán duyệt trước 2026 tiếp tục áp dụng theo phê duyệt</t>
+          <t>Áp dụng giai đoạn chuyển giao 2024-2025</t>
         </is>
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
-          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
-        </is>
-      </c>
-      <c r="M25" s="15" t="inlineStr"/>
+          <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
+        </is>
+      </c>
+      <c r="M25" s="14" t="inlineStr"/>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -2226,63 +2226,63 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Quản lý Chi phí &amp; Dự toán</t>
+          <t>Đấu thầu qua mạng</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>206/2026/NĐ-CP</t>
+          <t>79/2025/TT-BTC</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết về quản lý chi phí đầu tư xây dựng</t>
+          <t>Hướng dẫn việc cung cấp, đăng tải thông tin về đấu thầu và mẫu hồ sơ đấu thầu trên Hệ thống mạng đấu thầu quốc gia</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Tài chính</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="I26" s="14" t="inlineStr">
+          <t>01/01/2026</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 10/2021/NĐ-CP</t>
+          <t>Thay thế Thông tư 06/2024/TT-BKHĐT và Thông tư 22/2024/TT-BKHĐT</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>Căn cứ pháp lý then chốt về quản lý chi phí và dự toán hiện hành</t>
+          <t>Bộ mẫu E-HSMT chuẩn áp dụng bắt buộc hiện hành</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
+          <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
         </is>
       </c>
       <c r="M26" s="8" t="inlineStr"/>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Quản lý Chi phí &amp; Dự toán</t>
+          <t>Đấu thầu qua mạng</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -2302,53 +2302,53 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>11/2021/TT-BXD</t>
+          <t>07/2024/TT-BKHĐT</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>Hướng dẫn một số nội dung xác định và quản lý chi phí đầu tư xây dựng</t>
+          <t>Quy định chi tiết mẫu hồ sơ yêu cầu, báo cáo đánh giá, báo cáo thẩm định, kiểm tra, giám sát hoạt động đấu thầu</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Bộ Kế hoạch và Đầu tư</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>31/08/2021</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>15/10/2021</t>
-        </is>
-      </c>
-      <c r="I27" s="14" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>15/06/2024</t>
+        </is>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J27" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bị thay thế bởi Thông tư 23/2024/TT-BKHĐT và Thông tư 80/2025/TT-BTC</t>
         </is>
       </c>
       <c r="K27" s="10" t="inlineStr">
         <is>
-          <t>Phương pháp lập đơn giá xây dựng và tổng mức đầu tư</t>
+          <t>Áp dụng giai đoạn đầu 2024</t>
         </is>
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
-        </is>
-      </c>
-      <c r="M27" s="15" t="inlineStr"/>
+          <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
+        </is>
+      </c>
+      <c r="M27" s="14" t="inlineStr"/>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Quản lý Chi phí &amp; Dự toán</t>
+          <t>Đấu thầu qua mạng</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2368,53 +2368,53 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>12/2021/TT-BXD</t>
+          <t>23/2024/TT-BKHĐT</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Ban hành định mức xây dựng (Định mức dự toán, định mức chi phí tư vấn và QLDA)</t>
+          <t>Quy định chi tiết mẫu hồ sơ yêu cầu, báo cáo đánh giá, báo cáo thẩm định, kiểm tra, báo cáo tình hình thực hiện hoạt động đấu thầu</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Bộ Kế hoạch và Đầu tư</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>31/08/2021</t>
+          <t>18/11/2024</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>15/10/2021</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="I28" s="15" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 38/2026/TT-BXD</t>
+          <t>Bị thay thế bởi Thông tư 80/2025/TT-BTC</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>Bộ định mức gốc tính chi phí tư vấn và xây lắp giai đoạn 2021-2026</t>
+          <t>Áp dụng giai đoạn cuối 2024</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>ALL, DINH_MUC, DU_TOAN, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-08, TV-09, XD-01</t>
+          <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
         </is>
       </c>
       <c r="M28" s="8" t="inlineStr"/>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Quản lý Chi phí &amp; Dự toán</t>
+          <t>Đấu thầu qua mạng</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
@@ -2434,53 +2434,53 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>13/2021/TT-BXD</t>
+          <t>80/2025/TT-BTC</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>Hướng dẫn phương pháp xác định các chỉ tiêu kinh tế kỹ thuật và đo bóc khối lượng công trình</t>
+          <t>Quy định chi tiết mẫu hồ sơ yêu cầu, báo cáo đánh giá, báo cáo thẩm định, kiểm tra, báo cáo tình hình thực hiện hoạt động đấu thầu</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Bộ Tài chính</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>31/08/2021</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>15/10/2021</t>
-        </is>
-      </c>
-      <c r="I29" s="14" t="inlineStr">
+          <t>01/01/2026</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J29" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Thay thế Thông tư 07/2024/TT-BKHĐT và Thông tư 23/2024/TT-BKHĐT</t>
         </is>
       </c>
       <c r="K29" s="10" t="inlineStr">
         <is>
-          <t>Quy tắc đo bóc khối lượng từ bản vẽ thiết kế BVTC</t>
+          <t>Bộ mẫu HSYC, Báo cáo đánh giá, Thẩm định chỉ định thầu hiện hành</t>
         </is>
       </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
-          <t>DO_BOC_KHOI_LUONG, DU_TOAN, TV-04, TV-05</t>
-        </is>
-      </c>
-      <c r="M29" s="15" t="inlineStr"/>
+          <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
+        </is>
+      </c>
+      <c r="M29" s="14" t="inlineStr"/>
       <c r="N29" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Quản lý Chi phí &amp; Dự toán</t>
+          <t>Đấu thầu qua mạng</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2500,53 +2500,53 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>14/2023/TT-BXD</t>
+          <t>15/2024/TT-BKHĐT</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 11/2021/TT-BXD ngày 31 tháng 8 năm 2021 hướng dẫn một số nội dung xác định và quản lý chi phí đầu tư xây dựng</t>
+          <t>Quy định mẫu hồ sơ đấu thầu lựa chọn nhà đầu tư thực hiện dự án PPP, dự án đầu tư kinh doanh; cung cấp, đăng tải thông tin trên Hệ thống mạng đấu thầu quốc gia</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Bộ Kế hoạch và Đầu tư</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>29/12/2023</t>
+          <t>30/09/2024</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>15/02/2024</t>
-        </is>
-      </c>
-      <c r="I30" s="14" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>30/09/2024</t>
+        </is>
+      </c>
+      <c r="I30" s="15" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bị thay thế bởi Thông tư 98/2025/TT-BTC</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng định mức chi phí tư vấn lập dự án và thẩm tra</t>
+          <t>Áp dụng giai đoạn 2024</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
+          <t>DAU_THAU, DAU_TU_KINH_DOANH, PPP</t>
         </is>
       </c>
       <c r="M30" s="8" t="inlineStr"/>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Quản lý Chi phí &amp; Dự toán</t>
+          <t>Đấu thầu qua mạng</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
@@ -2566,53 +2566,53 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>01/2025/TT-BXD</t>
+          <t>98/2025/TT-BTC</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 13/2021/TT-BXD, Thông tư số 11/2021/TT-BXD, Thông tư số 14/2023/TT-BXD</t>
+          <t>Quy định mẫu hồ sơ đấu thầu lựa chọn nhà đầu tư thực hiện dự án đầu tư theo phương thức đối tác công tư, dự án đầu tư kinh doanh; cung cấp, đăng tải thông tin về đầu tư theo phương thức đối tác công tư, đấu thầu lựa chọn nhà đầu tư trên Hệ thống mạng đấu thầu quốc gia</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Bộ Tài chính</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>15/01/2025</t>
+          <t>15/11/2025</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>01/03/2025</t>
-        </is>
-      </c>
-      <c r="I31" s="14" t="inlineStr">
+          <t>01/01/2026</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J31" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Thay thế Thông tư 15/2024/TT-BKHĐT</t>
         </is>
       </c>
       <c r="K31" s="10" t="inlineStr">
         <is>
-          <t>Cập nhật phương pháp xác định chi phí và chỉ tiêu kinh tế kỹ thuật mới</t>
+          <t>Quy định mẫu đấu thầu dự án PPP và kinh doanh hiện hành</t>
         </is>
       </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
-          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
-        </is>
-      </c>
-      <c r="M31" s="15" t="inlineStr"/>
+          <t>DAU_THAU, DAU_TU_KINH_DOANH, PPP</t>
+        </is>
+      </c>
+      <c r="M31" s="14" t="inlineStr"/>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -2627,58 +2627,58 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>09/2024/TT-BXD</t>
+          <t>10/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 12/2021/TT-BXD ngày 31 tháng 8 năm 2021 ban hành định mức xây dựng</t>
+          <t>Về quản lý chi phí đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>30/08/2024</t>
+          <t>09/02/2021</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>15/10/2024</t>
-        </is>
-      </c>
-      <c r="I32" s="7" t="inlineStr">
+          <t>09/02/2021</t>
+        </is>
+      </c>
+      <c r="I32" s="15" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>Bị tích hợp và thay thế bởi Thông tư 38/2026/TT-BXD</t>
+          <t>Bị thay thế bởi Nghị định 206/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>Cập nhật định mức nhân công, ca máy giai đoạn 2024-2026</t>
+          <t>Dự toán duyệt trước 2026 tiếp tục áp dụng theo phê duyệt</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>ALL, DINH_MUC, DU_TOAN, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-08, TV-09, XD-01</t>
+          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
         </is>
       </c>
       <c r="M32" s="8" t="inlineStr"/>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -2693,58 +2693,58 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>38/2026/TT-BXD</t>
+          <t>206/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>Ban hành định mức xây dựng</t>
+          <t>Quy định chi tiết về quản lý chi phí đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
-        </is>
-      </c>
-      <c r="I33" s="14" t="inlineStr">
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J33" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 12/2021/TT-BXD và Thông tư 09/2024/TT-BXD</t>
+          <t>Thay thế Nghị định 10/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="K33" s="10" t="inlineStr">
         <is>
-          <t>Hệ thống định mức dự toán xây dựng hiện hành</t>
+          <t>Căn cứ pháp lý then chốt về quản lý chi phí và dự toán hiện hành</t>
         </is>
       </c>
       <c r="L33" s="10" t="inlineStr">
         <is>
-          <t>ALL, DINH_MUC, DU_TOAN, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-08, TV-09, XD-01</t>
-        </is>
-      </c>
-      <c r="M33" s="15" t="inlineStr"/>
+          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
+        </is>
+      </c>
+      <c r="M33" s="14" t="inlineStr"/>
       <c r="N33" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -2759,17 +2759,17 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Quyết định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>510/QĐ-BXD</t>
+          <t>11/2021/TT-BXD</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Công bố Suất vốn đầu tư xây dựng công trình và giá chuẩn nhà, công trình xây dựng</t>
+          <t>Hướng dẫn một số nội dung xác định và quản lý chi phí đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -2779,38 +2779,38 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>19/05/2023</t>
+          <t>31/08/2021</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>19/05/2023</t>
+          <t>15/10/2021</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Quyết định 425/QĐ-BXD</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>Suất vốn đầu tư năm 2022-2023</t>
+          <t>Phương pháp lập đơn giá xây dựng và tổng mức đầu tư</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>SUAT_VON_DAU_TU, TMDT, TV-01, TV-02, TV-03, TV-04</t>
+          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
         </is>
       </c>
       <c r="M34" s="8" t="inlineStr"/>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -2825,17 +2825,17 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Quyết định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>425/QĐ-BXD</t>
+          <t>12/2021/TT-BXD</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>Công bố suất vốn đầu tư xây dựng và giá xây dựng tổng hợp bộ phận kết cấu công trình năm 2025</t>
+          <t>Ban hành định mức xây dựng (Định mức dự toán, định mức chi phí tư vấn và QLDA)</t>
         </is>
       </c>
       <c r="F35" s="13" t="inlineStr">
@@ -2845,38 +2845,38 @@
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>25/04/2025</t>
+          <t>31/08/2021</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>25/04/2025</t>
-        </is>
-      </c>
-      <c r="I35" s="7" t="inlineStr">
+          <t>15/10/2021</t>
+        </is>
+      </c>
+      <c r="I35" s="15" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J35" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Quyết định 510/QĐ-BXD</t>
+          <t>Bị thay thế bởi Thông tư 38/2026/TT-BXD</t>
         </is>
       </c>
       <c r="K35" s="10" t="inlineStr">
         <is>
-          <t>Suất vốn đầu tư tính Tổng mức đầu tư và khái toán</t>
+          <t>Bộ định mức gốc tính chi phí tư vấn và xây lắp giai đoạn 2021-2026</t>
         </is>
       </c>
       <c r="L35" s="10" t="inlineStr">
         <is>
-          <t>SUAT_VON_DAU_TU, TMDT, TV-01, TV-02, TV-03, TV-04</t>
-        </is>
-      </c>
-      <c r="M35" s="15" t="inlineStr"/>
+          <t>ALL, DINH_MUC, DU_TOAN, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-08, TV-09, XD-01</t>
+        </is>
+      </c>
+      <c r="M35" s="14" t="inlineStr"/>
       <c r="N35" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -2886,40 +2886,40 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Chất lượng &amp; Nghiệm thu</t>
+          <t>Quản lý Chi phí &amp; Dự toán</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>06/2021/NĐ-CP</t>
+          <t>13/2021/TT-BXD</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng</t>
+          <t>Hướng dẫn phương pháp xác định các chỉ tiêu kinh tế kỹ thuật và đo bóc khối lượng công trình</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>26/01/2021</t>
+          <t>31/08/2021</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>26/01/2021</t>
-        </is>
-      </c>
-      <c r="I36" s="14" t="inlineStr">
+          <t>15/10/2021</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -2931,18 +2931,18 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>Quy định nền tảng về quản lý chất lượng và nghiệm thu công trình</t>
+          <t>Quy tắc đo bóc khối lượng từ bản vẽ thiết kế BVTC</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
+          <t>DO_BOC_KHOI_LUONG, DU_TOAN, TV-04, TV-05</t>
         </is>
       </c>
       <c r="M36" s="8" t="inlineStr"/>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -2952,63 +2952,63 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Chất lượng &amp; Nghiệm thu</t>
+          <t>Quản lý Chi phí &amp; Dự toán</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>207/2026/NĐ-CP</t>
+          <t>14/2023/TT-BXD</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Xây dựng về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng</t>
+          <t>Sửa đổi, bổ sung một số điều của Thông tư số 11/2021/TT-BXD ngày 31 tháng 8 năm 2021 hướng dẫn một số nội dung xác định và quản lý chi phí đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>29/12/2023</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="I37" s="14" t="inlineStr">
+          <t>15/02/2024</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J37" s="10" t="inlineStr">
         <is>
-          <t>Cập nhật và hoàn thiện Nghị định 06/2021/NĐ-CP theo Luật Xây dựng mới</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K37" s="10" t="inlineStr">
         <is>
-          <t>Quy chuẩn quản lý chất lượng công trình xây dựng hiện hành</t>
+          <t>Áp dụng định mức chi phí tư vấn lập dự án và thẩm tra</t>
         </is>
       </c>
       <c r="L37" s="10" t="inlineStr">
         <is>
-          <t>ALL, CHAT_LUONG, NGHIEM_THU, XD-01, TV-08, TV-07</t>
-        </is>
-      </c>
-      <c r="M37" s="15" t="inlineStr"/>
+          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
+        </is>
+      </c>
+      <c r="M37" s="14" t="inlineStr"/>
       <c r="N37" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Chất lượng &amp; Nghiệm thu</t>
+          <t>Quản lý Chi phí &amp; Dự toán</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>10/2021/TT-BXD</t>
+          <t>01/2025/TT-BXD</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Hướng dẫn một số điều của Nghị định số 06/2021/NĐ-CP và Nghị định số 44/2016/NĐ-CP</t>
+          <t>Sửa đổi, bổ sung một số điều của Thông tư số 13/2021/TT-BXD, Thông tư số 11/2021/TT-BXD, Thông tư số 14/2023/TT-BXD</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
@@ -3043,15 +3043,15 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>25/08/2021</t>
+          <t>15/01/2025</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>15/10/2021</t>
-        </is>
-      </c>
-      <c r="I38" s="14" t="inlineStr">
+          <t>01/03/2025</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -3063,18 +3063,18 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>Mẫu nhật ký thi công, biên bản nghiệm thu giai đoạn và hoàn thành</t>
+          <t>Cập nhật phương pháp xác định chi phí và chỉ tiêu kinh tế kỹ thuật mới</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
+          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
         </is>
       </c>
       <c r="M38" s="8" t="inlineStr"/>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Chất lượng &amp; Nghiệm thu</t>
+          <t>Quản lý Chi phí &amp; Dự toán</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>32/2026/TT-BXD</t>
+          <t>09/2024/TT-BXD</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Nghị định số 207/2026/NĐ-CP quy định chi tiết một số điều của Luật Xây dựng về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng</t>
+          <t>Sửa đổi, bổ sung một số điều của Thông tư số 12/2021/TT-BXD ngày 31 tháng 8 năm 2021 ban hành định mức xây dựng</t>
         </is>
       </c>
       <c r="F39" s="13" t="inlineStr">
@@ -3109,38 +3109,38 @@
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>30/08/2024</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
-        </is>
-      </c>
-      <c r="I39" s="14" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>15/10/2024</t>
+        </is>
+      </c>
+      <c r="I39" s="15" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>Hướng dẫn Nghị định 207/2026/NĐ-CP</t>
+          <t>Bị tích hợp và thay thế bởi Thông tư 38/2026/TT-BXD</t>
         </is>
       </c>
       <c r="K39" s="10" t="inlineStr">
         <is>
-          <t>Biểu mẫu quản lý chất lượng và kiểm tra công tác nghiệm thu mới nhất</t>
+          <t>Cập nhật định mức nhân công, ca máy giai đoạn 2024-2026</t>
         </is>
       </c>
       <c r="L39" s="10" t="inlineStr">
         <is>
-          <t>ALL, CHAT_LUONG, NGHIEM_THU, XD-01, TV-08</t>
-        </is>
-      </c>
-      <c r="M39" s="15" t="inlineStr"/>
+          <t>ALL, DINH_MUC, DU_TOAN, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-08, TV-09, XD-01</t>
+        </is>
+      </c>
+      <c r="M39" s="14" t="inlineStr"/>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -3150,22 +3150,22 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>PCCC &amp; Tiêu chuẩn Kỹ thuật</t>
+          <t>Quản lý Chi phí &amp; Dự toán</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Quy chuẩn</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>QCVN 06:2022/BXD &amp; Sửa đổi 1:2023</t>
+          <t>38/2026/TT-BXD</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Quy chuẩn kỹ thuật quốc gia về An toàn cháy cho nhà và công trình</t>
+          <t>Ban hành định mức xây dựng</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -3175,38 +3175,38 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>16/10/2023</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>01/12/2023</t>
-        </is>
-      </c>
-      <c r="I40" s="14" t="inlineStr">
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>QCVN 06:2021/BXD</t>
+          <t>Thay thế Thông tư 12/2021/TT-BXD và Thông tư 09/2024/TT-BXD</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>Hồ sơ thiết kế BVTC phải tuân thủ đúng yêu cầu ngăn cháy, thoát nạn</t>
+          <t>Hệ thống định mức dự toán xây dựng hiện hành</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>PCCC, THIET_KE, TV-04, TV-05, XD-01</t>
+          <t>ALL, DINH_MUC, DU_TOAN, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-08, TV-09, XD-01</t>
         </is>
       </c>
       <c r="M40" s="8" t="inlineStr"/>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -3216,63 +3216,63 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>PCCC &amp; Tiêu chuẩn Kỹ thuật</t>
+          <t>Quản lý Chi phí &amp; Dự toán</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Quyết định</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>136/2020/NĐ-CP</t>
+          <t>510/QĐ-BXD</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Phòng cháy và chữa cháy</t>
+          <t>Công bố Suất vốn đầu tư xây dựng công trình và giá chuẩn nhà, công trình xây dựng</t>
         </is>
       </c>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>24/11/2020</t>
+          <t>19/05/2023</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>10/01/2021</t>
-        </is>
-      </c>
-      <c r="I41" s="7" t="inlineStr">
+          <t>19/05/2023</t>
+        </is>
+      </c>
+      <c r="I41" s="15" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J41" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 105/2025/NĐ-CP</t>
+          <t>Bị thay thế bởi Quyết định 425/QĐ-BXD</t>
         </is>
       </c>
       <c r="K41" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng giai đoạn 2020-2025</t>
+          <t>Suất vốn đầu tư năm 2022-2023</t>
         </is>
       </c>
       <c r="L41" s="10" t="inlineStr">
         <is>
-          <t>PCCC, TV-02, TV-03, TV-04, TV-05, XD-01</t>
-        </is>
-      </c>
-      <c r="M41" s="15" t="inlineStr"/>
+          <t>SUAT_VON_DAU_TU, TMDT, TV-01, TV-02, TV-03, TV-04</t>
+        </is>
+      </c>
+      <c r="M41" s="14" t="inlineStr"/>
       <c r="N41" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -3282,63 +3282,63 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>PCCC &amp; Tiêu chuẩn Kỹ thuật</t>
+          <t>Quản lý Chi phí &amp; Dự toán</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Quyết định</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>105/2025/NĐ-CP</t>
+          <t>425/QĐ-BXD</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Phòng cháy, chữa cháy và cứu nạn, cứu hộ</t>
+          <t>Công bố suất vốn đầu tư xây dựng và giá xây dựng tổng hợp bộ phận kết cấu công trình năm 2025</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>25/04/2025</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
-        </is>
-      </c>
-      <c r="I42" s="14" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>25/04/2025</t>
+        </is>
+      </c>
+      <c r="I42" s="15" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 136/2020/NĐ-CP và Nghị định 50/2024/NĐ-CP</t>
+          <t>Thay thế Quyết định 510/QĐ-BXD</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>Quy định thẩm duyệt thiết kế và nghiệm thu PCCC hiện hành</t>
+          <t>Suất vốn đầu tư tính Tổng mức đầu tư và khái toán</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>ALL, PCCC, THIET_KE, TV-04, TV-05, XD-01</t>
+          <t>SUAT_VON_DAU_TU, TMDT, TV-01, TV-02, TV-03, TV-04</t>
         </is>
       </c>
       <c r="M42" s="8" t="inlineStr"/>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>PCCC &amp; Tiêu chuẩn Kỹ thuật</t>
+          <t>Chất lượng &amp; Nghiệm thu</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>50/2024/NĐ-CP</t>
+          <t>06/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 136/2020/NĐ-CP và Nghị định số 83/2017/NĐ-CP về PCCC và cứu nạn, cứu hộ</t>
+          <t>Quy định chi tiết về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng</t>
         </is>
       </c>
       <c r="F43" s="13" t="inlineStr">
@@ -3373,38 +3373,38 @@
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>10/05/2024</t>
+          <t>26/01/2021</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>15/05/2024</t>
+          <t>26/01/2021</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J43" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 105/2025/NĐ-CP</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K43" s="10" t="inlineStr">
         <is>
-          <t>Phân cấp thẩm duyệt PCCC giai đoạn 2024-2025</t>
+          <t>Quy định nền tảng về quản lý chất lượng và nghiệm thu công trình</t>
         </is>
       </c>
       <c r="L43" s="10" t="inlineStr">
         <is>
-          <t>PCCC, TV-02, TV-03, TV-04, TV-05, XD-01</t>
-        </is>
-      </c>
-      <c r="M43" s="15" t="inlineStr"/>
+          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
+        </is>
+      </c>
+      <c r="M43" s="14" t="inlineStr"/>
       <c r="N43" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Hợp đồng xây dựng</t>
+          <t>Chất lượng &amp; Nghiệm thu</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -3424,12 +3424,12 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>37/2015/NĐ-CP &amp; 50/2021/NĐ-CP</t>
+          <t>207/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết về hợp đồng xây dựng và sửa đổi, bổ sung Nghị định 37/2015/NĐ-CP</t>
+          <t>Quy định chi tiết một số điều của Luật Xây dựng về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -3439,38 +3439,38 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 210/2026/NĐ-CP</t>
+          <t>Cập nhật và hoàn thiện Nghị định 06/2021/NĐ-CP theo Luật Xây dựng mới</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>Hợp đồng ký trước 2026 thực hiện theo thỏa thuận đã ký</t>
+          <t>Quy chuẩn quản lý chất lượng công trình xây dựng hiện hành</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>HOP_DONG, XD-01, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01</t>
+          <t>ALL, CHAT_LUONG, NGHIEM_THU, XD-01, TV-08, TV-07</t>
         </is>
       </c>
       <c r="M44" s="8" t="inlineStr"/>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -3480,63 +3480,63 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Hợp đồng xây dựng</t>
+          <t>Chất lượng &amp; Nghiệm thu</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>210/2026/NĐ-CP</t>
+          <t>10/2021/TT-BXD</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết và hướng dẫn thi hành một số điều của Luật Xây dựng về hợp đồng xây dựng</t>
+          <t>Hướng dẫn một số điều của Nghị định số 06/2021/NĐ-CP và Nghị định số 44/2016/NĐ-CP</t>
         </is>
       </c>
       <c r="F45" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>25/08/2021</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="I45" s="14" t="inlineStr">
+          <t>15/10/2021</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J45" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 37/2015/NĐ-CP và Nghị định 50/2021/NĐ-CP</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K45" s="10" t="inlineStr">
         <is>
-          <t>Quy định tạm ứng, bảo lãnh thực hiện hợp đồng và thanh quyết toán hiện hành</t>
+          <t>Mẫu nhật ký thi công, biên bản nghiệm thu giai đoạn và hoàn thành</t>
         </is>
       </c>
       <c r="L45" s="10" t="inlineStr">
         <is>
-          <t>ALL, HOP_DONG, XD-01, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01</t>
-        </is>
-      </c>
-      <c r="M45" s="15" t="inlineStr"/>
+          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
+        </is>
+      </c>
+      <c r="M45" s="14" t="inlineStr"/>
       <c r="N45" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Hợp đồng xây dựng</t>
+          <t>Chất lượng &amp; Nghiệm thu</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>02/2023/TT-BXD</t>
+          <t>32/2026/TT-BXD</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Hướng dẫn một số nội dung về hợp đồng xây dựng (Mẫu hợp đồng thi công và tư vấn)</t>
+          <t>Quy định chi tiết một số điều của Nghị định số 207/2026/NĐ-CP quy định chi tiết một số điều của Luật Xây dựng về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -3571,38 +3571,38 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>03/03/2023</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>20/04/2023</t>
-        </is>
-      </c>
-      <c r="I46" s="14" t="inlineStr">
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 09/2016/TT-BXD và Thông tư 08/2016/TT-BXD</t>
+          <t>Hướng dẫn Nghị định 207/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>Mẫu hợp đồng áp dụng bắt buộc cho vốn nhà nước</t>
+          <t>Biểu mẫu quản lý chất lượng và kiểm tra công tác nghiệm thu mới nhất</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>HOP_DONG, XD-01, TV-04, TV-08</t>
+          <t>ALL, CHAT_LUONG, NGHIEM_THU, XD-01, TV-08</t>
         </is>
       </c>
       <c r="M46" s="8" t="inlineStr"/>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -3612,63 +3612,63 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>Tiêu chuẩn Kỹ thuật</t>
+          <t>PCCC &amp; Tiêu chuẩn Kỹ thuật</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Tiêu chuẩn</t>
+          <t>Quy chuẩn</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>TCVN 9393:2012</t>
+          <t>QCVN 06:2022/BXD &amp; Sửa đổi 1:2023</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>Cọc - Phương pháp thử nghiệm hiện trường bằng tải trọng tĩnh ép dọc trục</t>
+          <t>Quy chuẩn kỹ thuật quốc gia về An toàn cháy cho nhà và công trình</t>
         </is>
       </c>
       <c r="F47" s="13" t="inlineStr">
         <is>
-          <t>Bộ Khoa học và Công nghệ</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
-          <t>28/12/2012</t>
+          <t>16/10/2023</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>28/12/2012</t>
-        </is>
-      </c>
-      <c r="I47" s="14" t="inlineStr">
+          <t>01/12/2023</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>QCVN 06:2021/BXD</t>
         </is>
       </c>
       <c r="K47" s="10" t="inlineStr">
         <is>
-          <t>Căn cứ kỹ thuật duy nhất cho gói thầu Thí nghiệm nén tĩnh cọc TV-07</t>
+          <t>Hồ sơ thiết kế BVTC phải tuân thủ đúng yêu cầu ngăn cháy, thoát nạn</t>
         </is>
       </c>
       <c r="L47" s="10" t="inlineStr">
         <is>
-          <t>TV-07, THI_NGHIEM_COC, KIEM_DINH</t>
-        </is>
-      </c>
-      <c r="M47" s="15" t="inlineStr"/>
+          <t>PCCC, THIET_KE, TV-04, TV-05, XD-01</t>
+        </is>
+      </c>
+      <c r="M47" s="14" t="inlineStr"/>
       <c r="N47" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -3678,63 +3678,63 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Bảo hiểm công trình</t>
+          <t>PCCC &amp; Tiêu chuẩn Kỹ thuật</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>08/2022/QH15</t>
+          <t>136/2020/NĐ-CP</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Luật Kinh doanh bảo hiểm năm 2022</t>
+          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Phòng cháy và chữa cháy</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>16/06/2022</t>
+          <t>24/11/2020</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
-        </is>
-      </c>
-      <c r="I48" s="14" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>10/01/2021</t>
+        </is>
+      </c>
+      <c r="I48" s="15" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bị thay thế bởi Nghị định 105/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>Căn cứ pháp lý gói thầu Bảo hiểm công trình PTV-01</t>
+          <t>Áp dụng giai đoạn 2020-2025</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>PTV-01, BAO_HIEM</t>
+          <t>PCCC, TV-02, TV-03, TV-04, TV-05, XD-01</t>
         </is>
       </c>
       <c r="M48" s="8" t="inlineStr"/>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>Bảo hiểm công trình</t>
+          <t>PCCC &amp; Tiêu chuẩn Kỹ thuật</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>67/2023/NĐ-CP</t>
+          <t>105/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>Quy định về bảo hiểm bắt buộc trong hoạt động đầu tư xây dựng, bảo hiểm cháy nổ bắt buộc</t>
+          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Phòng cháy, chữa cháy và cứu nạn, cứu hộ</t>
         </is>
       </c>
       <c r="F49" s="13" t="inlineStr">
@@ -3769,38 +3769,38 @@
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
-          <t>06/09/2023</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>06/09/2023</t>
-        </is>
-      </c>
-      <c r="I49" s="14" t="inlineStr">
+          <t>01/07/2025</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J49" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 119/2015/NĐ-CP và Nghị định 20/2020/NĐ-CP</t>
+          <t>Thay thế Nghị định 136/2020/NĐ-CP và Nghị định 50/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="K49" s="10" t="inlineStr">
         <is>
-          <t>Biểu phí bảo hiểm công trình xây dựng áp dụng cho gói PTV-01</t>
+          <t>Quy định thẩm duyệt thiết kế và nghiệm thu PCCC hiện hành</t>
         </is>
       </c>
       <c r="L49" s="10" t="inlineStr">
         <is>
-          <t>PTV-01, BAO_HIEM, XD-01</t>
-        </is>
-      </c>
-      <c r="M49" s="15" t="inlineStr"/>
+          <t>ALL, PCCC, THIET_KE, TV-04, TV-05, XD-01</t>
+        </is>
+      </c>
+      <c r="M49" s="14" t="inlineStr"/>
       <c r="N49" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Bảo hiểm công trình</t>
+          <t>PCCC &amp; Tiêu chuẩn Kỹ thuật</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>220/2026/NĐ-CP</t>
+          <t>50/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 67/2023/NĐ-CP quy định về bảo hiểm bắt buộc trách nhiệm dân sự của chủ xe cơ giới, bảo hiểm cháy, nổ bắt buộc, bảo hiểm bắt buộc trong hoạt động đầu tư xây dựng</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 136/2020/NĐ-CP và Nghị định số 83/2017/NĐ-CP về PCCC và cứu nạn, cứu hộ</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -3835,38 +3835,38 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>10/05/2024</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
-        </is>
-      </c>
-      <c r="I50" s="14" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>15/05/2024</t>
+        </is>
+      </c>
+      <c r="I50" s="15" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bị thay thế bởi Nghị định 105/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>Cập nhật mức khấu trừ và biểu phí bảo hiểm công trình mới nhất</t>
+          <t>Phân cấp thẩm duyệt PCCC giai đoạn 2024-2025</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>ALL, PTV-01, BAO_HIEM, XD-01</t>
+          <t>PCCC, TV-02, TV-03, TV-04, TV-05, XD-01</t>
         </is>
       </c>
       <c r="M50" s="8" t="inlineStr"/>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>Bảo hiểm công trình</t>
+          <t>Hợp đồng xây dựng</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>119/2015/NĐ-CP</t>
+          <t>37/2015/NĐ-CP &amp; 50/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr">
         <is>
-          <t>Quy định bảo hiểm bắt buộc trong hoạt động đầu tư xây dựng</t>
+          <t>Quy định chi tiết về hợp đồng xây dựng và sửa đổi, bổ sung Nghị định 37/2015/NĐ-CP</t>
         </is>
       </c>
       <c r="F51" s="13" t="inlineStr">
@@ -3901,38 +3901,38 @@
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>13/11/2015</t>
+          <t>01/04/2021</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>10/02/2016</t>
-        </is>
-      </c>
-      <c r="I51" s="7" t="inlineStr">
+          <t>01/04/2021</t>
+        </is>
+      </c>
+      <c r="I51" s="15" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J51" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 67/2023/NĐ-CP</t>
+          <t>Bị thay thế bởi Nghị định 210/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="K51" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng cho hợp đồng bảo hiểm ký trước 06/09/2023</t>
+          <t>Hợp đồng ký trước 2026 thực hiện theo thỏa thuận đã ký</t>
         </is>
       </c>
       <c r="L51" s="10" t="inlineStr">
         <is>
-          <t>PTV-01, LICHSU</t>
-        </is>
-      </c>
-      <c r="M51" s="15" t="inlineStr"/>
+          <t>HOP_DONG, XD-01, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01</t>
+        </is>
+      </c>
+      <c r="M51" s="14" t="inlineStr"/>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -3942,63 +3942,63 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Kiểm toán độc lập</t>
+          <t>Hợp đồng xây dựng</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>67/2011/QH12</t>
+          <t>210/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Luật Kiểm toán độc lập</t>
+          <t>Quy định chi tiết và hướng dẫn thi hành một số điều của Luật Xây dựng về hợp đồng xây dựng</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>29/03/2011</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>01/01/2012</t>
-        </is>
-      </c>
-      <c r="I52" s="14" t="inlineStr">
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Thay thế Nghị định 37/2015/NĐ-CP và Nghị định 50/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>Căn cứ thực hiện gói thầu Kiểm toán độc lập TV-09</t>
+          <t>Quy định tạm ứng, bảo lãnh thực hiện hợp đồng và thanh quyết toán hiện hành</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>TV-09, KIEM_TOAN</t>
+          <t>ALL, HOP_DONG, XD-01, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01</t>
         </is>
       </c>
       <c r="M52" s="8" t="inlineStr"/>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>Kiểm toán độc lập</t>
+          <t>Hợp đồng xây dựng</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
@@ -4018,53 +4018,53 @@
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>67/2015/TT-BTC</t>
+          <t>02/2023/TT-BXD</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr">
         <is>
-          <t>Chuẩn mực kiểm toán Việt Nam số 1000 (VSA 1000) - Kiểm toán báo cáo quyết toán dự án hoàn thành</t>
+          <t>Hướng dẫn một số nội dung về hợp đồng xây dựng (Mẫu hợp đồng thi công và tư vấn)</t>
         </is>
       </c>
       <c r="F53" s="13" t="inlineStr">
         <is>
-          <t>Bộ Tài chính</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
         <is>
-          <t>08/05/2015</t>
+          <t>03/03/2023</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
-        </is>
-      </c>
-      <c r="I53" s="14" t="inlineStr">
+          <t>20/04/2023</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J53" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Thay thế Thông tư 09/2016/TT-BXD và Thông tư 08/2016/TT-BXD</t>
         </is>
       </c>
       <c r="K53" s="10" t="inlineStr">
         <is>
-          <t>Chuẩn mực kiểm toán áp dụng cho gói TV-09</t>
+          <t>Mẫu hợp đồng áp dụng bắt buộc cho vốn nhà nước</t>
         </is>
       </c>
       <c r="L53" s="10" t="inlineStr">
         <is>
-          <t>TV-09, KIEM_TOAN</t>
-        </is>
-      </c>
-      <c r="M53" s="15" t="inlineStr"/>
+          <t>HOP_DONG, XD-01, TV-04, TV-08</t>
+        </is>
+      </c>
+      <c r="M53" s="14" t="inlineStr"/>
       <c r="N53" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -4074,63 +4074,63 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Quyết toán vốn dự án</t>
+          <t>Tiêu chuẩn Kỹ thuật</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Tiêu chuẩn</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>58/2024/QH15</t>
+          <t>TCVN 9393:2012</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Luật Đầu tư công năm 2024 (Đẩy mạnh phân cấp, phân quyền, tách bồi thường GPMB)</t>
+          <t>Cọc - Phương pháp thử nghiệm hiện trường bằng tải trọng tĩnh ép dọc trục</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Bộ Khoa học và Công nghệ</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>29/11/2024</t>
+          <t>28/12/2012</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
-        </is>
-      </c>
-      <c r="I54" s="14" t="inlineStr">
+          <t>28/12/2012</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Luật Đầu tư công 39/2019/QH14</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>Quy định trình tự phê duyệt chủ trương, kế hoạch vốn và quyết toán</t>
+          <t>Căn cứ kỹ thuật duy nhất cho gói thầu Thí nghiệm nén tĩnh cọc TV-07</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>ALL, DAU_TU_CONG, CHU_TRUONG, TV-01, TV-02, TV-03, TV-09</t>
+          <t>TV-07, THI_NGHIEM_COC, KIEM_DINH</t>
         </is>
       </c>
       <c r="M54" s="8" t="inlineStr"/>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>Quyết toán vốn dự án</t>
+          <t>Bảo hiểm công trình</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>39/2019/QH14</t>
+          <t>08/2022/QH15</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>Luật Đầu tư công năm 2019</t>
+          <t>Luật Kinh doanh bảo hiểm năm 2022</t>
         </is>
       </c>
       <c r="F55" s="13" t="inlineStr">
@@ -4165,38 +4165,38 @@
       </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>13/06/2019</t>
+          <t>16/06/2022</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J55" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Luật Đầu tư công 58/2024/QH15</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K55" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng cho dự án đã duyệt chủ trương trước 2025</t>
+          <t>Căn cứ pháp lý gói thầu Bảo hiểm công trình PTV-01</t>
         </is>
       </c>
       <c r="L55" s="10" t="inlineStr">
         <is>
-          <t>ALL, DAU_TU_CONG, CHU_TRUONG, TV-01, TV-02, TV-03, TV-09</t>
-        </is>
-      </c>
-      <c r="M55" s="15" t="inlineStr"/>
+          <t>PTV-01, BAO_HIEM</t>
+        </is>
+      </c>
+      <c r="M55" s="14" t="inlineStr"/>
       <c r="N55" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Quyết toán vốn dự án</t>
+          <t>Bảo hiểm công trình</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>99/2021/NĐ-CP</t>
+          <t>67/2023/NĐ-CP</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Quy định về quản lý, thanh toán, quyết toán dự án sử dụng vốn đầu tư công</t>
+          <t>Quy định về bảo hiểm bắt buộc trong hoạt động đầu tư xây dựng, bảo hiểm cháy nổ bắt buộc</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -4231,38 +4231,38 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>11/11/2021</t>
+          <t>06/09/2023</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>06/09/2023</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 77/2015/NĐ-CP và Nghị định 120/2018/NĐ-CP về quyết toán vốn ĐTC</t>
+          <t>Thay thế Nghị định 119/2015/NĐ-CP và Nghị định 20/2020/NĐ-CP</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>Hồ sơ thanh toán, quyết toán vốn đầu tư công giai đoạn 2022-2025</t>
+          <t>Biểu phí bảo hiểm công trình xây dựng áp dụng cho gói PTV-01</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>ALL, QUYET_TOAN, TAI_CHINH, TV-09, XD-01</t>
+          <t>PTV-01, BAO_HIEM, XD-01</t>
         </is>
       </c>
       <c r="M56" s="8" t="inlineStr"/>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -4272,63 +4272,63 @@
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>Quyết toán vốn dự án</t>
+          <t>Bảo hiểm công trình</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>24/2024/TT-BTC</t>
+          <t>220/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
         <is>
-          <t>Hướng dẫn Chế độ kế toán Hành chính, sự nghiệp (Hạch toán tài sản và vốn dự án)</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 67/2023/NĐ-CP quy định về bảo hiểm bắt buộc trách nhiệm dân sự của chủ xe cơ giới, bảo hiểm cháy, nổ bắt buộc, bảo hiểm bắt buộc trong hoạt động đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F57" s="13" t="inlineStr">
         <is>
-          <t>Bộ Tài chính</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>17/04/2024</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
-        </is>
-      </c>
-      <c r="I57" s="14" t="inlineStr">
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J57" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 107/2017/TT-BTC</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K57" s="10" t="inlineStr">
         <is>
-          <t>Hạch toán sổ sách tài sản và vốn đầu tư hoàn thành hiện hành</t>
+          <t>Cập nhật mức khấu trừ và biểu phí bảo hiểm công trình mới nhất</t>
         </is>
       </c>
       <c r="L57" s="10" t="inlineStr">
         <is>
-          <t>ALL, QUYET_TOAN, TAI_CHINH, TV-09, XD-01</t>
-        </is>
-      </c>
-      <c r="M57" s="15" t="inlineStr"/>
+          <t>ALL, PTV-01, BAO_HIEM, XD-01</t>
+        </is>
+      </c>
+      <c r="M57" s="14" t="inlineStr"/>
       <c r="N57" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -4338,63 +4338,63 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Quốc phòng &amp; Doanh trại</t>
+          <t>Bảo hiểm công trình</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>150/2018/TT-BQP</t>
+          <t>119/2015/NĐ-CP</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Quy định về tiêu chuẩn, định mức sử dụng máy móc, thiết bị văn phòng phổ biến thuộc phạm vi quản lý của Bộ Quốc phòng</t>
+          <t>Quy định bảo hiểm bắt buộc trong hoạt động đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>Bộ Quốc phòng</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>11/10/2018</t>
+          <t>13/11/2015</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>26/11/2018</t>
-        </is>
-      </c>
-      <c r="I58" s="14" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>10/02/2016</t>
+        </is>
+      </c>
+      <c r="I58" s="15" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Quyết định 162/2002/QĐ-BQP</t>
+          <t>Bị thay thế bởi Nghị định 67/2023/NĐ-CP</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>Tiêu chuẩn định mức máy móc, thiết bị làm việc của cán bộ sĩ quan BQP</t>
+          <t>Áp dụng cho hợp đồng bảo hiểm ký trước 06/09/2023</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>BQP, DOANH_TRAI, TV-01, TV-02, TV-04, XD-01</t>
+          <t>PTV-01, LICHSU</t>
         </is>
       </c>
       <c r="M58" s="8" t="inlineStr"/>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -4404,63 +4404,63 @@
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>Quốc phòng &amp; Doanh trại</t>
+          <t>Kiểm toán độc lập</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>128/2021/TT-BQP</t>
+          <t>67/2011/QH12</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr">
         <is>
-          <t>Quy định phân cấp, ủy quyền quyết định chủ trương đầu tư và dự án đầu tư công trong Bộ Quốc phòng</t>
+          <t>Luật Kiểm toán độc lập</t>
         </is>
       </c>
       <c r="F59" s="13" t="inlineStr">
         <is>
-          <t>Bộ Quốc phòng</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
-          <t>06/10/2021</t>
+          <t>29/03/2011</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>20/11/2021</t>
+          <t>01/01/2012</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J59" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP từ ngày 30/08/2026</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K59" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng phân cấp thẩm quyền đầu tư BQP giai đoạn 2021-2026</t>
+          <t>Căn cứ thực hiện gói thầu Kiểm toán độc lập TV-09</t>
         </is>
       </c>
       <c r="L59" s="10" t="inlineStr">
         <is>
-          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
-        </is>
-      </c>
-      <c r="M59" s="15" t="inlineStr"/>
+          <t>TV-09, KIEM_TOAN</t>
+        </is>
+      </c>
+      <c r="M59" s="14" t="inlineStr"/>
       <c r="N59" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Quốc phòng &amp; Doanh trại</t>
+          <t>Kiểm toán độc lập</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -4480,53 +4480,53 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>174/2021/TT-BQP</t>
+          <t>67/2015/TT-BTC</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Quy định về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng trong Bộ Quốc phòng</t>
+          <t>Chuẩn mực kiểm toán Việt Nam số 1000 (VSA 1000) - Kiểm toán báo cáo quyết toán dự án hoàn thành</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>Bộ Quốc phòng</t>
+          <t>Bộ Tài chính</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>27/12/2021</t>
+          <t>08/05/2015</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>12/02/2022</t>
-        </is>
-      </c>
-      <c r="I60" s="14" t="inlineStr">
+          <t>01/01/2016</t>
+        </is>
+      </c>
+      <c r="I60" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>Được sửa đổi, bổ sung bởi Thông tư 24/2025/TT-BQP</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>Quy chuẩn nghiệm thu và quản lý chất lượng công trình quân sự</t>
+          <t>Chuẩn mực kiểm toán áp dụng cho gói TV-09</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
+          <t>TV-09, KIEM_TOAN</t>
         </is>
       </c>
       <c r="M60" s="8" t="inlineStr"/>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -4536,63 +4536,63 @@
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>Quốc phòng &amp; Doanh trại</t>
+          <t>Quyết toán vốn dự án</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>94/2024/TT-BQP</t>
+          <t>58/2024/QH15</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Nhà ở áp dụng trong Bộ Quốc phòng (Mẫu giấy tờ nhà ở công vụ và dự án nhà ở LLVT)</t>
+          <t>Luật Đầu tư công năm 2024 (Đẩy mạnh phân cấp, phân quyền, tách bồi thường GPMB)</t>
         </is>
       </c>
       <c r="F61" s="13" t="inlineStr">
         <is>
-          <t>Bộ Quốc phòng</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
-          <t>11/11/2024</t>
+          <t>29/11/2024</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
-        </is>
-      </c>
-      <c r="I61" s="14" t="inlineStr">
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J61" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Thay thế Luật Đầu tư công 39/2019/QH14</t>
         </is>
       </c>
       <c r="K61" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng cho các dự án đầu tư xây dựng nhà ở cho lực lượng vũ trang thuộc BQP</t>
+          <t>Quy định trình tự phê duyệt chủ trương, kế hoạch vốn và quyết toán</t>
         </is>
       </c>
       <c r="L61" s="10" t="inlineStr">
         <is>
-          <t>BQP, DOANH_TRAI, TV-01, TV-02, TV-04, XD-01</t>
-        </is>
-      </c>
-      <c r="M61" s="15" t="inlineStr"/>
+          <t>ALL, DAU_TU_CONG, CHU_TRUONG, TV-01, TV-02, TV-03, TV-09</t>
+        </is>
+      </c>
+      <c r="M61" s="14" t="inlineStr"/>
       <c r="N61" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -4602,63 +4602,63 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Quốc phòng &amp; Doanh trại</t>
+          <t>Quyết toán vốn dự án</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>73/2023/TT-BQP</t>
+          <t>39/2019/QH14</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 128/2021/TT-BQP ngày 01/10/2021 về quy định phân cấp, ủy quyền quyết định chủ trương đầu tư và dự án đầu tư công trong BQP</t>
+          <t>Luật Đầu tư công năm 2019</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>Bộ Quốc phòng</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>05/10/2023</t>
+          <t>13/06/2019</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>20/11/2023</t>
-        </is>
-      </c>
-      <c r="I62" s="7" t="inlineStr">
+          <t>01/01/2020</t>
+        </is>
+      </c>
+      <c r="I62" s="15" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP từ ngày 30/08/2026</t>
+          <t>Bị thay thế bởi Luật Đầu tư công 58/2024/QH15</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>Cập nhật phân cấp đầu tư BQP giai đoạn 2023-2026</t>
+          <t>Áp dụng cho dự án đã duyệt chủ trương trước 2025</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+          <t>ALL, DAU_TU_CONG, CHU_TRUONG, TV-01, TV-02, TV-03, TV-09</t>
         </is>
       </c>
       <c r="M62" s="8" t="inlineStr"/>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -4668,63 +4668,63 @@
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>Quốc phòng &amp; Doanh trại</t>
+          <t>Quyết toán vốn dự án</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>120/2024/TT-BQP</t>
+          <t>99/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 128/2021/TT-BQP về phân cấp quản lý và thực hiện dự án đầu tư công trong Bộ Quốc phòng</t>
+          <t>Quy định về quản lý, thanh toán, quyết toán dự án sử dụng vốn đầu tư công</t>
         </is>
       </c>
       <c r="F63" s="13" t="inlineStr">
         <is>
-          <t>Bộ Quốc phòng</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>11/11/2021</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
-        </is>
-      </c>
-      <c r="I63" s="7" t="inlineStr">
+          <t>01/01/2022</t>
+        </is>
+      </c>
+      <c r="I63" s="15" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J63" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP từ ngày 30/08/2026</t>
+          <t>Thay thế Nghị định 77/2015/NĐ-CP và Nghị định 120/2018/NĐ-CP về quyết toán vốn ĐTC</t>
         </is>
       </c>
       <c r="K63" s="10" t="inlineStr">
         <is>
-          <t>Phân cấp phê duyệt thiết kế, dự toán BQP giai đoạn 2024-2026</t>
+          <t>Hồ sơ thanh toán, quyết toán vốn đầu tư công giai đoạn 2022-2025</t>
         </is>
       </c>
       <c r="L63" s="10" t="inlineStr">
         <is>
-          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
-        </is>
-      </c>
-      <c r="M63" s="15" t="inlineStr"/>
+          <t>ALL, QUYET_TOAN, TAI_CHINH, TV-09, XD-01</t>
+        </is>
+      </c>
+      <c r="M63" s="14" t="inlineStr"/>
       <c r="N63" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Quốc phòng &amp; Doanh trại</t>
+          <t>Quyết toán vốn dự án</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -4744,53 +4744,53 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>24/2025/TT-BQP</t>
+          <t>24/2024/TT-BTC</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 174/2021/TT-BQP về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng trong Bộ Quốc phòng</t>
+          <t>Hướng dẫn Chế độ kế toán Hành chính, sự nghiệp (Hạch toán tài sản và vốn dự án)</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>Bộ Quốc phòng</t>
+          <t>Bộ Tài chính</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>06/05/2025</t>
+          <t>17/04/2024</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>20/06/2025</t>
-        </is>
-      </c>
-      <c r="I64" s="14" t="inlineStr">
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="I64" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung Thông tư 174/2021/TT-BQP về quản lý chất lượng công trình BQP</t>
+          <t>Thay thế Thông tư 107/2017/TT-BTC</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>Quy chuẩn kiểm tra công tác nghiệm thu công trình quân sự đặc thù hiện hành</t>
+          <t>Hạch toán sổ sách tài sản và vốn đầu tư hoàn thành hiện hành</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
+          <t>ALL, QUYET_TOAN, TAI_CHINH, TV-09, XD-01</t>
         </is>
       </c>
       <c r="M64" s="8" t="inlineStr"/>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>101/2026/TT-BQP</t>
+          <t>150/2018/TT-BQP</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết và biện pháp thực hiện một số nội dung của Luật Xây dựng thuộc phạm vi quản lý của Bộ Quốc phòng</t>
+          <t>Quy định về tiêu chuẩn, định mức sử dụng máy móc, thiết bị văn phòng phổ biến thuộc phạm vi quản lý của Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F65" s="13" t="inlineStr">
@@ -4825,38 +4825,38 @@
       </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>11/10/2018</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="I65" s="14" t="inlineStr">
+          <t>26/11/2018</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J65" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Thay thế Quyết định 162/2002/QĐ-BQP</t>
         </is>
       </c>
       <c r="K65" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng cho các dự án đầu tư xây dựng công trình trong toàn Bộ Quốc phòng</t>
+          <t>Tiêu chuẩn định mức máy móc, thiết bị làm việc của cán bộ sĩ quan BQP</t>
         </is>
       </c>
       <c r="L65" s="10" t="inlineStr">
         <is>
-          <t>ALL, BQP, QLDA, XD-01, TOAN_QUAN</t>
-        </is>
-      </c>
-      <c r="M65" s="15" t="inlineStr"/>
+          <t>BQP, DOANH_TRAI, TV-01, TV-02, TV-04, XD-01</t>
+        </is>
+      </c>
+      <c r="M65" s="14" t="inlineStr"/>
       <c r="N65" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -4876,12 +4876,12 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>102/2026/TT-BQP</t>
+          <t>128/2021/TT-BQP</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Quy định và hướng dẫn về lập, thẩm định, quyết định, phân cấp quyết định chủ trương đầu tư, dự án đầu tư trong Bộ Quốc phòng</t>
+          <t>Quy định phân cấp, ủy quyền quyết định chủ trương đầu tư và dự án đầu tư công trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
@@ -4891,27 +4891,27 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>06/10/2021</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
-        </is>
-      </c>
-      <c r="I66" s="14" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>20/11/2021</t>
+        </is>
+      </c>
+      <c r="I66" s="15" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 128/2021/TT-BQP, Thông tư 73/2023/TT-BQP và Thông tư 120/2024/TT-BQP</t>
+          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP từ ngày 30/08/2026</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>Văn bản xương sống về phân cấp, ủy quyền quyết định đầu tư và dự án đầu tư công mới nhất trong BQP</t>
+          <t>Áp dụng phân cấp thẩm quyền đầu tư BQP giai đoạn 2021-2026</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
@@ -4922,7 +4922,7 @@
       <c r="M66" s="8" t="inlineStr"/>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -4937,58 +4937,58 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Quyết định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>35/QĐ-TTg</t>
+          <t>174/2021/TT-BQP</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>Ban hành Danh mục bí mật Nhà nước trong lĩnh vực Quốc phòng</t>
+          <t>Quy định về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F67" s="13" t="inlineStr">
         <is>
-          <t>Thủ tướng Chính phủ</t>
+          <t>Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>27/12/2021</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
-        </is>
-      </c>
-      <c r="I67" s="14" t="inlineStr">
+          <t>12/02/2022</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J67" s="10" t="inlineStr">
         <is>
-          <t>Quyết định số 12/QĐ-TTg</t>
+          <t>Được sửa đổi, bổ sung bởi Thông tư 24/2025/TT-BQP</t>
         </is>
       </c>
       <c r="K67" s="10" t="inlineStr">
         <is>
-          <t>Quy định bảo mật hồ sơ, tài liệu thiết kế công trình quân sự</t>
+          <t>Quy chuẩn nghiệm thu và quản lý chất lượng công trình quân sự</t>
         </is>
       </c>
       <c r="L67" s="10" t="inlineStr">
         <is>
-          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
-        </is>
-      </c>
-      <c r="M67" s="15" t="inlineStr"/>
+          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
+        </is>
+      </c>
+      <c r="M67" s="14" t="inlineStr"/>
       <c r="N67" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -4998,63 +4998,63 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Chi thường xuyên &amp; Tài sản công</t>
+          <t>Quốc phòng &amp; Doanh trại</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>15/2017/QH14</t>
+          <t>94/2024/TT-BQP</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Luật Quản lý, sử dụng tài sản công</t>
+          <t>Quy định chi tiết một số điều của Luật Nhà ở áp dụng trong Bộ Quốc phòng (Mẫu giấy tờ nhà ở công vụ và dự án nhà ở LLVT)</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>21/06/2017</t>
+          <t>11/11/2024</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
-        </is>
-      </c>
-      <c r="I68" s="14" t="inlineStr">
+          <t>26/12/2024</t>
+        </is>
+      </c>
+      <c r="I68" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>Luật Quản lý tài sản nhà nước 2008</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>Chế độ quản lý, bảo dưỡng, nâng cấp và sử dụng tài sản công</t>
+          <t>Áp dụng cho các dự án đầu tư xây dựng nhà ở cho lực lượng vũ trang thuộc BQP</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
+          <t>BQP, DOANH_TRAI, TV-01, TV-02, TV-04, XD-01</t>
         </is>
       </c>
       <c r="M68" s="8" t="inlineStr"/>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -5064,63 +5064,63 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>Chi thường xuyên &amp; Tài sản công</t>
+          <t>Quốc phòng &amp; Doanh trại</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>151/2017/NĐ-CP</t>
+          <t>73/2023/TT-BQP</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
+          <t>Sửa đổi, bổ sung một số điều của Thông tư số 128/2021/TT-BQP ngày 01/10/2021 về quy định phân cấp, ủy quyền quyết định chủ trương đầu tư và dự án đầu tư công trong BQP</t>
         </is>
       </c>
       <c r="F69" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
-          <t>26/12/2017</t>
+          <t>05/10/2023</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
-        </is>
-      </c>
-      <c r="I69" s="7" t="inlineStr">
+          <t>20/11/2023</t>
+        </is>
+      </c>
+      <c r="I69" s="15" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J69" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 186/2025/NĐ-CP</t>
+          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP từ ngày 30/08/2026</t>
         </is>
       </c>
       <c r="K69" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng phân cấp tài sản công giai đoạn 2018-2025</t>
+          <t>Cập nhật phân cấp đầu tư BQP giai đoạn 2023-2026</t>
         </is>
       </c>
       <c r="L69" s="10" t="inlineStr">
         <is>
-          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
-        </is>
-      </c>
-      <c r="M69" s="15" t="inlineStr"/>
+          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+        </is>
+      </c>
+      <c r="M69" s="14" t="inlineStr"/>
       <c r="N69" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -5130,63 +5130,63 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Chi thường xuyên &amp; Tài sản công</t>
+          <t>Quốc phòng &amp; Doanh trại</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>186/2025/NĐ-CP</t>
+          <t>120/2024/TT-BQP</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
+          <t>Sửa đổi, bổ sung một số điều của Thông tư số 128/2021/TT-BQP về phân cấp quản lý và thực hiện dự án đầu tư công trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>18/09/2025</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
-        </is>
-      </c>
-      <c r="I70" s="14" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>10/02/2025</t>
+        </is>
+      </c>
+      <c r="I70" s="15" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 151/2017/NĐ-CP</t>
+          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP từ ngày 30/08/2026</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>Quy định phân cấp thẩm quyền quyết định mua sắm, sửa chữa, bàn giao tài sản công hiện hành</t>
+          <t>Phân cấp phê duyệt thiết kế, dự toán BQP giai đoạn 2024-2026</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
+          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M70" s="8" t="inlineStr"/>
       <c r="N70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -5196,63 +5196,63 @@
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>Chi thường xuyên &amp; Tài sản công</t>
+          <t>Quốc phòng &amp; Doanh trại</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>114/2024/NĐ-CP</t>
+          <t>24/2025/TT-BQP</t>
         </is>
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 151/2017/NĐ-CP quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
+          <t>Sửa đổi, bổ sung một số điều của Thông tư số 174/2021/TT-BQP về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F71" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>15/09/2024</t>
+          <t>06/05/2025</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>30/10/2024</t>
-        </is>
-      </c>
-      <c r="I71" s="14" t="inlineStr">
+          <t>20/06/2025</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J71" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung Nghị định 151/2017/NĐ-CP về tài sản công</t>
+          <t>Sửa đổi, bổ sung Thông tư 174/2021/TT-BQP về quản lý chất lượng công trình BQP</t>
         </is>
       </c>
       <c r="K71" s="10" t="inlineStr">
         <is>
-          <t>Quy định thẩm quyền mua sắm, thuê, xử lý tài sản công</t>
+          <t>Quy chuẩn kiểm tra công tác nghiệm thu công trình quân sự đặc thù hiện hành</t>
         </is>
       </c>
       <c r="L71" s="10" t="inlineStr">
         <is>
-          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
-        </is>
-      </c>
-      <c r="M71" s="15" t="inlineStr"/>
+          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
+        </is>
+      </c>
+      <c r="M71" s="14" t="inlineStr"/>
       <c r="N71" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -5262,63 +5262,63 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Chi thường xuyên &amp; Tài sản công</t>
+          <t>Quốc phòng &amp; Doanh trại</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>138/2024/NĐ-CP</t>
+          <t>101/2026/TT-BQP</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Quy định việc lập dự toán, quản lý, sử dụng kinh phí chi thường xuyên NSNN để mua sắm tài sản, trang thiết bị; cải tạo, nâng cấp, mở rộng, xây dựng mới hạng mục công trình</t>
+          <t>Quy định chi tiết và biện pháp thực hiện một số nội dung của Luật Xây dựng thuộc phạm vi quản lý của Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>24/10/2024</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>24/10/2024</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 98/2025/NĐ-CP và Nghị định 104/2026/NĐ-CP</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>Căn cứ giai đoạn cuối 2024</t>
+          <t>Áp dụng cho các dự án đầu tư xây dựng công trình trong toàn Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
+          <t>ALL, BQP, QLDA, XD-01, TOAN_QUAN</t>
         </is>
       </c>
       <c r="M72" s="8" t="inlineStr"/>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -5328,63 +5328,63 @@
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>Chi thường xuyên &amp; Tài sản công</t>
+          <t>Quốc phòng &amp; Doanh trại</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>98/2025/NĐ-CP</t>
+          <t>102/2026/TT-BQP</t>
         </is>
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>Quy định việc lập dự toán, quản lý, sử dụng và quyết toán chi thường xuyên ngân sách nhà nước để mua sắm, sửa chữa, cải tạo, nâng cấp tài sản, trang thiết bị; chi thuê hàng hóa, dịch vụ; sửa chữa, cải tạo, nâng cấp, mở rộng, xây dựng mới hạng mục công trình trong các dự án đã đầu tư xây dựng và các nhiệm vụ cần thiết khác</t>
+          <t>Quy định và hướng dẫn về lập, thẩm định, quyết định, phân cấp quyết định chủ trương đầu tư, dự án đầu tư trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F73" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>25/06/2025</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>15/08/2025</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J73" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 104/2026/NĐ-CP</t>
+          <t>Thay thế Thông tư 128/2021/TT-BQP, Thông tư 73/2023/TT-BQP và Thông tư 120/2024/TT-BQP</t>
         </is>
       </c>
       <c r="K73" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng giai đoạn 2025-2026</t>
+          <t>Văn bản xương sống về phân cấp, ủy quyền quyết định đầu tư và dự án đầu tư công mới nhất trong BQP</t>
         </is>
       </c>
       <c r="L73" s="10" t="inlineStr">
         <is>
-          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
-        </is>
-      </c>
-      <c r="M73" s="15" t="inlineStr"/>
+          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+        </is>
+      </c>
+      <c r="M73" s="14" t="inlineStr"/>
       <c r="N73" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -5394,63 +5394,63 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Chi thường xuyên &amp; Tài sản công</t>
+          <t>Quốc phòng &amp; Doanh trại</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Quyết định</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>104/2026/NĐ-CP</t>
+          <t>35/QĐ-TTg</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Quy định việc lập dự toán, quản lý, sử dụng và quyết toán chi thường xuyên để thực hiện các nhiệm vụ quy định tại Điều 40 Luật Ngân sách nhà nước</t>
+          <t>Ban hành Danh mục bí mật Nhà nước trong lĩnh vực Quốc phòng</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Thủ tướng Chính phủ</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
-        </is>
-      </c>
-      <c r="I74" s="14" t="inlineStr">
+          <t>11/03/2025</t>
+        </is>
+      </c>
+      <c r="I74" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 138/2024/NĐ-CP và Nghị định 98/2025/NĐ-CP</t>
+          <t>Quyết định số 12/QĐ-TTg</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>Căn cứ pháp lý then chốt cho các dự án sửa chữa, nâng cấp sử dụng nguồn chi thường xuyên hiện hành</t>
+          <t>Quy định bảo mật hồ sơ, tài liệu thiết kế công trình quân sự</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
+          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M74" s="8" t="inlineStr"/>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -5465,47 +5465,47 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>65/2021/TT-BTC</t>
+          <t>15/2017/QH14</t>
         </is>
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>Quy định về lập dự toán, phân bổ và quyết toán kinh phí bảo dưỡng, sửa chữa tài sản công</t>
+          <t>Luật Quản lý, sử dụng tài sản công</t>
         </is>
       </c>
       <c r="F75" s="13" t="inlineStr">
         <is>
-          <t>Bộ Tài chính</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
         <is>
-          <t>29/07/2021</t>
+          <t>21/06/2017</t>
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>15/09/2021</t>
-        </is>
-      </c>
-      <c r="I75" s="14" t="inlineStr">
+          <t>01/01/2018</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J75" s="10" t="inlineStr">
         <is>
-          <t>Thông tư 92/2017/TT-BTC</t>
+          <t>Luật Quản lý tài sản nhà nước 2008</t>
         </is>
       </c>
       <c r="K75" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng lập dự toán và thanh toán sửa chữa tài sản công dưới 500 triệu</t>
+          <t>Chế độ quản lý, bảo dưỡng, nâng cấp và sử dụng tài sản công</t>
         </is>
       </c>
       <c r="L75" s="10" t="inlineStr">
@@ -5513,10 +5513,10 @@
           <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
         </is>
       </c>
-      <c r="M75" s="15" t="inlineStr"/>
+      <c r="M75" s="14" t="inlineStr"/>
       <c r="N75" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -5526,59 +5526,63 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Chất lượng &amp; Nghiệm thu</t>
+          <t>Chi thường xuyên &amp; Tài sản công</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>84/2015/QH13</t>
+          <t>151/2017/NĐ-CP</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Luật An toàn, vệ sinh lao động (Quy định an toàn lao động, phòng ngừa sự cố trên công trường xây dựng)</t>
+          <t>Quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>25/06/2015</t>
+          <t>26/12/2017</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>01/07/2016</t>
-        </is>
-      </c>
-      <c r="I76" s="14" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
-        </is>
-      </c>
-      <c r="J76" s="3" t="inlineStr"/>
+          <t>01/01/2018</t>
+        </is>
+      </c>
+      <c r="I76" s="15" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>Bị thay thế bởi Nghị định 186/2025/NĐ-CP</t>
+        </is>
+      </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>Căn cứ bắt buộc trong Hợp đồng thi công gói XD-01 và Giám sát an toàn gói TV-08</t>
+          <t>Áp dụng phân cấp tài sản công giai đoạn 2018-2025</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>XD-01, TV-08, AN_TOAN_LAO_DONG</t>
+          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
         </is>
       </c>
       <c r="M76" s="8" t="inlineStr"/>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -5588,63 +5592,63 @@
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>Xây dựng &amp; Quản lý dự án</t>
+          <t>Chi thường xuyên &amp; Tài sản công</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>72/2020/QH14</t>
+          <t>186/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>Luật Bảo vệ môi trường năm 2020</t>
+          <t>Quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
         </is>
       </c>
       <c r="F77" s="13" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
         <is>
-          <t>17/11/2020</t>
+          <t>18/09/2025</t>
         </is>
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
-        </is>
-      </c>
-      <c r="I77" s="14" t="inlineStr">
+          <t>01/11/2025</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J77" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Luật Bảo vệ môi trường 55/2014/QH13</t>
+          <t>Thay thế Nghị định 151/2017/NĐ-CP</t>
         </is>
       </c>
       <c r="K77" s="10" t="inlineStr">
         <is>
-          <t>Căn cứ thực hiện thủ tục Đăng ký môi trường / ĐTM cho các hạng mục Kho xăng dầu, Bệnh xá, Bể bơi</t>
+          <t>Quy định phân cấp thẩm quyền quyết định mua sắm, sửa chữa, bàn giao tài sản công hiện hành</t>
         </is>
       </c>
       <c r="L77" s="10" t="inlineStr">
         <is>
-          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
-        </is>
-      </c>
-      <c r="M77" s="15" t="inlineStr"/>
+          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
+        </is>
+      </c>
+      <c r="M77" s="14" t="inlineStr"/>
       <c r="N77" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5658,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Xây dựng &amp; Quản lý dự án</t>
+          <t>Chi thường xuyên &amp; Tài sản công</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -5664,12 +5668,12 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>08/2022/NĐ-CP</t>
+          <t>114/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Bảo vệ môi trường</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 151/2017/NĐ-CP quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
@@ -5679,38 +5683,38 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>10/01/2022</t>
+          <t>15/09/2024</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>10/01/2022</t>
-        </is>
-      </c>
-      <c r="I78" s="14" t="inlineStr">
+          <t>30/10/2024</t>
+        </is>
+      </c>
+      <c r="I78" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>Được sửa đổi, bổ sung bởi Nghị định số 05/2025/NĐ-CP và Nghị định số 48/2026/NĐ-CP</t>
+          <t>Sửa đổi, bổ sung Nghị định 151/2017/NĐ-CP về tài sản công</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>Quy định đối tượng và hồ sơ Đăng ký môi trường công trình (bổ trợ Nghị quyết 66.19/2026/NQ-CP)</t>
+          <t>Quy định thẩm quyền mua sắm, thuê, xử lý tài sản công</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
+          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
         </is>
       </c>
       <c r="M78" s="8" t="inlineStr"/>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -5720,7 +5724,7 @@
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>Xây dựng &amp; Quản lý dự án</t>
+          <t>Chi thường xuyên &amp; Tài sản công</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
@@ -5730,12 +5734,12 @@
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>05/2025/NĐ-CP</t>
+          <t>138/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="E79" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP ngày 10 tháng 01 năm 2022 của Chính phủ quy định chi tiết một số điều của Luật Bảo vệ môi trường</t>
+          <t>Quy định việc lập dự toán, quản lý, sử dụng kinh phí chi thường xuyên NSNN để mua sắm tài sản, trang thiết bị; cải tạo, nâng cấp, mở rộng, xây dựng mới hạng mục công trình</t>
         </is>
       </c>
       <c r="F79" s="13" t="inlineStr">
@@ -5745,38 +5749,38 @@
       </c>
       <c r="G79" s="11" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>24/10/2024</t>
         </is>
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
-        </is>
-      </c>
-      <c r="I79" s="14" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>24/10/2024</t>
+        </is>
+      </c>
+      <c r="I79" s="15" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J79" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung Nghị định số 08/2022/NĐ-CP; được sửa đổi bởi Nghị định 48/2026/NĐ-CP</t>
+          <t>Bị thay thế bởi Nghị định 98/2025/NĐ-CP và Nghị định 104/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="K79" s="10" t="inlineStr">
         <is>
-          <t>Quy định phân quyền và cắt giảm thủ tục cấp Giấy phép môi trường, Đăng ký môi trường</t>
+          <t>Căn cứ giai đoạn cuối 2024</t>
         </is>
       </c>
       <c r="L79" s="10" t="inlineStr">
         <is>
-          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
-        </is>
-      </c>
-      <c r="M79" s="15" t="inlineStr"/>
+          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
+        </is>
+      </c>
+      <c r="M79" s="14" t="inlineStr"/>
       <c r="N79" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5790,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Xây dựng &amp; Quản lý dự án</t>
+          <t>Chi thường xuyên &amp; Tài sản công</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -5796,12 +5800,12 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>48/2026/NĐ-CP</t>
+          <t>98/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP ngày 10 tháng 01 năm 2022 của Chính phủ quy định chi tiết một số điều của Luật Bảo vệ môi trường được sửa đổi, bổ sung bởi Nghị định số 05/2025/NĐ-CP ngày 06 tháng 01 năm 2025</t>
+          <t>Quy định việc lập dự toán, quản lý, sử dụng và quyết toán chi thường xuyên ngân sách nhà nước để mua sắm, sửa chữa, cải tạo, nâng cấp tài sản, trang thiết bị; chi thuê hàng hóa, dịch vụ; sửa chữa, cải tạo, nâng cấp, mở rộng, xây dựng mới hạng mục công trình trong các dự án đã đầu tư xây dựng và các nhiệm vụ cần thiết khác</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
@@ -5811,38 +5815,496 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>25/06/2025</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="I80" s="14" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>15/08/2025</t>
+        </is>
+      </c>
+      <c r="I80" s="15" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung Nghị định số 08/2022/NĐ-CP và Nghị định số 05/2025/NĐ-CP</t>
+          <t>Bị thay thế bởi Nghị định 104/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>Đơn giản hóa tối đa thủ tục môi trường cho các công trình xây dựng và dự án đầu tư công hiện hành</t>
+          <t>Áp dụng giai đoạn 2025-2026</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
+          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
         </is>
       </c>
       <c r="M80" s="8" t="inlineStr"/>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:04</t>
+          <t>2026-08-21 15:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="26" customHeight="1">
+      <c r="A81" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>Chi thường xuyên &amp; Tài sản công</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>Nghị định</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>104/2026/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>Quy định việc lập dự toán, quản lý, sử dụng và quyết toán chi thường xuyên để thực hiện các nhiệm vụ quy định tại Điều 40 Luật Ngân sách nhà nước</t>
+        </is>
+      </c>
+      <c r="F81" s="13" t="inlineStr">
+        <is>
+          <t>Chính phủ</t>
+        </is>
+      </c>
+      <c r="G81" s="11" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="H81" s="11" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
+        </is>
+      </c>
+      <c r="J81" s="10" t="inlineStr">
+        <is>
+          <t>Thay thế Nghị định 138/2024/NĐ-CP và Nghị định 98/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="K81" s="10" t="inlineStr">
+        <is>
+          <t>Căn cứ pháp lý then chốt cho các dự án sửa chữa, nâng cấp sử dụng nguồn chi thường xuyên hiện hành</t>
+        </is>
+      </c>
+      <c r="L81" s="10" t="inlineStr">
+        <is>
+          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
+        </is>
+      </c>
+      <c r="M81" s="14" t="inlineStr"/>
+      <c r="N81" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="26" customHeight="1">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Chi thường xuyên &amp; Tài sản công</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Thông tư</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>65/2021/TT-BTC</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>Quy định về lập dự toán, phân bổ và quyết toán kinh phí bảo dưỡng, sửa chữa tài sản công</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>Bộ Tài chính</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>29/07/2021</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>15/09/2021</t>
+        </is>
+      </c>
+      <c r="I82" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>Thông tư 92/2017/TT-BTC</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>Áp dụng lập dự toán và thanh toán sửa chữa tài sản công dưới 500 triệu</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
+        </is>
+      </c>
+      <c r="M82" s="8" t="inlineStr"/>
+      <c r="N82" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="26" customHeight="1">
+      <c r="A83" s="9" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>Chất lượng &amp; Nghiệm thu</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>Luật</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>84/2015/QH13</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>Luật An toàn, vệ sinh lao động (Quy định an toàn lao động, phòng ngừa sự cố trên công trường xây dựng)</t>
+        </is>
+      </c>
+      <c r="F83" s="13" t="inlineStr">
+        <is>
+          <t>Quốc hội</t>
+        </is>
+      </c>
+      <c r="G83" s="11" t="inlineStr">
+        <is>
+          <t>25/06/2015</t>
+        </is>
+      </c>
+      <c r="H83" s="11" t="inlineStr">
+        <is>
+          <t>01/07/2016</t>
+        </is>
+      </c>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
+        </is>
+      </c>
+      <c r="J83" s="10" t="inlineStr"/>
+      <c r="K83" s="10" t="inlineStr">
+        <is>
+          <t>Căn cứ bắt buộc trong Hợp đồng thi công gói XD-01 và Giám sát an toàn gói TV-08</t>
+        </is>
+      </c>
+      <c r="L83" s="10" t="inlineStr">
+        <is>
+          <t>XD-01, TV-08, AN_TOAN_LAO_DONG</t>
+        </is>
+      </c>
+      <c r="M83" s="14" t="inlineStr"/>
+      <c r="N83" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="26" customHeight="1">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Xây dựng &amp; Quản lý dự án</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>Luật</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>72/2020/QH14</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>Luật Bảo vệ môi trường năm 2020</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>Quốc hội</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>17/11/2020</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>01/01/2022</t>
+        </is>
+      </c>
+      <c r="I84" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>Thay thế Luật Bảo vệ môi trường 55/2014/QH13</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>Căn cứ thực hiện thủ tục Đăng ký môi trường / ĐTM cho các hạng mục Kho xăng dầu, Bệnh xá, Bể bơi</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
+        </is>
+      </c>
+      <c r="M84" s="8" t="inlineStr"/>
+      <c r="N84" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="26" customHeight="1">
+      <c r="A85" s="9" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>Xây dựng &amp; Quản lý dự án</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>Nghị định</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>08/2022/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t>Quy định chi tiết một số điều của Luật Bảo vệ môi trường</t>
+        </is>
+      </c>
+      <c r="F85" s="13" t="inlineStr">
+        <is>
+          <t>Chính phủ</t>
+        </is>
+      </c>
+      <c r="G85" s="11" t="inlineStr">
+        <is>
+          <t>10/01/2022</t>
+        </is>
+      </c>
+      <c r="H85" s="11" t="inlineStr">
+        <is>
+          <t>10/01/2022</t>
+        </is>
+      </c>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
+        </is>
+      </c>
+      <c r="J85" s="10" t="inlineStr">
+        <is>
+          <t>Được sửa đổi, bổ sung bởi Nghị định số 05/2025/NĐ-CP và Nghị định số 48/2026/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="K85" s="10" t="inlineStr">
+        <is>
+          <t>Quy định đối tượng và hồ sơ Đăng ký môi trường công trình (bổ trợ Nghị quyết 66.19/2026/NQ-CP)</t>
+        </is>
+      </c>
+      <c r="L85" s="10" t="inlineStr">
+        <is>
+          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
+        </is>
+      </c>
+      <c r="M85" s="14" t="inlineStr"/>
+      <c r="N85" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="26" customHeight="1">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Xây dựng &amp; Quản lý dự án</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>Nghị định</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>05/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP ngày 10 tháng 01 năm 2022 của Chính phủ quy định chi tiết một số điều của Luật Bảo vệ môi trường</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>Chính phủ</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>06/01/2025</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>06/01/2025</t>
+        </is>
+      </c>
+      <c r="I86" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>Sửa đổi, bổ sung Nghị định số 08/2022/NĐ-CP; được sửa đổi bởi Nghị định 48/2026/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>Quy định phân quyền và cắt giảm thủ tục cấp Giấy phép môi trường, Đăng ký môi trường</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
+        </is>
+      </c>
+      <c r="M86" s="8" t="inlineStr"/>
+      <c r="N86" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="26" customHeight="1">
+      <c r="A87" s="9" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>Xây dựng &amp; Quản lý dự án</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>Nghị định</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>48/2026/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP ngày 10 tháng 01 năm 2022 của Chính phủ quy định chi tiết một số điều của Luật Bảo vệ môi trường được sửa đổi, bổ sung bởi Nghị định số 05/2025/NĐ-CP ngày 06 tháng 01 năm 2025</t>
+        </is>
+      </c>
+      <c r="F87" s="13" t="inlineStr">
+        <is>
+          <t>Chính phủ</t>
+        </is>
+      </c>
+      <c r="G87" s="11" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="H87" s="11" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="I87" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
+        </is>
+      </c>
+      <c r="J87" s="10" t="inlineStr">
+        <is>
+          <t>Sửa đổi, bổ sung Nghị định số 08/2022/NĐ-CP và Nghị định số 05/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="K87" s="10" t="inlineStr">
+        <is>
+          <t>Đơn giản hóa tối đa thủ tục môi trường cho các công trình xây dựng và dự án đầu tư công hiện hành</t>
+        </is>
+      </c>
+      <c r="L87" s="10" t="inlineStr">
+        <is>
+          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
+        </is>
+      </c>
+      <c r="M87" s="14" t="inlineStr"/>
+      <c r="N87" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:21</t>
         </is>
       </c>
     </row>

--- a/Kho_Can_Cu_Phap_Ly.xlsx
+++ b/Kho_Can_Cu_Phap_Ly.xlsx
@@ -45,13 +45,13 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00065F46"/>
+      <color rgb="00991B1B"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00991B1B"/>
+      <color rgb="00065F46"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -76,8 +76,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D1FAE5"/>
-        <bgColor rgb="00D1FAE5"/>
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
     <fill>
@@ -88,8 +88,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
-        <bgColor rgb="00FEE2E2"/>
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -174,11 +174,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -657,7 +657,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Luật Quy hoạch đô thị năm 2009 (sửa đổi, bổ sung bởi Luật số 35/2018/QH14)</t>
+          <t>Luật Quy hoạch đô thị năm 2009</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>Đang có hiệu lực</t>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bị thay thế bởi Luật Quy hoạch đô thị và nông thôn số 47/2024/QH15</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -698,7 +698,7 @@
       <c r="M2" s="8" t="inlineStr"/>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
           <t>30/06/2015</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -761,10 +761,10 @@
           <t>ALL, QUY_HOACH, TV-01, TV-02, QLDA</t>
         </is>
       </c>
-      <c r="M3" s="14" t="inlineStr"/>
+      <c r="M3" s="15" t="inlineStr"/>
       <c r="N3" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
           <t>01/01/2023</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -830,7 +830,7 @@
       <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
           <t>15/02/2020</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -893,10 +893,10 @@
           <t>QUY_HOACH, CHI_PHI_QUY_HOACH, DU_TOAN, TV-01</t>
         </is>
       </c>
-      <c r="M5" s="14" t="inlineStr"/>
+      <c r="M5" s="15" t="inlineStr"/>
       <c r="N5" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
           <t>05/07/2021</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -962,7 +962,7 @@
       <c r="M6" s="8" t="inlineStr"/>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
           <t>01/01/2019</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -1025,10 +1025,10 @@
           <t>KHAO_SAT, DO_DAC, TV-01, TV-02, XD-01</t>
         </is>
       </c>
-      <c r="M7" s="14" t="inlineStr"/>
+      <c r="M7" s="15" t="inlineStr"/>
       <c r="N7" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
           <t>01/05/2019</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -1094,7 +1094,7 @@
       <c r="M8" s="8" t="inlineStr"/>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
           <t>01/01/2015</t>
         </is>
       </c>
-      <c r="I9" s="15" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -1157,10 +1157,10 @@
           <t>ALL, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
-      <c r="M9" s="14" t="inlineStr"/>
+      <c r="M9" s="15" t="inlineStr"/>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
           <t>01/07/2026</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -1226,7 +1226,7 @@
       <c r="M10" s="8" t="inlineStr"/>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
           <t>01/01/2021</t>
         </is>
       </c>
-      <c r="I11" s="15" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -1289,10 +1289,10 @@
           <t>ALL, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
-      <c r="M11" s="14" t="inlineStr"/>
+      <c r="M11" s="15" t="inlineStr"/>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
           <t>03/03/2021</t>
         </is>
       </c>
-      <c r="I12" s="15" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -1358,7 +1358,7 @@
       <c r="M12" s="8" t="inlineStr"/>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
           <t>15/02/2025</t>
         </is>
       </c>
-      <c r="I13" s="15" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -1421,10 +1421,10 @@
           <t>ALL, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
-      <c r="M13" s="14" t="inlineStr"/>
+      <c r="M13" s="15" t="inlineStr"/>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
           <t>01/07/2026</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -1490,7 +1490,7 @@
       <c r="M14" s="8" t="inlineStr"/>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
           <t>20/06/2023</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I15" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -1553,10 +1553,10 @@
           <t>ALL, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
-      <c r="M15" s="14" t="inlineStr"/>
+      <c r="M15" s="15" t="inlineStr"/>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
           <t>28/02/2027</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -1622,7 +1622,7 @@
       <c r="M16" s="8" t="inlineStr"/>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
           <t>01/01/2024</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -1685,10 +1685,10 @@
           <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
         </is>
       </c>
-      <c r="M17" s="14" t="inlineStr"/>
+      <c r="M17" s="15" t="inlineStr"/>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
           <t>15/01/2025</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -1754,7 +1754,7 @@
       <c r="M18" s="8" t="inlineStr"/>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
           <t>01/08/2025</t>
         </is>
       </c>
-      <c r="I19" s="15" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -1817,10 +1817,10 @@
           <t>ALL, DAU_THAU, KHLCNT</t>
         </is>
       </c>
-      <c r="M19" s="14" t="inlineStr"/>
+      <c r="M19" s="15" t="inlineStr"/>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
           <t>01/07/2014</t>
         </is>
       </c>
-      <c r="I20" s="15" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -1886,7 +1886,7 @@
       <c r="M20" s="8" t="inlineStr"/>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
           <t>27/02/2024</t>
         </is>
       </c>
-      <c r="I21" s="15" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -1949,10 +1949,10 @@
           <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
         </is>
       </c>
-      <c r="M21" s="14" t="inlineStr"/>
+      <c r="M21" s="15" t="inlineStr"/>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -1995,7 +1995,7 @@
           <t>01/01/2026</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="I22" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -2018,7 +2018,7 @@
       <c r="M22" s="8" t="inlineStr"/>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
           <t>15/08/2014</t>
         </is>
       </c>
-      <c r="I23" s="15" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -2081,10 +2081,10 @@
           <t>DAU_THAU, LICHSU</t>
         </is>
       </c>
-      <c r="M23" s="14" t="inlineStr"/>
+      <c r="M23" s="15" t="inlineStr"/>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
           <t>26/04/2024</t>
         </is>
       </c>
-      <c r="I24" s="15" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -2150,7 +2150,7 @@
       <c r="M24" s="8" t="inlineStr"/>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
           <t>01/01/2025</t>
         </is>
       </c>
-      <c r="I25" s="15" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -2213,10 +2213,10 @@
           <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
         </is>
       </c>
-      <c r="M25" s="14" t="inlineStr"/>
+      <c r="M25" s="15" t="inlineStr"/>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
           <t>01/01/2026</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="I26" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -2282,7 +2282,7 @@
       <c r="M26" s="8" t="inlineStr"/>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
           <t>15/06/2024</t>
         </is>
       </c>
-      <c r="I27" s="15" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -2345,10 +2345,10 @@
           <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
         </is>
       </c>
-      <c r="M27" s="14" t="inlineStr"/>
+      <c r="M27" s="15" t="inlineStr"/>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
           <t>01/01/2025</t>
         </is>
       </c>
-      <c r="I28" s="15" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -2414,7 +2414,7 @@
       <c r="M28" s="8" t="inlineStr"/>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
           <t>01/01/2026</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I29" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -2477,10 +2477,10 @@
           <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
         </is>
       </c>
-      <c r="M29" s="14" t="inlineStr"/>
+      <c r="M29" s="15" t="inlineStr"/>
       <c r="N29" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
           <t>30/09/2024</t>
         </is>
       </c>
-      <c r="I30" s="15" t="inlineStr">
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -2546,7 +2546,7 @@
       <c r="M30" s="8" t="inlineStr"/>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
           <t>01/01/2026</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="I31" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -2609,10 +2609,10 @@
           <t>DAU_THAU, DAU_TU_KINH_DOANH, PPP</t>
         </is>
       </c>
-      <c r="M31" s="14" t="inlineStr"/>
+      <c r="M31" s="15" t="inlineStr"/>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
           <t>09/02/2021</t>
         </is>
       </c>
-      <c r="I32" s="15" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -2678,7 +2678,7 @@
       <c r="M32" s="8" t="inlineStr"/>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
           <t>01/07/2026</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I33" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -2741,10 +2741,10 @@
           <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
         </is>
       </c>
-      <c r="M33" s="14" t="inlineStr"/>
+      <c r="M33" s="15" t="inlineStr"/>
       <c r="N33" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
           <t>15/10/2021</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I34" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -2810,7 +2810,7 @@
       <c r="M34" s="8" t="inlineStr"/>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
           <t>15/10/2021</t>
         </is>
       </c>
-      <c r="I35" s="15" t="inlineStr">
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -2873,10 +2873,10 @@
           <t>ALL, DINH_MUC, DU_TOAN, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-08, TV-09, XD-01</t>
         </is>
       </c>
-      <c r="M35" s="14" t="inlineStr"/>
+      <c r="M35" s="15" t="inlineStr"/>
       <c r="N35" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
           <t>15/10/2021</t>
         </is>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="I36" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -2942,7 +2942,7 @@
       <c r="M36" s="8" t="inlineStr"/>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2985,7 @@
           <t>15/02/2024</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="I37" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -3005,10 +3005,10 @@
           <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
         </is>
       </c>
-      <c r="M37" s="14" t="inlineStr"/>
+      <c r="M37" s="15" t="inlineStr"/>
       <c r="N37" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
           <t>01/03/2025</t>
         </is>
       </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="I38" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -3074,7 +3074,7 @@
       <c r="M38" s="8" t="inlineStr"/>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3117,7 @@
           <t>15/10/2024</t>
         </is>
       </c>
-      <c r="I39" s="15" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -3137,10 +3137,10 @@
           <t>ALL, DINH_MUC, DU_TOAN, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-08, TV-09, XD-01</t>
         </is>
       </c>
-      <c r="M39" s="14" t="inlineStr"/>
+      <c r="M39" s="15" t="inlineStr"/>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="I40" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -3206,7 +3206,7 @@
       <c r="M40" s="8" t="inlineStr"/>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
           <t>19/05/2023</t>
         </is>
       </c>
-      <c r="I41" s="15" t="inlineStr">
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -3269,10 +3269,10 @@
           <t>SUAT_VON_DAU_TU, TMDT, TV-01, TV-02, TV-03, TV-04</t>
         </is>
       </c>
-      <c r="M41" s="14" t="inlineStr"/>
+      <c r="M41" s="15" t="inlineStr"/>
       <c r="N41" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
           <t>25/04/2025</t>
         </is>
       </c>
-      <c r="I42" s="15" t="inlineStr">
+      <c r="I42" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -3338,7 +3338,7 @@
       <c r="M42" s="8" t="inlineStr"/>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
           <t>26/01/2021</t>
         </is>
       </c>
-      <c r="I43" s="7" t="inlineStr">
+      <c r="I43" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -3401,10 +3401,10 @@
           <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
         </is>
       </c>
-      <c r="M43" s="14" t="inlineStr"/>
+      <c r="M43" s="15" t="inlineStr"/>
       <c r="N43" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3447,7 @@
           <t>01/07/2026</t>
         </is>
       </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="I44" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -3470,7 +3470,7 @@
       <c r="M44" s="8" t="inlineStr"/>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
           <t>15/10/2021</t>
         </is>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="I45" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -3533,10 +3533,10 @@
           <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
         </is>
       </c>
-      <c r="M45" s="14" t="inlineStr"/>
+      <c r="M45" s="15" t="inlineStr"/>
       <c r="N45" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="I46" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -3602,7 +3602,7 @@
       <c r="M46" s="8" t="inlineStr"/>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3645,7 @@
           <t>01/12/2023</t>
         </is>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="I47" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -3665,10 +3665,10 @@
           <t>PCCC, THIET_KE, TV-04, TV-05, XD-01</t>
         </is>
       </c>
-      <c r="M47" s="14" t="inlineStr"/>
+      <c r="M47" s="15" t="inlineStr"/>
       <c r="N47" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
           <t>10/01/2021</t>
         </is>
       </c>
-      <c r="I48" s="15" t="inlineStr">
+      <c r="I48" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -3734,7 +3734,7 @@
       <c r="M48" s="8" t="inlineStr"/>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
           <t>01/07/2025</t>
         </is>
       </c>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="I49" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -3797,10 +3797,10 @@
           <t>ALL, PCCC, THIET_KE, TV-04, TV-05, XD-01</t>
         </is>
       </c>
-      <c r="M49" s="14" t="inlineStr"/>
+      <c r="M49" s="15" t="inlineStr"/>
       <c r="N49" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3843,7 @@
           <t>15/05/2024</t>
         </is>
       </c>
-      <c r="I50" s="15" t="inlineStr">
+      <c r="I50" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -3866,7 +3866,7 @@
       <c r="M50" s="8" t="inlineStr"/>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
           <t>01/04/2021</t>
         </is>
       </c>
-      <c r="I51" s="15" t="inlineStr">
+      <c r="I51" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -3929,10 +3929,10 @@
           <t>HOP_DONG, XD-01, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01</t>
         </is>
       </c>
-      <c r="M51" s="14" t="inlineStr"/>
+      <c r="M51" s="15" t="inlineStr"/>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -3975,7 +3975,7 @@
           <t>01/07/2026</t>
         </is>
       </c>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="I52" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -3998,7 +3998,7 @@
       <c r="M52" s="8" t="inlineStr"/>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
           <t>20/04/2023</t>
         </is>
       </c>
-      <c r="I53" s="7" t="inlineStr">
+      <c r="I53" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -4061,10 +4061,10 @@
           <t>HOP_DONG, XD-01, TV-04, TV-08</t>
         </is>
       </c>
-      <c r="M53" s="14" t="inlineStr"/>
+      <c r="M53" s="15" t="inlineStr"/>
       <c r="N53" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4107,7 @@
           <t>28/12/2012</t>
         </is>
       </c>
-      <c r="I54" s="7" t="inlineStr">
+      <c r="I54" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -4130,7 +4130,7 @@
       <c r="M54" s="8" t="inlineStr"/>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4173,7 @@
           <t>01/01/2023</t>
         </is>
       </c>
-      <c r="I55" s="7" t="inlineStr">
+      <c r="I55" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -4193,10 +4193,10 @@
           <t>PTV-01, BAO_HIEM</t>
         </is>
       </c>
-      <c r="M55" s="14" t="inlineStr"/>
+      <c r="M55" s="15" t="inlineStr"/>
       <c r="N55" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
           <t>06/09/2023</t>
         </is>
       </c>
-      <c r="I56" s="7" t="inlineStr">
+      <c r="I56" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -4262,7 +4262,7 @@
       <c r="M56" s="8" t="inlineStr"/>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="I57" s="7" t="inlineStr">
+      <c r="I57" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -4325,10 +4325,10 @@
           <t>ALL, PTV-01, BAO_HIEM, XD-01</t>
         </is>
       </c>
-      <c r="M57" s="14" t="inlineStr"/>
+      <c r="M57" s="15" t="inlineStr"/>
       <c r="N57" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4371,7 @@
           <t>10/02/2016</t>
         </is>
       </c>
-      <c r="I58" s="15" t="inlineStr">
+      <c r="I58" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -4394,7 +4394,7 @@
       <c r="M58" s="8" t="inlineStr"/>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
           <t>01/01/2012</t>
         </is>
       </c>
-      <c r="I59" s="7" t="inlineStr">
+      <c r="I59" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -4457,10 +4457,10 @@
           <t>TV-09, KIEM_TOAN</t>
         </is>
       </c>
-      <c r="M59" s="14" t="inlineStr"/>
+      <c r="M59" s="15" t="inlineStr"/>
       <c r="N59" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
           <t>01/01/2016</t>
         </is>
       </c>
-      <c r="I60" s="7" t="inlineStr">
+      <c r="I60" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -4526,7 +4526,7 @@
       <c r="M60" s="8" t="inlineStr"/>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4569,7 @@
           <t>01/01/2025</t>
         </is>
       </c>
-      <c r="I61" s="7" t="inlineStr">
+      <c r="I61" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -4589,10 +4589,10 @@
           <t>ALL, DAU_TU_CONG, CHU_TRUONG, TV-01, TV-02, TV-03, TV-09</t>
         </is>
       </c>
-      <c r="M61" s="14" t="inlineStr"/>
+      <c r="M61" s="15" t="inlineStr"/>
       <c r="N61" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -4635,7 +4635,7 @@
           <t>01/01/2020</t>
         </is>
       </c>
-      <c r="I62" s="15" t="inlineStr">
+      <c r="I62" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -4658,7 +4658,7 @@
       <c r="M62" s="8" t="inlineStr"/>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
           <t>01/01/2022</t>
         </is>
       </c>
-      <c r="I63" s="15" t="inlineStr">
+      <c r="I63" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -4721,10 +4721,10 @@
           <t>ALL, QUYET_TOAN, TAI_CHINH, TV-09, XD-01</t>
         </is>
       </c>
-      <c r="M63" s="14" t="inlineStr"/>
+      <c r="M63" s="15" t="inlineStr"/>
       <c r="N63" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4767,7 @@
           <t>01/01/2025</t>
         </is>
       </c>
-      <c r="I64" s="7" t="inlineStr">
+      <c r="I64" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -4790,7 +4790,7 @@
       <c r="M64" s="8" t="inlineStr"/>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -4833,7 +4833,7 @@
           <t>26/11/2018</t>
         </is>
       </c>
-      <c r="I65" s="7" t="inlineStr">
+      <c r="I65" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -4853,10 +4853,10 @@
           <t>BQP, DOANH_TRAI, TV-01, TV-02, TV-04, XD-01</t>
         </is>
       </c>
-      <c r="M65" s="14" t="inlineStr"/>
+      <c r="M65" s="15" t="inlineStr"/>
       <c r="N65" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -4899,7 +4899,7 @@
           <t>20/11/2021</t>
         </is>
       </c>
-      <c r="I66" s="15" t="inlineStr">
+      <c r="I66" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -4922,7 +4922,7 @@
       <c r="M66" s="8" t="inlineStr"/>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4965,7 @@
           <t>12/02/2022</t>
         </is>
       </c>
-      <c r="I67" s="7" t="inlineStr">
+      <c r="I67" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -4985,10 +4985,10 @@
           <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
         </is>
       </c>
-      <c r="M67" s="14" t="inlineStr"/>
+      <c r="M67" s="15" t="inlineStr"/>
       <c r="N67" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
           <t>26/12/2024</t>
         </is>
       </c>
-      <c r="I68" s="7" t="inlineStr">
+      <c r="I68" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -5054,7 +5054,7 @@
       <c r="M68" s="8" t="inlineStr"/>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -5097,7 +5097,7 @@
           <t>20/11/2023</t>
         </is>
       </c>
-      <c r="I69" s="15" t="inlineStr">
+      <c r="I69" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -5117,10 +5117,10 @@
           <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
-      <c r="M69" s="14" t="inlineStr"/>
+      <c r="M69" s="15" t="inlineStr"/>
       <c r="N69" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5163,7 @@
           <t>10/02/2025</t>
         </is>
       </c>
-      <c r="I70" s="15" t="inlineStr">
+      <c r="I70" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -5186,7 +5186,7 @@
       <c r="M70" s="8" t="inlineStr"/>
       <c r="N70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
           <t>20/06/2025</t>
         </is>
       </c>
-      <c r="I71" s="7" t="inlineStr">
+      <c r="I71" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -5249,10 +5249,10 @@
           <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
         </is>
       </c>
-      <c r="M71" s="14" t="inlineStr"/>
+      <c r="M71" s="15" t="inlineStr"/>
       <c r="N71" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -5295,7 +5295,7 @@
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="I72" s="7" t="inlineStr">
+      <c r="I72" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -5318,7 +5318,7 @@
       <c r="M72" s="8" t="inlineStr"/>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
           <t>30/08/2026</t>
         </is>
       </c>
-      <c r="I73" s="7" t="inlineStr">
+      <c r="I73" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -5381,10 +5381,10 @@
           <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
-      <c r="M73" s="14" t="inlineStr"/>
+      <c r="M73" s="15" t="inlineStr"/>
       <c r="N73" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -5427,7 +5427,7 @@
           <t>11/03/2025</t>
         </is>
       </c>
-      <c r="I74" s="7" t="inlineStr">
+      <c r="I74" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -5450,7 +5450,7 @@
       <c r="M74" s="8" t="inlineStr"/>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
           <t>01/01/2018</t>
         </is>
       </c>
-      <c r="I75" s="7" t="inlineStr">
+      <c r="I75" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -5513,10 +5513,10 @@
           <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
         </is>
       </c>
-      <c r="M75" s="14" t="inlineStr"/>
+      <c r="M75" s="15" t="inlineStr"/>
       <c r="N75" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5559,7 @@
           <t>01/01/2018</t>
         </is>
       </c>
-      <c r="I76" s="15" t="inlineStr">
+      <c r="I76" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -5582,7 +5582,7 @@
       <c r="M76" s="8" t="inlineStr"/>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
           <t>01/11/2025</t>
         </is>
       </c>
-      <c r="I77" s="7" t="inlineStr">
+      <c r="I77" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -5645,10 +5645,10 @@
           <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
         </is>
       </c>
-      <c r="M77" s="14" t="inlineStr"/>
+      <c r="M77" s="15" t="inlineStr"/>
       <c r="N77" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -5691,7 +5691,7 @@
           <t>30/10/2024</t>
         </is>
       </c>
-      <c r="I78" s="7" t="inlineStr">
+      <c r="I78" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -5714,7 +5714,7 @@
       <c r="M78" s="8" t="inlineStr"/>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -5757,7 +5757,7 @@
           <t>24/10/2024</t>
         </is>
       </c>
-      <c r="I79" s="15" t="inlineStr">
+      <c r="I79" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -5777,10 +5777,10 @@
           <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
         </is>
       </c>
-      <c r="M79" s="14" t="inlineStr"/>
+      <c r="M79" s="15" t="inlineStr"/>
       <c r="N79" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
           <t>15/08/2025</t>
         </is>
       </c>
-      <c r="I80" s="15" t="inlineStr">
+      <c r="I80" s="7" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
@@ -5846,7 +5846,7 @@
       <c r="M80" s="8" t="inlineStr"/>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="I81" s="7" t="inlineStr">
+      <c r="I81" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -5909,10 +5909,10 @@
           <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
         </is>
       </c>
-      <c r="M81" s="14" t="inlineStr"/>
+      <c r="M81" s="15" t="inlineStr"/>
       <c r="N81" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
           <t>15/09/2021</t>
         </is>
       </c>
-      <c r="I82" s="7" t="inlineStr">
+      <c r="I82" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -5978,7 +5978,7 @@
       <c r="M82" s="8" t="inlineStr"/>
       <c r="N82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -6021,7 +6021,7 @@
           <t>01/07/2016</t>
         </is>
       </c>
-      <c r="I83" s="7" t="inlineStr">
+      <c r="I83" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -6037,10 +6037,10 @@
           <t>XD-01, TV-08, AN_TOAN_LAO_DONG</t>
         </is>
       </c>
-      <c r="M83" s="14" t="inlineStr"/>
+      <c r="M83" s="15" t="inlineStr"/>
       <c r="N83" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -6083,7 +6083,7 @@
           <t>01/01/2022</t>
         </is>
       </c>
-      <c r="I84" s="7" t="inlineStr">
+      <c r="I84" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -6106,7 +6106,7 @@
       <c r="M84" s="8" t="inlineStr"/>
       <c r="N84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6149,7 @@
           <t>10/01/2022</t>
         </is>
       </c>
-      <c r="I85" s="7" t="inlineStr">
+      <c r="I85" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -6169,10 +6169,10 @@
           <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
         </is>
       </c>
-      <c r="M85" s="14" t="inlineStr"/>
+      <c r="M85" s="15" t="inlineStr"/>
       <c r="N85" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
           <t>06/01/2025</t>
         </is>
       </c>
-      <c r="I86" s="7" t="inlineStr">
+      <c r="I86" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -6238,7 +6238,7 @@
       <c r="M86" s="8" t="inlineStr"/>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>
@@ -6281,7 +6281,7 @@
           <t>01/07/2026</t>
         </is>
       </c>
-      <c r="I87" s="7" t="inlineStr">
+      <c r="I87" s="14" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -6301,10 +6301,10 @@
           <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
         </is>
       </c>
-      <c r="M87" s="14" t="inlineStr"/>
+      <c r="M87" s="15" t="inlineStr"/>
       <c r="N87" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:21</t>
+          <t>2026-08-21 15:48</t>
         </is>
       </c>
     </row>

--- a/Kho_Can_Cu_Phap_Ly.xlsx
+++ b/Kho_Can_Cu_Phap_Ly.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N87"/>
+  <dimension ref="A1:N86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -698,7 +698,7 @@
       <c r="M2" s="8" t="inlineStr"/>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       <c r="M3" s="15" t="inlineStr"/>
       <c r="N3" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       <c r="M5" s="15" t="inlineStr"/>
       <c r="N5" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       <c r="M6" s="8" t="inlineStr"/>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       <c r="M7" s="15" t="inlineStr"/>
       <c r="N7" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       <c r="M8" s="8" t="inlineStr"/>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       <c r="M9" s="15" t="inlineStr"/>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       <c r="M10" s="8" t="inlineStr"/>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       <c r="M11" s="15" t="inlineStr"/>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       <c r="M12" s="8" t="inlineStr"/>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       <c r="M13" s="15" t="inlineStr"/>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       <c r="M14" s="8" t="inlineStr"/>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       <c r="M15" s="15" t="inlineStr"/>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
       <c r="M16" s="8" t="inlineStr"/>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
       <c r="M17" s="15" t="inlineStr"/>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       <c r="M18" s="8" t="inlineStr"/>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       <c r="M19" s="15" t="inlineStr"/>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       <c r="M20" s="8" t="inlineStr"/>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -1952,7 +1952,7 @@
       <c r="M21" s="15" t="inlineStr"/>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       <c r="M22" s="8" t="inlineStr"/>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       <c r="M23" s="15" t="inlineStr"/>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       <c r="M24" s="8" t="inlineStr"/>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       <c r="M25" s="15" t="inlineStr"/>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       <c r="M26" s="8" t="inlineStr"/>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       <c r="M27" s="15" t="inlineStr"/>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       <c r="M28" s="8" t="inlineStr"/>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       <c r="M29" s="15" t="inlineStr"/>
       <c r="N29" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2546,7 @@
       <c r="M30" s="8" t="inlineStr"/>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
       <c r="M31" s="15" t="inlineStr"/>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       <c r="M32" s="8" t="inlineStr"/>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       <c r="M33" s="15" t="inlineStr"/>
       <c r="N33" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
       <c r="M34" s="8" t="inlineStr"/>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       <c r="M35" s="15" t="inlineStr"/>
       <c r="N35" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       <c r="M36" s="8" t="inlineStr"/>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       <c r="M37" s="15" t="inlineStr"/>
       <c r="N37" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -3074,7 +3074,7 @@
       <c r="M38" s="8" t="inlineStr"/>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       <c r="M39" s="15" t="inlineStr"/>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       <c r="M40" s="8" t="inlineStr"/>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3272,7 @@
       <c r="M41" s="15" t="inlineStr"/>
       <c r="N41" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3338,7 @@
       <c r="M42" s="8" t="inlineStr"/>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       <c r="M43" s="15" t="inlineStr"/>
       <c r="N43" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3470,7 @@
       <c r="M44" s="8" t="inlineStr"/>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3536,7 @@
       <c r="M45" s="15" t="inlineStr"/>
       <c r="N45" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3602,7 @@
       <c r="M46" s="8" t="inlineStr"/>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
       <c r="M47" s="15" t="inlineStr"/>
       <c r="N47" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3734,7 @@
       <c r="M48" s="8" t="inlineStr"/>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
       <c r="M49" s="15" t="inlineStr"/>
       <c r="N49" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       <c r="M50" s="8" t="inlineStr"/>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3932,7 @@
       <c r="M51" s="15" t="inlineStr"/>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
       <c r="M52" s="8" t="inlineStr"/>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       <c r="M53" s="15" t="inlineStr"/>
       <c r="N53" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4130,7 @@
       <c r="M54" s="8" t="inlineStr"/>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
       <c r="M55" s="15" t="inlineStr"/>
       <c r="N55" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -4262,7 +4262,7 @@
       <c r="M56" s="8" t="inlineStr"/>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       <c r="M57" s="15" t="inlineStr"/>
       <c r="N57" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       <c r="M58" s="8" t="inlineStr"/>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4460,7 @@
       <c r="M59" s="15" t="inlineStr"/>
       <c r="N59" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -4526,7 +4526,7 @@
       <c r="M60" s="8" t="inlineStr"/>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       <c r="M61" s="15" t="inlineStr"/>
       <c r="N61" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4658,7 @@
       <c r="M62" s="8" t="inlineStr"/>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -4724,7 +4724,7 @@
       <c r="M63" s="15" t="inlineStr"/>
       <c r="N63" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4790,7 @@
       <c r="M64" s="8" t="inlineStr"/>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       <c r="M65" s="15" t="inlineStr"/>
       <c r="N65" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -4899,19 +4899,19 @@
           <t>20/11/2021</t>
         </is>
       </c>
-      <c r="I66" s="7" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+      <c r="I66" s="14" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP từ ngày 30/08/2026</t>
+          <t>Được sửa đổi, bổ sung bởi Thông tư 73/2023/TT-BQP và Thông tư 120/2024/TT-BQP</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng phân cấp thẩm quyền đầu tư BQP giai đoạn 2021-2026</t>
+          <t>Căn cứ pháp lý then chốt về phân cấp, ủy quyền quyết định đầu tư và dự án đầu tư công trong BQP</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
@@ -4922,7 +4922,7 @@
       <c r="M66" s="8" t="inlineStr"/>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -4988,7 +4988,7 @@
       <c r="M67" s="15" t="inlineStr"/>
       <c r="N67" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -5054,7 +5054,7 @@
       <c r="M68" s="8" t="inlineStr"/>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -5097,19 +5097,19 @@
           <t>20/11/2023</t>
         </is>
       </c>
-      <c r="I69" s="7" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+      <c r="I69" s="14" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J69" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP từ ngày 30/08/2026</t>
+          <t>Sửa đổi, bổ sung Thông tư 128/2021/TT-BQP</t>
         </is>
       </c>
       <c r="K69" s="10" t="inlineStr">
         <is>
-          <t>Cập nhật phân cấp đầu tư BQP giai đoạn 2023-2026</t>
+          <t>Cập nhật phân cấp đầu tư BQP</t>
         </is>
       </c>
       <c r="L69" s="10" t="inlineStr">
@@ -5120,7 +5120,7 @@
       <c r="M69" s="15" t="inlineStr"/>
       <c r="N69" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -5163,19 +5163,19 @@
           <t>10/02/2025</t>
         </is>
       </c>
-      <c r="I70" s="7" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+      <c r="I70" s="14" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP từ ngày 30/08/2026</t>
+          <t>Sửa đổi, bổ sung Thông tư 128/2021/TT-BQP</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>Phân cấp phê duyệt thiết kế, dự toán BQP giai đoạn 2024-2026</t>
+          <t>Phân cấp phê duyệt thiết kế, dự toán BQP</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
@@ -5186,7 +5186,7 @@
       <c r="M70" s="8" t="inlineStr"/>
       <c r="N70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5252,7 @@
       <c r="M71" s="15" t="inlineStr"/>
       <c r="N71" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       <c r="M72" s="8" t="inlineStr"/>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -5333,32 +5333,32 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Quyết định</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>102/2026/TT-BQP</t>
+          <t>35/QĐ-TTg</t>
         </is>
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>Quy định và hướng dẫn về lập, thẩm định, quyết định, phân cấp quyết định chủ trương đầu tư, dự án đầu tư trong Bộ Quốc phòng</t>
+          <t>Ban hành Danh mục bí mật Nhà nước trong lĩnh vực Quốc phòng</t>
         </is>
       </c>
       <c r="F73" s="13" t="inlineStr">
         <is>
-          <t>Bộ Quốc phòng</t>
+          <t>Thủ tướng Chính phủ</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="I73" s="14" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="J73" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 128/2021/TT-BQP, Thông tư 73/2023/TT-BQP và Thông tư 120/2024/TT-BQP</t>
+          <t>Quyết định số 12/QĐ-TTg</t>
         </is>
       </c>
       <c r="K73" s="10" t="inlineStr">
         <is>
-          <t>Văn bản xương sống về phân cấp, ủy quyền quyết định đầu tư và dự án đầu tư công mới nhất trong BQP</t>
+          <t>Quy định bảo mật hồ sơ, tài liệu thiết kế công trình quân sự</t>
         </is>
       </c>
       <c r="L73" s="10" t="inlineStr">
@@ -5384,7 +5384,7 @@
       <c r="M73" s="15" t="inlineStr"/>
       <c r="N73" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -5394,37 +5394,37 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Quốc phòng &amp; Doanh trại</t>
+          <t>Chi thường xuyên &amp; Tài sản công</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Quyết định</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>35/QĐ-TTg</t>
+          <t>15/2017/QH14</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Ban hành Danh mục bí mật Nhà nước trong lĩnh vực Quốc phòng</t>
+          <t>Luật Quản lý, sử dụng tài sản công</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>Thủ tướng Chính phủ</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>21/06/2017</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
@@ -5434,23 +5434,23 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>Quyết định số 12/QĐ-TTg</t>
+          <t>Luật Quản lý tài sản nhà nước 2008</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>Quy định bảo mật hồ sơ, tài liệu thiết kế công trình quân sự</t>
+          <t>Chế độ quản lý, bảo dưỡng, nâng cấp và sử dụng tài sản công</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
         </is>
       </c>
       <c r="M74" s="8" t="inlineStr"/>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -5465,27 +5465,27 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>15/2017/QH14</t>
+          <t>151/2017/NĐ-CP</t>
         </is>
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>Luật Quản lý, sử dụng tài sản công</t>
+          <t>Quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
         </is>
       </c>
       <c r="F75" s="13" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
         <is>
-          <t>21/06/2017</t>
+          <t>26/12/2017</t>
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr">
@@ -5493,19 +5493,19 @@
           <t>01/01/2018</t>
         </is>
       </c>
-      <c r="I75" s="14" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J75" s="10" t="inlineStr">
         <is>
-          <t>Luật Quản lý tài sản nhà nước 2008</t>
+          <t>Bị thay thế bởi Nghị định 186/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="K75" s="10" t="inlineStr">
         <is>
-          <t>Chế độ quản lý, bảo dưỡng, nâng cấp và sử dụng tài sản công</t>
+          <t>Áp dụng phân cấp tài sản công giai đoạn 2018-2025</t>
         </is>
       </c>
       <c r="L75" s="10" t="inlineStr">
@@ -5516,7 +5516,7 @@
       <c r="M75" s="15" t="inlineStr"/>
       <c r="N75" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>151/2017/NĐ-CP</t>
+          <t>186/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -5551,27 +5551,27 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>26/12/2017</t>
+          <t>18/09/2025</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
-        </is>
-      </c>
-      <c r="I76" s="7" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+          <t>01/11/2025</t>
+        </is>
+      </c>
+      <c r="I76" s="14" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 186/2025/NĐ-CP</t>
+          <t>Thay thế Nghị định 151/2017/NĐ-CP</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng phân cấp tài sản công giai đoạn 2018-2025</t>
+          <t>Quy định phân cấp thẩm quyền quyết định mua sắm, sửa chữa, bàn giao tài sản công hiện hành</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
@@ -5582,7 +5582,7 @@
       <c r="M76" s="8" t="inlineStr"/>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -5602,12 +5602,12 @@
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>186/2025/NĐ-CP</t>
+          <t>114/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 151/2017/NĐ-CP quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
         </is>
       </c>
       <c r="F77" s="13" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="G77" s="11" t="inlineStr">
         <is>
-          <t>18/09/2025</t>
+          <t>15/09/2024</t>
         </is>
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
+          <t>30/10/2024</t>
         </is>
       </c>
       <c r="I77" s="14" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="J77" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 151/2017/NĐ-CP</t>
+          <t>Sửa đổi, bổ sung Nghị định 151/2017/NĐ-CP về tài sản công</t>
         </is>
       </c>
       <c r="K77" s="10" t="inlineStr">
         <is>
-          <t>Quy định phân cấp thẩm quyền quyết định mua sắm, sửa chữa, bàn giao tài sản công hiện hành</t>
+          <t>Quy định thẩm quyền mua sắm, thuê, xử lý tài sản công</t>
         </is>
       </c>
       <c r="L77" s="10" t="inlineStr">
@@ -5648,7 +5648,7 @@
       <c r="M77" s="15" t="inlineStr"/>
       <c r="N77" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -5668,12 +5668,12 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>114/2024/NĐ-CP</t>
+          <t>138/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 151/2017/NĐ-CP quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
+          <t>Quy định việc lập dự toán, quản lý, sử dụng kinh phí chi thường xuyên NSNN để mua sắm tài sản, trang thiết bị; cải tạo, nâng cấp, mở rộng, xây dựng mới hạng mục công trình</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
@@ -5683,27 +5683,27 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>15/09/2024</t>
+          <t>24/10/2024</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>30/10/2024</t>
-        </is>
-      </c>
-      <c r="I78" s="14" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>24/10/2024</t>
+        </is>
+      </c>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung Nghị định 151/2017/NĐ-CP về tài sản công</t>
+          <t>Bị thay thế bởi Nghị định 98/2025/NĐ-CP và Nghị định 104/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>Quy định thẩm quyền mua sắm, thuê, xử lý tài sản công</t>
+          <t>Căn cứ giai đoạn cuối 2024</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
@@ -5714,7 +5714,7 @@
       <c r="M78" s="8" t="inlineStr"/>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -5734,12 +5734,12 @@
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>138/2024/NĐ-CP</t>
+          <t>98/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="E79" s="10" t="inlineStr">
         <is>
-          <t>Quy định việc lập dự toán, quản lý, sử dụng kinh phí chi thường xuyên NSNN để mua sắm tài sản, trang thiết bị; cải tạo, nâng cấp, mở rộng, xây dựng mới hạng mục công trình</t>
+          <t>Quy định việc lập dự toán, quản lý, sử dụng và quyết toán chi thường xuyên ngân sách nhà nước để mua sắm, sửa chữa, cải tạo, nâng cấp tài sản, trang thiết bị; chi thuê hàng hóa, dịch vụ; sửa chữa, cải tạo, nâng cấp, mở rộng, xây dựng mới hạng mục công trình trong các dự án đã đầu tư xây dựng và các nhiệm vụ cần thiết khác</t>
         </is>
       </c>
       <c r="F79" s="13" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="G79" s="11" t="inlineStr">
         <is>
-          <t>24/10/2024</t>
+          <t>25/06/2025</t>
         </is>
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>24/10/2024</t>
+          <t>15/08/2025</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="J79" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 98/2025/NĐ-CP và Nghị định 104/2026/NĐ-CP</t>
+          <t>Bị thay thế bởi Nghị định 104/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="K79" s="10" t="inlineStr">
         <is>
-          <t>Căn cứ giai đoạn cuối 2024</t>
+          <t>Áp dụng giai đoạn 2025-2026</t>
         </is>
       </c>
       <c r="L79" s="10" t="inlineStr">
@@ -5780,7 +5780,7 @@
       <c r="M79" s="15" t="inlineStr"/>
       <c r="N79" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -5800,12 +5800,12 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>98/2025/NĐ-CP</t>
+          <t>104/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Quy định việc lập dự toán, quản lý, sử dụng và quyết toán chi thường xuyên ngân sách nhà nước để mua sắm, sửa chữa, cải tạo, nâng cấp tài sản, trang thiết bị; chi thuê hàng hóa, dịch vụ; sửa chữa, cải tạo, nâng cấp, mở rộng, xây dựng mới hạng mục công trình trong các dự án đã đầu tư xây dựng và các nhiệm vụ cần thiết khác</t>
+          <t>Quy định việc lập dự toán, quản lý, sử dụng và quyết toán chi thường xuyên để thực hiện các nhiệm vụ quy định tại Điều 40 Luật Ngân sách nhà nước</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
@@ -5815,27 +5815,27 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>25/06/2025</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>15/08/2025</t>
-        </is>
-      </c>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="I80" s="14" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 104/2026/NĐ-CP</t>
+          <t>Thay thế Nghị định 138/2024/NĐ-CP và Nghị định 98/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng giai đoạn 2025-2026</t>
+          <t>Căn cứ pháp lý then chốt cho các dự án sửa chữa, nâng cấp sử dụng nguồn chi thường xuyên hiện hành</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
@@ -5846,7 +5846,7 @@
       <c r="M80" s="8" t="inlineStr"/>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -5861,32 +5861,32 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>104/2026/NĐ-CP</t>
+          <t>65/2021/TT-BTC</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
         <is>
-          <t>Quy định việc lập dự toán, quản lý, sử dụng và quyết toán chi thường xuyên để thực hiện các nhiệm vụ quy định tại Điều 40 Luật Ngân sách nhà nước</t>
+          <t>Quy định về lập dự toán, phân bổ và quyết toán kinh phí bảo dưỡng, sửa chữa tài sản công</t>
         </is>
       </c>
       <c r="F81" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Tài chính</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>29/07/2021</t>
         </is>
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>15/09/2021</t>
         </is>
       </c>
       <c r="I81" s="14" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="J81" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 138/2024/NĐ-CP và Nghị định 98/2025/NĐ-CP</t>
+          <t>Thông tư 92/2017/TT-BTC</t>
         </is>
       </c>
       <c r="K81" s="10" t="inlineStr">
         <is>
-          <t>Căn cứ pháp lý then chốt cho các dự án sửa chữa, nâng cấp sử dụng nguồn chi thường xuyên hiện hành</t>
+          <t>Áp dụng lập dự toán và thanh toán sửa chữa tài sản công dưới 500 triệu</t>
         </is>
       </c>
       <c r="L81" s="10" t="inlineStr">
@@ -5912,7 +5912,7 @@
       <c r="M81" s="15" t="inlineStr"/>
       <c r="N81" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -5922,37 +5922,37 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Chi thường xuyên &amp; Tài sản công</t>
+          <t>Chất lượng &amp; Nghiệm thu</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>65/2021/TT-BTC</t>
+          <t>84/2015/QH13</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Quy định về lập dự toán, phân bổ và quyết toán kinh phí bảo dưỡng, sửa chữa tài sản công</t>
+          <t>Luật An toàn, vệ sinh lao động (Quy định an toàn lao động, phòng ngừa sự cố trên công trường xây dựng)</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>Bộ Tài chính</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>29/07/2021</t>
+          <t>25/06/2015</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>15/09/2021</t>
+          <t>01/07/2016</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
@@ -5960,25 +5960,21 @@
           <t>Đang có hiệu lực</t>
         </is>
       </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>Thông tư 92/2017/TT-BTC</t>
-        </is>
-      </c>
+      <c r="J82" s="3" t="inlineStr"/>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng lập dự toán và thanh toán sửa chữa tài sản công dưới 500 triệu</t>
+          <t>Căn cứ bắt buộc trong Hợp đồng thi công gói XD-01 và Giám sát an toàn gói TV-08</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
+          <t>XD-01, TV-08, AN_TOAN_LAO_DONG</t>
         </is>
       </c>
       <c r="M82" s="8" t="inlineStr"/>
       <c r="N82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5984,7 @@
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>Chất lượng &amp; Nghiệm thu</t>
+          <t>Xây dựng &amp; Quản lý dự án</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
@@ -5998,12 +5994,12 @@
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>84/2015/QH13</t>
+          <t>72/2020/QH14</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>Luật An toàn, vệ sinh lao động (Quy định an toàn lao động, phòng ngừa sự cố trên công trường xây dựng)</t>
+          <t>Luật Bảo vệ môi trường năm 2020</t>
         </is>
       </c>
       <c r="F83" s="13" t="inlineStr">
@@ -6013,12 +6009,12 @@
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>25/06/2015</t>
+          <t>17/11/2020</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>01/07/2016</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="I83" s="14" t="inlineStr">
@@ -6026,21 +6022,25 @@
           <t>Đang có hiệu lực</t>
         </is>
       </c>
-      <c r="J83" s="10" t="inlineStr"/>
+      <c r="J83" s="10" t="inlineStr">
+        <is>
+          <t>Thay thế Luật Bảo vệ môi trường 55/2014/QH13</t>
+        </is>
+      </c>
       <c r="K83" s="10" t="inlineStr">
         <is>
-          <t>Căn cứ bắt buộc trong Hợp đồng thi công gói XD-01 và Giám sát an toàn gói TV-08</t>
+          <t>Căn cứ thực hiện thủ tục Đăng ký môi trường / ĐTM cho các hạng mục Kho xăng dầu, Bệnh xá, Bể bơi</t>
         </is>
       </c>
       <c r="L83" s="10" t="inlineStr">
         <is>
-          <t>XD-01, TV-08, AN_TOAN_LAO_DONG</t>
+          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
         </is>
       </c>
       <c r="M83" s="15" t="inlineStr"/>
       <c r="N83" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -6055,32 +6055,32 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>72/2020/QH14</t>
+          <t>08/2022/NĐ-CP</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Luật Bảo vệ môi trường năm 2020</t>
+          <t>Quy định chi tiết một số điều của Luật Bảo vệ môi trường</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>17/11/2020</t>
+          <t>10/01/2022</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>10/01/2022</t>
         </is>
       </c>
       <c r="I84" s="14" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Luật Bảo vệ môi trường 55/2014/QH13</t>
+          <t>Được sửa đổi, bổ sung bởi Nghị định số 05/2025/NĐ-CP và Nghị định số 48/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>Căn cứ thực hiện thủ tục Đăng ký môi trường / ĐTM cho các hạng mục Kho xăng dầu, Bệnh xá, Bể bơi</t>
+          <t>Quy định đối tượng và hồ sơ Đăng ký môi trường công trình (bổ trợ Nghị quyết 66.19/2026/NQ-CP)</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
@@ -6106,7 +6106,7 @@
       <c r="M84" s="8" t="inlineStr"/>
       <c r="N84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -6126,12 +6126,12 @@
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>08/2022/NĐ-CP</t>
+          <t>05/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Bảo vệ môi trường</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP ngày 10 tháng 01 năm 2022 của Chính phủ quy định chi tiết một số điều của Luật Bảo vệ môi trường</t>
         </is>
       </c>
       <c r="F85" s="13" t="inlineStr">
@@ -6141,12 +6141,12 @@
       </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
-          <t>10/01/2022</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>10/01/2022</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="I85" s="14" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="J85" s="10" t="inlineStr">
         <is>
-          <t>Được sửa đổi, bổ sung bởi Nghị định số 05/2025/NĐ-CP và Nghị định số 48/2026/NĐ-CP</t>
+          <t>Sửa đổi, bổ sung Nghị định số 08/2022/NĐ-CP; được sửa đổi bởi Nghị định 48/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="K85" s="10" t="inlineStr">
         <is>
-          <t>Quy định đối tượng và hồ sơ Đăng ký môi trường công trình (bổ trợ Nghị quyết 66.19/2026/NQ-CP)</t>
+          <t>Quy định phân quyền và cắt giảm thủ tục cấp Giấy phép môi trường, Đăng ký môi trường</t>
         </is>
       </c>
       <c r="L85" s="10" t="inlineStr">
@@ -6172,7 +6172,7 @@
       <c r="M85" s="15" t="inlineStr"/>
       <c r="N85" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>05/2025/NĐ-CP</t>
+          <t>48/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP ngày 10 tháng 01 năm 2022 của Chính phủ quy định chi tiết một số điều của Luật Bảo vệ môi trường</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP ngày 10 tháng 01 năm 2022 của Chính phủ quy định chi tiết một số điều của Luật Bảo vệ môi trường được sửa đổi, bổ sung bởi Nghị định số 05/2025/NĐ-CP ngày 06 tháng 01 năm 2025</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="I86" s="14" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung Nghị định số 08/2022/NĐ-CP; được sửa đổi bởi Nghị định 48/2026/NĐ-CP</t>
+          <t>Sửa đổi, bổ sung Nghị định số 08/2022/NĐ-CP và Nghị định số 05/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>Quy định phân quyền và cắt giảm thủ tục cấp Giấy phép môi trường, Đăng ký môi trường</t>
+          <t>Đơn giản hóa tối đa thủ tục môi trường cho các công trình xây dựng và dự án đầu tư công hiện hành</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
@@ -6238,73 +6238,7 @@
       <c r="M86" s="8" t="inlineStr"/>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:48</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="26" customHeight="1">
-      <c r="A87" s="9" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" s="10" t="inlineStr">
-        <is>
-          <t>Xây dựng &amp; Quản lý dự án</t>
-        </is>
-      </c>
-      <c r="C87" s="11" t="inlineStr">
-        <is>
-          <t>Nghị định</t>
-        </is>
-      </c>
-      <c r="D87" s="12" t="inlineStr">
-        <is>
-          <t>48/2026/NĐ-CP</t>
-        </is>
-      </c>
-      <c r="E87" s="10" t="inlineStr">
-        <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP ngày 10 tháng 01 năm 2022 của Chính phủ quy định chi tiết một số điều của Luật Bảo vệ môi trường được sửa đổi, bổ sung bởi Nghị định số 05/2025/NĐ-CP ngày 06 tháng 01 năm 2025</t>
-        </is>
-      </c>
-      <c r="F87" s="13" t="inlineStr">
-        <is>
-          <t>Chính phủ</t>
-        </is>
-      </c>
-      <c r="G87" s="11" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="H87" s="11" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="I87" s="14" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
-        </is>
-      </c>
-      <c r="J87" s="10" t="inlineStr">
-        <is>
-          <t>Sửa đổi, bổ sung Nghị định số 08/2022/NĐ-CP và Nghị định số 05/2025/NĐ-CP</t>
-        </is>
-      </c>
-      <c r="K87" s="10" t="inlineStr">
-        <is>
-          <t>Đơn giản hóa tối đa thủ tục môi trường cho các công trình xây dựng và dự án đầu tư công hiện hành</t>
-        </is>
-      </c>
-      <c r="L87" s="10" t="inlineStr">
-        <is>
-          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
-        </is>
-      </c>
-      <c r="M87" s="15" t="inlineStr"/>
-      <c r="N87" s="11" t="inlineStr">
-        <is>
-          <t>2026-08-21 15:48</t>
+          <t>2026-08-21 15:51</t>
         </is>
       </c>
     </row>

--- a/Kho_Can_Cu_Phap_Ly.xlsx
+++ b/Kho_Can_Cu_Phap_Ly.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N86"/>
+  <dimension ref="A1:N87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -698,7 +698,7 @@
       <c r="M2" s="8" t="inlineStr"/>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       <c r="M3" s="15" t="inlineStr"/>
       <c r="N3" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       <c r="M5" s="15" t="inlineStr"/>
       <c r="N5" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       <c r="M6" s="8" t="inlineStr"/>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       <c r="M7" s="15" t="inlineStr"/>
       <c r="N7" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       <c r="M8" s="8" t="inlineStr"/>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       <c r="M9" s="15" t="inlineStr"/>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       <c r="M10" s="8" t="inlineStr"/>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       <c r="M11" s="15" t="inlineStr"/>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       <c r="M12" s="8" t="inlineStr"/>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       <c r="M13" s="15" t="inlineStr"/>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       <c r="M14" s="8" t="inlineStr"/>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       <c r="M15" s="15" t="inlineStr"/>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
       <c r="M16" s="8" t="inlineStr"/>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
       <c r="M17" s="15" t="inlineStr"/>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       <c r="M18" s="8" t="inlineStr"/>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       <c r="M19" s="15" t="inlineStr"/>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       <c r="M20" s="8" t="inlineStr"/>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -1952,7 +1952,7 @@
       <c r="M21" s="15" t="inlineStr"/>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       <c r="M22" s="8" t="inlineStr"/>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       <c r="M23" s="15" t="inlineStr"/>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       <c r="M24" s="8" t="inlineStr"/>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       <c r="M25" s="15" t="inlineStr"/>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       <c r="M26" s="8" t="inlineStr"/>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       <c r="M27" s="15" t="inlineStr"/>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       <c r="M28" s="8" t="inlineStr"/>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       <c r="M29" s="15" t="inlineStr"/>
       <c r="N29" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2546,7 @@
       <c r="M30" s="8" t="inlineStr"/>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
       <c r="M31" s="15" t="inlineStr"/>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       <c r="M32" s="8" t="inlineStr"/>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       <c r="M33" s="15" t="inlineStr"/>
       <c r="N33" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
       <c r="M34" s="8" t="inlineStr"/>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       <c r="M35" s="15" t="inlineStr"/>
       <c r="N35" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       <c r="M36" s="8" t="inlineStr"/>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       <c r="M37" s="15" t="inlineStr"/>
       <c r="N37" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -3074,7 +3074,7 @@
       <c r="M38" s="8" t="inlineStr"/>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       <c r="M39" s="15" t="inlineStr"/>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       <c r="M40" s="8" t="inlineStr"/>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3272,7 @@
       <c r="M41" s="15" t="inlineStr"/>
       <c r="N41" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3338,7 @@
       <c r="M42" s="8" t="inlineStr"/>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       <c r="M43" s="15" t="inlineStr"/>
       <c r="N43" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3470,7 @@
       <c r="M44" s="8" t="inlineStr"/>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3536,7 @@
       <c r="M45" s="15" t="inlineStr"/>
       <c r="N45" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3602,7 @@
       <c r="M46" s="8" t="inlineStr"/>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
       <c r="M47" s="15" t="inlineStr"/>
       <c r="N47" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3734,7 @@
       <c r="M48" s="8" t="inlineStr"/>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
       <c r="M49" s="15" t="inlineStr"/>
       <c r="N49" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       <c r="M50" s="8" t="inlineStr"/>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3932,7 @@
       <c r="M51" s="15" t="inlineStr"/>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
       <c r="M52" s="8" t="inlineStr"/>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       <c r="M53" s="15" t="inlineStr"/>
       <c r="N53" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4130,7 @@
       <c r="M54" s="8" t="inlineStr"/>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
       <c r="M55" s="15" t="inlineStr"/>
       <c r="N55" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -4262,7 +4262,7 @@
       <c r="M56" s="8" t="inlineStr"/>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       <c r="M57" s="15" t="inlineStr"/>
       <c r="N57" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       <c r="M58" s="8" t="inlineStr"/>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4460,7 @@
       <c r="M59" s="15" t="inlineStr"/>
       <c r="N59" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -4526,7 +4526,7 @@
       <c r="M60" s="8" t="inlineStr"/>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       <c r="M61" s="15" t="inlineStr"/>
       <c r="N61" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4658,7 @@
       <c r="M62" s="8" t="inlineStr"/>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -4724,7 +4724,7 @@
       <c r="M63" s="15" t="inlineStr"/>
       <c r="N63" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4790,7 @@
       <c r="M64" s="8" t="inlineStr"/>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       <c r="M65" s="15" t="inlineStr"/>
       <c r="N65" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -4899,19 +4899,19 @@
           <t>20/11/2021</t>
         </is>
       </c>
-      <c r="I66" s="14" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>Được sửa đổi, bổ sung bởi Thông tư 73/2023/TT-BQP và Thông tư 120/2024/TT-BQP</t>
+          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>Căn cứ pháp lý then chốt về phân cấp, ủy quyền quyết định đầu tư và dự án đầu tư công trong BQP</t>
+          <t>Áp dụng phân cấp thẩm quyền đầu tư BQP giai đoạn 2021-2026</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
@@ -4922,7 +4922,7 @@
       <c r="M66" s="8" t="inlineStr"/>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -4988,7 +4988,7 @@
       <c r="M67" s="15" t="inlineStr"/>
       <c r="N67" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -5054,7 +5054,7 @@
       <c r="M68" s="8" t="inlineStr"/>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -5097,19 +5097,19 @@
           <t>20/11/2023</t>
         </is>
       </c>
-      <c r="I69" s="14" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J69" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung Thông tư 128/2021/TT-BQP</t>
+          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP</t>
         </is>
       </c>
       <c r="K69" s="10" t="inlineStr">
         <is>
-          <t>Cập nhật phân cấp đầu tư BQP</t>
+          <t>Cập nhật phân cấp đầu tư BQP giai đoạn 2023-2026</t>
         </is>
       </c>
       <c r="L69" s="10" t="inlineStr">
@@ -5120,7 +5120,7 @@
       <c r="M69" s="15" t="inlineStr"/>
       <c r="N69" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -5163,19 +5163,19 @@
           <t>10/02/2025</t>
         </is>
       </c>
-      <c r="I70" s="14" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung Thông tư 128/2021/TT-BQP</t>
+          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>Phân cấp phê duyệt thiết kế, dự toán BQP</t>
+          <t>Phân cấp phê duyệt thiết kế, dự toán BQP giai đoạn 2024-2026</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
@@ -5186,7 +5186,7 @@
       <c r="M70" s="8" t="inlineStr"/>
       <c r="N70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5252,7 @@
       <c r="M71" s="15" t="inlineStr"/>
       <c r="N71" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết và biện pháp thực hiện một số nội dung của Luật Xây dựng thuộc phạm vi quản lý của Bộ Quốc phòng</t>
+          <t>Quy định chi tiết và biện pháp thực hiện một số nội dung Luật Xây dựng thuộc phạm vi quản lý của Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -5318,7 +5318,7 @@
       <c r="M72" s="8" t="inlineStr"/>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -5333,32 +5333,32 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Quyết định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>35/QĐ-TTg</t>
+          <t>102/2026/TT-BQP</t>
         </is>
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>Ban hành Danh mục bí mật Nhà nước trong lĩnh vực Quốc phòng</t>
+          <t>Quy định và hướng dẫn về lập, thẩm định, quyết định, phân cấp quyết định chủ trương đầu tư, dự án đầu tư trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F73" s="13" t="inlineStr">
         <is>
-          <t>Thủ tướng Chính phủ</t>
+          <t>Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="I73" s="14" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="J73" s="10" t="inlineStr">
         <is>
-          <t>Quyết định số 12/QĐ-TTg</t>
+          <t>Thay thế Thông tư 128/2021/TT-BQP, Thông tư 73/2023/TT-BQP và Thông tư 120/2024/TT-BQP</t>
         </is>
       </c>
       <c r="K73" s="10" t="inlineStr">
         <is>
-          <t>Quy định bảo mật hồ sơ, tài liệu thiết kế công trình quân sự</t>
+          <t>Văn bản xương sống về phân cấp, ủy quyền quyết định đầu tư và dự án đầu tư công mới nhất trong BQP</t>
         </is>
       </c>
       <c r="L73" s="10" t="inlineStr">
@@ -5384,7 +5384,7 @@
       <c r="M73" s="15" t="inlineStr"/>
       <c r="N73" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -5394,37 +5394,37 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Chi thường xuyên &amp; Tài sản công</t>
+          <t>Quốc phòng &amp; Doanh trại</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Quyết định</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>15/2017/QH14</t>
+          <t>35/QĐ-TTg</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Luật Quản lý, sử dụng tài sản công</t>
+          <t>Ban hành Danh mục bí mật Nhà nước trong lĩnh vực Quốc phòng</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Thủ tướng Chính phủ</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>21/06/2017</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
@@ -5434,23 +5434,23 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>Luật Quản lý tài sản nhà nước 2008</t>
+          <t>Quyết định số 12/QĐ-TTg</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>Chế độ quản lý, bảo dưỡng, nâng cấp và sử dụng tài sản công</t>
+          <t>Quy định bảo mật hồ sơ, tài liệu thiết kế công trình quân sự</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
+          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M74" s="8" t="inlineStr"/>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -5465,27 +5465,27 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>151/2017/NĐ-CP</t>
+          <t>15/2017/QH14</t>
         </is>
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
+          <t>Luật Quản lý, sử dụng tài sản công</t>
         </is>
       </c>
       <c r="F75" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
         <is>
-          <t>26/12/2017</t>
+          <t>21/06/2017</t>
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr">
@@ -5493,19 +5493,19 @@
           <t>01/01/2018</t>
         </is>
       </c>
-      <c r="I75" s="7" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+      <c r="I75" s="14" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J75" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 186/2025/NĐ-CP</t>
+          <t>Luật Quản lý tài sản nhà nước 2008</t>
         </is>
       </c>
       <c r="K75" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng phân cấp tài sản công giai đoạn 2018-2025</t>
+          <t>Chế độ quản lý, bảo dưỡng, nâng cấp và sử dụng tài sản công</t>
         </is>
       </c>
       <c r="L75" s="10" t="inlineStr">
@@ -5516,7 +5516,7 @@
       <c r="M75" s="15" t="inlineStr"/>
       <c r="N75" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>186/2025/NĐ-CP</t>
+          <t>151/2017/NĐ-CP</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -5551,27 +5551,27 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>18/09/2025</t>
+          <t>26/12/2017</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
-        </is>
-      </c>
-      <c r="I76" s="14" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>01/01/2018</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 151/2017/NĐ-CP</t>
+          <t>Bị thay thế bởi Nghị định 186/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>Quy định phân cấp thẩm quyền quyết định mua sắm, sửa chữa, bàn giao tài sản công hiện hành</t>
+          <t>Áp dụng phân cấp tài sản công giai đoạn 2018-2025</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
@@ -5582,7 +5582,7 @@
       <c r="M76" s="8" t="inlineStr"/>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -5602,12 +5602,12 @@
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>114/2024/NĐ-CP</t>
+          <t>186/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 151/2017/NĐ-CP quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
+          <t>Quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
         </is>
       </c>
       <c r="F77" s="13" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="G77" s="11" t="inlineStr">
         <is>
-          <t>15/09/2024</t>
+          <t>18/09/2025</t>
         </is>
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>30/10/2024</t>
+          <t>01/11/2025</t>
         </is>
       </c>
       <c r="I77" s="14" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="J77" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung Nghị định 151/2017/NĐ-CP về tài sản công</t>
+          <t>Thay thế Nghị định 151/2017/NĐ-CP</t>
         </is>
       </c>
       <c r="K77" s="10" t="inlineStr">
         <is>
-          <t>Quy định thẩm quyền mua sắm, thuê, xử lý tài sản công</t>
+          <t>Quy định phân cấp thẩm quyền quyết định mua sắm, sửa chữa, bàn giao tài sản công hiện hành</t>
         </is>
       </c>
       <c r="L77" s="10" t="inlineStr">
@@ -5648,7 +5648,7 @@
       <c r="M77" s="15" t="inlineStr"/>
       <c r="N77" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -5668,12 +5668,12 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>138/2024/NĐ-CP</t>
+          <t>114/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Quy định việc lập dự toán, quản lý, sử dụng kinh phí chi thường xuyên NSNN để mua sắm tài sản, trang thiết bị; cải tạo, nâng cấp, mở rộng, xây dựng mới hạng mục công trình</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 151/2017/NĐ-CP quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
@@ -5683,27 +5683,27 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>24/10/2024</t>
+          <t>15/09/2024</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>24/10/2024</t>
-        </is>
-      </c>
-      <c r="I78" s="7" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+          <t>30/10/2024</t>
+        </is>
+      </c>
+      <c r="I78" s="14" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 98/2025/NĐ-CP và Nghị định 104/2026/NĐ-CP</t>
+          <t>Sửa đổi, bổ sung Nghị định 151/2017/NĐ-CP về tài sản công</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>Căn cứ giai đoạn cuối 2024</t>
+          <t>Quy định thẩm quyền mua sắm, thuê, xử lý tài sản công</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
@@ -5714,7 +5714,7 @@
       <c r="M78" s="8" t="inlineStr"/>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -5734,12 +5734,12 @@
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>98/2025/NĐ-CP</t>
+          <t>138/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="E79" s="10" t="inlineStr">
         <is>
-          <t>Quy định việc lập dự toán, quản lý, sử dụng và quyết toán chi thường xuyên ngân sách nhà nước để mua sắm, sửa chữa, cải tạo, nâng cấp tài sản, trang thiết bị; chi thuê hàng hóa, dịch vụ; sửa chữa, cải tạo, nâng cấp, mở rộng, xây dựng mới hạng mục công trình trong các dự án đã đầu tư xây dựng và các nhiệm vụ cần thiết khác</t>
+          <t>Quy định việc lập dự toán, quản lý, sử dụng kinh phí chi thường xuyên NSNN để mua sắm tài sản, trang thiết bị; cải tạo, nâng cấp, mở rộng, xây dựng mới hạng mục công trình</t>
         </is>
       </c>
       <c r="F79" s="13" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="G79" s="11" t="inlineStr">
         <is>
-          <t>25/06/2025</t>
+          <t>24/10/2024</t>
         </is>
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>15/08/2025</t>
+          <t>24/10/2024</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="J79" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 104/2026/NĐ-CP</t>
+          <t>Bị thay thế bởi Nghị định 98/2025/NĐ-CP và Nghị định 104/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="K79" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng giai đoạn 2025-2026</t>
+          <t>Căn cứ giai đoạn cuối 2024</t>
         </is>
       </c>
       <c r="L79" s="10" t="inlineStr">
@@ -5780,7 +5780,7 @@
       <c r="M79" s="15" t="inlineStr"/>
       <c r="N79" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -5800,12 +5800,12 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>104/2026/NĐ-CP</t>
+          <t>98/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Quy định việc lập dự toán, quản lý, sử dụng và quyết toán chi thường xuyên để thực hiện các nhiệm vụ quy định tại Điều 40 Luật Ngân sách nhà nước</t>
+          <t>Quy định việc lập dự toán, quản lý, sử dụng và quyết toán chi thường xuyên ngân sách nhà nước để mua sắm, sửa chữa, cải tạo, nâng cấp tài sản, trang thiết bị; chi thuê hàng hóa, dịch vụ; sửa chữa, cải tạo, nâng cấp, mở rộng, xây dựng mới hạng mục công trình trong các dự án đã đầu tư xây dựng và các nhiệm vụ cần thiết khác</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
@@ -5815,27 +5815,27 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>25/06/2025</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
-        </is>
-      </c>
-      <c r="I80" s="14" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>15/08/2025</t>
+        </is>
+      </c>
+      <c r="I80" s="7" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 138/2024/NĐ-CP và Nghị định 98/2025/NĐ-CP</t>
+          <t>Bị thay thế bởi Nghị định 104/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>Căn cứ pháp lý then chốt cho các dự án sửa chữa, nâng cấp sử dụng nguồn chi thường xuyên hiện hành</t>
+          <t>Áp dụng giai đoạn 2025-2026</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
@@ -5846,7 +5846,7 @@
       <c r="M80" s="8" t="inlineStr"/>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -5861,32 +5861,32 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>65/2021/TT-BTC</t>
+          <t>104/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
         <is>
-          <t>Quy định về lập dự toán, phân bổ và quyết toán kinh phí bảo dưỡng, sửa chữa tài sản công</t>
+          <t>Quy định việc lập dự toán, quản lý, sử dụng và quyết toán chi thường xuyên để thực hiện các nhiệm vụ quy định tại Điều 40 Luật Ngân sách nhà nước</t>
         </is>
       </c>
       <c r="F81" s="13" t="inlineStr">
         <is>
-          <t>Bộ Tài chính</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
         <is>
-          <t>29/07/2021</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>15/09/2021</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="I81" s="14" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="J81" s="10" t="inlineStr">
         <is>
-          <t>Thông tư 92/2017/TT-BTC</t>
+          <t>Thay thế Nghị định 138/2024/NĐ-CP và Nghị định 98/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="K81" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng lập dự toán và thanh toán sửa chữa tài sản công dưới 500 triệu</t>
+          <t>Căn cứ pháp lý then chốt cho các dự án sửa chữa, nâng cấp sử dụng nguồn chi thường xuyên hiện hành</t>
         </is>
       </c>
       <c r="L81" s="10" t="inlineStr">
@@ -5912,7 +5912,7 @@
       <c r="M81" s="15" t="inlineStr"/>
       <c r="N81" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -5922,37 +5922,37 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Chất lượng &amp; Nghiệm thu</t>
+          <t>Chi thường xuyên &amp; Tài sản công</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>84/2015/QH13</t>
+          <t>65/2021/TT-BTC</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Luật An toàn, vệ sinh lao động (Quy định an toàn lao động, phòng ngừa sự cố trên công trường xây dựng)</t>
+          <t>Quy định về lập dự toán, phân bổ và quyết toán kinh phí bảo dưỡng, sửa chữa tài sản công</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Bộ Tài chính</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>25/06/2015</t>
+          <t>29/07/2021</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>01/07/2016</t>
+          <t>15/09/2021</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
@@ -5960,21 +5960,25 @@
           <t>Đang có hiệu lực</t>
         </is>
       </c>
-      <c r="J82" s="3" t="inlineStr"/>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>Thông tư 92/2017/TT-BTC</t>
+        </is>
+      </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>Căn cứ bắt buộc trong Hợp đồng thi công gói XD-01 và Giám sát an toàn gói TV-08</t>
+          <t>Áp dụng lập dự toán và thanh toán sửa chữa tài sản công dưới 500 triệu</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>XD-01, TV-08, AN_TOAN_LAO_DONG</t>
+          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
         </is>
       </c>
       <c r="M82" s="8" t="inlineStr"/>
       <c r="N82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -5984,7 +5988,7 @@
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>Xây dựng &amp; Quản lý dự án</t>
+          <t>Chất lượng &amp; Nghiệm thu</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
@@ -5994,12 +5998,12 @@
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>72/2020/QH14</t>
+          <t>84/2015/QH13</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>Luật Bảo vệ môi trường năm 2020</t>
+          <t>Luật An toàn, vệ sinh lao động (Quy định an toàn lao động, phòng ngừa sự cố trên công trường xây dựng)</t>
         </is>
       </c>
       <c r="F83" s="13" t="inlineStr">
@@ -6009,12 +6013,12 @@
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>17/11/2020</t>
+          <t>25/06/2015</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/07/2016</t>
         </is>
       </c>
       <c r="I83" s="14" t="inlineStr">
@@ -6022,25 +6026,21 @@
           <t>Đang có hiệu lực</t>
         </is>
       </c>
-      <c r="J83" s="10" t="inlineStr">
-        <is>
-          <t>Thay thế Luật Bảo vệ môi trường 55/2014/QH13</t>
-        </is>
-      </c>
+      <c r="J83" s="10" t="inlineStr"/>
       <c r="K83" s="10" t="inlineStr">
         <is>
-          <t>Căn cứ thực hiện thủ tục Đăng ký môi trường / ĐTM cho các hạng mục Kho xăng dầu, Bệnh xá, Bể bơi</t>
+          <t>Căn cứ bắt buộc trong Hợp đồng thi công gói XD-01 và Giám sát an toàn gói TV-08</t>
         </is>
       </c>
       <c r="L83" s="10" t="inlineStr">
         <is>
-          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
+          <t>XD-01, TV-08, AN_TOAN_LAO_DONG</t>
         </is>
       </c>
       <c r="M83" s="15" t="inlineStr"/>
       <c r="N83" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -6055,32 +6055,32 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>08/2022/NĐ-CP</t>
+          <t>72/2020/QH14</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Bảo vệ môi trường</t>
+          <t>Luật Bảo vệ môi trường năm 2020</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>10/01/2022</t>
+          <t>17/11/2020</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>10/01/2022</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="I84" s="14" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>Được sửa đổi, bổ sung bởi Nghị định số 05/2025/NĐ-CP và Nghị định số 48/2026/NĐ-CP</t>
+          <t>Thay thế Luật Bảo vệ môi trường 55/2014/QH13</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>Quy định đối tượng và hồ sơ Đăng ký môi trường công trình (bổ trợ Nghị quyết 66.19/2026/NQ-CP)</t>
+          <t>Căn cứ thực hiện thủ tục Đăng ký môi trường / ĐTM cho các hạng mục Kho xăng dầu, Bệnh xá, Bể bơi</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
@@ -6106,7 +6106,7 @@
       <c r="M84" s="8" t="inlineStr"/>
       <c r="N84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -6126,12 +6126,12 @@
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>05/2025/NĐ-CP</t>
+          <t>08/2022/NĐ-CP</t>
         </is>
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP ngày 10 tháng 01 năm 2022 của Chính phủ quy định chi tiết một số điều của Luật Bảo vệ môi trường</t>
+          <t>Quy định chi tiết một số điều của Luật Bảo vệ môi trường</t>
         </is>
       </c>
       <c r="F85" s="13" t="inlineStr">
@@ -6141,12 +6141,12 @@
       </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>10/01/2022</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>10/01/2022</t>
         </is>
       </c>
       <c r="I85" s="14" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="J85" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung Nghị định số 08/2022/NĐ-CP; được sửa đổi bởi Nghị định 48/2026/NĐ-CP</t>
+          <t>Được sửa đổi, bổ sung bởi Nghị định số 05/2025/NĐ-CP và Nghị định số 48/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="K85" s="10" t="inlineStr">
         <is>
-          <t>Quy định phân quyền và cắt giảm thủ tục cấp Giấy phép môi trường, Đăng ký môi trường</t>
+          <t>Quy định đối tượng và hồ sơ Đăng ký môi trường công trình (bổ trợ Nghị quyết 66.19/2026/NQ-CP)</t>
         </is>
       </c>
       <c r="L85" s="10" t="inlineStr">
@@ -6172,7 +6172,7 @@
       <c r="M85" s="15" t="inlineStr"/>
       <c r="N85" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>48/2026/NĐ-CP</t>
+          <t>05/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP ngày 10 tháng 01 năm 2022 của Chính phủ quy định chi tiết một số điều của Luật Bảo vệ môi trường được sửa đổi, bổ sung bởi Nghị định số 05/2025/NĐ-CP ngày 06 tháng 01 năm 2025</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP ngày 10 tháng 01 năm 2022 của Chính phủ quy định chi tiết một số điều của Luật Bảo vệ môi trường</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="I86" s="14" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung Nghị định số 08/2022/NĐ-CP và Nghị định số 05/2025/NĐ-CP</t>
+          <t>Sửa đổi, bổ sung Nghị định số 08/2022/NĐ-CP; được sửa đổi bởi Nghị định 48/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>Đơn giản hóa tối đa thủ tục môi trường cho các công trình xây dựng và dự án đầu tư công hiện hành</t>
+          <t>Quy định phân quyền và cắt giảm thủ tục cấp Giấy phép môi trường, Đăng ký môi trường</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
@@ -6238,7 +6238,73 @@
       <c r="M86" s="8" t="inlineStr"/>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:51</t>
+          <t>2026-08-21 15:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="26" customHeight="1">
+      <c r="A87" s="9" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>Xây dựng &amp; Quản lý dự án</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>Nghị định</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>48/2026/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP ngày 10 tháng 01 năm 2022 của Chính phủ quy định chi tiết một số điều của Luật Bảo vệ môi trường được sửa đổi, bổ sung bởi Nghị định số 05/2025/NĐ-CP ngày 06 tháng 01 năm 2025</t>
+        </is>
+      </c>
+      <c r="F87" s="13" t="inlineStr">
+        <is>
+          <t>Chính phủ</t>
+        </is>
+      </c>
+      <c r="G87" s="11" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="H87" s="11" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="I87" s="14" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
+        </is>
+      </c>
+      <c r="J87" s="10" t="inlineStr">
+        <is>
+          <t>Sửa đổi, bổ sung Nghị định số 08/2022/NĐ-CP và Nghị định số 05/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="K87" s="10" t="inlineStr">
+        <is>
+          <t>Đơn giản hóa tối đa thủ tục môi trường cho các công trình xây dựng và dự án đầu tư công hiện hành</t>
+        </is>
+      </c>
+      <c r="L87" s="10" t="inlineStr">
+        <is>
+          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
+        </is>
+      </c>
+      <c r="M87" s="15" t="inlineStr"/>
+      <c r="N87" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:54</t>
         </is>
       </c>
     </row>

--- a/Kho_Can_Cu_Phap_Ly.xlsx
+++ b/Kho_Can_Cu_Phap_Ly.xlsx
@@ -45,13 +45,13 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00991B1B"/>
+      <color rgb="00065F46"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00065F46"/>
+      <color rgb="00991B1B"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -76,8 +76,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
-        <bgColor rgb="00FEE2E2"/>
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -88,8 +88,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D1FAE5"/>
-        <bgColor rgb="00D1FAE5"/>
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -652,12 +652,12 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>30/2009/QH12</t>
+          <t>47/2024/QH15</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Luật Quy hoạch đô thị năm 2009</t>
+          <t>Luật Quy hoạch đô thị và nông thôn năm 2024</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
@@ -667,27 +667,27 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>17/06/2009</t>
+          <t>26/11/2024</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>01/01/2010</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Luật Quy hoạch đô thị và nông thôn số 47/2024/QH15</t>
+          <t>Thay thế Luật Quy hoạch đô thị 30/2009/QH12</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Căn cứ pháp lý nền tảng cho việc lập, thẩm định và phê duyệt điều chỉnh Quy hoạch Tổng mặt bằng 1/500 doanh trại và khu chức năng</t>
+          <t>Có hiệu lực từ 01/07/2025; hợp nhất quy hoạch đô thị và nông thôn, phân cấp mạnh cho địa phương</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -698,7 +698,7 @@
       <c r="M2" s="8" t="inlineStr"/>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -713,58 +713,58 @@
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>44/2015/NĐ-CP</t>
+          <t>30/2009/QH12</t>
         </is>
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số nội dung về quy hoạch xây dựng</t>
+          <t>Luật Quy hoạch đô thị năm 2009</t>
         </is>
       </c>
       <c r="F3" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
-          <t>06/05/2015</t>
+          <t>17/06/2009</t>
         </is>
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
-          <t>30/06/2015</t>
+          <t>01/01/2010</t>
         </is>
       </c>
       <c r="I3" s="14" t="inlineStr">
         <is>
-          <t>Đang có hiệu lực</t>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J3" s="10" t="inlineStr">
         <is>
-          <t>Được sửa đổi, bổ sung bởi Nghị định số 35/2023/NĐ-CP và Nghị định số 72/2019/NĐ-CP</t>
+          <t>Bị thay thế bởi Luật Quy hoạch đô thị và nông thôn số 47/2024/QH15</t>
         </is>
       </c>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <t>Quy định trình tự, thủ tục lập và phê duyệt Quy hoạch chi tiết và Quy hoạch Tổng mặt bằng công trình</t>
+          <t>Hết hiệu lực từ ngày 01/07/2025</t>
         </is>
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <t>ALL, QUY_HOACH, TV-01, TV-02, QLDA</t>
+          <t>ALL, QUY_HOACH, TV-01, TV-02, BQP, LICHSU</t>
         </is>
       </c>
       <c r="M3" s="15" t="inlineStr"/>
       <c r="N3" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -779,58 +779,58 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>04/2022/TT-BXD</t>
+          <t>44/2015/NĐ-CP</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Quy định về hồ sơ nhiệm vụ và hồ sơ đồ án quy hoạch xây dựng vùng liên huyện, quy hoạch xây dựng vùng huyện, quy hoạch đô thị, quy hoạch xây dựng khu chức năng và quy hoạch nông thôn</t>
+          <t>Quy định chi tiết một số nội dung về quy hoạch xây dựng</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>24/10/2022</t>
+          <t>06/05/2015</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
-        </is>
-      </c>
-      <c r="I4" s="14" t="inlineStr">
+          <t>30/06/2015</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 12/2016/TT-BXD và Thông tư 02/2017/TT-BXD</t>
+          <t>Được sửa đổi, bổ sung bởi Nghị định số 72/2019/NĐ-CP và Nghị định số 35/2023/NĐ-CP</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Quy định thành phần hồ sơ bản vẽ, thuyết minh và quy cách đồ án quy hoạch Tổng mặt bằng tỷ lệ 1/500 gói TV-01</t>
+          <t>Quy định trình tự, thủ tục lập và phê duyệt Quy hoạch chi tiết và Quy hoạch Tổng mặt bằng công trình (Áp dụng VBHN 13/VBHN-BXD)</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>QUY_HOACH, TV-01, HO_SO_QUY_HOACH</t>
+          <t>ALL, QUY_HOACH, TV-01, TV-02, QLDA</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -850,12 +850,12 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>20/2019/TT-BXD</t>
+          <t>04/2022/TT-BXD</t>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>Hướng dẫn xác định, quản lý chi phí quy hoạch xây dựng và quy hoạch đô thị</t>
+          <t>Quy định về hồ sơ nhiệm vụ và hồ sơ đồ án quy hoạch xây dựng vùng liên huyện, quy hoạch xây dựng vùng huyện, quy hoạch đô thị, quy hoạch xây dựng khu chức năng và quy hoạch nông thôn</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -865,38 +865,38 @@
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>31/12/2019</t>
+          <t>24/10/2022</t>
         </is>
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>15/02/2020</t>
-        </is>
-      </c>
-      <c r="I5" s="14" t="inlineStr">
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 01/2013/TT-BXD</t>
+          <t>Thay thế Thông tư 12/2016/TT-BXD và Thông tư 02/2017/TT-BXD</t>
         </is>
       </c>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>Căn cứ lập dự toán chi phí gói thầu TV-01 Tư vấn lập quy hoạch Tổng mặt bằng tỷ lệ 1/500</t>
+          <t>Quy định thành phần hồ sơ bản vẽ, thuyết minh và quy cách đồ án quy hoạch Tổng mặt bằng tỷ lệ 1/500 gói TV-01</t>
         </is>
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
-          <t>QUY_HOACH, CHI_PHI_QUY_HOACH, DU_TOAN, TV-01</t>
+          <t>QUY_HOACH, TV-01, HO_SO_QUY_HOACH</t>
         </is>
       </c>
       <c r="M5" s="15" t="inlineStr"/>
       <c r="N5" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Quy chuẩn Xây dựng</t>
+          <t>Quy hoạch Xây dựng</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>01/2021/TT-BXD</t>
+          <t>20/2019/TT-BXD</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Ban hành Quy chuẩn kỹ thuật quốc gia về Quy hoạch xây dựng (Mã số: QCVN 01:2021/BXD)</t>
+          <t>Hướng dẫn xác định, quản lý chi phí quy hoạch xây dựng và quy hoạch đô thị</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>19/05/2021</t>
+          <t>31/12/2019</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>05/07/2021</t>
-        </is>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
+          <t>15/02/2020</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Thay thế QCVN 01:2019/BXD ban hành kèm Thông tư 22/2019/TT-BXD</t>
+          <t>Thay thế Thông tư 01/2013/TT-BXD</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Quy chuẩn bắt buộc áp dụng cho gói TV-01 về mật độ xây dựng, khoảng lùi công trình, khoảng cách an toàn PCCC, chỉ giới đường đỏ</t>
+          <t>Căn cứ lập dự toán chi phí gói thầu TV-01 Tư vấn lập quy hoạch Tổng mặt bằng tỷ lệ 1/500</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>QCVN, QUY_HOACH, TV-01, TV-02, TV-04, XD-01</t>
+          <t>QUY_HOACH, CHI_PHI_QUY_HOACH, DU_TOAN, TV-01</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr"/>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -972,63 +972,63 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Khảo sát &amp; Đo đạc</t>
+          <t>Quy chuẩn Xây dựng</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>27/2018/QH14</t>
+          <t>01/2021/TT-BXD</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>Luật Đo đạc và bản đồ năm 2018</t>
+          <t>Ban hành Quy chuẩn kỹ thuật quốc gia về Quy hoạch xây dựng (Mã số: QCVN 01:2021/BXD)</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>14/06/2018</t>
+          <t>19/05/2021</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
-        </is>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
+          <t>05/07/2021</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J7" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Thay thế QCVN 01:2019/BXD ban hành kèm Thông tư 22/2019/TT-BXD</t>
         </is>
       </c>
       <c r="K7" s="10" t="inlineStr">
         <is>
-          <t>Căn cứ pháp lý cho công tác đo đạc khảo sát địa hình, trắc địa công trình phục vụ lập quy hoạch TV-01 và khảo sát TV-02</t>
+          <t>Quy chuẩn bắt buộc áp dụng cho gói TV-01 về mật độ xây dựng, khoảng lùi công trình, khoảng cách an toàn PCCC, chỉ giới đường đỏ</t>
         </is>
       </c>
       <c r="L7" s="10" t="inlineStr">
         <is>
-          <t>KHAO_SAT, DO_DAC, TV-01, TV-02, XD-01</t>
+          <t>QCVN, QUY_HOACH, TV-01, TV-02, TV-04, XD-01</t>
         </is>
       </c>
       <c r="M7" s="15" t="inlineStr"/>
       <c r="N7" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -1043,47 +1043,47 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>27/2019/NĐ-CP</t>
+          <t>27/2018/QH14</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Đo đạc và bản đồ</t>
+          <t>Luật Đo đạc và bản đồ năm 2018</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>13/03/2019</t>
+          <t>14/06/2018</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>01/05/2019</t>
-        </is>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
+          <t>01/01/2019</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Được sửa đổi, bổ sung bởi Nghị định 136/2021/NĐ-CP</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Quy định quy chuẩn đo đạc bản đồ địa hình tỷ lệ 1/500 phục vụ lập quy hoạch TMB và thiết kế xây dựng</t>
+          <t>Căn cứ pháp lý cho công tác đo đạc khảo sát địa hình, trắc địa công trình phục vụ lập quy hoạch TV-01 và khảo sát TV-02</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -1094,7 +1094,7 @@
       <c r="M8" s="8" t="inlineStr"/>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -1104,63 +1104,63 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Xây dựng &amp; Quản lý dự án</t>
+          <t>Khảo sát &amp; Đo đạc</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>50/2014/QH13</t>
+          <t>27/2019/NĐ-CP</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>Luật Xây dựng năm 2014</t>
+          <t>Quy định chi tiết một số điều của Luật Đo đạc và bản đồ</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>18/06/2014</t>
+          <t>13/03/2019</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>01/01/2015</t>
+          <t>01/05/2019</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J9" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Luật Xây dựng số 135/2025/QH15</t>
+          <t>Được sửa đổi, bổ sung bởi Nghị định 136/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
-          <t>Dự án đã phê duyệt trước thời điểm luật mới thực hiện theo quy định chuyển tiếp</t>
+          <t>Quy định quy chuẩn đo đạc bản đồ địa hình tỷ lệ 1/500 phục vụ lập quy hoạch TMB và thiết kế xây dựng</t>
         </is>
       </c>
       <c r="L9" s="10" t="inlineStr">
         <is>
-          <t>ALL, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+          <t>KHAO_SAT, DO_DAC, TV-01, TV-02, XD-01</t>
         </is>
       </c>
       <c r="M9" s="15" t="inlineStr"/>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>10/12/2025</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1203,19 +1203,19 @@
           <t>01/07/2026</t>
         </is>
       </c>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Luật Xây dựng 50/2014/QH13 và Luật sửa đổi 62/2020/QH14</t>
+          <t>Thay thế Luật Xây dựng 50/2014/QH13 và Luật 62/2020/QH14</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng toàn diện cho các dự án đầu tư xây dựng mới</t>
+          <t>Luật khung hiện hành chi phối toàn bộ hoạt động đầu tư xây dựng công trình, thẩm định và cấp phép</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -1226,7 +1226,7 @@
       <c r="M10" s="8" t="inlineStr"/>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>62/2020/QH14</t>
+          <t>50/2014/QH13</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>Luật sửa đổi, bổ sung một số điều của Luật Xây dựng</t>
+          <t>Luật Xây dựng năm 2014</t>
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr">
@@ -1261,38 +1261,38 @@
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>17/06/2020</t>
+          <t>18/06/2014</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
+          <t>01/01/2015</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Luật Xây dựng số 135/2025/QH15</t>
+          <t>Bị thay thế bởi Luật Xây dựng số 135/2025/QH15 từ ngày 01/07/2026</t>
         </is>
       </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>Quy định chuyển tiếp thẩm định thiết kế, cấp phép</t>
+          <t>Dự án đã phê duyệt trước 01/07/2026 thực hiện theo quy định chuyển tiếp của Luật 135/2025</t>
         </is>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
-          <t>ALL, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+          <t>ALL, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01, LICHSU</t>
         </is>
       </c>
       <c r="M11" s="15" t="inlineStr"/>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -1307,58 +1307,58 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>15/2021/NĐ-CP</t>
+          <t>62/2020/QH14</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số nội dung về quản lý dự án đầu tư xây dựng</t>
+          <t>Luật sửa đổi, bổ sung một số điều của Luật Xây dựng năm 2020</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>03/03/2021</t>
+          <t>17/06/2020</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>03/03/2021</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
+          <t>01/01/2021</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 175/2024/NĐ-CP và Nghị định 217/2026/NĐ-CP</t>
+          <t>Bị thay thế bởi Luật Xây dựng số 135/2025/QH15 từ ngày 01/07/2026</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng cho các dự án đã trình thẩm định giai đoạn 2021-2024</t>
+          <t>Hết hiệu lực từ 01/07/2026</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>ALL, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+          <t>ALL, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01, LICHSU</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr"/>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>175/2024/NĐ-CP</t>
+          <t>217/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Xây dựng về quản lý hoạt động xây dựng</t>
+          <t>Quy định chi tiết một số điều của Luật Xây dựng về quản lý hoạt động đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F13" s="13" t="inlineStr">
@@ -1393,27 +1393,27 @@
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>30/12/2024</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>15/02/2025</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 217/2026/NĐ-CP</t>
+          <t>Thay thế Nghị định 15/2021/NĐ-CP, Nghị định 175/2024/NĐ-CP và Nghị định 35/2023/NĐ-CP</t>
         </is>
       </c>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng giai đoạn chuyển tiếp 2025</t>
+          <t>Nghị định xương sống hiện hành về thẩm tra, thẩm định thiết kế, dự toán và quản lý dự án xây dựng</t>
         </is>
       </c>
       <c r="L13" s="10" t="inlineStr">
@@ -1424,7 +1424,7 @@
       <c r="M13" s="15" t="inlineStr"/>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>217/2026/NĐ-CP</t>
+          <t>175/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Xây dựng về quản lý hoạt động xây dựng</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 15/2021/NĐ-CP quy định chi tiết một số nội dung về quản lý dự án đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -1459,38 +1459,38 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>30/12/2024</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>Đang có hiệu lực</t>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 15/2021/NĐ-CP và Nghị định 175/2024/NĐ-CP</t>
+          <t>Bị thay thế bởi Nghị định 217/2026/NĐ-CP từ ngày 01/07/2026</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Căn cứ pháp lý then chốt về quản lý dự án đầu tư xây dựng hiện hành</t>
+          <t>Hết hiệu lực từ 01/07/2026</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>ALL, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+          <t>ALL, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01, LICHSU</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr"/>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>35/2023/NĐ-CP</t>
+          <t>15/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của các Nghị định thuộc lĩnh vực quản lý nhà nước của Bộ Xây dựng</t>
+          <t>Quy định chi tiết một số nội dung về quản lý dự án đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
@@ -1525,38 +1525,38 @@
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>20/06/2023</t>
+          <t>03/03/2021</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>20/06/2023</t>
+          <t>03/03/2021</t>
         </is>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
-          <t>Đang có hiệu lực</t>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J15" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bị thay thế bởi Nghị định 175/2024/NĐ-CP và Nghị định 217/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="K15" s="10" t="inlineStr">
         <is>
-          <t>Phân cấp thẩm quyền thẩm định Báo cáo KT-KT và thiết kế dự toán</t>
+          <t>Hết hiệu lực toàn bộ</t>
         </is>
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>ALL, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+          <t>ALL, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01, LICHSU</t>
         </is>
       </c>
       <c r="M15" s="15" t="inlineStr"/>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Nghị quyết</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>66.19/2026/NQ-CP</t>
+          <t>35/2023/NĐ-CP</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Về cắt giảm, phân quyền, đơn giản hóa thủ tục hành chính và cắt giảm, đơn giản hóa điều kiện kinh doanh thuộc phạm vi quản lý của Bộ Nông nghiệp và Môi trường</t>
+          <t>Sửa đổi, bổ sung một số điều của các Nghị định thuộc lĩnh vực quản lý nhà nước của Bộ Xây dựng</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -1591,15 +1591,15 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/06/2023</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>28/02/2027</t>
-        </is>
-      </c>
-      <c r="I16" s="14" t="inlineStr">
+          <t>20/06/2023</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -1611,18 +1611,18 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Cắt giảm, phân quyền thủ tục môi trường và thủ tục hành chính</t>
+          <t>Cắt giảm, đơn giản hóa thủ tục hành chính trong lập quy hoạch và quản lý dự án xây dựng</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
+          <t>ALL, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr"/>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -1665,19 +1665,19 @@
           <t>01/01/2024</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J17" s="10" t="inlineStr">
         <is>
-          <t>Luật Đấu thầu 43/2013/QH13</t>
+          <t>Thay thế Luật Đấu thầu 43/2013/QH13</t>
         </is>
       </c>
       <c r="K17" s="10" t="inlineStr">
         <is>
-          <t>Gói thầu phát hành HSMT từ 01/01/2024 áp dụng Luật 22</t>
+          <t>Luật đấu thầu nền tảng chi phối toàn bộ các gói thầu TV, XD, PTV của dự án</t>
         </is>
       </c>
       <c r="L17" s="10" t="inlineStr">
@@ -1688,7 +1688,7 @@
       <c r="M17" s="15" t="inlineStr"/>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -1731,19 +1731,19 @@
           <t>15/01/2025</t>
         </is>
       </c>
-      <c r="I18" s="14" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Sửa đổi, bổ sung Luật Đấu thầu 22/2023/QH15</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Nâng hạn mức chỉ định thầu và đơn giản hóa thủ tục đầu tư</t>
+          <t>Mở rộng phân cấp thẩm quyền chỉ định thầu, rút ngắn thời gian chuẩn bị E-HSDT và mua sắm công</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -1754,7 +1754,7 @@
       <c r="M18" s="8" t="inlineStr"/>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1774,12 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>90/2025/QH15</t>
+          <t>43/2013/QH13</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>Luật sửa đổi bổ sung Luật Đấu thầu</t>
+          <t>Luật Đấu thầu năm 2013</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
@@ -1789,38 +1789,38 @@
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>25/06/2025</t>
+          <t>26/11/2013</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>01/08/2025</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
+          <t>01/07/2014</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J19" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Luật Đấu thầu số 22/2023/QH15</t>
+          <t>Bị thay thế bởi Luật Đấu thầu 22/2023/QH15</t>
         </is>
       </c>
       <c r="K19" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi bổ sung cơ chế đấu thầu thuốc, vật tư và mua sắm công</t>
+          <t>Hết hiệu lực từ 01/01/2024</t>
         </is>
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, KHLCNT</t>
+          <t>ALL, DAU_THAU, LICHSU</t>
         </is>
       </c>
       <c r="M19" s="15" t="inlineStr"/>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -1835,58 +1835,58 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>43/2013/QH13</t>
+          <t>214/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Luật Đấu thầu năm 2013</t>
+          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Đấu thầu về lựa chọn nhà thầu</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>26/11/2013</t>
+          <t>04/08/2025</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>01/07/2014</t>
+          <t>04/08/2025</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Luật Đấu thầu 22/2023/QH15</t>
+          <t>Thay thế Nghị định 24/2024/NĐ-CP và Nghị định 63/2014/NĐ-CP</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng cho các gói thầu mở trước 2024</t>
+          <t>Nghị định xương sống hiện hành về quy trình chỉ định thầu rút gọn, đấu thầu rộng rãi qua mạng</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>DAU_THAU, LICHSU</t>
+          <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
         </is>
       </c>
       <c r="M20" s="8" t="inlineStr"/>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -1929,30 +1929,30 @@
           <t>27/02/2024</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="14" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J21" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 214/2025/NĐ-CP</t>
+          <t>Bị thay thế bởi Nghị định 214/2025/NĐ-CP từ ngày 04/08/2025</t>
         </is>
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng cho các gói thầu phát hành E-HSMT giai đoạn 2024-2025</t>
+          <t>Áp dụng chuyển tiếp cho các gói thầu phát hành E-HSMT trước 04/08/2025</t>
         </is>
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
+          <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01, LICHSU</t>
         </is>
       </c>
       <c r="M21" s="15" t="inlineStr"/>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -1972,12 +1972,12 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>214/2025/NĐ-CP</t>
+          <t>63/2014/NĐ-CP</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Đấu thầu về lựa chọn nhà thầu</t>
+          <t>Quy định chi tiết thi hành một số điều của Luật Đấu thầu về lựa chọn nhà thầu</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -1987,38 +1987,38 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>15/12/2025</t>
+          <t>26/06/2014</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>01/01/2026</t>
+          <t>15/08/2014</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>Đang có hiệu lực</t>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 24/2024/NĐ-CP</t>
+          <t>Bị thay thế bởi Nghị định 24/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Quy định toàn diện về lựa chọn nhà thầu qua mạng trên Hệ thống e-GP mới</t>
+          <t>Hết hiệu lực từ 27/02/2024</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
+          <t>ALL, DAU_THAU, LICHSU</t>
         </is>
       </c>
       <c r="M22" s="8" t="inlineStr"/>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -2033,58 +2033,58 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>63/2014/NĐ-CP</t>
+          <t>79/2025/TT-BTC</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết thi hành một số điều của Luật Đấu thầu về lựa chọn nhà thầu</t>
+          <t>Hướng dẫn việc cung cấp, đăng tải thông tin về đấu thầu và mẫu hồ sơ đấu thầu trên Hệ thống mạng đấu thầu quốc gia</t>
         </is>
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Tài chính</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>26/06/2014</t>
+          <t>20/07/2025</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>15/08/2014</t>
+          <t>20/07/2025</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 24/2024/NĐ-CP</t>
+          <t>Thay thế Thông tư 06/2024/TT-BKHĐT và Thông tư 22/2024/TT-BKHĐT</t>
         </is>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng cho gói thầu mở trước 27/02/2024</t>
+          <t>Ban hành toàn bộ biểu mẫu E-HSMT xây lắp, tư vấn, phi tư vấn, E-HSYC chỉ định thầu hiện hành</t>
         </is>
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>DAU_THAU, LICHSU</t>
+          <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
         </is>
       </c>
       <c r="M23" s="15" t="inlineStr"/>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Hướng dẫn việc cung cấp, đăng tải thông tin về lựa chọn nhà thầu và mẫu hồ sơ đấu thầu trên Hệ thống mạng đấu thầu quốc gia</t>
+          <t>Hướng dẫn việc cung cấp, đăng tải thông tin về đấu thầu và mẫu hồ sơ đấu thầu trên Hệ thống mạng đấu thầu quốc gia</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -2127,30 +2127,30 @@
           <t>26/04/2024</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="I24" s="14" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 22/2024/TT-BKHĐT và Thông tư 79/2025/TT-BTC</t>
+          <t>Bị thay thế bởi Thông tư 79/2025/TT-BTC</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>Mẫu E-HSMT giai đoạn đầu 2024</t>
+          <t>Hết hiệu lực từ 20/07/2025</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
+          <t>ALL, DAU_THAU, E_HSMT, LICHSU</t>
         </is>
       </c>
       <c r="M24" s="8" t="inlineStr"/>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -2170,53 +2170,53 @@
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>22/2024/TT-BKHĐT</t>
+          <t>80/2025/TT-BTC</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>Hướng dẫn việc cung cấp, đăng tải thông tin về lựa chọn nhà thầu và mẫu hồ sơ đấu thầu trên Hệ thống mạng đấu thầu quốc gia</t>
+          <t>Quy định chi tiết mẫu hồ sơ yêu cầu, báo cáo đánh giá trong lựa chọn nhà thầu mua sắm công</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>Bộ Kế hoạch và Đầu tư</t>
+          <t>Bộ Tài chính</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>15/11/2024</t>
+          <t>22/07/2025</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>22/07/2025</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 79/2025/TT-BTC</t>
+          <t>Thay thế Thông tư 07/2024/TT-BKHĐT và Thông tư 23/2024/TT-BKHĐT</t>
         </is>
       </c>
       <c r="K25" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng giai đoạn chuyển giao 2024-2025</t>
+          <t>Áp dụng lập HSYC và đánh giá hồ sơ đề xuất gói thầu mua sắm hàng hóa, doanh cụ</t>
         </is>
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
+          <t>ALL, DAU_THAU, E_HSMT, TV-06, XD-01</t>
         </is>
       </c>
       <c r="M25" s="15" t="inlineStr"/>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -2226,63 +2226,63 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Đấu thầu qua mạng</t>
+          <t>Chi phí &amp; Định mức</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>79/2025/TT-BTC</t>
+          <t>206/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Hướng dẫn việc cung cấp, đăng tải thông tin về đấu thầu và mẫu hồ sơ đấu thầu trên Hệ thống mạng đấu thầu quốc gia</t>
+          <t>Quy định chi tiết một số điều của Luật Xây dựng về quản lý chi phí đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>Bộ Tài chính</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-      <c r="I26" s="14" t="inlineStr">
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 06/2024/TT-BKHĐT và Thông tư 22/2024/TT-BKHĐT</t>
+          <t>Thay thế Nghị định 10/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>Bộ mẫu E-HSMT chuẩn áp dụng bắt buộc hiện hành</t>
+          <t>Quy định phương pháp lập và quản lý Tổng mức đầu tư, Dự toán xây dựng công trình hiện hành</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
+          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
         </is>
       </c>
       <c r="M26" s="8" t="inlineStr"/>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -2292,63 +2292,63 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Đấu thầu qua mạng</t>
+          <t>Chi phí &amp; Định mức</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>07/2024/TT-BKHĐT</t>
+          <t>10/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết mẫu hồ sơ yêu cầu, báo cáo đánh giá, báo cáo thẩm định, kiểm tra, giám sát hoạt động đấu thầu</t>
+          <t>Về quản lý chi phí đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>Bộ Kế hoạch và Đầu tư</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>09/02/2021</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>15/06/2024</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
+          <t>09/02/2021</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J27" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 23/2024/TT-BKHĐT và Thông tư 80/2025/TT-BTC</t>
+          <t>Bị thay thế bởi Nghị định 206/2026/NĐ-CP từ ngày 01/07/2026</t>
         </is>
       </c>
       <c r="K27" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng giai đoạn đầu 2024</t>
+          <t>Dự án đã phê duyệt dự toán trước 01/07/2026 thực hiện theo điều khoản chuyển tiếp của NĐ 206</t>
         </is>
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
+          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01, LICHSU</t>
         </is>
       </c>
       <c r="M27" s="15" t="inlineStr"/>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Đấu thầu qua mạng</t>
+          <t>Chi phí &amp; Định mức</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2368,53 +2368,53 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>23/2024/TT-BKHĐT</t>
+          <t>38/2026/TT-BXD</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết mẫu hồ sơ yêu cầu, báo cáo đánh giá, báo cáo thẩm định, kiểm tra, báo cáo tình hình thực hiện hoạt động đấu thầu</t>
+          <t>Ban hành hệ thống định mức dự toán xây dựng công trình và định mức chi phí tư vấn đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>Bộ Kế hoạch và Đầu tư</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>18/11/2024</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 80/2025/TT-BTC</t>
+          <t>Thay thế Thông tư 12/2021/TT-BXD và Thông tư 09/2024/TT-BXD</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng giai đoạn cuối 2024</t>
+          <t>Hệ thống định mức xây dựng và tỷ lệ % chi phí quản lý dự án, tư vấn thiết kế, giám sát mới nhất</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
+          <t>ALL, DINH_MUC, DU_TOAN, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-08, TV-09, XD-01</t>
         </is>
       </c>
       <c r="M28" s="8" t="inlineStr"/>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Đấu thầu qua mạng</t>
+          <t>Chi phí &amp; Định mức</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
@@ -2434,53 +2434,53 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>80/2025/TT-BTC</t>
+          <t>12/2021/TT-BXD</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết mẫu hồ sơ yêu cầu, báo cáo đánh giá, báo cáo thẩm định, kiểm tra, báo cáo tình hình thực hiện hoạt động đấu thầu</t>
+          <t>Ban hành định mức xây dựng</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>Bộ Tài chính</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>31/08/2021</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>01/01/2026</t>
+          <t>15/10/2021</t>
         </is>
       </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
-          <t>Đang có hiệu lực</t>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J29" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 07/2024/TT-BKHĐT và Thông tư 23/2024/TT-BKHĐT</t>
+          <t>Bị thay thế bởi Thông tư 38/2026/TT-BXD từ ngày 01/08/2026</t>
         </is>
       </c>
       <c r="K29" s="10" t="inlineStr">
         <is>
-          <t>Bộ mẫu HSYC, Báo cáo đánh giá, Thẩm định chỉ định thầu hiện hành</t>
+          <t>Hết hiệu lực từ 01/08/2026</t>
         </is>
       </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
+          <t>ALL, DINH_MUC, DU_TOAN, LICHSU</t>
         </is>
       </c>
       <c r="M29" s="15" t="inlineStr"/>
       <c r="N29" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Đấu thầu qua mạng</t>
+          <t>Chi phí &amp; Định mức</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2500,53 +2500,53 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>15/2024/TT-BKHĐT</t>
+          <t>09/2024/TT-BXD</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Quy định mẫu hồ sơ đấu thầu lựa chọn nhà đầu tư thực hiện dự án PPP, dự án đầu tư kinh doanh; cung cấp, đăng tải thông tin trên Hệ thống mạng đấu thầu quốc gia</t>
+          <t>Sửa đổi, bổ sung một số định mức xây dựng ban hành tại Thông tư số 12/2021/TT-BXD</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>Bộ Kế hoạch và Đầu tư</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>30/09/2024</t>
+          <t>30/08/2024</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>30/09/2024</t>
-        </is>
-      </c>
-      <c r="I30" s="7" t="inlineStr">
+          <t>15/10/2024</t>
+        </is>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 98/2025/TT-BTC</t>
+          <t>Bị thay thế bởi Thông tư 38/2026/TT-BXD</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng giai đoạn 2024</t>
+          <t>Hết hiệu lực từ 01/08/2026</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>DAU_THAU, DAU_TU_KINH_DOANH, PPP</t>
+          <t>ALL, DINH_MUC, DU_TOAN, LICHSU</t>
         </is>
       </c>
       <c r="M30" s="8" t="inlineStr"/>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Đấu thầu qua mạng</t>
+          <t>Chi phí &amp; Định mức</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
@@ -2566,53 +2566,53 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>98/2025/TT-BTC</t>
+          <t>01/2025/TT-BXD</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>Quy định mẫu hồ sơ đấu thầu lựa chọn nhà đầu tư thực hiện dự án đầu tư theo phương thức đối tác công tư, dự án đầu tư kinh doanh; cung cấp, đăng tải thông tin về đầu tư theo phương thức đối tác công tư, đấu thầu lựa chọn nhà đầu tư trên Hệ thống mạng đấu thầu quốc gia</t>
+          <t>Sửa đổi, bổ sung một số điều của Thông tư số 11/2021/TT-BXD hướng dẫn một số nội dung xác định và quản lý chi phí đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>Bộ Tài chính</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>15/11/2025</t>
+          <t>15/01/2025</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-      <c r="I31" s="14" t="inlineStr">
+          <t>01/03/2025</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J31" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 15/2024/TT-BKHĐT</t>
+          <t>Sửa đổi, bổ sung Thông tư 11/2021/TT-BXD</t>
         </is>
       </c>
       <c r="K31" s="10" t="inlineStr">
         <is>
-          <t>Quy định mẫu đấu thầu dự án PPP và kinh doanh hiện hành</t>
+          <t>Cập nhật phương pháp lập và quản lý chi phí đầu tư xây dựng hiện hành</t>
         </is>
       </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
-          <t>DAU_THAU, DAU_TU_KINH_DOANH, PPP</t>
+          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
         </is>
       </c>
       <c r="M31" s="15" t="inlineStr"/>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -2622,52 +2622,52 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Quản lý Chi phí &amp; Dự toán</t>
+          <t>Chi phí &amp; Định mức</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>10/2021/NĐ-CP</t>
+          <t>11/2021/TT-BXD</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Về quản lý chi phí đầu tư xây dựng</t>
+          <t>Hướng dẫn một số nội dung xác định và quản lý chi phí đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>09/02/2021</t>
+          <t>31/08/2021</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>09/02/2021</t>
+          <t>15/10/2021</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 206/2026/NĐ-CP</t>
+          <t>Được sửa đổi, bổ sung bởi Thông tư 14/2023/TT-BXD và Thông tư 01/2025/TT-BXD</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>Dự toán duyệt trước 2026 tiếp tục áp dụng theo phê duyệt</t>
+          <t>Quy định cơ cấu chi phí xây dựng, chi phí gián tiếp, chi phí chung trong dự toán</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -2678,7 +2678,7 @@
       <c r="M32" s="8" t="inlineStr"/>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -2688,52 +2688,52 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Quản lý Chi phí &amp; Dự toán</t>
+          <t>Chi phí &amp; Định mức</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>206/2026/NĐ-CP</t>
+          <t>14/2023/TT-BXD</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết về quản lý chi phí đầu tư xây dựng</t>
+          <t>Sửa đổi, bổ sung một số điều của Thông tư số 11/2021/TT-BXD hướng dẫn một số nội dung xác định và quản lý chi phí đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/12/2023</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="I33" s="14" t="inlineStr">
+          <t>15/02/2024</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J33" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 10/2021/NĐ-CP</t>
+          <t>Sửa đổi Thông tư 11/2021/TT-BXD</t>
         </is>
       </c>
       <c r="K33" s="10" t="inlineStr">
         <is>
-          <t>Căn cứ pháp lý then chốt về quản lý chi phí và dự toán hiện hành</t>
+          <t>Cập nhật hệ số chi phí chung, chi phí nhà tạm</t>
         </is>
       </c>
       <c r="L33" s="10" t="inlineStr">
@@ -2744,7 +2744,7 @@
       <c r="M33" s="15" t="inlineStr"/>
       <c r="N33" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Quản lý Chi phí &amp; Dự toán</t>
+          <t>Chi phí &amp; Định mức</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>11/2021/TT-BXD</t>
+          <t>13/2021/TT-BXD</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Hướng dẫn một số nội dung xác định và quản lý chi phí đầu tư xây dựng</t>
+          <t>Hướng dẫn phương pháp xác định các chỉ tiêu kinh tế kỹ thuật và đo bóc khối lượng công trình</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -2787,7 +2787,7 @@
           <t>15/10/2021</t>
         </is>
       </c>
-      <c r="I34" s="14" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -2799,18 +2799,18 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>Phương pháp lập đơn giá xây dựng và tổng mức đầu tư</t>
+          <t>Quy chuẩn phương pháp đo bóc khối lượng phục vụ lập dự toán và nghiệm thu công trình</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
+          <t>ALL, DU_TOAN, DO_BOC_KHOI_LUONG, TV-04, TV-05, XD-01</t>
         </is>
       </c>
       <c r="M34" s="8" t="inlineStr"/>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -2820,22 +2820,22 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Quản lý Chi phí &amp; Dự toán</t>
+          <t>Suất vốn đầu tư</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Quyết định</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>12/2021/TT-BXD</t>
+          <t>425/QĐ-BXD</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>Ban hành định mức xây dựng (Định mức dự toán, định mức chi phí tư vấn và QLDA)</t>
+          <t>Công bố Suất vốn đầu tư xây dựng công trình và giá xây dựng tổng hợp bộ phận kết cấu công trình</t>
         </is>
       </c>
       <c r="F35" s="13" t="inlineStr">
@@ -2845,38 +2845,38 @@
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>31/08/2021</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>15/10/2021</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J35" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 38/2026/TT-BXD</t>
+          <t>Thay thế Quyết định 510/QĐ-BXD</t>
         </is>
       </c>
       <c r="K35" s="10" t="inlineStr">
         <is>
-          <t>Bộ định mức gốc tính chi phí tư vấn và xây lắp giai đoạn 2021-2026</t>
+          <t>Suất vốn đầu tư hiện hành phục vụ tính Tổng mức đầu tư BCNCKT (FS/BKTKT gói TV-02, TV-03)</t>
         </is>
       </c>
       <c r="L35" s="10" t="inlineStr">
         <is>
-          <t>ALL, DINH_MUC, DU_TOAN, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-08, TV-09, XD-01</t>
+          <t>SUAT_VON_DAU_TU, TMDT, TV-01, TV-02, TV-03, TV-04</t>
         </is>
       </c>
       <c r="M35" s="15" t="inlineStr"/>
       <c r="N35" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -2886,22 +2886,22 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Quản lý Chi phí &amp; Dự toán</t>
+          <t>Suất vốn đầu tư</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Quyết định</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>13/2021/TT-BXD</t>
+          <t>510/QĐ-BXD</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Hướng dẫn phương pháp xác định các chỉ tiêu kinh tế kỹ thuật và đo bóc khối lượng công trình</t>
+          <t>Công bố Suất vốn đầu tư xây dựng công trình và giá xây dựng tổng hợp bộ phận kết cấu công trình năm 2023</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -2911,38 +2911,38 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>31/08/2021</t>
+          <t>19/05/2024</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>15/10/2021</t>
+          <t>19/05/2024</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>Đang có hiệu lực</t>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bị thay thế bởi Quyết định 425/QĐ-BXD</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>Quy tắc đo bóc khối lượng từ bản vẽ thiết kế BVTC</t>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>DO_BOC_KHOI_LUONG, DU_TOAN, TV-04, TV-05</t>
+          <t>SUAT_VON_DAU_TU, TMDT, LICHSU</t>
         </is>
       </c>
       <c r="M36" s="8" t="inlineStr"/>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Quản lý Chi phí &amp; Dự toán</t>
+          <t>Quốc phòng &amp; Doanh trại</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
@@ -2962,30 +2962,30 @@
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>14/2023/TT-BXD</t>
+          <t>101/2026/TT-BQP</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 11/2021/TT-BXD ngày 31 tháng 8 năm 2021 hướng dẫn một số nội dung xác định và quản lý chi phí đầu tư xây dựng</t>
+          <t>Quy định chi tiết và biện pháp thực hiện một số nội dung Luật Xây dựng thuộc phạm vi quản lý của Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>29/12/2023</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>15/02/2024</t>
-        </is>
-      </c>
-      <c r="I37" s="14" t="inlineStr">
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -2997,18 +2997,18 @@
       </c>
       <c r="K37" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng định mức chi phí tư vấn lập dự án và thẩm tra</t>
+          <t>Áp dụng cho các dự án đầu tư xây dựng công trình trong toàn Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="L37" s="10" t="inlineStr">
         <is>
-          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
+          <t>ALL, BQP, QLDA, XD-01, TOAN_QUAN</t>
         </is>
       </c>
       <c r="M37" s="15" t="inlineStr"/>
       <c r="N37" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Quản lý Chi phí &amp; Dự toán</t>
+          <t>Quốc phòng &amp; Doanh trại</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3028,53 +3028,53 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>01/2025/TT-BXD</t>
+          <t>102/2026/TT-BQP</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 13/2021/TT-BXD, Thông tư số 11/2021/TT-BXD, Thông tư số 14/2023/TT-BXD</t>
+          <t>Quy định và hướng dẫn về lập, thẩm định, quyết định, phân cấp quyết định chủ trương đầu tư, dự án đầu tư trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>15/01/2025</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>01/03/2025</t>
-        </is>
-      </c>
-      <c r="I38" s="14" t="inlineStr">
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Thay thế Thông tư 128/2021/TT-BQP, Thông tư 73/2023/TT-BQP và Thông tư 120/2024/TT-BQP</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>Cập nhật phương pháp xác định chi phí và chỉ tiêu kinh tế kỹ thuật mới</t>
+          <t>Văn bản xương sống về phân cấp, ủy quyền quyết định đầu tư và dự án đầu tư công mới nhất trong BQP</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
+          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M38" s="8" t="inlineStr"/>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Quản lý Chi phí &amp; Dự toán</t>
+          <t>Quốc phòng &amp; Doanh trại</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
@@ -3094,53 +3094,53 @@
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>09/2024/TT-BXD</t>
+          <t>128/2021/TT-BQP</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 12/2021/TT-BXD ngày 31 tháng 8 năm 2021 ban hành định mức xây dựng</t>
+          <t>Quy định phân cấp, ủy quyền quyết định chủ trương đầu tư và dự án đầu tư công trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>30/08/2024</t>
+          <t>06/10/2021</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>15/10/2024</t>
-        </is>
-      </c>
-      <c r="I39" s="7" t="inlineStr">
+          <t>20/11/2021</t>
+        </is>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>Bị tích hợp và thay thế bởi Thông tư 38/2026/TT-BXD</t>
+          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP</t>
         </is>
       </c>
       <c r="K39" s="10" t="inlineStr">
         <is>
-          <t>Cập nhật định mức nhân công, ca máy giai đoạn 2024-2026</t>
+          <t>Áp dụng phân cấp thẩm quyền đầu tư BQP giai đoạn 2021-2026</t>
         </is>
       </c>
       <c r="L39" s="10" t="inlineStr">
         <is>
-          <t>ALL, DINH_MUC, DU_TOAN, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-08, TV-09, XD-01</t>
+          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01, LICHSU</t>
         </is>
       </c>
       <c r="M39" s="15" t="inlineStr"/>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Quản lý Chi phí &amp; Dự toán</t>
+          <t>Quốc phòng &amp; Doanh trại</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -3160,53 +3160,53 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>38/2026/TT-BXD</t>
+          <t>73/2023/TT-BQP</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Ban hành định mức xây dựng</t>
+          <t>Sửa đổi, bổ sung một số điều của Thông tư số 128/2021/TT-BQP ngày 01/10/2021 về quy định phân cấp, ủy quyền quyết định chủ trương đầu tư và dự án đầu tư công trong BQP</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>05/10/2023</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>20/11/2023</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>Đang có hiệu lực</t>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 12/2021/TT-BXD và Thông tư 09/2024/TT-BXD</t>
+          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>Hệ thống định mức dự toán xây dựng hiện hành</t>
+          <t>Cập nhật phân cấp đầu tư BQP giai đoạn 2023-2026</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>ALL, DINH_MUC, DU_TOAN, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-08, TV-09, XD-01</t>
+          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01, LICHSU</t>
         </is>
       </c>
       <c r="M40" s="8" t="inlineStr"/>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -3216,63 +3216,63 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Quản lý Chi phí &amp; Dự toán</t>
+          <t>Quốc phòng &amp; Doanh trại</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Quyết định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>510/QĐ-BXD</t>
+          <t>120/2024/TT-BQP</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>Công bố Suất vốn đầu tư xây dựng công trình và giá chuẩn nhà, công trình xây dựng</t>
+          <t>Sửa đổi, bổ sung một số điều của Thông tư số 128/2021/TT-BQP về phân cấp quản lý và thực hiện dự án đầu tư công trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>19/05/2023</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>19/05/2023</t>
-        </is>
-      </c>
-      <c r="I41" s="7" t="inlineStr">
+          <t>10/02/2025</t>
+        </is>
+      </c>
+      <c r="I41" s="14" t="inlineStr">
         <is>
           <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J41" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Quyết định 425/QĐ-BXD</t>
+          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP</t>
         </is>
       </c>
       <c r="K41" s="10" t="inlineStr">
         <is>
-          <t>Suất vốn đầu tư năm 2022-2023</t>
+          <t>Phân cấp phê duyệt thiết kế, dự toán BQP giai đoạn 2024-2026</t>
         </is>
       </c>
       <c r="L41" s="10" t="inlineStr">
         <is>
-          <t>SUAT_VON_DAU_TU, TMDT, TV-01, TV-02, TV-03, TV-04</t>
+          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01, LICHSU</t>
         </is>
       </c>
       <c r="M41" s="15" t="inlineStr"/>
       <c r="N41" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -3282,63 +3282,63 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Quản lý Chi phí &amp; Dự toán</t>
+          <t>Quốc phòng &amp; Doanh trại</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Quyết định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>425/QĐ-BXD</t>
+          <t>174/2021/TT-BQP</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Công bố suất vốn đầu tư xây dựng và giá xây dựng tổng hợp bộ phận kết cấu công trình năm 2025</t>
+          <t>Quy định về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>25/04/2025</t>
+          <t>27/12/2021</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>25/04/2025</t>
+          <t>12/02/2022</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Quyết định 510/QĐ-BXD</t>
+          <t>Được sửa đổi, bổ sung bởi Thông tư 24/2025/TT-BQP</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>Suất vốn đầu tư tính Tổng mức đầu tư và khái toán</t>
+          <t>Quy chuẩn nghiệm thu và quản lý chất lượng công trình quân sự</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>SUAT_VON_DAU_TU, TMDT, TV-01, TV-02, TV-03, TV-04</t>
+          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M42" s="8" t="inlineStr"/>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -3348,52 +3348,52 @@
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Chất lượng &amp; Nghiệm thu</t>
+          <t>Quốc phòng &amp; Doanh trại</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>06/2021/NĐ-CP</t>
+          <t>24/2025/TT-BQP</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng</t>
+          <t>Sửa đổi, bổ sung một số điều của Thông tư số 174/2021/TT-BQP về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F43" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>26/01/2021</t>
+          <t>06/05/2025</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>26/01/2021</t>
-        </is>
-      </c>
-      <c r="I43" s="14" t="inlineStr">
+          <t>20/06/2025</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J43" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Sửa đổi, bổ sung Thông tư 174/2021/TT-BQP về quản lý chất lượng công trình BQP</t>
         </is>
       </c>
       <c r="K43" s="10" t="inlineStr">
         <is>
-          <t>Quy định nền tảng về quản lý chất lượng và nghiệm thu công trình</t>
+          <t>Quy chuẩn kiểm tra công tác nghiệm thu công trình quân sự đặc thù hiện hành</t>
         </is>
       </c>
       <c r="L43" s="10" t="inlineStr">
@@ -3404,7 +3404,7 @@
       <c r="M43" s="15" t="inlineStr"/>
       <c r="N43" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -3414,63 +3414,63 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Chất lượng &amp; Nghiệm thu</t>
+          <t>Quốc phòng &amp; Doanh trại</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>207/2026/NĐ-CP</t>
+          <t>36/2023/TT-BQP</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Xây dựng về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng</t>
+          <t>Ban hành Điều lệ Doanh trại Quân đội nhân dân Việt Nam</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>14/04/2023</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="I44" s="14" t="inlineStr">
+          <t>30/05/2023</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>Cập nhật và hoàn thiện Nghị định 06/2021/NĐ-CP theo Luật Xây dựng mới</t>
+          <t>Thay thế Điều lệ Doanh trại QĐNDVN năm 2002</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>Quy chuẩn quản lý chất lượng công trình xây dựng hiện hành</t>
+          <t>Điều lệ xương sống về quy hoạch tổng mặt bằng, bảo dưỡng, quản lý và sử dụng doanh trại</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>ALL, CHAT_LUONG, NGHIEM_THU, XD-01, TV-08, TV-07</t>
+          <t>BQP, DOANH_TRAI, TV-01, TV-02, TV-04, XD-01</t>
         </is>
       </c>
       <c r="M44" s="8" t="inlineStr"/>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Chất lượng &amp; Nghiệm thu</t>
+          <t>Quốc phòng &amp; Doanh trại</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
@@ -3490,53 +3490,53 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>10/2021/TT-BXD</t>
+          <t>150/2018/TT-BQP</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr">
         <is>
-          <t>Hướng dẫn một số điều của Nghị định số 06/2021/NĐ-CP và Nghị định số 44/2016/NĐ-CP</t>
+          <t>Quy định về tiêu chuẩn, định mức sử dụng máy móc, thiết bị văn phòng phổ biến thuộc phạm vi quản lý của Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F45" s="13" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
-          <t>25/08/2021</t>
+          <t>11/10/2018</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>15/10/2021</t>
-        </is>
-      </c>
-      <c r="I45" s="14" t="inlineStr">
+          <t>26/11/2018</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J45" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Thay thế Quyết định 162/2002/QĐ-BQP</t>
         </is>
       </c>
       <c r="K45" s="10" t="inlineStr">
         <is>
-          <t>Mẫu nhật ký thi công, biên bản nghiệm thu giai đoạn và hoàn thành</t>
+          <t>Tiêu chuẩn định mức máy móc, thiết bị làm việc của cán bộ sĩ quan BQP (gói Doanh cụ XD-01)</t>
         </is>
       </c>
       <c r="L45" s="10" t="inlineStr">
         <is>
-          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
+          <t>BQP, DOANH_TRAI, TV-01, TV-02, TV-04, XD-01</t>
         </is>
       </c>
       <c r="M45" s="15" t="inlineStr"/>
       <c r="N45" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Chất lượng &amp; Nghiệm thu</t>
+          <t>Quốc phòng &amp; Doanh trại</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -3556,53 +3556,53 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>32/2026/TT-BXD</t>
+          <t>94/2024/TT-BQP</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Nghị định số 207/2026/NĐ-CP quy định chi tiết một số điều của Luật Xây dựng về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng</t>
+          <t>Quy định chi tiết một số điều của Luật Nhà ở áp dụng trong Bộ Quốc phòng (Mẫu giấy tờ nhà ở công vụ và dự án nhà ở LLVT)</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>11/11/2024</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
-        </is>
-      </c>
-      <c r="I46" s="14" t="inlineStr">
+          <t>26/12/2024</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>Hướng dẫn Nghị định 207/2026/NĐ-CP</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>Biểu mẫu quản lý chất lượng và kiểm tra công tác nghiệm thu mới nhất</t>
+          <t>Áp dụng cho các dự án đầu tư xây dựng nhà ở cho lực lượng vũ trang thuộc BQP</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>ALL, CHAT_LUONG, NGHIEM_THU, XD-01, TV-08</t>
+          <t>BQP, DOANH_TRAI, TV-01, TV-02, TV-04, XD-01</t>
         </is>
       </c>
       <c r="M46" s="8" t="inlineStr"/>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -3612,63 +3612,63 @@
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>PCCC &amp; Tiêu chuẩn Kỹ thuật</t>
+          <t>Quốc phòng &amp; Doanh trại</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Quy chuẩn</t>
+          <t>Quyết định</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>QCVN 06:2022/BXD &amp; Sửa đổi 1:2023</t>
+          <t>35/QĐ-TTg</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>Quy chuẩn kỹ thuật quốc gia về An toàn cháy cho nhà và công trình</t>
+          <t>Ban hành Danh mục bí mật Nhà nước trong lĩnh vực Quốc phòng</t>
         </is>
       </c>
       <c r="F47" s="13" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Thủ tướng Chính phủ</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
-          <t>16/10/2023</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>01/12/2023</t>
-        </is>
-      </c>
-      <c r="I47" s="14" t="inlineStr">
+          <t>11/03/2025</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>QCVN 06:2021/BXD</t>
+          <t>Quyết định số 12/QĐ-TTg</t>
         </is>
       </c>
       <c r="K47" s="10" t="inlineStr">
         <is>
-          <t>Hồ sơ thiết kế BVTC phải tuân thủ đúng yêu cầu ngăn cháy, thoát nạn</t>
+          <t>Quy định bảo mật hồ sơ, tài liệu thiết kế công trình quân sự</t>
         </is>
       </c>
       <c r="L47" s="10" t="inlineStr">
         <is>
-          <t>PCCC, THIET_KE, TV-04, TV-05, XD-01</t>
+          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M47" s="15" t="inlineStr"/>
       <c r="N47" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>PCCC &amp; Tiêu chuẩn Kỹ thuật</t>
+          <t>Chất lượng &amp; Nghiệm thu</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -3688,12 +3688,12 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>136/2020/NĐ-CP</t>
+          <t>06/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Phòng cháy và chữa cháy</t>
+          <t>Quy định chi tiết một số nội dung về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
@@ -3703,38 +3703,38 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>24/11/2020</t>
+          <t>26/01/2021</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>10/01/2021</t>
+          <t>26/01/2021</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 105/2025/NĐ-CP</t>
+          <t>Thay thế Nghị định 46/2015/NĐ-CP</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng giai đoạn 2020-2025</t>
+          <t>Xương sống về quản lý chất lượng thi công, nhật ký công trình và biên bản nghiệm thu hoàn thành</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>PCCC, TV-02, TV-03, TV-04, TV-05, XD-01</t>
+          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M48" s="8" t="inlineStr"/>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -3744,63 +3744,63 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>PCCC &amp; Tiêu chuẩn Kỹ thuật</t>
+          <t>Chất lượng &amp; Nghiệm thu</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>105/2025/NĐ-CP</t>
+          <t>10/2021/TT-BXD</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Phòng cháy, chữa cháy và cứu nạn, cứu hộ</t>
+          <t>Hướng dẫn một số điều và biện pháp thi hành Nghị định số 06/2021/NĐ-CP và Nghị định số 15/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="F49" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>25/08/2021</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
-        </is>
-      </c>
-      <c r="I49" s="14" t="inlineStr">
+          <t>15/10/2021</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J49" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 136/2020/NĐ-CP và Nghị định 50/2024/NĐ-CP</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K49" s="10" t="inlineStr">
         <is>
-          <t>Quy định thẩm duyệt thiết kế và nghiệm thu PCCC hiện hành</t>
+          <t>Quy chuẩn đánh giá an toàn công trình, kiểm định và lập danh mục hồ sơ hoàn thành công trình</t>
         </is>
       </c>
       <c r="L49" s="10" t="inlineStr">
         <is>
-          <t>ALL, PCCC, THIET_KE, TV-04, TV-05, XD-01</t>
+          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M49" s="15" t="inlineStr"/>
       <c r="N49" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>PCCC &amp; Tiêu chuẩn Kỹ thuật</t>
+          <t>Hợp đồng Xây dựng</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>50/2024/NĐ-CP</t>
+          <t>37/2015/NĐ-CP</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 136/2020/NĐ-CP và Nghị định số 83/2017/NĐ-CP về PCCC và cứu nạn, cứu hộ</t>
+          <t>Quy định chi tiết về hợp đồng xây dựng</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -3835,38 +3835,38 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>10/05/2024</t>
+          <t>22/04/2015</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>15/05/2024</t>
+          <t>15/06/2015</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 105/2025/NĐ-CP</t>
+          <t>Được sửa đổi, bổ sung bởi Nghị định 50/2021/NĐ-CP và Nghị định 35/2023/NĐ-CP</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>Phân cấp thẩm duyệt PCCC giai đoạn 2024-2025</t>
+          <t>Quy định tạm ứng, thanh toán, điều chỉnh giá và thanh lý hợp đồng xây dựng</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>PCCC, TV-02, TV-03, TV-04, TV-05, XD-01</t>
+          <t>ALL, HOP_DONG, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
         </is>
       </c>
       <c r="M50" s="8" t="inlineStr"/>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>Hợp đồng xây dựng</t>
+          <t>Hợp đồng Xây dựng</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>37/2015/NĐ-CP &amp; 50/2021/NĐ-CP</t>
+          <t>50/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết về hợp đồng xây dựng và sửa đổi, bổ sung Nghị định 37/2015/NĐ-CP</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 37/2015/NĐ-CP quy định chi tiết về hợp đồng xây dựng</t>
         </is>
       </c>
       <c r="F51" s="13" t="inlineStr">
@@ -3911,28 +3911,28 @@
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J51" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 210/2026/NĐ-CP</t>
+          <t>Sửa đổi Nghị định 37/2015/NĐ-CP</t>
         </is>
       </c>
       <c r="K51" s="10" t="inlineStr">
         <is>
-          <t>Hợp đồng ký trước 2026 thực hiện theo thỏa thuận đã ký</t>
+          <t>Quy định bảo đảm thực hiện hợp đồng và điều chỉnh giá hợp đồng trọn gói, đơn giá</t>
         </is>
       </c>
       <c r="L51" s="10" t="inlineStr">
         <is>
-          <t>HOP_DONG, XD-01, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01</t>
+          <t>ALL, HOP_DONG, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
         </is>
       </c>
       <c r="M51" s="15" t="inlineStr"/>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -3942,63 +3942,63 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Hợp đồng xây dựng</t>
+          <t>Hợp đồng Xây dựng</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>210/2026/NĐ-CP</t>
+          <t>02/2023/TT-BXD</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết và hướng dẫn thi hành một số điều của Luật Xây dựng về hợp đồng xây dựng</t>
+          <t>Hướng dẫn một số nội dung về hợp đồng xây dựng</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/03/2023</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="I52" s="14" t="inlineStr">
+          <t>20/04/2023</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 37/2015/NĐ-CP và Nghị định 50/2021/NĐ-CP</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>Quy định tạm ứng, bảo lãnh thực hiện hợp đồng và thanh quyết toán hiện hành</t>
+          <t>Ban hành mẫu hợp đồng tư vấn thiết kế, tư vấn giám sát và hợp đồng thi công xây dựng</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>ALL, HOP_DONG, XD-01, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01</t>
+          <t>ALL, HOP_DONG, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
         </is>
       </c>
       <c r="M52" s="8" t="inlineStr"/>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -4008,63 +4008,63 @@
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>Hợp đồng xây dựng</t>
+          <t>Tiêu chuẩn Kỹ thuật</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Tiêu chuẩn</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>02/2023/TT-BXD</t>
+          <t>TCVN 9393:2012</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr">
         <is>
-          <t>Hướng dẫn một số nội dung về hợp đồng xây dựng (Mẫu hợp đồng thi công và tư vấn)</t>
+          <t>Cọc - Phương pháp thử nghiệm hiện trường bằng tải trọng tĩnh ép dọc trục</t>
         </is>
       </c>
       <c r="F53" s="13" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Bộ Khoa học và Công nghệ</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
         <is>
-          <t>03/03/2023</t>
+          <t>28/12/2012</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>20/04/2023</t>
-        </is>
-      </c>
-      <c r="I53" s="14" t="inlineStr">
+          <t>28/12/2012</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J53" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 09/2016/TT-BXD và Thông tư 08/2016/TT-BXD</t>
+          <t>Thay thế TCXDVN 269:2002</t>
         </is>
       </c>
       <c r="K53" s="10" t="inlineStr">
         <is>
-          <t>Mẫu hợp đồng áp dụng bắt buộc cho vốn nhà nước</t>
+          <t>Tiêu chuẩn kỹ thuật bắt buộc áp dụng cho gói thầu TV-07 Thí nghiệm nén tĩnh cọc</t>
         </is>
       </c>
       <c r="L53" s="10" t="inlineStr">
         <is>
-          <t>HOP_DONG, XD-01, TV-04, TV-08</t>
+          <t>THI_NGHIEM_COC, TV-07, XD-01</t>
         </is>
       </c>
       <c r="M53" s="15" t="inlineStr"/>
       <c r="N53" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>TCVN 9393:2012</t>
+          <t>TCVN 9363:2012</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Cọc - Phương pháp thử nghiệm hiện trường bằng tải trọng tĩnh ép dọc trục</t>
+          <t>Khảo sát địa chất công trình cho nhà cao tầng</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -4107,7 +4107,7 @@
           <t>28/12/2012</t>
         </is>
       </c>
-      <c r="I54" s="14" t="inlineStr">
+      <c r="I54" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -4119,18 +4119,18 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>Căn cứ kỹ thuật duy nhất cho gói thầu Thí nghiệm nén tĩnh cọc TV-07</t>
+          <t>Tiêu chuẩn kỹ thuật cho công tác khoan khảo sát địa chất gói TV-02</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>TV-07, THI_NGHIEM_COC, KIEM_DINH</t>
+          <t>KHAO_SAT, TV-02</t>
         </is>
       </c>
       <c r="M54" s="8" t="inlineStr"/>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -4140,40 +4140,40 @@
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>Bảo hiểm công trình</t>
+          <t>Tiêu chuẩn Kỹ thuật</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Tiêu chuẩn</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>08/2022/QH15</t>
+          <t>TCVN 9401:2012</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>Luật Kinh doanh bảo hiểm năm 2022</t>
+          <t>Kỹ thuật đo và xử lý số liệu GPS trong trắc địa công trình</t>
         </is>
       </c>
       <c r="F55" s="13" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Bộ Khoa học và Công nghệ</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>16/06/2022</t>
+          <t>28/12/2012</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
-        </is>
-      </c>
-      <c r="I55" s="14" t="inlineStr">
+          <t>28/12/2012</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -4185,18 +4185,18 @@
       </c>
       <c r="K55" s="10" t="inlineStr">
         <is>
-          <t>Căn cứ pháp lý gói thầu Bảo hiểm công trình PTV-01</t>
+          <t>Tiêu chuẩn kỹ thuật cho công tác đo đạc địa hình, định vị công trình gói TV-01</t>
         </is>
       </c>
       <c r="L55" s="10" t="inlineStr">
         <is>
-          <t>PTV-01, BAO_HIEM</t>
+          <t>DO_DAC, TV-01</t>
         </is>
       </c>
       <c r="M55" s="15" t="inlineStr"/>
       <c r="N55" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -4206,63 +4206,63 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Bảo hiểm công trình</t>
+          <t>Bảo hiểm Xây dựng</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>67/2023/NĐ-CP</t>
+          <t>08/2022/QH15</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Quy định về bảo hiểm bắt buộc trong hoạt động đầu tư xây dựng, bảo hiểm cháy nổ bắt buộc</t>
+          <t>Luật Kinh doanh bảo hiểm năm 2022</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>06/09/2023</t>
+          <t>16/06/2022</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>06/09/2023</t>
-        </is>
-      </c>
-      <c r="I56" s="14" t="inlineStr">
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 119/2015/NĐ-CP và Nghị định 20/2020/NĐ-CP</t>
+          <t>Thay thế Luật Kinh doanh bảo hiểm 2000</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>Biểu phí bảo hiểm công trình xây dựng áp dụng cho gói PTV-01</t>
+          <t>Luật nền tảng điều chỉnh hoạt động bảo hiểm công trình xây dựng (gói PTV-01)</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>PTV-01, BAO_HIEM, XD-01</t>
+          <t>BAO_HIEM, PTV-01, XD-01</t>
         </is>
       </c>
       <c r="M56" s="8" t="inlineStr"/>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>Bảo hiểm công trình</t>
+          <t>Bảo hiểm Xây dựng</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>220/2026/NĐ-CP</t>
+          <t>67/2023/NĐ-CP</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 67/2023/NĐ-CP quy định về bảo hiểm bắt buộc trách nhiệm dân sự của chủ xe cơ giới, bảo hiểm cháy, nổ bắt buộc, bảo hiểm bắt buộc trong hoạt động đầu tư xây dựng</t>
+          <t>Quy định về bảo hiểm bắt buộc trách nhiệm dân sự của chủ xe cơ giới, bảo hiểm cháy, nổ bắt buộc, bảo hiểm bắt buộc trong hoạt động đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F57" s="13" t="inlineStr">
@@ -4297,38 +4297,38 @@
       </c>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>06/09/2023</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
-        </is>
-      </c>
-      <c r="I57" s="14" t="inlineStr">
+          <t>06/09/2023</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J57" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Thay thế Nghị định 119/2015/NĐ-CP</t>
         </is>
       </c>
       <c r="K57" s="10" t="inlineStr">
         <is>
-          <t>Cập nhật mức khấu trừ và biểu phí bảo hiểm công trình mới nhất</t>
+          <t>Nghị định chi phối biểu phí và điều kiện bảo hiểm công trình trong thời gian thi công (gói PTV-01)</t>
         </is>
       </c>
       <c r="L57" s="10" t="inlineStr">
         <is>
-          <t>ALL, PTV-01, BAO_HIEM, XD-01</t>
+          <t>BAO_HIEM, PTV-01, XD-01</t>
         </is>
       </c>
       <c r="M57" s="15" t="inlineStr"/>
       <c r="N57" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -4338,63 +4338,63 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Bảo hiểm công trình</t>
+          <t>Kiểm toán Độc lập</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>119/2015/NĐ-CP</t>
+          <t>67/2011/QH12</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Quy định bảo hiểm bắt buộc trong hoạt động đầu tư xây dựng</t>
+          <t>Luật Kiểm toán độc lập năm 2011</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>13/11/2015</t>
+          <t>29/03/2011</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>10/02/2016</t>
+          <t>01/01/2012</t>
         </is>
       </c>
       <c r="I58" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 67/2023/NĐ-CP</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng cho hợp đồng bảo hiểm ký trước 06/09/2023</t>
+          <t>Căn cứ pháp lý then chốt cho gói TV-09 Kiểm toán độc lập quyết toán vốn đầu tư hoàn thành</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>PTV-01, LICHSU</t>
+          <t>KIEM_TOAN, TV-09</t>
         </is>
       </c>
       <c r="M58" s="8" t="inlineStr"/>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -4404,40 +4404,40 @@
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>Kiểm toán độc lập</t>
+          <t>Kiểm toán Độc lập</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>67/2011/QH12</t>
+          <t>67/2015/TT-BTC</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr">
         <is>
-          <t>Luật Kiểm toán độc lập</t>
+          <t>Ban hành Chuẩn mực kiểm toán Việt Nam số 1000 - Kiểm toán báo cáo quyết toán dự án hoàn thành (VSA 1000)</t>
         </is>
       </c>
       <c r="F59" s="13" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Bộ Tài chính</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
-          <t>29/03/2011</t>
+          <t>08/05/2015</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>01/01/2012</t>
-        </is>
-      </c>
-      <c r="I59" s="14" t="inlineStr">
+          <t>01/01/2016</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
@@ -4449,18 +4449,18 @@
       </c>
       <c r="K59" s="10" t="inlineStr">
         <is>
-          <t>Căn cứ thực hiện gói thầu Kiểm toán độc lập TV-09</t>
+          <t>Quy chuẩn phương pháp kiểm toán báo cáo quyết toán dự án hoàn thành gói TV-09</t>
         </is>
       </c>
       <c r="L59" s="10" t="inlineStr">
         <is>
-          <t>TV-09, KIEM_TOAN</t>
+          <t>KIEM_TOAN, TV-09</t>
         </is>
       </c>
       <c r="M59" s="15" t="inlineStr"/>
       <c r="N59" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -4470,63 +4470,63 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Kiểm toán độc lập</t>
+          <t>Đầu tư công</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>67/2015/TT-BTC</t>
+          <t>58/2024/QH15</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Chuẩn mực kiểm toán Việt Nam số 1000 (VSA 1000) - Kiểm toán báo cáo quyết toán dự án hoàn thành</t>
+          <t>Luật Đầu tư công năm 2024</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>Bộ Tài chính</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>08/05/2015</t>
+          <t>29/11/2024</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
-        </is>
-      </c>
-      <c r="I60" s="14" t="inlineStr">
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="I60" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Thay thế Luật Đầu tư công 39/2019/QH14</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>Chuẩn mực kiểm toán áp dụng cho gói TV-09</t>
+          <t>Quy định thẩm quyền quyết định chủ trương đầu tư, phân cấp quản lý dự án sử dụng vốn ngân sách nhà nước</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>TV-09, KIEM_TOAN</t>
+          <t>ALL, DAU_TU_CONG, CHU_TRUONG, TV-01, TV-02, TV-03, TV-09</t>
         </is>
       </c>
       <c r="M60" s="8" t="inlineStr"/>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>Quyết toán vốn dự án</t>
+          <t>Đầu tư công</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>58/2024/QH15</t>
+          <t>39/2019/QH14</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
         <is>
-          <t>Luật Đầu tư công năm 2024 (Đẩy mạnh phân cấp, phân quyền, tách bồi thường GPMB)</t>
+          <t>Luật Đầu tư công năm 2019</t>
         </is>
       </c>
       <c r="F61" s="13" t="inlineStr">
@@ -4561,38 +4561,38 @@
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
-          <t>29/11/2024</t>
+          <t>13/06/2019</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="I61" s="14" t="inlineStr">
         <is>
-          <t>Đang có hiệu lực</t>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J61" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Luật Đầu tư công 39/2019/QH14</t>
+          <t>Bị thay thế bởi Luật Đầu tư công 58/2024/QH15</t>
         </is>
       </c>
       <c r="K61" s="10" t="inlineStr">
         <is>
-          <t>Quy định trình tự phê duyệt chủ trương, kế hoạch vốn và quyết toán</t>
+          <t>Hết hiệu lực từ 01/01/2025</t>
         </is>
       </c>
       <c r="L61" s="10" t="inlineStr">
         <is>
-          <t>ALL, DAU_TU_CONG, CHU_TRUONG, TV-01, TV-02, TV-03, TV-09</t>
+          <t>ALL, DAU_TU_CONG, LICHSU</t>
         </is>
       </c>
       <c r="M61" s="15" t="inlineStr"/>
       <c r="N61" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -4602,63 +4602,63 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Quyết toán vốn dự án</t>
+          <t>Đầu tư công</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>39/2019/QH14</t>
+          <t>40/2020/NĐ-CP</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Luật Đầu tư công năm 2019</t>
+          <t>Quy định chi tiết thi hành một số điều của Luật Đầu tư công</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>13/06/2019</t>
+          <t>06/04/2020</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>06/04/2020</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Luật Đầu tư công 58/2024/QH15</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng cho dự án đã duyệt chủ trương trước 2025</t>
+          <t>Quy định trình tự, thủ tục lập và giao kế hoạch đầu tư công trung hạn và hàng năm</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>ALL, DAU_TU_CONG, CHU_TRUONG, TV-01, TV-02, TV-03, TV-09</t>
+          <t>ALL, DAU_TU_CONG, TV-01, TV-02, TV-03</t>
         </is>
       </c>
       <c r="M62" s="8" t="inlineStr"/>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>Quyết toán vốn dự án</t>
+          <t>Quyết toán vốn</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
@@ -4703,17 +4703,17 @@
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J63" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 77/2015/NĐ-CP và Nghị định 120/2018/NĐ-CP về quyết toán vốn ĐTC</t>
+          <t>Thay thế Nghị định 11/2020/NĐ-CP và Thông tư 10/2020/TT-BTC</t>
         </is>
       </c>
       <c r="K63" s="10" t="inlineStr">
         <is>
-          <t>Hồ sơ thanh toán, quyết toán vốn đầu tư công giai đoạn 2022-2025</t>
+          <t>Nghị định xương sống về thẩm tra, phê duyệt quyết toán vốn đầu tư công dự án hoàn thành</t>
         </is>
       </c>
       <c r="L63" s="10" t="inlineStr">
@@ -4724,7 +4724,7 @@
       <c r="M63" s="15" t="inlineStr"/>
       <c r="N63" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Quyết toán vốn dự án</t>
+          <t>Quyết toán vốn</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>24/2024/TT-BTC</t>
+          <t>96/2021/TT-BTC</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Hướng dẫn Chế độ kế toán Hành chính, sự nghiệp (Hạch toán tài sản và vốn dự án)</t>
+          <t>Quy định về hệ thống mẫu biểu hồ sơ quyết toán vốn đầu tư công dự án hoàn thành</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
@@ -4759,27 +4759,27 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>17/04/2024</t>
+          <t>11/11/2021</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
-        </is>
-      </c>
-      <c r="I64" s="14" t="inlineStr">
+          <t>01/01/2022</t>
+        </is>
+      </c>
+      <c r="I64" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 107/2017/TT-BTC</t>
+          <t>Được sửa đổi, bổ sung bởi Thông tư 24/2024/TT-BTC</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>Hạch toán sổ sách tài sản và vốn đầu tư hoàn thành hiện hành</t>
+          <t>Ban hành toàn bộ mẫu biểu Báo cáo quyết toán A-B, Báo cáo quyết toán hoàn thành</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
@@ -4790,7 +4790,7 @@
       <c r="M64" s="8" t="inlineStr"/>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>Quốc phòng &amp; Doanh trại</t>
+          <t>Quyết toán vốn</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
@@ -4810,53 +4810,53 @@
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>150/2018/TT-BQP</t>
+          <t>24/2024/TT-BTC</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>Quy định về tiêu chuẩn, định mức sử dụng máy móc, thiết bị văn phòng phổ biến thuộc phạm vi quản lý của Bộ Quốc phòng</t>
+          <t>Sửa đổi, bổ sung một số điều của Thông tư số 96/2021/TT-BTC quy định về hệ thống mẫu biểu hồ sơ quyết toán vốn đầu tư công dự án hoàn thành</t>
         </is>
       </c>
       <c r="F65" s="13" t="inlineStr">
         <is>
-          <t>Bộ Quốc phòng</t>
+          <t>Bộ Tài chính</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>11/10/2018</t>
+          <t>19/04/2024</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>26/11/2018</t>
-        </is>
-      </c>
-      <c r="I65" s="14" t="inlineStr">
+          <t>05/06/2024</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J65" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Quyết định 162/2002/QĐ-BQP</t>
+          <t>Sửa đổi Thông tư 96/2021/TT-BTC</t>
         </is>
       </c>
       <c r="K65" s="10" t="inlineStr">
         <is>
-          <t>Tiêu chuẩn định mức máy móc, thiết bị làm việc của cán bộ sĩ quan BQP</t>
+          <t>Cập nhật quy trình kiểm toán độc lập và thẩm tra quyết toán vốn đầu tư công hiện hành</t>
         </is>
       </c>
       <c r="L65" s="10" t="inlineStr">
         <is>
-          <t>BQP, DOANH_TRAI, TV-01, TV-02, TV-04, XD-01</t>
+          <t>ALL, QUYET_TOAN, TAI_CHINH, TV-09, XD-01</t>
         </is>
       </c>
       <c r="M65" s="15" t="inlineStr"/>
       <c r="N65" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -4866,63 +4866,63 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Quốc phòng &amp; Doanh trại</t>
+          <t>Phòng cháy chữa cháy</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>128/2021/TT-BQP</t>
+          <t>136/2020/NĐ-CP</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Quy định phân cấp, ủy quyền quyết định chủ trương đầu tư và dự án đầu tư công trong Bộ Quốc phòng</t>
+          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Phòng cháy và chữa cháy và Luật sửa đổi, bổ sung một số điều của Luật Phòng cháy và chữa cháy</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>Bộ Quốc phòng</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>06/10/2021</t>
+          <t>24/11/2020</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>20/11/2021</t>
+          <t>10/01/2021</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP</t>
+          <t>Được sửa đổi, bổ sung bởi Nghị định 50/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng phân cấp thẩm quyền đầu tư BQP giai đoạn 2021-2026</t>
+          <t>Quy định danh mục công trình phải thẩm duyệt thiết kế PCCC và nghiệm thu PCCC trước khi đưa vào sử dụng</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+          <t>PCCC, TV-02, TV-03, TV-04, TV-05, XD-01</t>
         </is>
       </c>
       <c r="M66" s="8" t="inlineStr"/>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -4932,63 +4932,63 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Quốc phòng &amp; Doanh trại</t>
+          <t>Phòng cháy chữa cháy</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>174/2021/TT-BQP</t>
+          <t>50/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>Quy định về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng trong Bộ Quốc phòng</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 136/2020/NĐ-CP và Nghị định số 83/2017/NĐ-CP</t>
         </is>
       </c>
       <c r="F67" s="13" t="inlineStr">
         <is>
-          <t>Bộ Quốc phòng</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
         <is>
-          <t>27/12/2021</t>
+          <t>10/05/2024</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>12/02/2022</t>
-        </is>
-      </c>
-      <c r="I67" s="14" t="inlineStr">
+          <t>15/05/2024</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J67" s="10" t="inlineStr">
         <is>
-          <t>Được sửa đổi, bổ sung bởi Thông tư 24/2025/TT-BQP</t>
+          <t>Sửa đổi Nghị định 136/2020/NĐ-CP</t>
         </is>
       </c>
       <c r="K67" s="10" t="inlineStr">
         <is>
-          <t>Quy chuẩn nghiệm thu và quản lý chất lượng công trình quân sự</t>
+          <t>Phân cấp thẩm quyền thẩm duyệt PCCC và cắt giảm danh mục công trình phải thẩm duyệt</t>
         </is>
       </c>
       <c r="L67" s="10" t="inlineStr">
         <is>
-          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
+          <t>PCCC, TV-02, TV-03, TV-04, TV-05, XD-01</t>
         </is>
       </c>
       <c r="M67" s="15" t="inlineStr"/>
       <c r="N67" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Quốc phòng &amp; Doanh trại</t>
+          <t>Quy chuẩn PCCC</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -5008,53 +5008,53 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>94/2024/TT-BQP</t>
+          <t>06:2022/BXD</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Nhà ở áp dụng trong Bộ Quốc phòng (Mẫu giấy tờ nhà ở công vụ và dự án nhà ở LLVT)</t>
+          <t>Ban hành QCVN 06:2022/BXD Quy chuẩn kỹ thuật quốc gia về An toàn cháy cho nhà và công trình</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>Bộ Quốc phòng</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>11/11/2024</t>
+          <t>30/11/2022</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
-        </is>
-      </c>
-      <c r="I68" s="14" t="inlineStr">
+          <t>16/01/2023</t>
+        </is>
+      </c>
+      <c r="I68" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Được sửa đổi bởi Thông tư 09/2023/TT-BXD (Sửa đổi 1:2023 QCVN 06:2022/BXD)</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng cho các dự án đầu tư xây dựng nhà ở cho lực lượng vũ trang thuộc BQP</t>
+          <t>Quy chuẩn bắt buộc áp dụng khi lập hồ sơ thiết kế BVTC công trình (TV-04, TV-05, XD-01)</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>BQP, DOANH_TRAI, TV-01, TV-02, TV-04, XD-01</t>
+          <t>PCCC, TV-02, TV-03, TV-04, TV-05, XD-01</t>
         </is>
       </c>
       <c r="M68" s="8" t="inlineStr"/>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -5064,63 +5064,63 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>Quốc phòng &amp; Doanh trại</t>
+          <t>Bảo vệ Môi trường</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>73/2023/TT-BQP</t>
+          <t>72/2020/QH14</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 128/2021/TT-BQP ngày 01/10/2021 về quy định phân cấp, ủy quyền quyết định chủ trương đầu tư và dự án đầu tư công trong BQP</t>
+          <t>Luật Bảo vệ môi trường năm 2020</t>
         </is>
       </c>
       <c r="F69" s="13" t="inlineStr">
         <is>
-          <t>Bộ Quốc phòng</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
-          <t>05/10/2023</t>
+          <t>17/11/2020</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>20/11/2023</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J69" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP</t>
+          <t>Thay thế Luật Bảo vệ môi trường 2014</t>
         </is>
       </c>
       <c r="K69" s="10" t="inlineStr">
         <is>
-          <t>Cập nhật phân cấp đầu tư BQP giai đoạn 2023-2026</t>
+          <t>Luật nền tảng về Đánh giá tác động môi trường (ĐTM), Giấy phép môi trường và Đăng ký môi trường</t>
         </is>
       </c>
       <c r="L69" s="10" t="inlineStr">
         <is>
-          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
         </is>
       </c>
       <c r="M69" s="15" t="inlineStr"/>
       <c r="N69" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -5130,63 +5130,63 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Quốc phòng &amp; Doanh trại</t>
+          <t>Bảo vệ Môi trường</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>120/2024/TT-BQP</t>
+          <t>08/2022/NĐ-CP</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 128/2021/TT-BQP về phân cấp quản lý và thực hiện dự án đầu tư công trong Bộ Quốc phòng</t>
+          <t>Quy định chi tiết một số điều của Luật Bảo vệ môi trường</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>Bộ Quốc phòng</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>10/01/2022</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>10/01/2022</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP</t>
+          <t>Được sửa đổi, bổ sung bởi Nghị định 05/2025/NĐ-CP và Nghị định 48/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>Phân cấp phê duyệt thiết kế, dự toán BQP giai đoạn 2024-2026</t>
+          <t>Quy định phân nhóm dự án đầu tư theo tiêu chí môi trường để lập ĐTM hoặc đăng ký môi trường</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
         </is>
       </c>
       <c r="M70" s="8" t="inlineStr"/>
       <c r="N70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -5196,63 +5196,63 @@
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>Quốc phòng &amp; Doanh trại</t>
+          <t>Bảo vệ Môi trường</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>24/2025/TT-BQP</t>
+          <t>05/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 174/2021/TT-BQP về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng trong Bộ Quốc phòng</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP quy định chi tiết một số điều của Luật Bảo vệ môi trường</t>
         </is>
       </c>
       <c r="F71" s="13" t="inlineStr">
         <is>
-          <t>Bộ Quốc phòng</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>06/05/2025</t>
+          <t>08/01/2025</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>20/06/2025</t>
-        </is>
-      </c>
-      <c r="I71" s="14" t="inlineStr">
+          <t>01/03/2025</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J71" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung Thông tư 174/2021/TT-BQP về quản lý chất lượng công trình BQP</t>
+          <t>Sửa đổi Nghị định 08/2022/NĐ-CP</t>
         </is>
       </c>
       <c r="K71" s="10" t="inlineStr">
         <is>
-          <t>Quy chuẩn kiểm tra công tác nghiệm thu công trình quân sự đặc thù hiện hành</t>
+          <t>Đơn giản hóa thủ tục cấp giấy phép môi trường và đăng ký môi trường cho dự án xây dựng</t>
         </is>
       </c>
       <c r="L71" s="10" t="inlineStr">
         <is>
-          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
+          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
         </is>
       </c>
       <c r="M71" s="15" t="inlineStr"/>
       <c r="N71" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -5262,63 +5262,63 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Quốc phòng &amp; Doanh trại</t>
+          <t>Bảo vệ Môi trường</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>101/2026/TT-BQP</t>
+          <t>48/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết và biện pháp thực hiện một số nội dung Luật Xây dựng thuộc phạm vi quản lý của Bộ Quốc phòng</t>
+          <t>Sửa đổi, bổ sung một số điều của các Nghị định quy định chi tiết Luật Bảo vệ môi trường</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>Bộ Quốc phòng</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="I72" s="14" t="inlineStr">
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Sửa đổi Nghị định 08/2022/NĐ-CP</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng cho các dự án đầu tư xây dựng công trình trong toàn Bộ Quốc phòng</t>
+          <t>Cập nhật quy chuẩn kỹ thuật quốc gia về môi trường trong thi công xây dựng</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>ALL, BQP, QLDA, XD-01, TOAN_QUAN</t>
+          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
         </is>
       </c>
       <c r="M72" s="8" t="inlineStr"/>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -5328,63 +5328,63 @@
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>Quốc phòng &amp; Doanh trại</t>
+          <t>Bảo vệ Môi trường</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị quyết</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>102/2026/TT-BQP</t>
+          <t>66.19/2026/NQ-CP</t>
         </is>
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>Quy định và hướng dẫn về lập, thẩm định, quyết định, phân cấp quyết định chủ trương đầu tư, dự án đầu tư trong Bộ Quốc phòng</t>
+          <t>Nghị quyết về việc tháo gỡ khó khăn, vướng mắc trong thực hiện thủ tục môi trường cho các dự án đầu tư công</t>
         </is>
       </c>
       <c r="F73" s="13" t="inlineStr">
         <is>
-          <t>Bộ Quốc phòng</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>15/03/2026</t>
         </is>
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
-        </is>
-      </c>
-      <c r="I73" s="14" t="inlineStr">
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J73" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 128/2021/TT-BQP, Thông tư 73/2023/TT-BQP và Thông tư 120/2024/TT-BQP</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K73" s="10" t="inlineStr">
         <is>
-          <t>Văn bản xương sống về phân cấp, ủy quyền quyết định đầu tư và dự án đầu tư công mới nhất trong BQP</t>
+          <t>Cơ chế đặc thù tháo gỡ thủ tục đăng ký môi trường đối với dự án cải tạo, sửa chữa doanh trại</t>
         </is>
       </c>
       <c r="L73" s="10" t="inlineStr">
         <is>
-          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
         </is>
       </c>
       <c r="M73" s="15" t="inlineStr"/>
       <c r="N73" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -5394,63 +5394,63 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Quốc phòng &amp; Doanh trại</t>
+          <t>Chi thường xuyên &amp; Tài sản công</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Quyết định</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>35/QĐ-TTg</t>
+          <t>15/2017/QH14</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Ban hành Danh mục bí mật Nhà nước trong lĩnh vực Quốc phòng</t>
+          <t>Luật Quản lý, sử dụng tài sản công</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>Thủ tướng Chính phủ</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>21/06/2017</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
-        </is>
-      </c>
-      <c r="I74" s="14" t="inlineStr">
+          <t>01/01/2018</t>
+        </is>
+      </c>
+      <c r="I74" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>Quyết định số 12/QĐ-TTg</t>
+          <t>Thay thế Luật Quản lý tài sản nhà nước 2008</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>Quy định bảo mật hồ sơ, tài liệu thiết kế công trình quân sự</t>
+          <t>Chế độ quản lý, bảo dưỡng, nâng cấp và sử dụng tài sản công trong các cơ quan, đơn vị</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
         </is>
       </c>
       <c r="M74" s="8" t="inlineStr"/>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -5465,27 +5465,27 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>15/2017/QH14</t>
+          <t>151/2017/NĐ-CP</t>
         </is>
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>Luật Quản lý, sử dụng tài sản công</t>
+          <t>Quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
         </is>
       </c>
       <c r="F75" s="13" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
         <is>
-          <t>21/06/2017</t>
+          <t>26/12/2017</t>
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr">
@@ -5493,19 +5493,19 @@
           <t>01/01/2018</t>
         </is>
       </c>
-      <c r="I75" s="14" t="inlineStr">
+      <c r="I75" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J75" s="10" t="inlineStr">
         <is>
-          <t>Luật Quản lý tài sản nhà nước 2008</t>
+          <t>Được sửa đổi, bổ sung bởi Nghị định 114/2024/NĐ-CP và Nghị định 186/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="K75" s="10" t="inlineStr">
         <is>
-          <t>Chế độ quản lý, bảo dưỡng, nâng cấp và sử dụng tài sản công</t>
+          <t>Quy trình sử dụng tài sản công, sửa chữa và bảo dưỡng tài sản</t>
         </is>
       </c>
       <c r="L75" s="10" t="inlineStr">
@@ -5516,7 +5516,7 @@
       <c r="M75" s="15" t="inlineStr"/>
       <c r="N75" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -5536,12 +5536,12 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>151/2017/NĐ-CP</t>
+          <t>114/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 151/2017/NĐ-CP quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
@@ -5551,27 +5551,27 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>26/12/2017</t>
+          <t>15/09/2024</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>30/10/2024</t>
         </is>
       </c>
       <c r="I76" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 186/2025/NĐ-CP</t>
+          <t>Sửa đổi Nghị định 151/2017/NĐ-CP</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng phân cấp tài sản công giai đoạn 2018-2025</t>
+          <t>Phân cấp thẩm quyền bảo dưỡng, sửa chữa tài sản công trong các đơn vị dự toán</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
@@ -5582,7 +5582,7 @@
       <c r="M76" s="8" t="inlineStr"/>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 151/2017/NĐ-CP về quản lý, sử dụng tài sản công</t>
         </is>
       </c>
       <c r="F77" s="13" t="inlineStr">
@@ -5617,27 +5617,27 @@
       </c>
       <c r="G77" s="11" t="inlineStr">
         <is>
-          <t>18/09/2025</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
-        </is>
-      </c>
-      <c r="I77" s="14" t="inlineStr">
+          <t>01/08/2025</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J77" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 151/2017/NĐ-CP</t>
+          <t>Sửa đổi Nghị định 151/2017/NĐ-CP</t>
         </is>
       </c>
       <c r="K77" s="10" t="inlineStr">
         <is>
-          <t>Quy định phân cấp thẩm quyền quyết định mua sắm, sửa chữa, bàn giao tài sản công hiện hành</t>
+          <t>Hướng dẫn cụ thể về trình tự phê duyệt dự toán sửa chữa, cải tạo tài sản công</t>
         </is>
       </c>
       <c r="L77" s="10" t="inlineStr">
@@ -5648,7 +5648,7 @@
       <c r="M77" s="15" t="inlineStr"/>
       <c r="N77" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -5668,12 +5668,12 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>114/2024/NĐ-CP</t>
+          <t>138/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 151/2017/NĐ-CP quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
+          <t>Quy định việc sử dụng kinh phí chi thường xuyên ngân sách nhà nước để thực hiện mua sắm tài sản, trang thiết bị; cải tạo, nâng cấp, mở rộng, xây dựng mới hạng mục công trình trong các dự án đã đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
@@ -5683,27 +5683,27 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>15/09/2024</t>
+          <t>24/10/2024</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>30/10/2024</t>
-        </is>
-      </c>
-      <c r="I78" s="14" t="inlineStr">
+          <t>24/10/2024</t>
+        </is>
+      </c>
+      <c r="I78" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung Nghị định 151/2017/NĐ-CP về tài sản công</t>
+          <t>Được sửa đổi, bổ sung bởi Nghị định 98/2025/NĐ-CP và Nghị định 104/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>Quy định thẩm quyền mua sắm, thuê, xử lý tài sản công</t>
+          <t>Nghị định xương sống cho phép dùng nguồn chi thường xuyên để sửa chữa, cải tạo công trình dưới 15 tỷ đồng</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
@@ -5714,7 +5714,7 @@
       <c r="M78" s="8" t="inlineStr"/>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -5734,12 +5734,12 @@
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>138/2024/NĐ-CP</t>
+          <t>98/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="E79" s="10" t="inlineStr">
         <is>
-          <t>Quy định việc lập dự toán, quản lý, sử dụng kinh phí chi thường xuyên NSNN để mua sắm tài sản, trang thiết bị; cải tạo, nâng cấp, mở rộng, xây dựng mới hạng mục công trình</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 138/2024/NĐ-CP về sử dụng kinh phí chi thường xuyên ngân sách nhà nước</t>
         </is>
       </c>
       <c r="F79" s="13" t="inlineStr">
@@ -5749,27 +5749,27 @@
       </c>
       <c r="G79" s="11" t="inlineStr">
         <is>
-          <t>24/10/2024</t>
+          <t>12/05/2025</t>
         </is>
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>24/10/2024</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J79" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 98/2025/NĐ-CP và Nghị định 104/2026/NĐ-CP</t>
+          <t>Sửa đổi Nghị định 138/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="K79" s="10" t="inlineStr">
         <is>
-          <t>Căn cứ giai đoạn cuối 2024</t>
+          <t>Phân cấp thẩm quyền quyết định dự toán mua sắm, cải tạo tài sản cho Thủ trưởng đơn vị dự toán</t>
         </is>
       </c>
       <c r="L79" s="10" t="inlineStr">
@@ -5780,7 +5780,7 @@
       <c r="M79" s="15" t="inlineStr"/>
       <c r="N79" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -5800,12 +5800,12 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>98/2025/NĐ-CP</t>
+          <t>104/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Quy định việc lập dự toán, quản lý, sử dụng và quyết toán chi thường xuyên ngân sách nhà nước để mua sắm, sửa chữa, cải tạo, nâng cấp tài sản, trang thiết bị; chi thuê hàng hóa, dịch vụ; sửa chữa, cải tạo, nâng cấp, mở rộng, xây dựng mới hạng mục công trình trong các dự án đã đầu tư xây dựng và các nhiệm vụ cần thiết khác</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 138/2024/NĐ-CP về quản lý và thanh toán kinh phí chi thường xuyên sửa chữa cơ sở vật chất</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
@@ -5815,27 +5815,27 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>25/06/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>15/08/2025</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="I80" s="7" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 104/2026/NĐ-CP</t>
+          <t>Sửa đổi Nghị định 138/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng giai đoạn 2025-2026</t>
+          <t>Quy định quy trình giải ngân kinh phí chi thường xuyên tại Kho bạc Nhà nước</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
@@ -5846,7 +5846,7 @@
       <c r="M80" s="8" t="inlineStr"/>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -5861,47 +5861,47 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>104/2026/NĐ-CP</t>
+          <t>65/2021/TT-BTC</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
         <is>
-          <t>Quy định việc lập dự toán, quản lý, sử dụng và quyết toán chi thường xuyên để thực hiện các nhiệm vụ quy định tại Điều 40 Luật Ngân sách nhà nước</t>
+          <t>Quy định về lập dự toán, quản lý, sử dụng và quyết toán kinh phí bảo dưỡng, sửa chữa tài sản công</t>
         </is>
       </c>
       <c r="F81" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Tài chính</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>29/07/2021</t>
         </is>
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
-        </is>
-      </c>
-      <c r="I81" s="14" t="inlineStr">
+          <t>15/09/2021</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J81" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 138/2024/NĐ-CP và Nghị định 98/2025/NĐ-CP</t>
+          <t>Thay thế Thông tư 92/2017/TT-BTC</t>
         </is>
       </c>
       <c r="K81" s="10" t="inlineStr">
         <is>
-          <t>Căn cứ pháp lý then chốt cho các dự án sửa chữa, nâng cấp sử dụng nguồn chi thường xuyên hiện hành</t>
+          <t>Hướng dẫn chi tiết định mức lập dự toán chi thường xuyên sửa chữa cơ sở vật chất, doanh trại</t>
         </is>
       </c>
       <c r="L81" s="10" t="inlineStr">
@@ -5912,7 +5912,7 @@
       <c r="M81" s="15" t="inlineStr"/>
       <c r="N81" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -5922,63 +5922,63 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Chi thường xuyên &amp; Tài sản công</t>
+          <t>Thể thức Văn bản</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>65/2021/TT-BTC</t>
+          <t>30/2020/NĐ-CP</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Quy định về lập dự toán, phân bổ và quyết toán kinh phí bảo dưỡng, sửa chữa tài sản công</t>
+          <t>Về công tác văn thư</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>Bộ Tài chính</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>29/07/2021</t>
+          <t>05/03/2020</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>15/09/2021</t>
-        </is>
-      </c>
-      <c r="I82" s="14" t="inlineStr">
+          <t>05/03/2020</t>
+        </is>
+      </c>
+      <c r="I82" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>Thông tư 92/2017/TT-BTC</t>
+          <t>Thay thế Nghị định 110/2004/NĐ-CP</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng lập dự toán và thanh toán sửa chữa tài sản công dưới 500 triệu</t>
+          <t>Quy chuẩn thể thức văn bản hành chính (Tờ trình, Quyết định, Biên bản, font Times New Roman 13pt/14pt)</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
+          <t>ALL, THE_THUC, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
         </is>
       </c>
       <c r="M82" s="8" t="inlineStr"/>
       <c r="N82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>Chất lượng &amp; Nghiệm thu</t>
+          <t>Đối tác công tư</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>84/2015/QH13</t>
+          <t>64/2020/QH14</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>Luật An toàn, vệ sinh lao động (Quy định an toàn lao động, phòng ngừa sự cố trên công trường xây dựng)</t>
+          <t>Luật Đầu tư theo phương thức đối tác công tư (PPP)</t>
         </is>
       </c>
       <c r="F83" s="13" t="inlineStr">
@@ -6013,34 +6013,38 @@
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>25/06/2015</t>
+          <t>18/06/2020</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>01/07/2016</t>
-        </is>
-      </c>
-      <c r="I83" s="14" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
-        </is>
-      </c>
-      <c r="J83" s="10" t="inlineStr"/>
+          <t>01/01/2021</t>
+        </is>
+      </c>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
+        </is>
+      </c>
+      <c r="J83" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="K83" s="10" t="inlineStr">
         <is>
-          <t>Căn cứ bắt buộc trong Hợp đồng thi công gói XD-01 và Giám sát an toàn gói TV-08</t>
+          <t>Căn cứ pháp lý cho các dự án đầu tư theo hình thức đối tác công tư</t>
         </is>
       </c>
       <c r="L83" s="10" t="inlineStr">
         <is>
-          <t>XD-01, TV-08, AN_TOAN_LAO_DONG</t>
+          <t>PPP, DAU_TU_CONG</t>
         </is>
       </c>
       <c r="M83" s="15" t="inlineStr"/>
       <c r="N83" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -6050,63 +6054,63 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Xây dựng &amp; Quản lý dự án</t>
+          <t>Đối tác công tư</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>72/2020/QH14</t>
+          <t>35/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Luật Bảo vệ môi trường năm 2020</t>
+          <t>Quy định chi tiết và hướng dẫn thi hành Luật Đầu tư theo phương thức đối tác công tư</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>17/11/2020</t>
+          <t>29/03/2021</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
-        </is>
-      </c>
-      <c r="I84" s="14" t="inlineStr">
+          <t>29/03/2021</t>
+        </is>
+      </c>
+      <c r="I84" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Luật Bảo vệ môi trường 55/2014/QH13</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>Căn cứ thực hiện thủ tục Đăng ký môi trường / ĐTM cho các hạng mục Kho xăng dầu, Bệnh xá, Bể bơi</t>
+          <t>Quy định chi tiết quy trình lập dự án và lựa chọn nhà đầu tư PPP</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
+          <t>PPP, DAU_TU_CONG</t>
         </is>
       </c>
       <c r="M84" s="8" t="inlineStr"/>
       <c r="N84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -6116,63 +6120,63 @@
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>Xây dựng &amp; Quản lý dự án</t>
+          <t>Đầu tư kinh doanh</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>08/2022/NĐ-CP</t>
+          <t>61/2020/QH14</t>
         </is>
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Bảo vệ môi trường</t>
+          <t>Luật Đầu tư năm 2020 (sửa đổi bởi Luật số 57/2024/QH15)</t>
         </is>
       </c>
       <c r="F85" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
-          <t>10/01/2022</t>
+          <t>17/06/2020</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>10/01/2022</t>
-        </is>
-      </c>
-      <c r="I85" s="14" t="inlineStr">
+          <t>01/01/2021</t>
+        </is>
+      </c>
+      <c r="I85" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J85" s="10" t="inlineStr">
         <is>
-          <t>Được sửa đổi, bổ sung bởi Nghị định số 05/2025/NĐ-CP và Nghị định số 48/2026/NĐ-CP</t>
+          <t>Thay thế Luật Đầu tư 2014</t>
         </is>
       </c>
       <c r="K85" s="10" t="inlineStr">
         <is>
-          <t>Quy định đối tượng và hồ sơ Đăng ký môi trường công trình (bổ trợ Nghị quyết 66.19/2026/NQ-CP)</t>
+          <t>Căn cứ pháp lý về thủ tục chấp thuận chủ trương đầu tư dự án</t>
         </is>
       </c>
       <c r="L85" s="10" t="inlineStr">
         <is>
-          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
+          <t>DAU_TU_KINH_DOANH</t>
         </is>
       </c>
       <c r="M85" s="15" t="inlineStr"/>
       <c r="N85" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6186,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Xây dựng &amp; Quản lý dự án</t>
+          <t>Đầu tư kinh doanh</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -6192,12 +6196,12 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>05/2025/NĐ-CP</t>
+          <t>31/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP ngày 10 tháng 01 năm 2022 của Chính phủ quy định chi tiết một số điều của Luật Bảo vệ môi trường</t>
+          <t>Quy định chi tiết và hướng dẫn thi hành một số điều của Luật Đầu tư</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
@@ -6207,38 +6211,38 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>26/03/2021</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
-        </is>
-      </c>
-      <c r="I86" s="14" t="inlineStr">
+          <t>26/03/2021</t>
+        </is>
+      </c>
+      <c r="I86" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung Nghị định số 08/2022/NĐ-CP; được sửa đổi bởi Nghị định 48/2026/NĐ-CP</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>Quy định phân quyền và cắt giảm thủ tục cấp Giấy phép môi trường, Đăng ký môi trường</t>
+          <t>Quy định chi tiết trình tự, thủ tục đầu tư và ưu đãi đầu tư</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
+          <t>DAU_TU_KINH_DOANH</t>
         </is>
       </c>
       <c r="M86" s="8" t="inlineStr"/>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>
@@ -6248,63 +6252,63 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>Xây dựng &amp; Quản lý dự án</t>
+          <t>Quốc phòng &amp; Doanh trại</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Văn bản Hợp nhất</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>48/2026/NĐ-CP</t>
+          <t>15/VBHN-BQP</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP ngày 10 tháng 01 năm 2022 của Chính phủ quy định chi tiết một số điều của Luật Bảo vệ môi trường được sửa đổi, bổ sung bởi Nghị định số 05/2025/NĐ-CP ngày 06 tháng 01 năm 2025</t>
+          <t>Văn bản hợp nhất Thông tư quy định về phân cấp, ủy quyền quyết định chủ trương đầu tư và dự án đầu tư công trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F87" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>15/03/2025</t>
         </is>
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="I87" s="14" t="inlineStr">
+          <t>15/03/2025</t>
+        </is>
+      </c>
+      <c r="I87" s="7" t="inlineStr">
         <is>
           <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J87" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung Nghị định số 08/2022/NĐ-CP và Nghị định số 05/2025/NĐ-CP</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K87" s="10" t="inlineStr">
         <is>
-          <t>Đơn giản hóa tối đa thủ tục môi trường cho các công trình xây dựng và dự án đầu tư công hiện hành</t>
+          <t>Văn bản hợp nhất hướng dẫn công tác quản lý dự án và phân cấp trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="L87" s="10" t="inlineStr">
         <is>
-          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
+          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M87" s="15" t="inlineStr"/>
       <c r="N87" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:54</t>
+          <t>2026-08-21 16:14</t>
         </is>
       </c>
     </row>

--- a/Kho_Can_Cu_Phap_Ly.xlsx
+++ b/Kho_Can_Cu_Phap_Ly.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N87"/>
+  <dimension ref="A1:N89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -687,7 +687,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Có hiệu lực từ 01/07/2025; hợp nhất quy hoạch đô thị và nông thôn, phân cấp mạnh cho địa phương</t>
+          <t>Có hiệu lực từ 01/07/2025; hợp nhất quản lý quy hoạch đô thị và nông thôn, phân cấp mạnh cho địa phương</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -698,7 +698,7 @@
       <c r="M2" s="8" t="inlineStr"/>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       <c r="M3" s="15" t="inlineStr"/>
       <c r="N3" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       <c r="M5" s="15" t="inlineStr"/>
       <c r="N5" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       <c r="M6" s="8" t="inlineStr"/>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Quy chuẩn</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>01/2021/TT-BXD</t>
+          <t>QCVN 01:2021/BXD</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>Ban hành Quy chuẩn kỹ thuật quốc gia về Quy hoạch xây dựng (Mã số: QCVN 01:2021/BXD)</t>
+          <t>Quy chuẩn kỹ thuật quốc gia về Quy hoạch xây dựng (ban hành kèm Thông tư 01/2021/TT-BXD)</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -1028,7 +1028,7 @@
       <c r="M7" s="15" t="inlineStr"/>
       <c r="N7" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       <c r="M8" s="8" t="inlineStr"/>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       <c r="M9" s="15" t="inlineStr"/>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       <c r="M10" s="8" t="inlineStr"/>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       <c r="M11" s="15" t="inlineStr"/>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       <c r="M12" s="8" t="inlineStr"/>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
@@ -1424,7 +1424,7 @@
       <c r="M13" s="15" t="inlineStr"/>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       <c r="M14" s="8" t="inlineStr"/>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       <c r="M15" s="15" t="inlineStr"/>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
       <c r="M16" s="8" t="inlineStr"/>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Đấu thầu qua mạng</t>
+          <t>An toàn Lao động</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -1642,12 +1642,12 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>22/2023/QH15</t>
+          <t>84/2015/QH13</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>Luật Đấu thầu năm 2023</t>
+          <t>Luật An toàn, vệ sinh lao động năm 2015</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>23/06/2023</t>
+          <t>25/06/2015</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/07/2016</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
@@ -1672,23 +1672,23 @@
       </c>
       <c r="J17" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Luật Đấu thầu 43/2013/QH13</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K17" s="10" t="inlineStr">
         <is>
-          <t>Luật đấu thầu nền tảng chi phối toàn bộ các gói thầu TV, XD, PTV của dự án</t>
+          <t>Quy định biện pháp an toàn lao động bắt buộc trong thi công xây dựng và giám sát công trường</t>
         </is>
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
+          <t>AN_TOAN_LAO_DONG, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M17" s="15" t="inlineStr"/>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -1708,12 +1708,12 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>57/2024/QH15</t>
+          <t>22/2023/QH15</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Luật sửa đổi, bổ sung một số điều của Luật Quy hoạch, Luật Đầu tư, Luật Đầu tư theo phương thức đối tác công tư và Luật Đấu thầu</t>
+          <t>Luật Đấu thầu năm 2023</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>29/11/2024</t>
+          <t>23/06/2023</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>15/01/2025</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung Luật Đấu thầu 22/2023/QH15</t>
+          <t>Thay thế Luật Đấu thầu 43/2013/QH13</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Mở rộng phân cấp thẩm quyền chỉ định thầu, rút ngắn thời gian chuẩn bị E-HSDT và mua sắm công</t>
+          <t>Luật đấu thầu nền tảng chi phối toàn bộ các gói thầu TV, XD, PTV của dự án</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -1754,7 +1754,7 @@
       <c r="M18" s="8" t="inlineStr"/>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1774,12 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>43/2013/QH13</t>
+          <t>57/2024/QH15</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>Luật Đấu thầu năm 2013</t>
+          <t>Luật sửa đổi, bổ sung một số điều của Luật Quy hoạch, Luật Đầu tư, Luật Đầu tư theo phương thức đối tác công tư và Luật Đấu thầu</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
@@ -1789,38 +1789,38 @@
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>26/11/2013</t>
+          <t>29/11/2024</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>01/07/2014</t>
-        </is>
-      </c>
-      <c r="I19" s="14" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+          <t>15/01/2025</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J19" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Luật Đấu thầu 22/2023/QH15</t>
+          <t>Sửa đổi, bổ sung Luật Đấu thầu 22/2023/QH15</t>
         </is>
       </c>
       <c r="K19" s="10" t="inlineStr">
         <is>
-          <t>Hết hiệu lực từ 01/01/2024</t>
+          <t>Mở rộng phân cấp thẩm quyền chỉ định thầu, rút ngắn thời gian chuẩn bị E-HSDT và mua sắm công</t>
         </is>
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, LICHSU</t>
+          <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
         </is>
       </c>
       <c r="M19" s="15" t="inlineStr"/>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -1835,32 +1835,32 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>214/2025/NĐ-CP</t>
+          <t>90/2025/QH15</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Đấu thầu về lựa chọn nhà thầu</t>
+          <t>Luật sửa đổi, bổ sung một số điều của Luật Đấu thầu, Luật Đầu tư công, Luật Quản lý tài sản công</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>04/08/2025</t>
+          <t>25/06/2025</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>04/08/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 24/2024/NĐ-CP và Nghị định 63/2014/NĐ-CP</t>
+          <t>Sửa đổi Luật Đấu thầu 22/2023/QH15</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Nghị định xương sống hiện hành về quy trình chỉ định thầu rút gọn, đấu thầu rộng rãi qua mạng</t>
+          <t>Phân cấp triệt để thẩm quyền lựa chọn nhà thầu cho Chủ đầu tư và nâng hạn mức chỉ định thầu</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -1886,7 +1886,7 @@
       <c r="M20" s="8" t="inlineStr"/>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -1901,32 +1901,32 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>24/2024/NĐ-CP</t>
+          <t>43/2013/QH13</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Đấu thầu về lựa chọn nhà thầu</t>
+          <t>Luật Đấu thầu năm 2013</t>
         </is>
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>27/02/2024</t>
+          <t>26/11/2013</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>27/02/2024</t>
+          <t>01/07/2014</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
@@ -1936,23 +1936,23 @@
       </c>
       <c r="J21" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 214/2025/NĐ-CP từ ngày 04/08/2025</t>
+          <t>Bị thay thế bởi Luật Đấu thầu 22/2023/QH15</t>
         </is>
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng chuyển tiếp cho các gói thầu phát hành E-HSMT trước 04/08/2025</t>
+          <t>Hết hiệu lực từ 01/01/2024</t>
         </is>
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01, LICHSU</t>
+          <t>ALL, DAU_THAU, LICHSU</t>
         </is>
       </c>
       <c r="M21" s="15" t="inlineStr"/>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -1972,12 +1972,12 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>63/2014/NĐ-CP</t>
+          <t>214/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết thi hành một số điều của Luật Đấu thầu về lựa chọn nhà thầu</t>
+          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Đấu thầu về lựa chọn nhà thầu</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -1987,38 +1987,38 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>26/06/2014</t>
+          <t>04/08/2025</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>15/08/2014</t>
-        </is>
-      </c>
-      <c r="I22" s="14" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+          <t>04/08/2025</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 24/2024/NĐ-CP</t>
+          <t>Thay thế Nghị định 24/2024/NĐ-CP và Nghị định 63/2014/NĐ-CP</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Hết hiệu lực từ 27/02/2024</t>
+          <t>Nghị định xương sống hiện hành về quy trình chỉ định thầu rút gọn, đấu thầu rộng rãi qua mạng</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, LICHSU</t>
+          <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
         </is>
       </c>
       <c r="M22" s="8" t="inlineStr"/>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -2033,58 +2033,58 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>79/2025/TT-BTC</t>
+          <t>24/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>Hướng dẫn việc cung cấp, đăng tải thông tin về đấu thầu và mẫu hồ sơ đấu thầu trên Hệ thống mạng đấu thầu quốc gia</t>
+          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Đấu thầu về lựa chọn nhà thầu</t>
         </is>
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>Bộ Tài chính</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>20/07/2025</t>
+          <t>27/02/2024</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>20/07/2025</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>27/02/2024</t>
+        </is>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 06/2024/TT-BKHĐT và Thông tư 22/2024/TT-BKHĐT</t>
+          <t>Bị thay thế bởi Nghị định 214/2025/NĐ-CP từ ngày 04/08/2025</t>
         </is>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
-          <t>Ban hành toàn bộ biểu mẫu E-HSMT xây lắp, tư vấn, phi tư vấn, E-HSYC chỉ định thầu hiện hành</t>
+          <t>Áp dụng chuyển tiếp cho các gói thầu phát hành E-HSMT trước 04/08/2025</t>
         </is>
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
+          <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01, LICHSU</t>
         </is>
       </c>
       <c r="M23" s="15" t="inlineStr"/>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -2099,32 +2099,32 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>06/2024/TT-BKHĐT</t>
+          <t>63/2014/NĐ-CP</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Hướng dẫn việc cung cấp, đăng tải thông tin về đấu thầu và mẫu hồ sơ đấu thầu trên Hệ thống mạng đấu thầu quốc gia</t>
+          <t>Quy định chi tiết thi hành một số điều của Luật Đấu thầu về lựa chọn nhà thầu</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>Bộ Kế hoạch và Đầu tư</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>26/06/2014</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>15/08/2014</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
@@ -2134,23 +2134,23 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 79/2025/TT-BTC</t>
+          <t>Bị thay thế bởi Nghị định 24/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>Hết hiệu lực từ 20/07/2025</t>
+          <t>Hết hiệu lực từ 27/02/2024</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, E_HSMT, LICHSU</t>
+          <t>ALL, DAU_THAU, LICHSU</t>
         </is>
       </c>
       <c r="M24" s="8" t="inlineStr"/>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -2170,12 +2170,12 @@
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>80/2025/TT-BTC</t>
+          <t>79/2025/TT-BTC</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết mẫu hồ sơ yêu cầu, báo cáo đánh giá trong lựa chọn nhà thầu mua sắm công</t>
+          <t>Hướng dẫn việc cung cấp, đăng tải thông tin về đấu thầu và mẫu hồ sơ đấu thầu trên Hệ thống mạng đấu thầu quốc gia</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>22/07/2025</t>
+          <t>20/07/2025</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>22/07/2025</t>
+          <t>04/08/2025</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
@@ -2200,23 +2200,23 @@
       </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 07/2024/TT-BKHĐT và Thông tư 23/2024/TT-BKHĐT</t>
+          <t>Thay thế Thông tư 06/2024/TT-BKHĐT và Thông tư 22/2024/TT-BKHĐT</t>
         </is>
       </c>
       <c r="K25" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng lập HSYC và đánh giá hồ sơ đề xuất gói thầu mua sắm hàng hóa, doanh cụ</t>
+          <t>Ban hành toàn bộ biểu mẫu E-HSMT xây lắp, tư vấn, phi tư vấn, E-HSYC chỉ định thầu hiện hành</t>
         </is>
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, E_HSMT, TV-06, XD-01</t>
+          <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
         </is>
       </c>
       <c r="M25" s="15" t="inlineStr"/>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -2226,63 +2226,63 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Chi phí &amp; Định mức</t>
+          <t>Đấu thầu qua mạng</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>206/2026/NĐ-CP</t>
+          <t>06/2024/TT-BKHĐT</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Xây dựng về quản lý chi phí đầu tư xây dựng</t>
+          <t>Hướng dẫn việc cung cấp, đăng tải thông tin về đấu thầu và mẫu hồ sơ đấu thầu trên Hệ thống mạng đấu thầu quốc gia</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Kế hoạch và Đầu tư</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>26/04/2024</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 10/2021/NĐ-CP</t>
+          <t>Bị thay thế bởi Thông tư 79/2025/TT-BTC</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>Quy định phương pháp lập và quản lý Tổng mức đầu tư, Dự toán xây dựng công trình hiện hành</t>
+          <t>Hết hiệu lực từ 04/08/2025</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
+          <t>ALL, DAU_THAU, E_HSMT, LICHSU</t>
         </is>
       </c>
       <c r="M26" s="8" t="inlineStr"/>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -2292,63 +2292,63 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Chi phí &amp; Định mức</t>
+          <t>Đấu thầu qua mạng</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>10/2021/NĐ-CP</t>
+          <t>80/2025/TT-BTC</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>Về quản lý chi phí đầu tư xây dựng</t>
+          <t>Quy định chi tiết mẫu hồ sơ yêu cầu, báo cáo đánh giá trong lựa chọn nhà thầu mua sắm công</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Tài chính</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>09/02/2021</t>
+          <t>22/07/2025</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>09/02/2021</t>
-        </is>
-      </c>
-      <c r="I27" s="14" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+          <t>08/08/2025</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J27" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 206/2026/NĐ-CP từ ngày 01/07/2026</t>
+          <t>Thay thế Thông tư 07/2024/TT-BKHĐT và Thông tư 23/2024/TT-BKHĐT</t>
         </is>
       </c>
       <c r="K27" s="10" t="inlineStr">
         <is>
-          <t>Dự án đã phê duyệt dự toán trước 01/07/2026 thực hiện theo điều khoản chuyển tiếp của NĐ 206</t>
+          <t>Áp dụng lập HSYC và đánh giá hồ sơ đề xuất gói thầu mua sắm hàng hóa, doanh cụ</t>
         </is>
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01, LICHSU</t>
+          <t>ALL, DAU_THAU, E_HSMT, TV-06, XD-01</t>
         </is>
       </c>
       <c r="M27" s="15" t="inlineStr"/>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -2363,32 +2363,32 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>38/2026/TT-BXD</t>
+          <t>206/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Ban hành hệ thống định mức dự toán xây dựng công trình và định mức chi phí tư vấn đầu tư xây dựng</t>
+          <t>Quy định chi tiết một số điều của Luật Xây dựng về quản lý chi phí đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
@@ -2398,23 +2398,23 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 12/2021/TT-BXD và Thông tư 09/2024/TT-BXD</t>
+          <t>Thay thế Nghị định 10/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>Hệ thống định mức xây dựng và tỷ lệ % chi phí quản lý dự án, tư vấn thiết kế, giám sát mới nhất</t>
+          <t>Quy định phương pháp lập và quản lý Tổng mức đầu tư, Dự toán xây dựng công trình hiện hành</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>ALL, DINH_MUC, DU_TOAN, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-08, TV-09, XD-01</t>
+          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
         </is>
       </c>
       <c r="M28" s="8" t="inlineStr"/>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -2429,32 +2429,32 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>12/2021/TT-BXD</t>
+          <t>10/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>Ban hành định mức xây dựng</t>
+          <t>Về quản lý chi phí đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>31/08/2021</t>
+          <t>09/02/2021</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>15/10/2021</t>
+          <t>09/02/2021</t>
         </is>
       </c>
       <c r="I29" s="14" t="inlineStr">
@@ -2464,23 +2464,23 @@
       </c>
       <c r="J29" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 38/2026/TT-BXD từ ngày 01/08/2026</t>
+          <t>Bị thay thế bởi Nghị định 206/2026/NĐ-CP từ ngày 01/07/2026</t>
         </is>
       </c>
       <c r="K29" s="10" t="inlineStr">
         <is>
-          <t>Hết hiệu lực từ 01/08/2026</t>
+          <t>Dự án đã phê duyệt dự toán trước 01/07/2026 thực hiện theo điều khoản chuyển tiếp của NĐ 206</t>
         </is>
       </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
-          <t>ALL, DINH_MUC, DU_TOAN, LICHSU</t>
+          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01, LICHSU</t>
         </is>
       </c>
       <c r="M29" s="15" t="inlineStr"/>
       <c r="N29" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -2500,12 +2500,12 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>09/2024/TT-BXD</t>
+          <t>38/2026/TT-BXD</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số định mức xây dựng ban hành tại Thông tư số 12/2021/TT-BXD</t>
+          <t>Ban hành hệ thống định mức dự toán xây dựng công trình và định mức chi phí tư vấn đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -2515,38 +2515,38 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>30/08/2024</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>15/10/2024</t>
-        </is>
-      </c>
-      <c r="I30" s="14" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 38/2026/TT-BXD</t>
+          <t>Thay thế Thông tư 12/2021/TT-BXD và Thông tư 09/2024/TT-BXD</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>Hết hiệu lực từ 01/08/2026</t>
+          <t>Hệ thống định mức xây dựng và tỷ lệ % chi phí quản lý dự án, tư vấn thiết kế, giám sát mới nhất</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>ALL, DINH_MUC, DU_TOAN, LICHSU</t>
+          <t>ALL, DINH_MUC, DU_TOAN, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-08, TV-09, XD-01</t>
         </is>
       </c>
       <c r="M30" s="8" t="inlineStr"/>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -2566,12 +2566,12 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>01/2025/TT-BXD</t>
+          <t>12/2021/TT-BXD</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 11/2021/TT-BXD hướng dẫn một số nội dung xác định và quản lý chi phí đầu tư xây dựng</t>
+          <t>Ban hành định mức xây dựng</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr">
@@ -2581,38 +2581,38 @@
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>15/01/2025</t>
+          <t>31/08/2021</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>01/03/2025</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>15/10/2021</t>
+        </is>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J31" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung Thông tư 11/2021/TT-BXD</t>
+          <t>Bị thay thế bởi Thông tư 38/2026/TT-BXD từ ngày 01/07/2026</t>
         </is>
       </c>
       <c r="K31" s="10" t="inlineStr">
         <is>
-          <t>Cập nhật phương pháp lập và quản lý chi phí đầu tư xây dựng hiện hành</t>
+          <t>Hết hiệu lực từ 01/07/2026</t>
         </is>
       </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
-          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
+          <t>ALL, DINH_MUC, DU_TOAN, LICHSU</t>
         </is>
       </c>
       <c r="M31" s="15" t="inlineStr"/>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -2632,12 +2632,12 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>11/2021/TT-BXD</t>
+          <t>09/2024/TT-BXD</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Hướng dẫn một số nội dung xác định và quản lý chi phí đầu tư xây dựng</t>
+          <t>Sửa đổi, bổ sung một số định mức xây dựng ban hành tại Thông tư số 12/2021/TT-BXD</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -2647,38 +2647,38 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>31/08/2021</t>
+          <t>30/08/2024</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>15/10/2021</t>
-        </is>
-      </c>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>15/10/2024</t>
+        </is>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>Được sửa đổi, bổ sung bởi Thông tư 14/2023/TT-BXD và Thông tư 01/2025/TT-BXD</t>
+          <t>Bị thay thế bởi Thông tư 38/2026/TT-BXD</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>Quy định cơ cấu chi phí xây dựng, chi phí gián tiếp, chi phí chung trong dự toán</t>
+          <t>Hết hiệu lực từ 01/07/2026</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
+          <t>ALL, DINH_MUC, DU_TOAN, LICHSU</t>
         </is>
       </c>
       <c r="M32" s="8" t="inlineStr"/>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>14/2023/TT-BXD</t>
+          <t>01/2025/TT-BXD</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>29/12/2023</t>
+          <t>15/01/2025</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>15/02/2024</t>
+          <t>01/03/2025</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="J33" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi Thông tư 11/2021/TT-BXD</t>
+          <t>Sửa đổi, bổ sung Thông tư 11/2021/TT-BXD</t>
         </is>
       </c>
       <c r="K33" s="10" t="inlineStr">
         <is>
-          <t>Cập nhật hệ số chi phí chung, chi phí nhà tạm</t>
+          <t>Cập nhật phương pháp lập và quản lý chi phí đầu tư xây dựng hiện hành</t>
         </is>
       </c>
       <c r="L33" s="10" t="inlineStr">
@@ -2744,7 +2744,7 @@
       <c r="M33" s="15" t="inlineStr"/>
       <c r="N33" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -2764,12 +2764,12 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>13/2021/TT-BXD</t>
+          <t>11/2021/TT-BXD</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Hướng dẫn phương pháp xác định các chỉ tiêu kinh tế kỹ thuật và đo bóc khối lượng công trình</t>
+          <t>Hướng dẫn một số nội dung xác định và quản lý chi phí đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -2794,23 +2794,23 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Được sửa đổi, bổ sung bởi Thông tư 14/2023/TT-BXD và Thông tư 01/2025/TT-BXD</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>Quy chuẩn phương pháp đo bóc khối lượng phục vụ lập dự toán và nghiệm thu công trình</t>
+          <t>Quy định cơ cấu chi phí xây dựng, chi phí gián tiếp, chi phí chung trong dự toán</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>ALL, DU_TOAN, DO_BOC_KHOI_LUONG, TV-04, TV-05, XD-01</t>
+          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
         </is>
       </c>
       <c r="M34" s="8" t="inlineStr"/>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -2820,22 +2820,22 @@
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Suất vốn đầu tư</t>
+          <t>Chi phí &amp; Định mức</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Quyết định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>425/QĐ-BXD</t>
+          <t>14/2023/TT-BXD</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>Công bố Suất vốn đầu tư xây dựng công trình và giá xây dựng tổng hợp bộ phận kết cấu công trình</t>
+          <t>Sửa đổi, bổ sung một số điều của Thông tư số 11/2021/TT-BXD hướng dẫn một số nội dung xác định và quản lý chi phí đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F35" s="13" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>29/12/2023</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>15/02/2024</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
@@ -2860,23 +2860,23 @@
       </c>
       <c r="J35" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Quyết định 510/QĐ-BXD</t>
+          <t>Sửa đổi Thông tư 11/2021/TT-BXD</t>
         </is>
       </c>
       <c r="K35" s="10" t="inlineStr">
         <is>
-          <t>Suất vốn đầu tư hiện hành phục vụ tính Tổng mức đầu tư BCNCKT (FS/BKTKT gói TV-02, TV-03)</t>
+          <t>Cập nhật hệ số chi phí chung, chi phí nhà tạm</t>
         </is>
       </c>
       <c r="L35" s="10" t="inlineStr">
         <is>
-          <t>SUAT_VON_DAU_TU, TMDT, TV-01, TV-02, TV-03, TV-04</t>
+          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
         </is>
       </c>
       <c r="M35" s="15" t="inlineStr"/>
       <c r="N35" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -2886,22 +2886,22 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Suất vốn đầu tư</t>
+          <t>Chi phí &amp; Định mức</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Quyết định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>510/QĐ-BXD</t>
+          <t>13/2021/TT-BXD</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Công bố Suất vốn đầu tư xây dựng công trình và giá xây dựng tổng hợp bộ phận kết cấu công trình năm 2023</t>
+          <t>Hướng dẫn phương pháp xác định các chỉ tiêu kinh tế kỹ thuật và đo bóc khối lượng công trình</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -2911,38 +2911,38 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>19/05/2024</t>
+          <t>31/08/2021</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>19/05/2024</t>
-        </is>
-      </c>
-      <c r="I36" s="14" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+          <t>15/10/2021</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Quyết định 425/QĐ-BXD</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Quy chuẩn phương pháp đo bóc khối lượng phục vụ lập dự toán và nghiệm thu công trình</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>SUAT_VON_DAU_TU, TMDT, LICHSU</t>
+          <t>ALL, DU_TOAN, DO_BOC_KHOI_LUONG, TV-04, TV-05, XD-01</t>
         </is>
       </c>
       <c r="M36" s="8" t="inlineStr"/>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -2952,37 +2952,37 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Quốc phòng &amp; Doanh trại</t>
+          <t>Suất vốn đầu tư</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Quyết định</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>101/2026/TT-BQP</t>
+          <t>425/QĐ-BXD</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết và biện pháp thực hiện một số nội dung Luật Xây dựng thuộc phạm vi quản lý của Bộ Quốc phòng</t>
+          <t>Công bố Suất vốn đầu tư xây dựng công trình và giá xây dựng tổng hợp bộ phận kết cấu công trình</t>
         </is>
       </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>Bộ Quốc phòng</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
@@ -2992,23 +2992,23 @@
       </c>
       <c r="J37" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Thay thế Quyết định 510/QĐ-BXD</t>
         </is>
       </c>
       <c r="K37" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng cho các dự án đầu tư xây dựng công trình trong toàn Bộ Quốc phòng</t>
+          <t>Suất vốn đầu tư hiện hành phục vụ tính Tổng mức đầu tư BCNCKT (FS/BKTKT gói TV-02, TV-03)</t>
         </is>
       </c>
       <c r="L37" s="10" t="inlineStr">
         <is>
-          <t>ALL, BQP, QLDA, XD-01, TOAN_QUAN</t>
+          <t>SUAT_VON_DAU_TU, TMDT, TV-01, TV-02, TV-03, TV-04</t>
         </is>
       </c>
       <c r="M37" s="15" t="inlineStr"/>
       <c r="N37" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -3018,63 +3018,63 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Quốc phòng &amp; Doanh trại</t>
+          <t>Suất vốn đầu tư</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Quyết định</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>102/2026/TT-BQP</t>
+          <t>510/QĐ-BXD</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Quy định và hướng dẫn về lập, thẩm định, quyết định, phân cấp quyết định chủ trương đầu tư, dự án đầu tư trong Bộ Quốc phòng</t>
+          <t>Công bố Suất vốn đầu tư xây dựng công trình và giá xây dựng tổng hợp bộ phận kết cấu công trình năm 2023</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>Bộ Quốc phòng</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>19/05/2024</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
-        </is>
-      </c>
-      <c r="I38" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>19/05/2024</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 128/2021/TT-BQP, Thông tư 73/2023/TT-BQP và Thông tư 120/2024/TT-BQP</t>
+          <t>Bị thay thế bởi Quyết định 425/QĐ-BXD</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>Văn bản xương sống về phân cấp, ủy quyền quyết định đầu tư và dự án đầu tư công mới nhất trong BQP</t>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+          <t>SUAT_VON_DAU_TU, TMDT, LICHSU</t>
         </is>
       </c>
       <c r="M38" s="8" t="inlineStr"/>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>128/2021/TT-BQP</t>
+          <t>101/2026/TT-BQP</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>Quy định phân cấp, ủy quyền quyết định chủ trương đầu tư và dự án đầu tư công trong Bộ Quốc phòng</t>
+          <t>Quy định chi tiết và biện pháp thực hiện một số nội dung Luật Xây dựng thuộc phạm vi quản lý của Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F39" s="13" t="inlineStr">
@@ -3109,38 +3109,38 @@
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>06/10/2021</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>20/11/2021</t>
-        </is>
-      </c>
-      <c r="I39" s="14" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K39" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng phân cấp thẩm quyền đầu tư BQP giai đoạn 2021-2026</t>
+          <t>Áp dụng cho các dự án đầu tư xây dựng công trình trong toàn Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="L39" s="10" t="inlineStr">
         <is>
-          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01, LICHSU</t>
+          <t>ALL, BQP, QLDA, XD-01, TOAN_QUAN</t>
         </is>
       </c>
       <c r="M39" s="15" t="inlineStr"/>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -3160,12 +3160,12 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>73/2023/TT-BQP</t>
+          <t>102/2026/TT-BQP</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 128/2021/TT-BQP ngày 01/10/2021 về quy định phân cấp, ủy quyền quyết định chủ trương đầu tư và dự án đầu tư công trong BQP</t>
+          <t>Quy định và hướng dẫn về lập, thẩm định, quyết định, phân cấp quyết định chủ trương đầu tư, dự án đầu tư trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -3175,38 +3175,38 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>05/10/2023</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>20/11/2023</t>
-        </is>
-      </c>
-      <c r="I40" s="14" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP</t>
+          <t>Thay thế Thông tư 128/2021/TT-BQP, Thông tư 73/2023/TT-BQP và Thông tư 120/2024/TT-BQP</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>Cập nhật phân cấp đầu tư BQP giai đoạn 2023-2026</t>
+          <t>Văn bản xương sống về phân cấp, ủy quyền quyết định đầu tư và dự án đầu tư công mới nhất trong BQP</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01, LICHSU</t>
+          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M40" s="8" t="inlineStr"/>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -3226,12 +3226,12 @@
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>120/2024/TT-BQP</t>
+          <t>128/2021/TT-BQP</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 128/2021/TT-BQP về phân cấp quản lý và thực hiện dự án đầu tư công trong Bộ Quốc phòng</t>
+          <t>Quy định phân cấp, ủy quyền quyết định chủ trương đầu tư và dự án đầu tư công trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F41" s="13" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>20/11/2021</t>
         </is>
       </c>
       <c r="I41" s="14" t="inlineStr">
@@ -3256,12 +3256,12 @@
       </c>
       <c r="J41" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP</t>
+          <t>Bị thay thế bởi Thông tư 101/2026/TT-BQP và Thông tư 102/2026/TT-BQP</t>
         </is>
       </c>
       <c r="K41" s="10" t="inlineStr">
         <is>
-          <t>Phân cấp phê duyệt thiết kế, dự toán BQP giai đoạn 2024-2026</t>
+          <t>Áp dụng phân cấp thẩm quyền đầu tư BQP giai đoạn 2021-2026</t>
         </is>
       </c>
       <c r="L41" s="10" t="inlineStr">
@@ -3272,7 +3272,7 @@
       <c r="M41" s="15" t="inlineStr"/>
       <c r="N41" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -3292,12 +3292,12 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>174/2021/TT-BQP</t>
+          <t>73/2023/TT-BQP</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Quy định về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng trong Bộ Quốc phòng</t>
+          <t>Sửa đổi, bổ sung một số điều của Thông tư số 128/2021/TT-BQP ngày 01/10/2021 về quy định phân cấp, ủy quyền quyết định chủ trương đầu tư và dự án đầu tư công trong BQP</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -3307,38 +3307,38 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>27/12/2021</t>
+          <t>05/10/2023</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>12/02/2022</t>
-        </is>
-      </c>
-      <c r="I42" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>20/11/2023</t>
+        </is>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Được sửa đổi, bổ sung bởi Thông tư 24/2025/TT-BQP</t>
+          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>Quy chuẩn nghiệm thu và quản lý chất lượng công trình quân sự</t>
+          <t>Cập nhật phân cấp đầu tư BQP giai đoạn 2023-2026</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
+          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01, LICHSU</t>
         </is>
       </c>
       <c r="M42" s="8" t="inlineStr"/>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>24/2025/TT-BQP</t>
+          <t>120/2024/TT-BQP</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 174/2021/TT-BQP về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng trong Bộ Quốc phòng</t>
+          <t>Sửa đổi, bổ sung một số điều của Thông tư số 128/2021/TT-BQP về phân cấp quản lý và thực hiện dự án đầu tư công trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F43" s="13" t="inlineStr">
@@ -3373,38 +3373,38 @@
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>06/05/2025</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>20/06/2025</t>
-        </is>
-      </c>
-      <c r="I43" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>10/02/2025</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J43" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung Thông tư 174/2021/TT-BQP về quản lý chất lượng công trình BQP</t>
+          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP</t>
         </is>
       </c>
       <c r="K43" s="10" t="inlineStr">
         <is>
-          <t>Quy chuẩn kiểm tra công tác nghiệm thu công trình quân sự đặc thù hiện hành</t>
+          <t>Phân cấp phê duyệt thiết kế, dự toán BQP giai đoạn 2024-2026</t>
         </is>
       </c>
       <c r="L43" s="10" t="inlineStr">
         <is>
-          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
+          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01, LICHSU</t>
         </is>
       </c>
       <c r="M43" s="15" t="inlineStr"/>
       <c r="N43" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -3424,12 +3424,12 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>36/2023/TT-BQP</t>
+          <t>174/2021/TT-BQP</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Ban hành Điều lệ Doanh trại Quân đội nhân dân Việt Nam</t>
+          <t>Quy định về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>14/04/2023</t>
+          <t>27/12/2021</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>30/05/2023</t>
+          <t>12/02/2022</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
@@ -3454,23 +3454,23 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Điều lệ Doanh trại QĐNDVN năm 2002</t>
+          <t>Được sửa đổi, bổ sung bởi Thông tư 24/2025/TT-BQP</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>Điều lệ xương sống về quy hoạch tổng mặt bằng, bảo dưỡng, quản lý và sử dụng doanh trại</t>
+          <t>Quy chuẩn nghiệm thu và quản lý chất lượng công trình quân sự</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>BQP, DOANH_TRAI, TV-01, TV-02, TV-04, XD-01</t>
+          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M44" s="8" t="inlineStr"/>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -3490,12 +3490,12 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>150/2018/TT-BQP</t>
+          <t>24/2025/TT-BQP</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr">
         <is>
-          <t>Quy định về tiêu chuẩn, định mức sử dụng máy móc, thiết bị văn phòng phổ biến thuộc phạm vi quản lý của Bộ Quốc phòng</t>
+          <t>Sửa đổi, bổ sung một số điều của Thông tư số 174/2021/TT-BQP về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F45" s="13" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
-          <t>11/10/2018</t>
+          <t>06/05/2025</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>26/11/2018</t>
+          <t>20/06/2025</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
@@ -3520,23 +3520,23 @@
       </c>
       <c r="J45" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Quyết định 162/2002/QĐ-BQP</t>
+          <t>Sửa đổi, bổ sung Thông tư 174/2021/TT-BQP về quản lý chất lượng công trình BQP</t>
         </is>
       </c>
       <c r="K45" s="10" t="inlineStr">
         <is>
-          <t>Tiêu chuẩn định mức máy móc, thiết bị làm việc của cán bộ sĩ quan BQP (gói Doanh cụ XD-01)</t>
+          <t>Quy chuẩn kiểm tra công tác nghiệm thu công trình quân sự đặc thù hiện hành</t>
         </is>
       </c>
       <c r="L45" s="10" t="inlineStr">
         <is>
-          <t>BQP, DOANH_TRAI, TV-01, TV-02, TV-04, XD-01</t>
+          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M45" s="15" t="inlineStr"/>
       <c r="N45" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -3556,12 +3556,12 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>94/2024/TT-BQP</t>
+          <t>36/2023/TT-BQP</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Nhà ở áp dụng trong Bộ Quốc phòng (Mẫu giấy tờ nhà ở công vụ và dự án nhà ở LLVT)</t>
+          <t>Ban hành Điều lệ Doanh trại Quân đội nhân dân Việt Nam</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -3571,12 +3571,12 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>11/11/2024</t>
+          <t>29/05/2023</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>13/07/2023</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Thay thế Điều lệ Doanh trại QĐNDVN năm 2002</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng cho các dự án đầu tư xây dựng nhà ở cho lực lượng vũ trang thuộc BQP</t>
+          <t>Điều lệ xương sống về quy hoạch tổng mặt bằng, bảo dưỡng, quản lý và sử dụng doanh trại</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -3602,7 +3602,7 @@
       <c r="M46" s="8" t="inlineStr"/>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -3617,32 +3617,32 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Quyết định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>35/QĐ-TTg</t>
+          <t>150/2018/TT-BQP</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>Ban hành Danh mục bí mật Nhà nước trong lĩnh vực Quốc phòng</t>
+          <t>Quy định về tiêu chuẩn, định mức sử dụng máy móc, thiết bị văn phòng phổ biến thuộc phạm vi quản lý của Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F47" s="13" t="inlineStr">
         <is>
-          <t>Thủ tướng Chính phủ</t>
+          <t>Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>11/10/2018</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>26/11/2018</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
@@ -3652,23 +3652,23 @@
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>Quyết định số 12/QĐ-TTg</t>
+          <t>Thay thế Quyết định 162/2002/QĐ-BQP</t>
         </is>
       </c>
       <c r="K47" s="10" t="inlineStr">
         <is>
-          <t>Quy định bảo mật hồ sơ, tài liệu thiết kế công trình quân sự</t>
+          <t>Tiêu chuẩn định mức máy móc, thiết bị làm việc của cán bộ sĩ quan BQP (gói Doanh cụ XD-01)</t>
         </is>
       </c>
       <c r="L47" s="10" t="inlineStr">
         <is>
-          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+          <t>BQP, DOANH_TRAI, TV-01, TV-02, TV-04, XD-01</t>
         </is>
       </c>
       <c r="M47" s="15" t="inlineStr"/>
       <c r="N47" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -3678,37 +3678,37 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Chất lượng &amp; Nghiệm thu</t>
+          <t>Quốc phòng &amp; Doanh trại</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>06/2021/NĐ-CP</t>
+          <t>94/2024/TT-BQP</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số nội dung về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng</t>
+          <t>Quy định chi tiết một số điều của Luật Nhà ở áp dụng trong Bộ Quốc phòng (Mẫu giấy tờ nhà ở công vụ và dự án nhà ở LLVT)</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>26/01/2021</t>
+          <t>11/11/2024</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>26/01/2021</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
@@ -3718,23 +3718,23 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 46/2015/NĐ-CP</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>Xương sống về quản lý chất lượng thi công, nhật ký công trình và biên bản nghiệm thu hoàn thành</t>
+          <t>Áp dụng cho các dự án đầu tư xây dựng nhà ở cho lực lượng vũ trang thuộc BQP</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
+          <t>BQP, DOANH_TRAI, TV-01, TV-02, TV-04, XD-01</t>
         </is>
       </c>
       <c r="M48" s="8" t="inlineStr"/>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -3744,37 +3744,37 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>Chất lượng &amp; Nghiệm thu</t>
+          <t>Quốc phòng &amp; Doanh trại</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Quyết định</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>10/2021/TT-BXD</t>
+          <t>35/QĐ-TTg</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>Hướng dẫn một số điều và biện pháp thi hành Nghị định số 06/2021/NĐ-CP và Nghị định số 15/2021/NĐ-CP</t>
+          <t>Ban hành Danh mục bí mật Nhà nước trong lĩnh vực Quốc phòng</t>
         </is>
       </c>
       <c r="F49" s="13" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Thủ tướng Chính phủ</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
-          <t>25/08/2021</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>15/10/2021</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
@@ -3784,23 +3784,23 @@
       </c>
       <c r="J49" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Quyết định số 12/QĐ-TTg</t>
         </is>
       </c>
       <c r="K49" s="10" t="inlineStr">
         <is>
-          <t>Quy chuẩn đánh giá an toàn công trình, kiểm định và lập danh mục hồ sơ hoàn thành công trình</t>
+          <t>Quy định bảo mật hồ sơ, tài liệu thiết kế công trình quân sự</t>
         </is>
       </c>
       <c r="L49" s="10" t="inlineStr">
         <is>
-          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
+          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M49" s="15" t="inlineStr"/>
       <c r="N49" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Hợp đồng Xây dựng</t>
+          <t>Chất lượng &amp; Nghiệm thu</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>37/2015/NĐ-CP</t>
+          <t>06/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết về hợp đồng xây dựng</t>
+          <t>Quy định chi tiết một số nội dung về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>22/04/2015</t>
+          <t>26/01/2021</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>15/06/2015</t>
+          <t>26/01/2021</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
@@ -3850,23 +3850,23 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>Được sửa đổi, bổ sung bởi Nghị định 50/2021/NĐ-CP và Nghị định 35/2023/NĐ-CP</t>
+          <t>Thay thế Nghị định 46/2015/NĐ-CP</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>Quy định tạm ứng, thanh toán, điều chỉnh giá và thanh lý hợp đồng xây dựng</t>
+          <t>Xương sống về quản lý chất lượng thi công, nhật ký công trình và biên bản nghiệm thu hoàn thành</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>ALL, HOP_DONG, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
+          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M50" s="8" t="inlineStr"/>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -3876,37 +3876,37 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>Hợp đồng Xây dựng</t>
+          <t>Chất lượng &amp; Nghiệm thu</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>50/2021/NĐ-CP</t>
+          <t>10/2021/TT-BXD</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 37/2015/NĐ-CP quy định chi tiết về hợp đồng xây dựng</t>
+          <t>Hướng dẫn một số điều và biện pháp thi hành Nghị định số 06/2021/NĐ-CP và Nghị định số 15/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="F51" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>25/08/2021</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>15/10/2021</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
@@ -3916,23 +3916,23 @@
       </c>
       <c r="J51" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi Nghị định 37/2015/NĐ-CP</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K51" s="10" t="inlineStr">
         <is>
-          <t>Quy định bảo đảm thực hiện hợp đồng và điều chỉnh giá hợp đồng trọn gói, đơn giá</t>
+          <t>Quy chuẩn đánh giá an toàn công trình, kiểm định và lập danh mục hồ sơ hoàn thành công trình</t>
         </is>
       </c>
       <c r="L51" s="10" t="inlineStr">
         <is>
-          <t>ALL, HOP_DONG, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
+          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M51" s="15" t="inlineStr"/>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -3947,32 +3947,32 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>02/2023/TT-BXD</t>
+          <t>37/2015/NĐ-CP</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Hướng dẫn một số nội dung về hợp đồng xây dựng</t>
+          <t>Quy định chi tiết về hợp đồng xây dựng</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>03/03/2023</t>
+          <t>22/04/2015</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>20/04/2023</t>
+          <t>15/06/2015</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Được sửa đổi, bổ sung bởi Nghị định 50/2021/NĐ-CP và Nghị định 35/2023/NĐ-CP</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>Ban hành mẫu hợp đồng tư vấn thiết kế, tư vấn giám sát và hợp đồng thi công xây dựng</t>
+          <t>Quy định tạm ứng, thanh toán, điều chỉnh giá và thanh lý hợp đồng xây dựng</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -3998,7 +3998,7 @@
       <c r="M52" s="8" t="inlineStr"/>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -4008,37 +4008,37 @@
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>Tiêu chuẩn Kỹ thuật</t>
+          <t>Hợp đồng Xây dựng</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Tiêu chuẩn</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>TCVN 9393:2012</t>
+          <t>50/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr">
         <is>
-          <t>Cọc - Phương pháp thử nghiệm hiện trường bằng tải trọng tĩnh ép dọc trục</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 37/2015/NĐ-CP quy định chi tiết về hợp đồng xây dựng</t>
         </is>
       </c>
       <c r="F53" s="13" t="inlineStr">
         <is>
-          <t>Bộ Khoa học và Công nghệ</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
         <is>
-          <t>28/12/2012</t>
+          <t>01/04/2021</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>28/12/2012</t>
+          <t>01/04/2021</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
@@ -4048,23 +4048,23 @@
       </c>
       <c r="J53" s="10" t="inlineStr">
         <is>
-          <t>Thay thế TCXDVN 269:2002</t>
+          <t>Sửa đổi Nghị định 37/2015/NĐ-CP</t>
         </is>
       </c>
       <c r="K53" s="10" t="inlineStr">
         <is>
-          <t>Tiêu chuẩn kỹ thuật bắt buộc áp dụng cho gói thầu TV-07 Thí nghiệm nén tĩnh cọc</t>
+          <t>Quy định bảo đảm thực hiện hợp đồng và điều chỉnh giá hợp đồng trọn gói, đơn giá</t>
         </is>
       </c>
       <c r="L53" s="10" t="inlineStr">
         <is>
-          <t>THI_NGHIEM_COC, TV-07, XD-01</t>
+          <t>ALL, HOP_DONG, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
         </is>
       </c>
       <c r="M53" s="15" t="inlineStr"/>
       <c r="N53" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -4074,37 +4074,37 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Tiêu chuẩn Kỹ thuật</t>
+          <t>Hợp đồng Xây dựng</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Tiêu chuẩn</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>TCVN 9363:2012</t>
+          <t>02/2023/TT-BXD</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Khảo sát địa chất công trình cho nhà cao tầng</t>
+          <t>Hướng dẫn một số nội dung về hợp đồng xây dựng</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>Bộ Khoa học và Công nghệ</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>28/12/2012</t>
+          <t>03/03/2023</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>28/12/2012</t>
+          <t>20/04/2023</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
@@ -4119,18 +4119,18 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>Tiêu chuẩn kỹ thuật cho công tác khoan khảo sát địa chất gói TV-02</t>
+          <t>Ban hành mẫu hợp đồng tư vấn thiết kế, tư vấn giám sát và hợp đồng thi công xây dựng</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>KHAO_SAT, TV-02</t>
+          <t>ALL, HOP_DONG, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
         </is>
       </c>
       <c r="M54" s="8" t="inlineStr"/>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>TCVN 9401:2012</t>
+          <t>TCVN 9393:2012</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>Kỹ thuật đo và xử lý số liệu GPS trong trắc địa công trình</t>
+          <t>Cọc - Phương pháp thử nghiệm hiện trường bằng tải trọng tĩnh ép dọc trục</t>
         </is>
       </c>
       <c r="F55" s="13" t="inlineStr">
@@ -4180,23 +4180,23 @@
       </c>
       <c r="J55" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Thay thế TCXDVN 269:2002</t>
         </is>
       </c>
       <c r="K55" s="10" t="inlineStr">
         <is>
-          <t>Tiêu chuẩn kỹ thuật cho công tác đo đạc địa hình, định vị công trình gói TV-01</t>
+          <t>Tiêu chuẩn kỹ thuật bắt buộc áp dụng cho gói thầu TV-07 Thí nghiệm nén tĩnh cọc</t>
         </is>
       </c>
       <c r="L55" s="10" t="inlineStr">
         <is>
-          <t>DO_DAC, TV-01</t>
+          <t>THI_NGHIEM_COC, TV-07, XD-01</t>
         </is>
       </c>
       <c r="M55" s="15" t="inlineStr"/>
       <c r="N55" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -4206,37 +4206,37 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Bảo hiểm Xây dựng</t>
+          <t>Tiêu chuẩn Kỹ thuật</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Tiêu chuẩn</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>08/2022/QH15</t>
+          <t>TCVN 9363:2012</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Luật Kinh doanh bảo hiểm năm 2022</t>
+          <t>Khảo sát địa chất công trình cho nhà cao tầng</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Bộ Khoa học và Công nghệ</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>16/06/2022</t>
+          <t>28/12/2012</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>28/12/2012</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
@@ -4246,23 +4246,23 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Luật Kinh doanh bảo hiểm 2000</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>Luật nền tảng điều chỉnh hoạt động bảo hiểm công trình xây dựng (gói PTV-01)</t>
+          <t>Tiêu chuẩn kỹ thuật cho công tác khoan khảo sát địa chất gói TV-02</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>BAO_HIEM, PTV-01, XD-01</t>
+          <t>KHAO_SAT, TV-02</t>
         </is>
       </c>
       <c r="M56" s="8" t="inlineStr"/>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -4272,37 +4272,37 @@
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>Bảo hiểm Xây dựng</t>
+          <t>Tiêu chuẩn Kỹ thuật</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Tiêu chuẩn</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>67/2023/NĐ-CP</t>
+          <t>TCVN 9401:2012</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
         <is>
-          <t>Quy định về bảo hiểm bắt buộc trách nhiệm dân sự của chủ xe cơ giới, bảo hiểm cháy, nổ bắt buộc, bảo hiểm bắt buộc trong hoạt động đầu tư xây dựng</t>
+          <t>Kỹ thuật đo và xử lý số liệu GPS trong trắc địa công trình</t>
         </is>
       </c>
       <c r="F57" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Khoa học và Công nghệ</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>06/09/2023</t>
+          <t>28/12/2012</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>06/09/2023</t>
+          <t>28/12/2012</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
@@ -4312,23 +4312,23 @@
       </c>
       <c r="J57" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 119/2015/NĐ-CP</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K57" s="10" t="inlineStr">
         <is>
-          <t>Nghị định chi phối biểu phí và điều kiện bảo hiểm công trình trong thời gian thi công (gói PTV-01)</t>
+          <t>Tiêu chuẩn kỹ thuật cho công tác đo đạc địa hình, định vị công trình gói TV-01</t>
         </is>
       </c>
       <c r="L57" s="10" t="inlineStr">
         <is>
-          <t>BAO_HIEM, PTV-01, XD-01</t>
+          <t>DO_DAC, TV-01</t>
         </is>
       </c>
       <c r="M57" s="15" t="inlineStr"/>
       <c r="N57" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Kiểm toán Độc lập</t>
+          <t>Bảo hiểm Xây dựng</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -4348,12 +4348,12 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>67/2011/QH12</t>
+          <t>08/2022/QH15</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Luật Kiểm toán độc lập năm 2011</t>
+          <t>Luật Kinh doanh bảo hiểm năm 2022</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
@@ -4363,12 +4363,12 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>29/03/2011</t>
+          <t>16/06/2022</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>01/01/2012</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="I58" s="7" t="inlineStr">
@@ -4378,23 +4378,23 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Thay thế Luật Kinh doanh bảo hiểm 2000</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>Căn cứ pháp lý then chốt cho gói TV-09 Kiểm toán độc lập quyết toán vốn đầu tư hoàn thành</t>
+          <t>Luật nền tảng điều chỉnh hoạt động bảo hiểm công trình xây dựng (gói PTV-01)</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>KIEM_TOAN, TV-09</t>
+          <t>BAO_HIEM, PTV-01, XD-01</t>
         </is>
       </c>
       <c r="M58" s="8" t="inlineStr"/>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -4404,37 +4404,37 @@
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>Kiểm toán Độc lập</t>
+          <t>Bảo hiểm Xây dựng</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>67/2015/TT-BTC</t>
+          <t>67/2023/NĐ-CP</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr">
         <is>
-          <t>Ban hành Chuẩn mực kiểm toán Việt Nam số 1000 - Kiểm toán báo cáo quyết toán dự án hoàn thành (VSA 1000)</t>
+          <t>Quy định về bảo hiểm bắt buộc trách nhiệm dân sự của chủ xe cơ giới, bảo hiểm cháy, nổ bắt buộc, bảo hiểm bắt buộc trong hoạt động đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F59" s="13" t="inlineStr">
         <is>
-          <t>Bộ Tài chính</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
-          <t>08/05/2015</t>
+          <t>06/09/2023</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>06/09/2023</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
@@ -4444,23 +4444,23 @@
       </c>
       <c r="J59" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Thay thế Nghị định 119/2015/NĐ-CP</t>
         </is>
       </c>
       <c r="K59" s="10" t="inlineStr">
         <is>
-          <t>Quy chuẩn phương pháp kiểm toán báo cáo quyết toán dự án hoàn thành gói TV-09</t>
+          <t>Nghị định chi phối biểu phí và điều kiện bảo hiểm công trình trong thời gian thi công (gói PTV-01)</t>
         </is>
       </c>
       <c r="L59" s="10" t="inlineStr">
         <is>
-          <t>KIEM_TOAN, TV-09</t>
+          <t>BAO_HIEM, PTV-01, XD-01</t>
         </is>
       </c>
       <c r="M59" s="15" t="inlineStr"/>
       <c r="N59" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Đầu tư công</t>
+          <t>Kiểm toán Độc lập</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>58/2024/QH15</t>
+          <t>67/2011/QH12</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Luật Đầu tư công năm 2024</t>
+          <t>Luật Kiểm toán độc lập năm 2011</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>29/11/2024</t>
+          <t>29/03/2011</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>01/01/2012</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
@@ -4510,23 +4510,23 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Luật Đầu tư công 39/2019/QH14</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>Quy định thẩm quyền quyết định chủ trương đầu tư, phân cấp quản lý dự án sử dụng vốn ngân sách nhà nước</t>
+          <t>Căn cứ pháp lý then chốt cho gói TV-09 Kiểm toán độc lập quyết toán vốn đầu tư hoàn thành</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>ALL, DAU_TU_CONG, CHU_TRUONG, TV-01, TV-02, TV-03, TV-09</t>
+          <t>KIEM_TOAN, TV-09</t>
         </is>
       </c>
       <c r="M60" s="8" t="inlineStr"/>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -4536,63 +4536,63 @@
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>Đầu tư công</t>
+          <t>Kiểm toán Độc lập</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>39/2019/QH14</t>
+          <t>67/2015/TT-BTC</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
         <is>
-          <t>Luật Đầu tư công năm 2019</t>
+          <t>Ban hành Chuẩn mực kiểm toán Việt Nam số 1000 - Kiểm toán báo cáo quyết toán dự án hoàn thành (VSA 1000)</t>
         </is>
       </c>
       <c r="F61" s="13" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Bộ Tài chính</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
-          <t>13/06/2019</t>
+          <t>08/05/2015</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
-        </is>
-      </c>
-      <c r="I61" s="14" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+          <t>01/01/2016</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J61" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Luật Đầu tư công 58/2024/QH15</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K61" s="10" t="inlineStr">
         <is>
-          <t>Hết hiệu lực từ 01/01/2025</t>
+          <t>Quy chuẩn phương pháp kiểm toán báo cáo quyết toán dự án hoàn thành gói TV-09</t>
         </is>
       </c>
       <c r="L61" s="10" t="inlineStr">
         <is>
-          <t>ALL, DAU_TU_CONG, LICHSU</t>
+          <t>KIEM_TOAN, TV-09</t>
         </is>
       </c>
       <c r="M61" s="15" t="inlineStr"/>
       <c r="N61" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -4607,32 +4607,32 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>40/2020/NĐ-CP</t>
+          <t>58/2024/QH15</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết thi hành một số điều của Luật Đầu tư công</t>
+          <t>Luật Đầu tư công năm 2024</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>06/04/2020</t>
+          <t>29/11/2024</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>06/04/2020</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
@@ -4642,23 +4642,23 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Thay thế Luật Đầu tư công 39/2019/QH14</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>Quy định trình tự, thủ tục lập và giao kế hoạch đầu tư công trung hạn và hàng năm</t>
+          <t>Quy định thẩm quyền quyết định chủ trương đầu tư, phân cấp quản lý dự án sử dụng vốn ngân sách nhà nước</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>ALL, DAU_TU_CONG, TV-01, TV-02, TV-03</t>
+          <t>ALL, DAU_TU_CONG, CHU_TRUONG, TV-01, TV-02, TV-03, TV-09</t>
         </is>
       </c>
       <c r="M62" s="8" t="inlineStr"/>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -4668,63 +4668,63 @@
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>Quyết toán vốn</t>
+          <t>Đầu tư công</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>99/2021/NĐ-CP</t>
+          <t>39/2019/QH14</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>Quy định về quản lý, thanh toán, quyết toán dự án sử dụng vốn đầu tư công</t>
+          <t>Luật Đầu tư công năm 2019</t>
         </is>
       </c>
       <c r="F63" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>11/11/2021</t>
+          <t>13/06/2019</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
-        </is>
-      </c>
-      <c r="I63" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>01/01/2020</t>
+        </is>
+      </c>
+      <c r="I63" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J63" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 11/2020/NĐ-CP và Thông tư 10/2020/TT-BTC</t>
+          <t>Bị thay thế bởi Luật Đầu tư công 58/2024/QH15</t>
         </is>
       </c>
       <c r="K63" s="10" t="inlineStr">
         <is>
-          <t>Nghị định xương sống về thẩm tra, phê duyệt quyết toán vốn đầu tư công dự án hoàn thành</t>
+          <t>Hết hiệu lực từ 01/01/2025</t>
         </is>
       </c>
       <c r="L63" s="10" t="inlineStr">
         <is>
-          <t>ALL, QUYET_TOAN, TAI_CHINH, TV-09, XD-01</t>
+          <t>ALL, DAU_TU_CONG, LICHSU</t>
         </is>
       </c>
       <c r="M63" s="15" t="inlineStr"/>
       <c r="N63" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -4734,37 +4734,37 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Quyết toán vốn</t>
+          <t>Đầu tư công</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>96/2021/TT-BTC</t>
+          <t>40/2020/NĐ-CP</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Quy định về hệ thống mẫu biểu hồ sơ quyết toán vốn đầu tư công dự án hoàn thành</t>
+          <t>Quy định chi tiết thi hành một số điều của Luật Đầu tư công</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>Bộ Tài chính</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>11/11/2021</t>
+          <t>06/04/2020</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>06/04/2020</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
@@ -4774,23 +4774,23 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>Được sửa đổi, bổ sung bởi Thông tư 24/2024/TT-BTC</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>Ban hành toàn bộ mẫu biểu Báo cáo quyết toán A-B, Báo cáo quyết toán hoàn thành</t>
+          <t>Quy định trình tự, thủ tục lập và giao kế hoạch đầu tư công trung hạn và hàng năm</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>ALL, QUYET_TOAN, TAI_CHINH, TV-09, XD-01</t>
+          <t>ALL, DAU_TU_CONG, TV-01, TV-02, TV-03</t>
         </is>
       </c>
       <c r="M64" s="8" t="inlineStr"/>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -4805,32 +4805,32 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>24/2024/TT-BTC</t>
+          <t>99/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 96/2021/TT-BTC quy định về hệ thống mẫu biểu hồ sơ quyết toán vốn đầu tư công dự án hoàn thành</t>
+          <t>Quy định về quản lý, thanh toán, quyết toán dự án sử dụng vốn đầu tư công</t>
         </is>
       </c>
       <c r="F65" s="13" t="inlineStr">
         <is>
-          <t>Bộ Tài chính</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>19/04/2024</t>
+          <t>11/11/2021</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>05/06/2024</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="J65" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi Thông tư 96/2021/TT-BTC</t>
+          <t>Thay thế Nghị định 11/2020/NĐ-CP và Thông tư 10/2020/TT-BTC</t>
         </is>
       </c>
       <c r="K65" s="10" t="inlineStr">
         <is>
-          <t>Cập nhật quy trình kiểm toán độc lập và thẩm tra quyết toán vốn đầu tư công hiện hành</t>
+          <t>Nghị định xương sống về thẩm tra, phê duyệt quyết toán vốn đầu tư công dự án hoàn thành</t>
         </is>
       </c>
       <c r="L65" s="10" t="inlineStr">
@@ -4856,7 +4856,7 @@
       <c r="M65" s="15" t="inlineStr"/>
       <c r="N65" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -4866,37 +4866,37 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Phòng cháy chữa cháy</t>
+          <t>Quyết toán vốn</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>136/2020/NĐ-CP</t>
+          <t>96/2021/TT-BTC</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Phòng cháy và chữa cháy và Luật sửa đổi, bổ sung một số điều của Luật Phòng cháy và chữa cháy</t>
+          <t>Quy định về hệ thống mẫu biểu hồ sơ quyết toán vốn đầu tư công dự án hoàn thành</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Tài chính</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>24/11/2020</t>
+          <t>11/11/2021</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>10/01/2021</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
@@ -4906,23 +4906,23 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>Được sửa đổi, bổ sung bởi Nghị định 50/2024/NĐ-CP</t>
+          <t>Được sửa đổi, bổ sung bởi Thông tư 24/2024/TT-BTC</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>Quy định danh mục công trình phải thẩm duyệt thiết kế PCCC và nghiệm thu PCCC trước khi đưa vào sử dụng</t>
+          <t>Ban hành toàn bộ mẫu biểu Báo cáo quyết toán A-B, Báo cáo quyết toán hoàn thành</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>PCCC, TV-02, TV-03, TV-04, TV-05, XD-01</t>
+          <t>ALL, QUYET_TOAN, TAI_CHINH, TV-09, XD-01</t>
         </is>
       </c>
       <c r="M66" s="8" t="inlineStr"/>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -4932,37 +4932,37 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Phòng cháy chữa cháy</t>
+          <t>Quyết toán vốn</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>50/2024/NĐ-CP</t>
+          <t>24/2024/TT-BTC</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 136/2020/NĐ-CP và Nghị định số 83/2017/NĐ-CP</t>
+          <t>Sửa đổi, bổ sung một số điều của Thông tư số 96/2021/TT-BTC quy định về hệ thống mẫu biểu hồ sơ quyết toán vốn đầu tư công dự án hoàn thành</t>
         </is>
       </c>
       <c r="F67" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Tài chính</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
         <is>
-          <t>10/05/2024</t>
+          <t>19/04/2024</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>15/05/2024</t>
+          <t>05/06/2024</t>
         </is>
       </c>
       <c r="I67" s="7" t="inlineStr">
@@ -4972,23 +4972,23 @@
       </c>
       <c r="J67" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi Nghị định 136/2020/NĐ-CP</t>
+          <t>Sửa đổi Thông tư 96/2021/TT-BTC</t>
         </is>
       </c>
       <c r="K67" s="10" t="inlineStr">
         <is>
-          <t>Phân cấp thẩm quyền thẩm duyệt PCCC và cắt giảm danh mục công trình phải thẩm duyệt</t>
+          <t>Cập nhật quy trình kiểm toán độc lập và thẩm tra quyết toán vốn đầu tư công hiện hành</t>
         </is>
       </c>
       <c r="L67" s="10" t="inlineStr">
         <is>
-          <t>PCCC, TV-02, TV-03, TV-04, TV-05, XD-01</t>
+          <t>ALL, QUYET_TOAN, TAI_CHINH, TV-09, XD-01</t>
         </is>
       </c>
       <c r="M67" s="15" t="inlineStr"/>
       <c r="N67" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -4998,37 +4998,37 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Quy chuẩn PCCC</t>
+          <t>Phòng cháy chữa cháy</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>06:2022/BXD</t>
+          <t>136/2020/NĐ-CP</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Ban hành QCVN 06:2022/BXD Quy chuẩn kỹ thuật quốc gia về An toàn cháy cho nhà và công trình</t>
+          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Phòng cháy và chữa cháy và Luật sửa đổi, bổ sung một số điều của Luật Phòng cháy và chữa cháy</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>30/11/2022</t>
+          <t>24/11/2020</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>16/01/2023</t>
+          <t>10/01/2021</t>
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>Được sửa đổi bởi Thông tư 09/2023/TT-BXD (Sửa đổi 1:2023 QCVN 06:2022/BXD)</t>
+          <t>Được sửa đổi, bổ sung bởi Nghị định 50/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>Quy chuẩn bắt buộc áp dụng khi lập hồ sơ thiết kế BVTC công trình (TV-04, TV-05, XD-01)</t>
+          <t>Quy định danh mục công trình phải thẩm duyệt thiết kế PCCC và nghiệm thu PCCC trước khi đưa vào sử dụng</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
@@ -5054,7 +5054,7 @@
       <c r="M68" s="8" t="inlineStr"/>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -5064,37 +5064,37 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>Bảo vệ Môi trường</t>
+          <t>Phòng cháy chữa cháy</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>72/2020/QH14</t>
+          <t>50/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>Luật Bảo vệ môi trường năm 2020</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 136/2020/NĐ-CP và Nghị định số 83/2017/NĐ-CP</t>
         </is>
       </c>
       <c r="F69" s="13" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
-          <t>17/11/2020</t>
+          <t>10/05/2024</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>15/05/2024</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr">
@@ -5104,23 +5104,23 @@
       </c>
       <c r="J69" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Luật Bảo vệ môi trường 2014</t>
+          <t>Sửa đổi Nghị định 136/2020/NĐ-CP</t>
         </is>
       </c>
       <c r="K69" s="10" t="inlineStr">
         <is>
-          <t>Luật nền tảng về Đánh giá tác động môi trường (ĐTM), Giấy phép môi trường và Đăng ký môi trường</t>
+          <t>Phân cấp thẩm quyền thẩm duyệt PCCC và cắt giảm danh mục công trình phải thẩm duyệt</t>
         </is>
       </c>
       <c r="L69" s="10" t="inlineStr">
         <is>
-          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
+          <t>PCCC, TV-02, TV-03, TV-04, TV-05, XD-01</t>
         </is>
       </c>
       <c r="M69" s="15" t="inlineStr"/>
       <c r="N69" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -5130,37 +5130,37 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Bảo vệ Môi trường</t>
+          <t>Quy chuẩn PCCC</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Quy chuẩn</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>08/2022/NĐ-CP</t>
+          <t>QCVN 06:2022/BXD</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Bảo vệ môi trường</t>
+          <t>Quy chuẩn kỹ thuật quốc gia về An toàn cháy cho nhà và công trình (ban hành kèm Thông tư 06/2022/TT-BXD)</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>10/01/2022</t>
+          <t>30/11/2022</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>10/01/2022</t>
+          <t>16/01/2023</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr">
@@ -5170,23 +5170,23 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>Được sửa đổi, bổ sung bởi Nghị định 05/2025/NĐ-CP và Nghị định 48/2026/NĐ-CP</t>
+          <t>Được sửa đổi bởi Thông tư 09/2023/TT-BXD (Sửa đổi 1:2023 QCVN 06:2022/BXD)</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>Quy định phân nhóm dự án đầu tư theo tiêu chí môi trường để lập ĐTM hoặc đăng ký môi trường</t>
+          <t>Quy chuẩn bắt buộc áp dụng khi lập hồ sơ thiết kế BVTC công trình (TV-04, TV-05, XD-01)</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
+          <t>PCCC, TV-02, TV-03, TV-04, TV-05, XD-01</t>
         </is>
       </c>
       <c r="M70" s="8" t="inlineStr"/>
       <c r="N70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -5201,32 +5201,32 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>05/2025/NĐ-CP</t>
+          <t>72/2020/QH14</t>
         </is>
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP quy định chi tiết một số điều của Luật Bảo vệ môi trường</t>
+          <t>Luật Bảo vệ môi trường năm 2020</t>
         </is>
       </c>
       <c r="F71" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>08/01/2025</t>
+          <t>17/11/2020</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>01/03/2025</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="J71" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi Nghị định 08/2022/NĐ-CP</t>
+          <t>Thay thế Luật Bảo vệ môi trường 2014</t>
         </is>
       </c>
       <c r="K71" s="10" t="inlineStr">
         <is>
-          <t>Đơn giản hóa thủ tục cấp giấy phép môi trường và đăng ký môi trường cho dự án xây dựng</t>
+          <t>Luật nền tảng về Đánh giá tác động môi trường (ĐTM), Giấy phép môi trường và Đăng ký môi trường</t>
         </is>
       </c>
       <c r="L71" s="10" t="inlineStr">
@@ -5252,7 +5252,7 @@
       <c r="M71" s="15" t="inlineStr"/>
       <c r="N71" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -5272,12 +5272,12 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>48/2026/NĐ-CP</t>
+          <t>08/2022/NĐ-CP</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của các Nghị định quy định chi tiết Luật Bảo vệ môi trường</t>
+          <t>Quy định chi tiết một số điều của Luật Bảo vệ môi trường</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>10/01/2022</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>10/01/2022</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi Nghị định 08/2022/NĐ-CP</t>
+          <t>Được sửa đổi, bổ sung bởi Nghị định 05/2025/NĐ-CP và Nghị định 48/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>Cập nhật quy chuẩn kỹ thuật quốc gia về môi trường trong thi công xây dựng</t>
+          <t>Quy định phân nhóm dự án đầu tư theo tiêu chí môi trường để lập ĐTM hoặc đăng ký môi trường</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
@@ -5318,7 +5318,7 @@
       <c r="M72" s="8" t="inlineStr"/>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -5333,17 +5333,17 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Nghị quyết</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>66.19/2026/NQ-CP</t>
+          <t>05/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>Nghị quyết về việc tháo gỡ khó khăn, vướng mắc trong thực hiện thủ tục môi trường cho các dự án đầu tư công</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP quy định chi tiết một số điều của Luật Bảo vệ môi trường</t>
         </is>
       </c>
       <c r="F73" s="13" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>15/03/2026</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>15/03/2026</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="J73" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Sửa đổi Nghị định 08/2022/NĐ-CP</t>
         </is>
       </c>
       <c r="K73" s="10" t="inlineStr">
         <is>
-          <t>Cơ chế đặc thù tháo gỡ thủ tục đăng ký môi trường đối với dự án cải tạo, sửa chữa doanh trại</t>
+          <t>Đơn giản hóa thủ tục cấp giấy phép môi trường và phân cấp thẩm quyền thẩm định ĐTM</t>
         </is>
       </c>
       <c r="L73" s="10" t="inlineStr">
@@ -5384,7 +5384,7 @@
       <c r="M73" s="15" t="inlineStr"/>
       <c r="N73" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -5394,37 +5394,37 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Chi thường xuyên &amp; Tài sản công</t>
+          <t>Bảo vệ Môi trường</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>15/2017/QH14</t>
+          <t>48/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Luật Quản lý, sử dụng tài sản công</t>
+          <t>Sửa đổi, bổ sung một số điều của các Nghị định quy định chi tiết Luật Bảo vệ môi trường</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>21/06/2017</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="I74" s="7" t="inlineStr">
@@ -5434,23 +5434,23 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Luật Quản lý tài sản nhà nước 2008</t>
+          <t>Sửa đổi Nghị định 08/2022/NĐ-CP</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>Chế độ quản lý, bảo dưỡng, nâng cấp và sử dụng tài sản công trong các cơ quan, đơn vị</t>
+          <t>Bãi bỏ cấp đổi GPMT, cho phép lập ĐTM cuốn chiếu theo từng giai đoạn dự án</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
+          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
         </is>
       </c>
       <c r="M74" s="8" t="inlineStr"/>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -5460,22 +5460,22 @@
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>Chi thường xuyên &amp; Tài sản công</t>
+          <t>Bảo vệ Môi trường</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Nghị quyết</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>151/2017/NĐ-CP</t>
+          <t>66.19/2026/NQ-CP</t>
         </is>
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
+          <t>Nghị quyết về việc tháo gỡ khó khăn, vướng mắc trong thực hiện thủ tục môi trường cho các dự án đầu tư công</t>
         </is>
       </c>
       <c r="F75" s="13" t="inlineStr">
@@ -5485,12 +5485,12 @@
       </c>
       <c r="G75" s="11" t="inlineStr">
         <is>
-          <t>26/12/2017</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="I75" s="7" t="inlineStr">
@@ -5500,23 +5500,23 @@
       </c>
       <c r="J75" s="10" t="inlineStr">
         <is>
-          <t>Được sửa đổi, bổ sung bởi Nghị định 114/2024/NĐ-CP và Nghị định 186/2025/NĐ-CP</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K75" s="10" t="inlineStr">
         <is>
-          <t>Quy trình sử dụng tài sản công, sửa chữa và bảo dưỡng tài sản</t>
+          <t>Cơ chế đặc thù tháo gỡ thủ tục đăng ký môi trường đối với dự án cải tạo, sửa chữa doanh trại</t>
         </is>
       </c>
       <c r="L75" s="10" t="inlineStr">
         <is>
-          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
+          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
         </is>
       </c>
       <c r="M75" s="15" t="inlineStr"/>
       <c r="N75" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -5531,32 +5531,32 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>114/2024/NĐ-CP</t>
+          <t>15/2017/QH14</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 151/2017/NĐ-CP quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
+          <t>Luật Quản lý, sử dụng tài sản công</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>15/09/2024</t>
+          <t>21/06/2017</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>30/10/2024</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="I76" s="7" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi Nghị định 151/2017/NĐ-CP</t>
+          <t>Thay thế Luật Quản lý tài sản nhà nước 2008</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>Phân cấp thẩm quyền bảo dưỡng, sửa chữa tài sản công trong các đơn vị dự toán</t>
+          <t>Chế độ quản lý, bảo dưỡng, nâng cấp và sử dụng tài sản công trong các cơ quan, đơn vị</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
@@ -5582,7 +5582,7 @@
       <c r="M76" s="8" t="inlineStr"/>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -5602,12 +5602,12 @@
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>186/2025/NĐ-CP</t>
+          <t>151/2017/NĐ-CP</t>
         </is>
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 151/2017/NĐ-CP về quản lý, sử dụng tài sản công</t>
+          <t>Quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
         </is>
       </c>
       <c r="F77" s="13" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="G77" s="11" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>26/12/2017</t>
         </is>
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>01/08/2025</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="I77" s="7" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="J77" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi Nghị định 151/2017/NĐ-CP</t>
+          <t>Được sửa đổi, bổ sung bởi Nghị định 114/2024/NĐ-CP và Nghị định 186/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="K77" s="10" t="inlineStr">
         <is>
-          <t>Hướng dẫn cụ thể về trình tự phê duyệt dự toán sửa chữa, cải tạo tài sản công</t>
+          <t>Quy trình sử dụng tài sản công, sửa chữa và bảo dưỡng tài sản</t>
         </is>
       </c>
       <c r="L77" s="10" t="inlineStr">
@@ -5648,7 +5648,7 @@
       <c r="M77" s="15" t="inlineStr"/>
       <c r="N77" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -5668,12 +5668,12 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>138/2024/NĐ-CP</t>
+          <t>114/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Quy định việc sử dụng kinh phí chi thường xuyên ngân sách nhà nước để thực hiện mua sắm tài sản, trang thiết bị; cải tạo, nâng cấp, mở rộng, xây dựng mới hạng mục công trình trong các dự án đã đầu tư xây dựng</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 151/2017/NĐ-CP quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>24/10/2024</t>
+          <t>15/09/2024</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>24/10/2024</t>
+          <t>30/10/2024</t>
         </is>
       </c>
       <c r="I78" s="7" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>Được sửa đổi, bổ sung bởi Nghị định 98/2025/NĐ-CP và Nghị định 104/2026/NĐ-CP</t>
+          <t>Sửa đổi Nghị định 151/2017/NĐ-CP</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>Nghị định xương sống cho phép dùng nguồn chi thường xuyên để sửa chữa, cải tạo công trình dưới 15 tỷ đồng</t>
+          <t>Phân cấp thẩm quyền bảo dưỡng, sửa chữa tài sản công trong các đơn vị dự toán</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
@@ -5714,7 +5714,7 @@
       <c r="M78" s="8" t="inlineStr"/>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -5734,12 +5734,12 @@
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>98/2025/NĐ-CP</t>
+          <t>186/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="E79" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 138/2024/NĐ-CP về sử dụng kinh phí chi thường xuyên ngân sách nhà nước</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 151/2017/NĐ-CP về quản lý, sử dụng tài sản công</t>
         </is>
       </c>
       <c r="F79" s="13" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="G79" s="11" t="inlineStr">
         <is>
-          <t>12/05/2025</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>01/08/2025</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="J79" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi Nghị định 138/2024/NĐ-CP</t>
+          <t>Sửa đổi Nghị định 151/2017/NĐ-CP</t>
         </is>
       </c>
       <c r="K79" s="10" t="inlineStr">
         <is>
-          <t>Phân cấp thẩm quyền quyết định dự toán mua sắm, cải tạo tài sản cho Thủ trưởng đơn vị dự toán</t>
+          <t>Hướng dẫn cụ thể về trình tự phê duyệt dự toán sửa chữa, cải tạo tài sản công</t>
         </is>
       </c>
       <c r="L79" s="10" t="inlineStr">
@@ -5780,7 +5780,7 @@
       <c r="M79" s="15" t="inlineStr"/>
       <c r="N79" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -5800,12 +5800,12 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>104/2026/NĐ-CP</t>
+          <t>138/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 138/2024/NĐ-CP về quản lý và thanh toán kinh phí chi thường xuyên sửa chữa cơ sở vật chất</t>
+          <t>Quy định việc sử dụng kinh phí chi thường xuyên ngân sách nhà nước để thực hiện mua sắm tài sản, trang thiết bị; cải tạo, nâng cấp, mở rộng, xây dựng mới hạng mục công trình trong các dự án đã đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
@@ -5815,38 +5815,38 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>24/10/2024</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>24/10/2024</t>
+        </is>
+      </c>
+      <c r="I80" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi Nghị định 138/2024/NĐ-CP</t>
+          <t>Bị thay thế bởi Nghị định 98/2025/NĐ-CP và Nghị định 104/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>Quy định quy trình giải ngân kinh phí chi thường xuyên tại Kho bạc Nhà nước</t>
+          <t>Nghị định nền tảng cho phép dùng nguồn chi thường xuyên để sửa chữa, cải tạo công trình dưới 15 tỷ đồng</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
+          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01, LICHSU</t>
         </is>
       </c>
       <c r="M80" s="8" t="inlineStr"/>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -5861,32 +5861,32 @@
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>65/2021/TT-BTC</t>
+          <t>98/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
         <is>
-          <t>Quy định về lập dự toán, quản lý, sử dụng và quyết toán kinh phí bảo dưỡng, sửa chữa tài sản công</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 138/2024/NĐ-CP về sử dụng kinh phí chi thường xuyên ngân sách nhà nước</t>
         </is>
       </c>
       <c r="F81" s="13" t="inlineStr">
         <is>
-          <t>Bộ Tài chính</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
         <is>
-          <t>29/07/2021</t>
+          <t>12/05/2025</t>
         </is>
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>15/09/2021</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="I81" s="7" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="J81" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 92/2017/TT-BTC</t>
+          <t>Thay thế Nghị định 138/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="K81" s="10" t="inlineStr">
         <is>
-          <t>Hướng dẫn chi tiết định mức lập dự toán chi thường xuyên sửa chữa cơ sở vật chất, doanh trại</t>
+          <t>Phân cấp thẩm quyền quyết định dự toán mua sắm, cải tạo tài sản cho Thủ trưởng đơn vị dự toán</t>
         </is>
       </c>
       <c r="L81" s="10" t="inlineStr">
@@ -5912,7 +5912,7 @@
       <c r="M81" s="15" t="inlineStr"/>
       <c r="N81" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Thể thức Văn bản</t>
+          <t>Chi thường xuyên &amp; Tài sản công</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>30/2020/NĐ-CP</t>
+          <t>104/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Về công tác văn thư</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 138/2024/NĐ-CP và Nghị định 98/2025/NĐ-CP về quản lý và thanh toán kinh phí chi thường xuyên sửa chữa cơ sở vật chất</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
@@ -5947,12 +5947,12 @@
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>05/03/2020</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>05/03/2020</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="I82" s="7" t="inlineStr">
@@ -5962,23 +5962,23 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 110/2004/NĐ-CP</t>
+          <t>Sửa đổi Nghị định 98/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>Quy chuẩn thể thức văn bản hành chính (Tờ trình, Quyết định, Biên bản, font Times New Roman 13pt/14pt)</t>
+          <t>Quy định quy trình giải ngân kinh phí chi thường xuyên tại Kho bạc Nhà nước</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>ALL, THE_THUC, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
+          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
         </is>
       </c>
       <c r="M82" s="8" t="inlineStr"/>
       <c r="N82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -5988,37 +5988,37 @@
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>Đối tác công tư</t>
+          <t>Chi thường xuyên &amp; Tài sản công</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>64/2020/QH14</t>
+          <t>65/2021/TT-BTC</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>Luật Đầu tư theo phương thức đối tác công tư (PPP)</t>
+          <t>Quy định về lập dự toán, quản lý, sử dụng và quyết toán kinh phí bảo dưỡng, sửa chữa tài sản công</t>
         </is>
       </c>
       <c r="F83" s="13" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Bộ Tài chính</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>18/06/2020</t>
+          <t>29/07/2021</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
+          <t>15/09/2021</t>
         </is>
       </c>
       <c r="I83" s="7" t="inlineStr">
@@ -6028,23 +6028,23 @@
       </c>
       <c r="J83" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Thay thế Thông tư 92/2017/TT-BTC</t>
         </is>
       </c>
       <c r="K83" s="10" t="inlineStr">
         <is>
-          <t>Căn cứ pháp lý cho các dự án đầu tư theo hình thức đối tác công tư</t>
+          <t>Hướng dẫn chi tiết định mức lập dự toán chi thường xuyên sửa chữa cơ sở vật chất, doanh trại</t>
         </is>
       </c>
       <c r="L83" s="10" t="inlineStr">
         <is>
-          <t>PPP, DAU_TU_CONG</t>
+          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
         </is>
       </c>
       <c r="M83" s="15" t="inlineStr"/>
       <c r="N83" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Đối tác công tư</t>
+          <t>Thể thức Văn bản</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -6064,12 +6064,12 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>35/2021/NĐ-CP</t>
+          <t>30/2020/NĐ-CP</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết và hướng dẫn thi hành Luật Đầu tư theo phương thức đối tác công tư</t>
+          <t>Về công tác văn thư</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
@@ -6079,12 +6079,12 @@
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>29/03/2021</t>
+          <t>05/03/2020</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>29/03/2021</t>
+          <t>05/03/2020</t>
         </is>
       </c>
       <c r="I84" s="7" t="inlineStr">
@@ -6094,23 +6094,23 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Thay thế Nghị định 110/2004/NĐ-CP</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết quy trình lập dự án và lựa chọn nhà đầu tư PPP</t>
+          <t>Quy chuẩn thể thức văn bản hành chính (Tờ trình, Quyết định, Biên bản, font Times New Roman 13pt/14pt)</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>PPP, DAU_TU_CONG</t>
+          <t>ALL, THE_THUC, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
         </is>
       </c>
       <c r="M84" s="8" t="inlineStr"/>
       <c r="N84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>Đầu tư kinh doanh</t>
+          <t>Đối tác công tư</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>61/2020/QH14</t>
+          <t>64/2020/QH14</t>
         </is>
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>Luật Đầu tư năm 2020 (sửa đổi bởi Luật số 57/2024/QH15)</t>
+          <t>Luật Đầu tư theo phương thức đối tác công tư (PPP)</t>
         </is>
       </c>
       <c r="F85" s="13" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
-          <t>17/06/2020</t>
+          <t>18/06/2020</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
@@ -6160,23 +6160,23 @@
       </c>
       <c r="J85" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Luật Đầu tư 2014</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K85" s="10" t="inlineStr">
         <is>
-          <t>Căn cứ pháp lý về thủ tục chấp thuận chủ trương đầu tư dự án</t>
+          <t>Căn cứ pháp lý cho các dự án đầu tư theo hình thức đối tác công tư</t>
         </is>
       </c>
       <c r="L85" s="10" t="inlineStr">
         <is>
-          <t>DAU_TU_KINH_DOANH</t>
+          <t>PPP, DAU_TU_CONG</t>
         </is>
       </c>
       <c r="M85" s="15" t="inlineStr"/>
       <c r="N85" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Đầu tư kinh doanh</t>
+          <t>Đối tác công tư</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>31/2021/NĐ-CP</t>
+          <t>35/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết và hướng dẫn thi hành một số điều của Luật Đầu tư</t>
+          <t>Quy định chi tiết và hướng dẫn thi hành Luật Đầu tư theo phương thức đối tác công tư</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>26/03/2021</t>
+          <t>29/03/2021</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>26/03/2021</t>
+          <t>29/03/2021</t>
         </is>
       </c>
       <c r="I86" s="7" t="inlineStr">
@@ -6231,18 +6231,18 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết trình tự, thủ tục đầu tư và ưu đãi đầu tư</t>
+          <t>Quy định chi tiết quy trình lập dự án và lựa chọn nhà đầu tư PPP</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>DAU_TU_KINH_DOANH</t>
+          <t>PPP, DAU_TU_CONG</t>
         </is>
       </c>
       <c r="M86" s="8" t="inlineStr"/>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>
@@ -6252,37 +6252,37 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>Quốc phòng &amp; Doanh trại</t>
+          <t>Đầu tư kinh doanh</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Văn bản Hợp nhất</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>15/VBHN-BQP</t>
+          <t>61/2020/QH14</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
-          <t>Văn bản hợp nhất Thông tư quy định về phân cấp, ủy quyền quyết định chủ trương đầu tư và dự án đầu tư công trong Bộ Quốc phòng</t>
+          <t>Luật Đầu tư năm 2020 (sửa đổi bởi Luật số 57/2024/QH15)</t>
         </is>
       </c>
       <c r="F87" s="13" t="inlineStr">
         <is>
-          <t>Bộ Quốc phòng</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr">
         <is>
-          <t>15/03/2025</t>
+          <t>17/06/2020</t>
         </is>
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>15/03/2025</t>
+          <t>01/01/2021</t>
         </is>
       </c>
       <c r="I87" s="7" t="inlineStr">
@@ -6292,23 +6292,155 @@
       </c>
       <c r="J87" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Thay thế Luật Đầu tư 2014</t>
         </is>
       </c>
       <c r="K87" s="10" t="inlineStr">
         <is>
-          <t>Văn bản hợp nhất hướng dẫn công tác quản lý dự án và phân cấp trong Bộ Quốc phòng</t>
+          <t>Căn cứ pháp lý về thủ tục chấp thuận chủ trương đầu tư dự án</t>
         </is>
       </c>
       <c r="L87" s="10" t="inlineStr">
         <is>
-          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+          <t>DAU_TU_KINH_DOANH</t>
         </is>
       </c>
       <c r="M87" s="15" t="inlineStr"/>
       <c r="N87" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:14</t>
+          <t>2026-08-21 16:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="26" customHeight="1">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>Đầu tư kinh doanh</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>Nghị định</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>31/2021/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>Quy định chi tiết và hướng dẫn thi hành một số điều của Luật Đầu tư</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>Chính phủ</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>26/03/2021</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>26/03/2021</t>
+        </is>
+      </c>
+      <c r="I88" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>Quy định chi tiết trình tự, thủ tục đầu tư và ưu đãi đầu tư</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>DAU_TU_KINH_DOANH</t>
+        </is>
+      </c>
+      <c r="M88" s="8" t="inlineStr"/>
+      <c r="N88" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="26" customHeight="1">
+      <c r="A89" s="9" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>Quốc phòng &amp; Doanh trại</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="inlineStr">
+        <is>
+          <t>Văn bản Hợp nhất</t>
+        </is>
+      </c>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>15/VBHN-BQP</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>Văn bản hợp nhất Thông tư quy định về phân cấp, ủy quyền quyết định chủ trương đầu tư và dự án đầu tư công trong Bộ Quốc phòng</t>
+        </is>
+      </c>
+      <c r="F89" s="13" t="inlineStr">
+        <is>
+          <t>Bộ Quốc phòng</t>
+        </is>
+      </c>
+      <c r="G89" s="11" t="inlineStr">
+        <is>
+          <t>15/03/2025</t>
+        </is>
+      </c>
+      <c r="H89" s="11" t="inlineStr">
+        <is>
+          <t>15/03/2025</t>
+        </is>
+      </c>
+      <c r="I89" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
+        </is>
+      </c>
+      <c r="J89" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K89" s="10" t="inlineStr">
+        <is>
+          <t>Văn bản hợp nhất hướng dẫn công tác quản lý dự án và phân cấp trong Bộ Quốc phòng</t>
+        </is>
+      </c>
+      <c r="L89" s="10" t="inlineStr">
+        <is>
+          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+        </is>
+      </c>
+      <c r="M89" s="15" t="inlineStr"/>
+      <c r="N89" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:26</t>
         </is>
       </c>
     </row>

--- a/Kho_Can_Cu_Phap_Ly.xlsx
+++ b/Kho_Can_Cu_Phap_Ly.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N89"/>
+  <dimension ref="A1:N95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -698,7 +698,7 @@
       <c r="M2" s="8" t="inlineStr"/>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       <c r="M3" s="15" t="inlineStr"/>
       <c r="N3" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>44/2015/NĐ-CP</t>
+          <t>178/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số nội dung về quy hoạch xây dựng</t>
+          <t>Quy định chi tiết một số điều của Luật Quy hoạch đô thị và nông thôn</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -799,12 +799,12 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>06/05/2015</t>
+          <t>30/06/2025</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>30/06/2015</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Được sửa đổi, bổ sung bởi Nghị định số 72/2019/NĐ-CP và Nghị định số 35/2023/NĐ-CP</t>
+          <t>Thay thế Nghị định 44/2015/NĐ-CP và Nghị định 72/2019/NĐ-CP</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Quy định trình tự, thủ tục lập và phê duyệt Quy hoạch chi tiết và Quy hoạch Tổng mặt bằng công trình (Áp dụng VBHN 13/VBHN-BXD)</t>
+          <t>Quy định chi tiết trình tự lập, thẩm định và phê duyệt quy hoạch đô thị và nông thôn mới nhất</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -830,7 +830,7 @@
       <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -845,58 +845,58 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>04/2022/TT-BXD</t>
+          <t>44/2015/NĐ-CP</t>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>Quy định về hồ sơ nhiệm vụ và hồ sơ đồ án quy hoạch xây dựng vùng liên huyện, quy hoạch xây dựng vùng huyện, quy hoạch đô thị, quy hoạch xây dựng khu chức năng và quy hoạch nông thôn</t>
+          <t>Quy định chi tiết một số nội dung về quy hoạch xây dựng</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>24/10/2022</t>
+          <t>06/05/2015</t>
         </is>
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>30/06/2015</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 12/2016/TT-BXD và Thông tư 02/2017/TT-BXD</t>
+          <t>Bị thay thế bởi Nghị định 178/2025/NĐ-CP từ ngày 01/07/2025</t>
         </is>
       </c>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>Quy định thành phần hồ sơ bản vẽ, thuyết minh và quy cách đồ án quy hoạch Tổng mặt bằng tỷ lệ 1/500 gói TV-01</t>
+          <t>Đã hết hiệu lực từ 01/07/2025 khi Luật Quy hoạch ĐT&amp;NT 47/2024 có hiệu lực</t>
         </is>
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
-          <t>QUY_HOACH, TV-01, HO_SO_QUY_HOACH</t>
+          <t>ALL, QUY_HOACH, TV-01, TV-02, QLDA, LICHSU</t>
         </is>
       </c>
       <c r="M5" s="15" t="inlineStr"/>
       <c r="N5" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>20/2019/TT-BXD</t>
+          <t>04/2022/TT-BXD</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Hướng dẫn xác định, quản lý chi phí quy hoạch xây dựng và quy hoạch đô thị</t>
+          <t>Quy định về hồ sơ nhiệm vụ và hồ sơ đồ án quy hoạch xây dựng vùng liên huyện, quy hoạch xây dựng vùng huyện, quy hoạch đô thị, quy hoạch xây dựng khu chức năng và quy hoạch nông thôn</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>31/12/2019</t>
+          <t>24/10/2022</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>15/02/2020</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
@@ -946,23 +946,23 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 01/2013/TT-BXD</t>
+          <t>Thay thế Thông tư 12/2016/TT-BXD và Thông tư 02/2017/TT-BXD</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Căn cứ lập dự toán chi phí gói thầu TV-01 Tư vấn lập quy hoạch Tổng mặt bằng tỷ lệ 1/500</t>
+          <t>Quy định thành phần hồ sơ bản vẽ, thuyết minh và quy cách đồ án quy hoạch Tổng mặt bằng tỷ lệ 1/500 gói TV-01</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>QUY_HOACH, CHI_PHI_QUY_HOACH, DU_TOAN, TV-01</t>
+          <t>QUY_HOACH, TV-01, HO_SO_QUY_HOACH</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr"/>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -972,22 +972,22 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Quy chuẩn Xây dựng</t>
+          <t>Quy hoạch Xây dựng</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Quy chuẩn</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>QCVN 01:2021/BXD</t>
+          <t>20/2019/TT-BXD</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>Quy chuẩn kỹ thuật quốc gia về Quy hoạch xây dựng (ban hành kèm Thông tư 01/2021/TT-BXD)</t>
+          <t>Hướng dẫn xác định, quản lý chi phí quy hoạch xây dựng và quy hoạch đô thị</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -997,38 +997,38 @@
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>19/05/2021</t>
+          <t>31/12/2019</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>05/07/2021</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>15/02/2020</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J7" s="10" t="inlineStr">
         <is>
-          <t>Thay thế QCVN 01:2019/BXD ban hành kèm Thông tư 22/2019/TT-BXD</t>
+          <t>Hết hiệu lực từ 01/07/2025 theo Luật Quy hoạch 47/2024/QH15</t>
         </is>
       </c>
       <c r="K7" s="10" t="inlineStr">
         <is>
-          <t>Quy chuẩn bắt buộc áp dụng cho gói TV-01 về mật độ xây dựng, khoảng lùi công trình, khoảng cách an toàn PCCC, chỉ giới đường đỏ</t>
+          <t>Đã hết hiệu lực</t>
         </is>
       </c>
       <c r="L7" s="10" t="inlineStr">
         <is>
-          <t>QCVN, QUY_HOACH, TV-01, TV-02, TV-04, XD-01</t>
+          <t>QUY_HOACH, CHI_PHI_QUY_HOACH, DU_TOAN, TV-01, LICHSU</t>
         </is>
       </c>
       <c r="M7" s="15" t="inlineStr"/>
       <c r="N7" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -1038,37 +1038,37 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Khảo sát &amp; Đo đạc</t>
+          <t>Quy chuẩn Xây dựng</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Quy chuẩn</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>27/2018/QH14</t>
+          <t>QCVN 01:2021/BXD</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Luật Đo đạc và bản đồ năm 2018</t>
+          <t>Quy chuẩn kỹ thuật quốc gia về Quy hoạch xây dựng (ban hành kèm Thông tư 01/2021/TT-BXD)</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>14/06/2018</t>
+          <t>19/05/2021</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>05/07/2021</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
@@ -1078,23 +1078,23 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Thay thế QCVN 01:2019/BXD ban hành kèm Thông tư 22/2019/TT-BXD</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Căn cứ pháp lý cho công tác đo đạc khảo sát địa hình, trắc địa công trình phục vụ lập quy hoạch TV-01 và khảo sát TV-02</t>
+          <t>Quy chuẩn bắt buộc áp dụng cho gói TV-01 về mật độ xây dựng, khoảng lùi công trình, khoảng cách an toàn PCCC, chỉ giới đường đỏ</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>KHAO_SAT, DO_DAC, TV-01, TV-02, XD-01</t>
+          <t>QCVN, QUY_HOACH, TV-01, TV-02, TV-04, XD-01</t>
         </is>
       </c>
       <c r="M8" s="8" t="inlineStr"/>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -1109,32 +1109,32 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>27/2019/NĐ-CP</t>
+          <t>27/2018/QH14</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Đo đạc và bản đồ</t>
+          <t>Luật Đo đạc và bản đồ năm 2018</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>13/03/2019</t>
+          <t>14/06/2018</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>01/05/2019</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="J9" s="10" t="inlineStr">
         <is>
-          <t>Được sửa đổi, bổ sung bởi Nghị định 136/2021/NĐ-CP</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
-          <t>Quy định quy chuẩn đo đạc bản đồ địa hình tỷ lệ 1/500 phục vụ lập quy hoạch TMB và thiết kế xây dựng</t>
+          <t>Căn cứ pháp lý cho công tác đo đạc khảo sát địa hình, trắc địa công trình phục vụ lập quy hoạch TV-01 và khảo sát TV-02</t>
         </is>
       </c>
       <c r="L9" s="10" t="inlineStr">
@@ -1160,7 +1160,7 @@
       <c r="M9" s="15" t="inlineStr"/>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -1170,37 +1170,37 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Xây dựng &amp; Quản lý dự án</t>
+          <t>Khảo sát &amp; Đo đạc</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>135/2025/QH15</t>
+          <t>27/2019/NĐ-CP</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Luật Xây dựng năm 2025</t>
+          <t>Quy định chi tiết một số điều của Luật Đo đạc và bản đồ</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>10/12/2025</t>
+          <t>13/03/2019</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>01/05/2019</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
@@ -1210,23 +1210,23 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Luật Xây dựng 50/2014/QH13 và Luật 62/2020/QH14</t>
+          <t>Được sửa đổi, bổ sung bởi Nghị định 136/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Luật khung hiện hành chi phối toàn bộ hoạt động đầu tư xây dựng công trình, thẩm định và cấp phép</t>
+          <t>Quy định quy chuẩn đo đạc bản đồ địa hình tỷ lệ 1/500 phục vụ lập quy hoạch TMB và thiết kế xây dựng</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>ALL, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+          <t>KHAO_SAT, DO_DAC, TV-01, TV-02, XD-01</t>
         </is>
       </c>
       <c r="M10" s="8" t="inlineStr"/>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>50/2014/QH13</t>
+          <t>135/2025/QH15</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>Luật Xây dựng năm 2014</t>
+          <t>Luật Xây dựng năm 2025</t>
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr">
@@ -1261,38 +1261,38 @@
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>18/06/2014</t>
+          <t>10/12/2025</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>01/01/2015</t>
-        </is>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Luật Xây dựng số 135/2025/QH15 từ ngày 01/07/2026</t>
+          <t>Thay thế Luật Xây dựng 50/2014/QH13 và Luật 62/2020/QH14</t>
         </is>
       </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>Dự án đã phê duyệt trước 01/07/2026 thực hiện theo quy định chuyển tiếp của Luật 135/2025</t>
+          <t>Luật khung hiện hành chi phối toàn bộ hoạt động đầu tư xây dựng công trình, thẩm định và cấp phép</t>
         </is>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
-          <t>ALL, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01, LICHSU</t>
+          <t>ALL, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M11" s="15" t="inlineStr"/>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>62/2020/QH14</t>
+          <t>50/2014/QH13</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Luật sửa đổi, bổ sung một số điều của Luật Xây dựng năm 2020</t>
+          <t>Luật Xây dựng năm 2014</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -1327,12 +1327,12 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>17/06/2020</t>
+          <t>18/06/2014</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
+          <t>01/01/2015</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Hết hiệu lực từ 01/07/2026</t>
+          <t>Dự án đã phê duyệt trước 01/07/2026 thực hiện theo quy định chuyển tiếp của Luật 135/2025</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       <c r="M12" s="8" t="inlineStr"/>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -1373,58 +1373,58 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>217/2026/NĐ-CP</t>
+          <t>62/2020/QH14</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Xây dựng về quản lý hoạt động đầu tư xây dựng</t>
+          <t>Luật sửa đổi, bổ sung một số điều của Luật Xây dựng năm 2020</t>
         </is>
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>17/06/2020</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>01/01/2021</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 15/2021/NĐ-CP, Nghị định 175/2024/NĐ-CP và Nghị định 35/2023/NĐ-CP</t>
+          <t>Bị thay thế bởi Luật Xây dựng số 135/2025/QH15 từ ngày 01/07/2026</t>
         </is>
       </c>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t>Nghị định xương sống hiện hành về thẩm tra, thẩm định thiết kế, dự toán và quản lý dự án xây dựng</t>
+          <t>Hết hiệu lực từ 01/07/2026</t>
         </is>
       </c>
       <c r="L13" s="10" t="inlineStr">
         <is>
-          <t>ALL, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+          <t>ALL, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01, LICHSU</t>
         </is>
       </c>
       <c r="M13" s="15" t="inlineStr"/>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>175/2024/NĐ-CP</t>
+          <t>217/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 15/2021/NĐ-CP quy định chi tiết một số nội dung về quản lý dự án đầu tư xây dựng</t>
+          <t>Quy định chi tiết một số điều của Luật Xây dựng về quản lý hoạt động đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -1459,38 +1459,38 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>30/12/2024</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>31/12/2024</t>
-        </is>
-      </c>
-      <c r="I14" s="14" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 217/2026/NĐ-CP từ ngày 01/07/2026</t>
+          <t>Thay thế Nghị định 15/2021/NĐ-CP, Nghị định 175/2024/NĐ-CP và Nghị định 35/2023/NĐ-CP</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Hết hiệu lực từ 01/07/2026</t>
+          <t>Nghị định xương sống hiện hành về thẩm tra, thẩm định thiết kế, dự toán và quản lý dự án xây dựng</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>ALL, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01, LICHSU</t>
+          <t>ALL, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr"/>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>15/2021/NĐ-CP</t>
+          <t>175/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số nội dung về quản lý dự án đầu tư xây dựng</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 15/2021/NĐ-CP quy định chi tiết một số nội dung về quản lý dự án đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
@@ -1525,12 +1525,12 @@
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>03/03/2021</t>
+          <t>30/12/2024</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>03/03/2021</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="I15" s="14" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="J15" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 175/2024/NĐ-CP và Nghị định 217/2026/NĐ-CP</t>
+          <t>Bị thay thế bởi Nghị định 217/2026/NĐ-CP từ ngày 01/07/2026</t>
         </is>
       </c>
       <c r="K15" s="10" t="inlineStr">
         <is>
-          <t>Hết hiệu lực toàn bộ</t>
+          <t>Hết hiệu lực từ 01/07/2026</t>
         </is>
       </c>
       <c r="L15" s="10" t="inlineStr">
@@ -1556,7 +1556,7 @@
       <c r="M15" s="15" t="inlineStr"/>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>35/2023/NĐ-CP</t>
+          <t>15/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của các Nghị định thuộc lĩnh vực quản lý nhà nước của Bộ Xây dựng</t>
+          <t>Quy định chi tiết một số nội dung về quản lý dự án đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -1591,38 +1591,38 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>20/06/2023</t>
+          <t>03/03/2021</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>20/06/2023</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>03/03/2021</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bị thay thế bởi Nghị định 175/2024/NĐ-CP và Nghị định 217/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Cắt giảm, đơn giản hóa thủ tục hành chính trong lập quy hoạch và quản lý dự án xây dựng</t>
+          <t>Hết hiệu lực toàn bộ</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>ALL, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+          <t>ALL, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01, LICHSU</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr"/>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -1632,37 +1632,37 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>An toàn Lao động</t>
+          <t>Xây dựng &amp; Quản lý dự án</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>84/2015/QH13</t>
+          <t>35/2023/NĐ-CP</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>Luật An toàn, vệ sinh lao động năm 2015</t>
+          <t>Sửa đổi, bổ sung một số điều của các Nghị định thuộc lĩnh vực quản lý nhà nước của Bộ Xây dựng</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>25/06/2015</t>
+          <t>20/06/2023</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>01/07/2016</t>
+          <t>20/06/2023</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
@@ -1672,23 +1672,23 @@
       </c>
       <c r="J17" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Được sửa đổi một phần bởi NĐ 210/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="K17" s="10" t="inlineStr">
         <is>
-          <t>Quy định biện pháp an toàn lao động bắt buộc trong thi công xây dựng và giám sát công trường</t>
+          <t>Cắt giảm, đơn giản hóa thủ tục hành chính trong lập quy hoạch và quản lý dự án xây dựng</t>
         </is>
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>AN_TOAN_LAO_DONG, TV-08, XD-01</t>
+          <t>ALL, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M17" s="15" t="inlineStr"/>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Đấu thầu qua mạng</t>
+          <t>An toàn Lao động</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>22/2023/QH15</t>
+          <t>84/2015/QH13</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Luật Đấu thầu năm 2023</t>
+          <t>Luật An toàn, vệ sinh lao động năm 2015</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>23/06/2023</t>
+          <t>25/06/2015</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/07/2016</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
@@ -1738,23 +1738,23 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Luật Đấu thầu 43/2013/QH13</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Luật đấu thầu nền tảng chi phối toàn bộ các gói thầu TV, XD, PTV của dự án</t>
+          <t>Quy định biện pháp an toàn lao động bắt buộc trong thi công xây dựng và giám sát công trường</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
+          <t>AN_TOAN_LAO_DONG, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M18" s="8" t="inlineStr"/>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1774,12 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>57/2024/QH15</t>
+          <t>22/2023/QH15</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>Luật sửa đổi, bổ sung một số điều của Luật Quy hoạch, Luật Đầu tư, Luật Đầu tư theo phương thức đối tác công tư và Luật Đấu thầu</t>
+          <t>Luật Đấu thầu năm 2023</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>29/11/2024</t>
+          <t>23/06/2023</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>15/01/2025</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="J19" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung Luật Đấu thầu 22/2023/QH15</t>
+          <t>Thay thế Luật Đấu thầu 43/2013/QH13</t>
         </is>
       </c>
       <c r="K19" s="10" t="inlineStr">
         <is>
-          <t>Mở rộng phân cấp thẩm quyền chỉ định thầu, rút ngắn thời gian chuẩn bị E-HSDT và mua sắm công</t>
+          <t>Luật đấu thầu nền tảng chi phối toàn bộ các gói thầu TV, XD, PTV của dự án</t>
         </is>
       </c>
       <c r="L19" s="10" t="inlineStr">
@@ -1820,7 +1820,7 @@
       <c r="M19" s="15" t="inlineStr"/>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>90/2025/QH15</t>
+          <t>57/2024/QH15</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Luật sửa đổi, bổ sung một số điều của Luật Đấu thầu, Luật Đầu tư công, Luật Quản lý tài sản công</t>
+          <t>Luật sửa đổi, bổ sung một số điều của Luật Quy hoạch, Luật Đầu tư, Luật Đầu tư theo phương thức đối tác công tư và Luật Đấu thầu</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -1855,12 +1855,12 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>25/06/2025</t>
+          <t>29/11/2024</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>15/01/2025</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi Luật Đấu thầu 22/2023/QH15</t>
+          <t>Sửa đổi, bổ sung Luật Đấu thầu 22/2023/QH15</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân cấp triệt để thẩm quyền lựa chọn nhà thầu cho Chủ đầu tư và nâng hạn mức chỉ định thầu</t>
+          <t>Mở rộng phân cấp thẩm quyền chỉ định thầu, rút ngắn thời gian chuẩn bị E-HSDT và mua sắm công</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -1886,7 +1886,7 @@
       <c r="M20" s="8" t="inlineStr"/>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -1906,12 +1906,12 @@
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>43/2013/QH13</t>
+          <t>90/2025/QH15</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>Luật Đấu thầu năm 2013</t>
+          <t>Luật sửa đổi, bổ sung một số điều của Luật Đấu thầu, Luật Đầu tư công, Luật Quản lý tài sản công</t>
         </is>
       </c>
       <c r="F21" s="13" t="inlineStr">
@@ -1921,38 +1921,38 @@
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>26/11/2013</t>
+          <t>25/06/2025</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>01/07/2014</t>
-        </is>
-      </c>
-      <c r="I21" s="14" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+          <t>01/07/2025</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J21" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Luật Đấu thầu 22/2023/QH15</t>
+          <t>Sửa đổi Luật Đấu thầu 22/2023/QH15</t>
         </is>
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
-          <t>Hết hiệu lực từ 01/01/2024</t>
+          <t>Phân cấp triệt để thẩm quyền lựa chọn nhà thầu cho Chủ đầu tư và nâng hạn mức chỉ định thầu</t>
         </is>
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, LICHSU</t>
+          <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
         </is>
       </c>
       <c r="M21" s="15" t="inlineStr"/>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -1967,58 +1967,58 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>214/2025/NĐ-CP</t>
+          <t>43/2013/QH13</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Đấu thầu về lựa chọn nhà thầu</t>
+          <t>Luật Đấu thầu năm 2013</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>04/08/2025</t>
+          <t>26/11/2013</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>04/08/2025</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>01/07/2014</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 24/2024/NĐ-CP và Nghị định 63/2014/NĐ-CP</t>
+          <t>Bị thay thế bởi Luật Đấu thầu 22/2023/QH15</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Nghị định xương sống hiện hành về quy trình chỉ định thầu rút gọn, đấu thầu rộng rãi qua mạng</t>
+          <t>Hết hiệu lực từ 01/01/2024</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
+          <t>ALL, DAU_THAU, LICHSU</t>
         </is>
       </c>
       <c r="M22" s="8" t="inlineStr"/>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>24/2024/NĐ-CP</t>
+          <t>214/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
@@ -2053,38 +2053,38 @@
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>27/02/2024</t>
+          <t>04/08/2025</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>27/02/2024</t>
-        </is>
-      </c>
-      <c r="I23" s="14" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+          <t>04/08/2025</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 214/2025/NĐ-CP từ ngày 04/08/2025</t>
+          <t>Thay thế Nghị định 24/2024/NĐ-CP và Nghị định 63/2014/NĐ-CP</t>
         </is>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng chuyển tiếp cho các gói thầu phát hành E-HSMT trước 04/08/2025</t>
+          <t>Nghị định xương sống hiện hành về quy trình chỉ định thầu rút gọn, đấu thầu rộng rãi qua mạng</t>
         </is>
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01, LICHSU</t>
+          <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
         </is>
       </c>
       <c r="M23" s="15" t="inlineStr"/>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>63/2014/NĐ-CP</t>
+          <t>24/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết thi hành một số điều của Luật Đấu thầu về lựa chọn nhà thầu</t>
+          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Đấu thầu về lựa chọn nhà thầu</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>26/06/2014</t>
+          <t>27/02/2024</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>15/08/2014</t>
+          <t>27/02/2024</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
@@ -2134,23 +2134,23 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 24/2024/NĐ-CP</t>
+          <t>Bị thay thế bởi Nghị định 214/2025/NĐ-CP từ ngày 04/08/2025</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>Hết hiệu lực từ 27/02/2024</t>
+          <t>Áp dụng chuyển tiếp cho các gói thầu phát hành E-HSMT trước 04/08/2025</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, LICHSU</t>
+          <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01, LICHSU</t>
         </is>
       </c>
       <c r="M24" s="8" t="inlineStr"/>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -2165,58 +2165,58 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>79/2025/TT-BTC</t>
+          <t>63/2014/NĐ-CP</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>Hướng dẫn việc cung cấp, đăng tải thông tin về đấu thầu và mẫu hồ sơ đấu thầu trên Hệ thống mạng đấu thầu quốc gia</t>
+          <t>Quy định chi tiết thi hành một số điều của Luật Đấu thầu về lựa chọn nhà thầu</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>Bộ Tài chính</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>20/07/2025</t>
+          <t>26/06/2014</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>04/08/2025</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>15/08/2014</t>
+        </is>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 06/2024/TT-BKHĐT và Thông tư 22/2024/TT-BKHĐT</t>
+          <t>Bị thay thế bởi Nghị định 24/2024/NĐ-CP, Bị thay thế bởi 24/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="K25" s="10" t="inlineStr">
         <is>
-          <t>Ban hành toàn bộ biểu mẫu E-HSMT xây lắp, tư vấn, phi tư vấn, E-HSYC chỉ định thầu hiện hành</t>
+          <t>Hết hiệu lực từ 27/02/2024</t>
         </is>
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
+          <t>ALL, DAU_THAU, LICHSU</t>
         </is>
       </c>
       <c r="M25" s="15" t="inlineStr"/>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>06/2024/TT-BKHĐT</t>
+          <t>79/2025/TT-BTC</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -2246,43 +2246,43 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>Bộ Kế hoạch và Đầu tư</t>
+          <t>Bộ Tài chính</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>20/07/2025</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
-        </is>
-      </c>
-      <c r="I26" s="14" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+          <t>04/08/2025</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 79/2025/TT-BTC</t>
+          <t>Thay thế Thông tư 06/2024/TT-BKHĐT và Thông tư 22/2024/TT-BKHĐT</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>Hết hiệu lực từ 04/08/2025</t>
+          <t>Ban hành toàn bộ biểu mẫu E-HSMT xây lắp, tư vấn, phi tư vấn, E-HSYC chỉ định thầu hiện hành</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, E_HSMT, LICHSU</t>
+          <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
         </is>
       </c>
       <c r="M26" s="8" t="inlineStr"/>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -2302,53 +2302,53 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>80/2025/TT-BTC</t>
+          <t>06/2024/TT-BKHĐT</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết mẫu hồ sơ yêu cầu, báo cáo đánh giá trong lựa chọn nhà thầu mua sắm công</t>
+          <t>Hướng dẫn việc cung cấp, đăng tải thông tin về đấu thầu và mẫu hồ sơ đấu thầu trên Hệ thống mạng đấu thầu quốc gia</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>Bộ Tài chính</t>
+          <t>Bộ Kế hoạch và Đầu tư</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>22/07/2025</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>08/08/2025</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>26/04/2024</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J27" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 07/2024/TT-BKHĐT và Thông tư 23/2024/TT-BKHĐT</t>
+          <t>Bị thay thế bởi Thông tư 79/2025/TT-BTC</t>
         </is>
       </c>
       <c r="K27" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng lập HSYC và đánh giá hồ sơ đề xuất gói thầu mua sắm hàng hóa, doanh cụ</t>
+          <t>Hết hiệu lực từ 04/08/2025</t>
         </is>
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>ALL, DAU_THAU, E_HSMT, TV-06, XD-01</t>
+          <t>ALL, DAU_THAU, E_HSMT, LICHSU</t>
         </is>
       </c>
       <c r="M27" s="15" t="inlineStr"/>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -2358,37 +2358,37 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Chi phí &amp; Định mức</t>
+          <t>Đấu thầu qua mạng</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>206/2026/NĐ-CP</t>
+          <t>80/2025/TT-BTC</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Xây dựng về quản lý chi phí đầu tư xây dựng</t>
+          <t>Quy định chi tiết mẫu hồ sơ yêu cầu, báo cáo đánh giá trong lựa chọn nhà thầu mua sắm công</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Tài chính</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/07/2025</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>08/08/2025</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
@@ -2398,23 +2398,23 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 10/2021/NĐ-CP</t>
+          <t>Thay thế Thông tư 07/2024/TT-BKHĐT và Thông tư 23/2024/TT-BKHĐT</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>Quy định phương pháp lập và quản lý Tổng mức đầu tư, Dự toán xây dựng công trình hiện hành</t>
+          <t>Áp dụng lập HSYC và đánh giá hồ sơ đề xuất gói thầu mua sắm hàng hóa, doanh cụ</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
+          <t>ALL, DAU_THAU, E_HSMT, TV-06, XD-01</t>
         </is>
       </c>
       <c r="M28" s="8" t="inlineStr"/>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>10/2021/NĐ-CP</t>
+          <t>206/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>Về quản lý chi phí đầu tư xây dựng</t>
+          <t>Quy định chi tiết một số điều của Luật Xây dựng về quản lý chi phí đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
@@ -2449,38 +2449,38 @@
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>09/02/2021</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>09/02/2021</t>
-        </is>
-      </c>
-      <c r="I29" s="14" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J29" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 206/2026/NĐ-CP từ ngày 01/07/2026</t>
+          <t>Thay thế Nghị định 10/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="K29" s="10" t="inlineStr">
         <is>
-          <t>Dự án đã phê duyệt dự toán trước 01/07/2026 thực hiện theo điều khoản chuyển tiếp của NĐ 206</t>
+          <t>Quy định phương pháp lập và quản lý Tổng mức đầu tư, Dự toán xây dựng công trình hiện hành</t>
         </is>
       </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
-          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01, LICHSU</t>
+          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
         </is>
       </c>
       <c r="M29" s="15" t="inlineStr"/>
       <c r="N29" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -2495,58 +2495,58 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>38/2026/TT-BXD</t>
+          <t>10/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Ban hành hệ thống định mức dự toán xây dựng công trình và định mức chi phí tư vấn đầu tư xây dựng</t>
+          <t>Về quản lý chi phí đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>09/02/2021</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>09/02/2021</t>
+        </is>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 12/2021/TT-BXD và Thông tư 09/2024/TT-BXD</t>
+          <t>Bị thay thế bởi Nghị định 206/2026/NĐ-CP từ ngày 01/07/2026</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>Hệ thống định mức xây dựng và tỷ lệ % chi phí quản lý dự án, tư vấn thiết kế, giám sát mới nhất</t>
+          <t>Dự án đã phê duyệt dự toán trước 01/07/2026 thực hiện theo điều khoản chuyển tiếp của NĐ 206</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>ALL, DINH_MUC, DU_TOAN, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-08, TV-09, XD-01</t>
+          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01, LICHSU</t>
         </is>
       </c>
       <c r="M30" s="8" t="inlineStr"/>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -2566,12 +2566,12 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>12/2021/TT-BXD</t>
+          <t>36/2026/TT-BXD</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>Ban hành định mức xây dựng</t>
+          <t>Hướng dẫn một số nội dung xác định và quản lý chi phí đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr">
@@ -2581,38 +2581,38 @@
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>31/08/2021</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>15/10/2021</t>
-        </is>
-      </c>
-      <c r="I31" s="14" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J31" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 38/2026/TT-BXD từ ngày 01/07/2026</t>
+          <t>Thay thế Thông tư 11/2021/TT-BXD, Thông tư 14/2023/TT-BXD và Thông tư 01/2025/TT-BXD</t>
         </is>
       </c>
       <c r="K31" s="10" t="inlineStr">
         <is>
-          <t>Hết hiệu lực từ 01/07/2026</t>
+          <t>Quy định cơ cấu chi phí xây dựng, chi phí gián tiếp, chi phí chung trong dự toán mới nhất</t>
         </is>
       </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
-          <t>ALL, DINH_MUC, DU_TOAN, LICHSU</t>
+          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
         </is>
       </c>
       <c r="M31" s="15" t="inlineStr"/>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -2632,12 +2632,12 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>09/2024/TT-BXD</t>
+          <t>38/2026/TT-BXD</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số định mức xây dựng ban hành tại Thông tư số 12/2021/TT-BXD</t>
+          <t>Ban hành hệ thống định mức dự toán xây dựng công trình và định mức chi phí tư vấn đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -2647,38 +2647,38 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>30/08/2024</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>15/10/2024</t>
-        </is>
-      </c>
-      <c r="I32" s="14" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 38/2026/TT-BXD</t>
+          <t>Thay thế Thông tư 12/2021/TT-BXD và Thông tư 09/2024/TT-BXD</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>Hết hiệu lực từ 01/07/2026</t>
+          <t>Hệ thống định mức xây dựng và tỷ lệ % chi phí quản lý dự án, tư vấn thiết kế, giám sát mới nhất</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>ALL, DINH_MUC, DU_TOAN, LICHSU</t>
+          <t>ALL, DINH_MUC, DU_TOAN, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-08, TV-09, XD-01</t>
         </is>
       </c>
       <c r="M32" s="8" t="inlineStr"/>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -2698,12 +2698,12 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>01/2025/TT-BXD</t>
+          <t>12/2021/TT-BXD</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 11/2021/TT-BXD hướng dẫn một số nội dung xác định và quản lý chi phí đầu tư xây dựng</t>
+          <t>Ban hành định mức xây dựng</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
@@ -2713,38 +2713,38 @@
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>15/01/2025</t>
+          <t>31/08/2021</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>01/03/2025</t>
-        </is>
-      </c>
-      <c r="I33" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>15/10/2021</t>
+        </is>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J33" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung Thông tư 11/2021/TT-BXD</t>
+          <t>Bị thay thế bởi Thông tư 38/2026/TT-BXD từ ngày 01/07/2026</t>
         </is>
       </c>
       <c r="K33" s="10" t="inlineStr">
         <is>
-          <t>Cập nhật phương pháp lập và quản lý chi phí đầu tư xây dựng hiện hành</t>
+          <t>Hết hiệu lực từ 01/07/2026</t>
         </is>
       </c>
       <c r="L33" s="10" t="inlineStr">
         <is>
-          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
+          <t>ALL, DINH_MUC, DU_TOAN, LICHSU</t>
         </is>
       </c>
       <c r="M33" s="15" t="inlineStr"/>
       <c r="N33" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -2764,12 +2764,12 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>11/2021/TT-BXD</t>
+          <t>09/2024/TT-BXD</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Hướng dẫn một số nội dung xác định và quản lý chi phí đầu tư xây dựng</t>
+          <t>Sửa đổi, bổ sung một số định mức xây dựng ban hành tại Thông tư số 12/2021/TT-BXD</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -2779,38 +2779,38 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>31/08/2021</t>
+          <t>30/08/2024</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>15/10/2021</t>
-        </is>
-      </c>
-      <c r="I34" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>15/10/2024</t>
+        </is>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>Được sửa đổi, bổ sung bởi Thông tư 14/2023/TT-BXD và Thông tư 01/2025/TT-BXD</t>
+          <t>Bị thay thế bởi Thông tư 38/2026/TT-BXD</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>Quy định cơ cấu chi phí xây dựng, chi phí gián tiếp, chi phí chung trong dự toán</t>
+          <t>Hết hiệu lực từ 01/07/2026</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
+          <t>ALL, DINH_MUC, DU_TOAN, LICHSU</t>
         </is>
       </c>
       <c r="M34" s="8" t="inlineStr"/>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>14/2023/TT-BXD</t>
+          <t>01/2025/TT-BXD</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
@@ -2845,38 +2845,38 @@
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>29/12/2023</t>
+          <t>15/01/2025</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>15/02/2024</t>
-        </is>
-      </c>
-      <c r="I35" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>01/03/2025</t>
+        </is>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J35" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi Thông tư 11/2021/TT-BXD</t>
+          <t>Bị thay thế bởi Thông tư 36/2026/TT-BXD</t>
         </is>
       </c>
       <c r="K35" s="10" t="inlineStr">
         <is>
-          <t>Cập nhật hệ số chi phí chung, chi phí nhà tạm</t>
+          <t>Hết hiệu lực từ 01/07/2026</t>
         </is>
       </c>
       <c r="L35" s="10" t="inlineStr">
         <is>
-          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
+          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, LICHSU</t>
         </is>
       </c>
       <c r="M35" s="15" t="inlineStr"/>
       <c r="N35" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -2896,12 +2896,12 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>13/2021/TT-BXD</t>
+          <t>11/2021/TT-BXD</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Hướng dẫn phương pháp xác định các chỉ tiêu kinh tế kỹ thuật và đo bóc khối lượng công trình</t>
+          <t>Hướng dẫn một số nội dung xác định và quản lý chi phí đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -2919,30 +2919,30 @@
           <t>15/10/2021</t>
         </is>
       </c>
-      <c r="I36" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bị thay thế bởi Thông tư 36/2026/TT-BXD từ ngày 01/07/2026</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>Quy chuẩn phương pháp đo bóc khối lượng phục vụ lập dự toán và nghiệm thu công trình</t>
+          <t>Hết hiệu lực từ 01/07/2026</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>ALL, DU_TOAN, DO_BOC_KHOI_LUONG, TV-04, TV-05, XD-01</t>
+          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, LICHSU</t>
         </is>
       </c>
       <c r="M36" s="8" t="inlineStr"/>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -2952,22 +2952,22 @@
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Suất vốn đầu tư</t>
+          <t>Chi phí &amp; Định mức</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Quyết định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>425/QĐ-BXD</t>
+          <t>14/2023/TT-BXD</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>Công bố Suất vốn đầu tư xây dựng công trình và giá xây dựng tổng hợp bộ phận kết cấu công trình</t>
+          <t>Sửa đổi, bổ sung một số điều của Thông tư số 11/2021/TT-BXD hướng dẫn một số nội dung xác định và quản lý chi phí đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F37" s="13" t="inlineStr">
@@ -2977,38 +2977,38 @@
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>29/12/2023</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
-        </is>
-      </c>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>15/02/2024</t>
+        </is>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J37" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Quyết định 510/QĐ-BXD</t>
+          <t>Bị thay thế bởi Thông tư 36/2026/TT-BXD từ ngày 01/07/2026</t>
         </is>
       </c>
       <c r="K37" s="10" t="inlineStr">
         <is>
-          <t>Suất vốn đầu tư hiện hành phục vụ tính Tổng mức đầu tư BCNCKT (FS/BKTKT gói TV-02, TV-03)</t>
+          <t>Hết hiệu lực từ 01/07/2026</t>
         </is>
       </c>
       <c r="L37" s="10" t="inlineStr">
         <is>
-          <t>SUAT_VON_DAU_TU, TMDT, TV-01, TV-02, TV-03, TV-04</t>
+          <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, LICHSU</t>
         </is>
       </c>
       <c r="M37" s="15" t="inlineStr"/>
       <c r="N37" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -3018,22 +3018,22 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Suất vốn đầu tư</t>
+          <t>Chi phí &amp; Định mức</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Quyết định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>510/QĐ-BXD</t>
+          <t>13/2021/TT-BXD</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Công bố Suất vốn đầu tư xây dựng công trình và giá xây dựng tổng hợp bộ phận kết cấu công trình năm 2023</t>
+          <t>Hướng dẫn phương pháp xác định các chỉ tiêu kinh tế kỹ thuật và đo bóc khối lượng công trình</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
@@ -3043,38 +3043,38 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>19/05/2024</t>
+          <t>31/08/2021</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>19/05/2024</t>
-        </is>
-      </c>
-      <c r="I38" s="14" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+          <t>15/10/2021</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Quyết định 425/QĐ-BXD</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>Hết hiệu lực</t>
+          <t>Quy chuẩn phương pháp đo bóc khối lượng phục vụ lập dự toán và nghiệm thu công trình</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>SUAT_VON_DAU_TU, TMDT, LICHSU</t>
+          <t>ALL, DU_TOAN, DO_BOC_KHOI_LUONG, TV-04, TV-05, XD-01</t>
         </is>
       </c>
       <c r="M38" s="8" t="inlineStr"/>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -3084,37 +3084,37 @@
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Quốc phòng &amp; Doanh trại</t>
+          <t>Suất vốn đầu tư</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Quyết định</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>101/2026/TT-BQP</t>
+          <t>425/QĐ-BXD</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết và biện pháp thực hiện một số nội dung Luật Xây dựng thuộc phạm vi quản lý của Bộ Quốc phòng</t>
+          <t>Công bố Suất vốn đầu tư xây dựng công trình và giá xây dựng tổng hợp bộ phận kết cấu công trình</t>
         </is>
       </c>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>Bộ Quốc phòng</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
@@ -3124,23 +3124,23 @@
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Thay thế Quyết định 510/QĐ-BXD</t>
         </is>
       </c>
       <c r="K39" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng cho các dự án đầu tư xây dựng công trình trong toàn Bộ Quốc phòng</t>
+          <t>Suất vốn đầu tư hiện hành phục vụ tính Tổng mức đầu tư BCNCKT (FS/BKTKT gói TV-02, TV-03)</t>
         </is>
       </c>
       <c r="L39" s="10" t="inlineStr">
         <is>
-          <t>ALL, BQP, QLDA, XD-01, TOAN_QUAN</t>
+          <t>SUAT_VON_DAU_TU, TMDT, TV-01, TV-02, TV-03, TV-04</t>
         </is>
       </c>
       <c r="M39" s="15" t="inlineStr"/>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -3150,63 +3150,63 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Quốc phòng &amp; Doanh trại</t>
+          <t>Suất vốn đầu tư</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Quyết định</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>102/2026/TT-BQP</t>
+          <t>510/QĐ-BXD</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Quy định và hướng dẫn về lập, thẩm định, quyết định, phân cấp quyết định chủ trương đầu tư, dự án đầu tư trong Bộ Quốc phòng</t>
+          <t>Công bố Suất vốn đầu tư xây dựng công trình và giá xây dựng tổng hợp bộ phận kết cấu công trình năm 2023</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>Bộ Quốc phòng</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>19/05/2024</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
-        </is>
-      </c>
-      <c r="I40" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>19/05/2024</t>
+        </is>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 128/2021/TT-BQP, Thông tư 73/2023/TT-BQP và Thông tư 120/2024/TT-BQP</t>
+          <t>Bị thay thế bởi Quyết định 425/QĐ-BXD</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>Văn bản xương sống về phân cấp, ủy quyền quyết định đầu tư và dự án đầu tư công mới nhất trong BQP</t>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+          <t>SUAT_VON_DAU_TU, TMDT, LICHSU</t>
         </is>
       </c>
       <c r="M40" s="8" t="inlineStr"/>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -3226,12 +3226,12 @@
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>128/2021/TT-BQP</t>
+          <t>101/2026/TT-BQP</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>Quy định phân cấp, ủy quyền quyết định chủ trương đầu tư và dự án đầu tư công trong Bộ Quốc phòng</t>
+          <t>Quy định chi tiết và biện pháp thực hiện một số nội dung Luật Xây dựng thuộc phạm vi quản lý của Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F41" s="13" t="inlineStr">
@@ -3241,38 +3241,38 @@
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>20/11/2021</t>
-        </is>
-      </c>
-      <c r="I41" s="14" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J41" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 101/2026/TT-BQP và Thông tư 102/2026/TT-BQP</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K41" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng phân cấp thẩm quyền đầu tư BQP giai đoạn 2021-2026</t>
+          <t>Áp dụng cho các dự án đầu tư xây dựng công trình trong toàn Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="L41" s="10" t="inlineStr">
         <is>
-          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01, LICHSU</t>
+          <t>ALL, BQP, QLDA, XD-01, TOAN_QUAN</t>
         </is>
       </c>
       <c r="M41" s="15" t="inlineStr"/>
       <c r="N41" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -3292,12 +3292,12 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>73/2023/TT-BQP</t>
+          <t>102/2026/TT-BQP</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 128/2021/TT-BQP ngày 01/10/2021 về quy định phân cấp, ủy quyền quyết định chủ trương đầu tư và dự án đầu tư công trong BQP</t>
+          <t>Quy định và hướng dẫn về lập, thẩm định, quyết định, phân cấp quyết định chủ trương đầu tư, dự án đầu tư trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -3307,38 +3307,38 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>05/10/2023</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>20/11/2023</t>
-        </is>
-      </c>
-      <c r="I42" s="14" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP</t>
+          <t>Thay thế Thông tư 128/2021/TT-BQP, Thông tư 73/2023/TT-BQP và Thông tư 120/2024/TT-BQP</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>Cập nhật phân cấp đầu tư BQP giai đoạn 2023-2026</t>
+          <t>Văn bản xương sống về phân cấp, ủy quyền quyết định đầu tư và dự án đầu tư công mới nhất trong BQP</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01, LICHSU</t>
+          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M42" s="8" t="inlineStr"/>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>120/2024/TT-BQP</t>
+          <t>128/2021/TT-BQP</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 128/2021/TT-BQP về phân cấp quản lý và thực hiện dự án đầu tư công trong Bộ Quốc phòng</t>
+          <t>Quy định phân cấp, ủy quyền quyết định chủ trương đầu tư và dự án đầu tư công trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F43" s="13" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>20/11/2021</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="J43" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP</t>
+          <t>Bị thay thế bởi Thông tư 101/2026/TT-BQP và Thông tư 102/2026/TT-BQP</t>
         </is>
       </c>
       <c r="K43" s="10" t="inlineStr">
         <is>
-          <t>Phân cấp phê duyệt thiết kế, dự toán BQP giai đoạn 2024-2026</t>
+          <t>Áp dụng phân cấp thẩm quyền đầu tư BQP giai đoạn 2021-2026</t>
         </is>
       </c>
       <c r="L43" s="10" t="inlineStr">
@@ -3404,7 +3404,7 @@
       <c r="M43" s="15" t="inlineStr"/>
       <c r="N43" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -3424,12 +3424,12 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>174/2021/TT-BQP</t>
+          <t>73/2023/TT-BQP</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Quy định về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng trong Bộ Quốc phòng</t>
+          <t>Sửa đổi, bổ sung một số điều của Thông tư số 128/2021/TT-BQP ngày 01/10/2021 về quy định phân cấp, ủy quyền quyết định chủ trương đầu tư và dự án đầu tư công trong BQP</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -3439,38 +3439,38 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>27/12/2021</t>
+          <t>05/10/2023</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>12/02/2022</t>
-        </is>
-      </c>
-      <c r="I44" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>20/11/2023</t>
+        </is>
+      </c>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>Được sửa đổi, bổ sung bởi Thông tư 24/2025/TT-BQP</t>
+          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>Quy chuẩn nghiệm thu và quản lý chất lượng công trình quân sự</t>
+          <t>Cập nhật phân cấp đầu tư BQP giai đoạn 2023-2026</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
+          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01, LICHSU</t>
         </is>
       </c>
       <c r="M44" s="8" t="inlineStr"/>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -3490,12 +3490,12 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>24/2025/TT-BQP</t>
+          <t>120/2024/TT-BQP</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 174/2021/TT-BQP về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng trong Bộ Quốc phòng</t>
+          <t>Sửa đổi, bổ sung một số điều của Thông tư số 128/2021/TT-BQP về phân cấp quản lý và thực hiện dự án đầu tư công trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F45" s="13" t="inlineStr">
@@ -3505,38 +3505,38 @@
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
-          <t>06/05/2025</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>20/06/2025</t>
-        </is>
-      </c>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>10/02/2025</t>
+        </is>
+      </c>
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J45" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung Thông tư 174/2021/TT-BQP về quản lý chất lượng công trình BQP</t>
+          <t>Bị thay thế bởi Thông tư 102/2026/TT-BQP</t>
         </is>
       </c>
       <c r="K45" s="10" t="inlineStr">
         <is>
-          <t>Quy chuẩn kiểm tra công tác nghiệm thu công trình quân sự đặc thù hiện hành</t>
+          <t>Phân cấp phê duyệt thiết kế, dự toán BQP giai đoạn 2024-2026</t>
         </is>
       </c>
       <c r="L45" s="10" t="inlineStr">
         <is>
-          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
+          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01, LICHSU</t>
         </is>
       </c>
       <c r="M45" s="15" t="inlineStr"/>
       <c r="N45" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -3556,12 +3556,12 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>36/2023/TT-BQP</t>
+          <t>174/2021/TT-BQP</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Ban hành Điều lệ Doanh trại Quân đội nhân dân Việt Nam</t>
+          <t>Quy định về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -3571,12 +3571,12 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>29/05/2023</t>
+          <t>27/12/2021</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>13/07/2023</t>
+          <t>12/02/2022</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
@@ -3586,23 +3586,23 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Điều lệ Doanh trại QĐNDVN năm 2002</t>
+          <t>Được sửa đổi, bổ sung bởi Thông tư 24/2025/TT-BQP</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>Điều lệ xương sống về quy hoạch tổng mặt bằng, bảo dưỡng, quản lý và sử dụng doanh trại</t>
+          <t>Quy chuẩn nghiệm thu và quản lý chất lượng công trình quân sự</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>BQP, DOANH_TRAI, TV-01, TV-02, TV-04, XD-01</t>
+          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M46" s="8" t="inlineStr"/>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -3622,12 +3622,12 @@
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>150/2018/TT-BQP</t>
+          <t>24/2025/TT-BQP</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>Quy định về tiêu chuẩn, định mức sử dụng máy móc, thiết bị văn phòng phổ biến thuộc phạm vi quản lý của Bộ Quốc phòng</t>
+          <t>Sửa đổi, bổ sung một số điều của Thông tư số 174/2021/TT-BQP về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F47" s="13" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
-          <t>11/10/2018</t>
+          <t>06/05/2025</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>26/11/2018</t>
+          <t>20/06/2025</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
@@ -3652,23 +3652,23 @@
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Quyết định 162/2002/QĐ-BQP</t>
+          <t>Sửa đổi, bổ sung Thông tư 174/2021/TT-BQP về quản lý chất lượng công trình BQP</t>
         </is>
       </c>
       <c r="K47" s="10" t="inlineStr">
         <is>
-          <t>Tiêu chuẩn định mức máy móc, thiết bị làm việc của cán bộ sĩ quan BQP (gói Doanh cụ XD-01)</t>
+          <t>Quy chuẩn kiểm tra công tác nghiệm thu công trình quân sự đặc thù hiện hành</t>
         </is>
       </c>
       <c r="L47" s="10" t="inlineStr">
         <is>
-          <t>BQP, DOANH_TRAI, TV-01, TV-02, TV-04, XD-01</t>
+          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M47" s="15" t="inlineStr"/>
       <c r="N47" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>94/2024/TT-BQP</t>
+          <t>36/2023/TT-BQP</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Nhà ở áp dụng trong Bộ Quốc phòng (Mẫu giấy tờ nhà ở công vụ và dự án nhà ở LLVT)</t>
+          <t>Ban hành Điều lệ Doanh trại Quân đội nhân dân Việt Nam</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>11/11/2024</t>
+          <t>29/05/2023</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>13/07/2023</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Thay thế Điều lệ Doanh trại QĐNDVN năm 2002</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng cho các dự án đầu tư xây dựng nhà ở cho lực lượng vũ trang thuộc BQP</t>
+          <t>Điều lệ xương sống về quy hoạch tổng mặt bằng, bảo dưỡng, quản lý và sử dụng doanh trại</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -3734,7 +3734,7 @@
       <c r="M48" s="8" t="inlineStr"/>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -3749,32 +3749,32 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Quyết định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>35/QĐ-TTg</t>
+          <t>150/2018/TT-BQP</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>Ban hành Danh mục bí mật Nhà nước trong lĩnh vực Quốc phòng</t>
+          <t>Quy định về tiêu chuẩn, định mức sử dụng máy móc, thiết bị văn phòng phổ biến thuộc phạm vi quản lý của Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F49" s="13" t="inlineStr">
         <is>
-          <t>Thủ tướng Chính phủ</t>
+          <t>Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>11/10/2018</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>26/11/2018</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
@@ -3784,23 +3784,23 @@
       </c>
       <c r="J49" s="10" t="inlineStr">
         <is>
-          <t>Quyết định số 12/QĐ-TTg</t>
+          <t>Thay thế Quyết định 162/2002/QĐ-BQP</t>
         </is>
       </c>
       <c r="K49" s="10" t="inlineStr">
         <is>
-          <t>Quy định bảo mật hồ sơ, tài liệu thiết kế công trình quân sự</t>
+          <t>Tiêu chuẩn định mức máy móc, thiết bị làm việc của cán bộ sĩ quan BQP (gói Doanh cụ XD-01)</t>
         </is>
       </c>
       <c r="L49" s="10" t="inlineStr">
         <is>
-          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+          <t>BQP, DOANH_TRAI, TV-01, TV-02, TV-04, XD-01</t>
         </is>
       </c>
       <c r="M49" s="15" t="inlineStr"/>
       <c r="N49" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -3810,37 +3810,37 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Chất lượng &amp; Nghiệm thu</t>
+          <t>Quốc phòng &amp; Doanh trại</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>06/2021/NĐ-CP</t>
+          <t>94/2024/TT-BQP</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số nội dung về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng</t>
+          <t>Quy định chi tiết một số điều của Luật Nhà ở áp dụng trong Bộ Quốc phòng (Mẫu giấy tờ nhà ở công vụ và dự án nhà ở LLVT)</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>26/01/2021</t>
+          <t>11/11/2024</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>26/01/2021</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
@@ -3850,23 +3850,23 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 46/2015/NĐ-CP</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>Xương sống về quản lý chất lượng thi công, nhật ký công trình và biên bản nghiệm thu hoàn thành</t>
+          <t>Áp dụng cho các dự án đầu tư xây dựng nhà ở cho lực lượng vũ trang thuộc BQP</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
+          <t>BQP, DOANH_TRAI, TV-01, TV-02, TV-04, XD-01</t>
         </is>
       </c>
       <c r="M50" s="8" t="inlineStr"/>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -3876,37 +3876,37 @@
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>Chất lượng &amp; Nghiệm thu</t>
+          <t>Quốc phòng &amp; Doanh trại</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Quyết định</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>10/2021/TT-BXD</t>
+          <t>35/QĐ-TTg</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr">
         <is>
-          <t>Hướng dẫn một số điều và biện pháp thi hành Nghị định số 06/2021/NĐ-CP và Nghị định số 15/2021/NĐ-CP</t>
+          <t>Ban hành Danh mục bí mật Nhà nước trong lĩnh vực Quốc phòng</t>
         </is>
       </c>
       <c r="F51" s="13" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Thủ tướng Chính phủ</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>25/08/2021</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>15/10/2021</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
@@ -3916,23 +3916,23 @@
       </c>
       <c r="J51" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Quyết định số 12/QĐ-TTg</t>
         </is>
       </c>
       <c r="K51" s="10" t="inlineStr">
         <is>
-          <t>Quy chuẩn đánh giá an toàn công trình, kiểm định và lập danh mục hồ sơ hoàn thành công trình</t>
+          <t>Quy định bảo mật hồ sơ, tài liệu thiết kế công trình quân sự</t>
         </is>
       </c>
       <c r="L51" s="10" t="inlineStr">
         <is>
-          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
+          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M51" s="15" t="inlineStr"/>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -3942,7 +3942,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Hợp đồng Xây dựng</t>
+          <t>Chất lượng &amp; Nghiệm thu</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>37/2015/NĐ-CP</t>
+          <t>207/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết về hợp đồng xây dựng</t>
+          <t>Quy định chi tiết một số nội dung về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>22/04/2015</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>15/06/2015</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
@@ -3982,23 +3982,23 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>Được sửa đổi, bổ sung bởi Nghị định 50/2021/NĐ-CP và Nghị định 35/2023/NĐ-CP</t>
+          <t>Thay thế Nghị định 06/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>Quy định tạm ứng, thanh toán, điều chỉnh giá và thanh lý hợp đồng xây dựng</t>
+          <t>Nghị định hiện hành chi phối quản lý chất lượng, nhật ký điện tử và nghiệm thu công trình</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>ALL, HOP_DONG, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
+          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M52" s="8" t="inlineStr"/>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>Hợp đồng Xây dựng</t>
+          <t>Chất lượng &amp; Nghiệm thu</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
@@ -4018,12 +4018,12 @@
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>50/2021/NĐ-CP</t>
+          <t>06/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 37/2015/NĐ-CP quy định chi tiết về hợp đồng xây dựng</t>
+          <t>Quy định chi tiết một số nội dung về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng</t>
         </is>
       </c>
       <c r="F53" s="13" t="inlineStr">
@@ -4033,38 +4033,38 @@
       </c>
       <c r="G53" s="11" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
+          <t>26/01/2021</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>01/04/2021</t>
-        </is>
-      </c>
-      <c r="I53" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>26/01/2021</t>
+        </is>
+      </c>
+      <c r="I53" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J53" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi Nghị định 37/2015/NĐ-CP</t>
+          <t>Bị thay thế bởi Nghị định 207/2026/NĐ-CP từ ngày 01/07/2026</t>
         </is>
       </c>
       <c r="K53" s="10" t="inlineStr">
         <is>
-          <t>Quy định bảo đảm thực hiện hợp đồng và điều chỉnh giá hợp đồng trọn gói, đơn giá</t>
+          <t>Hết hiệu lực từ 01/07/2026</t>
         </is>
       </c>
       <c r="L53" s="10" t="inlineStr">
         <is>
-          <t>ALL, HOP_DONG, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
+          <t>CHAT_LUONG, NGHIEM_THU, LICHSU</t>
         </is>
       </c>
       <c r="M53" s="15" t="inlineStr"/>
       <c r="N53" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Hợp đồng Xây dựng</t>
+          <t>Chất lượng &amp; Nghiệm thu</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>02/2023/TT-BXD</t>
+          <t>10/2021/TT-BXD</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Hướng dẫn một số nội dung về hợp đồng xây dựng</t>
+          <t>Hướng dẫn một số điều và biện pháp thi hành Nghị định số 06/2021/NĐ-CP và Nghị định số 15/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>03/03/2023</t>
+          <t>25/08/2021</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>20/04/2023</t>
+          <t>15/10/2021</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
@@ -4119,18 +4119,18 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>Ban hành mẫu hợp đồng tư vấn thiết kế, tư vấn giám sát và hợp đồng thi công xây dựng</t>
+          <t>Quy chuẩn đánh giá an toàn công trình, kiểm định và lập danh mục hồ sơ hoàn thành công trình (áp dụng phần còn phù hợp)</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>ALL, HOP_DONG, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
+          <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
         </is>
       </c>
       <c r="M54" s="8" t="inlineStr"/>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -4140,37 +4140,37 @@
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>Tiêu chuẩn Kỹ thuật</t>
+          <t>Hợp đồng Xây dựng</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Tiêu chuẩn</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>TCVN 9393:2012</t>
+          <t>210/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>Cọc - Phương pháp thử nghiệm hiện trường bằng tải trọng tĩnh ép dọc trục</t>
+          <t>Quy định chi tiết về hợp đồng xây dựng</t>
         </is>
       </c>
       <c r="F55" s="13" t="inlineStr">
         <is>
-          <t>Bộ Khoa học và Công nghệ</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>28/12/2012</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>28/12/2012</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
@@ -4180,23 +4180,23 @@
       </c>
       <c r="J55" s="10" t="inlineStr">
         <is>
-          <t>Thay thế TCXDVN 269:2002</t>
+          <t>Thay thế Nghị định 37/2015/NĐ-CP và Nghị định 50/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="K55" s="10" t="inlineStr">
         <is>
-          <t>Tiêu chuẩn kỹ thuật bắt buộc áp dụng cho gói thầu TV-07 Thí nghiệm nén tĩnh cọc</t>
+          <t>Nghị định xương sống hiện hành về hợp đồng xây dựng, tạm ứng, điều chỉnh giá và thanh lý hợp đồng</t>
         </is>
       </c>
       <c r="L55" s="10" t="inlineStr">
         <is>
-          <t>THI_NGHIEM_COC, TV-07, XD-01</t>
+          <t>ALL, HOP_DONG, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
         </is>
       </c>
       <c r="M55" s="15" t="inlineStr"/>
       <c r="N55" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -4206,63 +4206,63 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Tiêu chuẩn Kỹ thuật</t>
+          <t>Hợp đồng Xây dựng</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Tiêu chuẩn</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>TCVN 9363:2012</t>
+          <t>37/2015/NĐ-CP</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Khảo sát địa chất công trình cho nhà cao tầng</t>
+          <t>Quy định chi tiết về hợp đồng xây dựng</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>Bộ Khoa học và Công nghệ</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>28/12/2012</t>
+          <t>22/04/2015</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>28/12/2012</t>
-        </is>
-      </c>
-      <c r="I56" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>15/06/2015</t>
+        </is>
+      </c>
+      <c r="I56" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bị thay thế bởi Nghị định 210/2026/NĐ-CP từ ngày 01/07/2026</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>Tiêu chuẩn kỹ thuật cho công tác khoan khảo sát địa chất gói TV-02</t>
+          <t>Hết hiệu lực từ 01/07/2026; áp dụng chuyển tiếp cho các hợp đồng đã ký trước 01/07/2026</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>KHAO_SAT, TV-02</t>
+          <t>ALL, HOP_DONG, LICHSU</t>
         </is>
       </c>
       <c r="M56" s="8" t="inlineStr"/>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -4272,63 +4272,63 @@
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>Tiêu chuẩn Kỹ thuật</t>
+          <t>Hợp đồng Xây dựng</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Tiêu chuẩn</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>TCVN 9401:2012</t>
+          <t>50/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
         <is>
-          <t>Kỹ thuật đo và xử lý số liệu GPS trong trắc địa công trình</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 37/2015/NĐ-CP quy định chi tiết về hợp đồng xây dựng</t>
         </is>
       </c>
       <c r="F57" s="13" t="inlineStr">
         <is>
-          <t>Bộ Khoa học và Công nghệ</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>28/12/2012</t>
+          <t>01/04/2021</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>28/12/2012</t>
-        </is>
-      </c>
-      <c r="I57" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>01/04/2021</t>
+        </is>
+      </c>
+      <c r="I57" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J57" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bị thay thế bởi Nghị định 210/2026/NĐ-CP từ ngày 01/07/2026</t>
         </is>
       </c>
       <c r="K57" s="10" t="inlineStr">
         <is>
-          <t>Tiêu chuẩn kỹ thuật cho công tác đo đạc địa hình, định vị công trình gói TV-01</t>
+          <t>Hết hiệu lực từ 01/07/2026</t>
         </is>
       </c>
       <c r="L57" s="10" t="inlineStr">
         <is>
-          <t>DO_DAC, TV-01</t>
+          <t>ALL, HOP_DONG, LICHSU</t>
         </is>
       </c>
       <c r="M57" s="15" t="inlineStr"/>
       <c r="N57" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -4338,37 +4338,37 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Bảo hiểm Xây dựng</t>
+          <t>Hợp đồng Xây dựng</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>08/2022/QH15</t>
+          <t>02/2023/TT-BXD</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Luật Kinh doanh bảo hiểm năm 2022</t>
+          <t>Hướng dẫn một số nội dung về hợp đồng xây dựng</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>16/06/2022</t>
+          <t>03/03/2023</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>20/04/2023</t>
         </is>
       </c>
       <c r="I58" s="7" t="inlineStr">
@@ -4378,23 +4378,23 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Luật Kinh doanh bảo hiểm 2000</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>Luật nền tảng điều chỉnh hoạt động bảo hiểm công trình xây dựng (gói PTV-01)</t>
+          <t>Ban hành mẫu hợp đồng tư vấn thiết kế, tư vấn giám sát và hợp đồng thi công xây dựng (lưu ý đối chiếu NĐ 210/2026)</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>BAO_HIEM, PTV-01, XD-01</t>
+          <t>ALL, HOP_DONG, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
         </is>
       </c>
       <c r="M58" s="8" t="inlineStr"/>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -4404,37 +4404,37 @@
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>Bảo hiểm Xây dựng</t>
+          <t>Tiêu chuẩn Kỹ thuật</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Tiêu chuẩn</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>67/2023/NĐ-CP</t>
+          <t>TCVN 9393:2012</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr">
         <is>
-          <t>Quy định về bảo hiểm bắt buộc trách nhiệm dân sự của chủ xe cơ giới, bảo hiểm cháy, nổ bắt buộc, bảo hiểm bắt buộc trong hoạt động đầu tư xây dựng</t>
+          <t>Cọc - Phương pháp thử nghiệm hiện trường bằng tải trọng tĩnh ép dọc trục</t>
         </is>
       </c>
       <c r="F59" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Khoa học và Công nghệ</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
-          <t>06/09/2023</t>
+          <t>28/12/2012</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>06/09/2023</t>
+          <t>28/12/2012</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
@@ -4444,23 +4444,23 @@
       </c>
       <c r="J59" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 119/2015/NĐ-CP</t>
+          <t>Thay thế TCXDVN 269:2002</t>
         </is>
       </c>
       <c r="K59" s="10" t="inlineStr">
         <is>
-          <t>Nghị định chi phối biểu phí và điều kiện bảo hiểm công trình trong thời gian thi công (gói PTV-01)</t>
+          <t>Tiêu chuẩn kỹ thuật bắt buộc áp dụng cho gói thầu TV-07 Thí nghiệm nén tĩnh cọc</t>
         </is>
       </c>
       <c r="L59" s="10" t="inlineStr">
         <is>
-          <t>BAO_HIEM, PTV-01, XD-01</t>
+          <t>THI_NGHIEM_COC, TV-07, XD-01</t>
         </is>
       </c>
       <c r="M59" s="15" t="inlineStr"/>
       <c r="N59" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -4470,37 +4470,37 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Kiểm toán Độc lập</t>
+          <t>Tiêu chuẩn Kỹ thuật</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Tiêu chuẩn</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>67/2011/QH12</t>
+          <t>TCVN 9363:2012</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Luật Kiểm toán độc lập năm 2011</t>
+          <t>Khảo sát địa chất công trình cho nhà cao tầng</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Bộ Khoa học và Công nghệ</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>29/03/2011</t>
+          <t>28/12/2012</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>01/01/2012</t>
+          <t>28/12/2012</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
@@ -4515,18 +4515,18 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>Căn cứ pháp lý then chốt cho gói TV-09 Kiểm toán độc lập quyết toán vốn đầu tư hoàn thành</t>
+          <t>Tiêu chuẩn kỹ thuật cho công tác khoan khảo sát địa chất gói TV-02</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>KIEM_TOAN, TV-09</t>
+          <t>KHAO_SAT, TV-02</t>
         </is>
       </c>
       <c r="M60" s="8" t="inlineStr"/>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -4536,37 +4536,37 @@
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>Kiểm toán Độc lập</t>
+          <t>Tiêu chuẩn Kỹ thuật</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Tiêu chuẩn</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>67/2015/TT-BTC</t>
+          <t>TCVN 9401:2012</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
         <is>
-          <t>Ban hành Chuẩn mực kiểm toán Việt Nam số 1000 - Kiểm toán báo cáo quyết toán dự án hoàn thành (VSA 1000)</t>
+          <t>Kỹ thuật đo và xử lý số liệu GPS trong trắc địa công trình</t>
         </is>
       </c>
       <c r="F61" s="13" t="inlineStr">
         <is>
-          <t>Bộ Tài chính</t>
+          <t>Bộ Khoa học và Công nghệ</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
-          <t>08/05/2015</t>
+          <t>28/12/2012</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>28/12/2012</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
@@ -4581,18 +4581,18 @@
       </c>
       <c r="K61" s="10" t="inlineStr">
         <is>
-          <t>Quy chuẩn phương pháp kiểm toán báo cáo quyết toán dự án hoàn thành gói TV-09</t>
+          <t>Tiêu chuẩn kỹ thuật cho công tác đo đạc địa hình, định vị công trình gói TV-01</t>
         </is>
       </c>
       <c r="L61" s="10" t="inlineStr">
         <is>
-          <t>KIEM_TOAN, TV-09</t>
+          <t>DO_DAC, TV-01</t>
         </is>
       </c>
       <c r="M61" s="15" t="inlineStr"/>
       <c r="N61" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Đầu tư công</t>
+          <t>Bảo hiểm Xây dựng</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -4612,12 +4612,12 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>58/2024/QH15</t>
+          <t>08/2022/QH15</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Luật Đầu tư công năm 2024</t>
+          <t>Luật Kinh doanh bảo hiểm năm 2022</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>29/11/2024</t>
+          <t>16/06/2022</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
@@ -4642,23 +4642,23 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Luật Đầu tư công 39/2019/QH14</t>
+          <t>Thay thế Luật Kinh doanh bảo hiểm 2000</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>Quy định thẩm quyền quyết định chủ trương đầu tư, phân cấp quản lý dự án sử dụng vốn ngân sách nhà nước</t>
+          <t>Luật nền tảng điều chỉnh hoạt động bảo hiểm công trình xây dựng (gói PTV-01)</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>ALL, DAU_TU_CONG, CHU_TRUONG, TV-01, TV-02, TV-03, TV-09</t>
+          <t>BAO_HIEM, PTV-01, XD-01</t>
         </is>
       </c>
       <c r="M62" s="8" t="inlineStr"/>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -4668,63 +4668,63 @@
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>Đầu tư công</t>
+          <t>Bảo hiểm Xây dựng</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>39/2019/QH14</t>
+          <t>67/2023/NĐ-CP</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>Luật Đầu tư công năm 2019</t>
+          <t>Quy định về bảo hiểm bắt buộc trách nhiệm dân sự của chủ xe cơ giới, bảo hiểm cháy, nổ bắt buộc, bảo hiểm bắt buộc trong hoạt động đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F63" s="13" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>13/06/2019</t>
+          <t>06/09/2023</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
-        </is>
-      </c>
-      <c r="I63" s="14" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+          <t>06/09/2023</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J63" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Luật Đầu tư công 58/2024/QH15</t>
+          <t>Thay thế Nghị định 119/2015/NĐ-CP</t>
         </is>
       </c>
       <c r="K63" s="10" t="inlineStr">
         <is>
-          <t>Hết hiệu lực từ 01/01/2025</t>
+          <t>Nghị định chi phối biểu phí và điều kiện bảo hiểm công trình trong thời gian thi công (gói PTV-01)</t>
         </is>
       </c>
       <c r="L63" s="10" t="inlineStr">
         <is>
-          <t>ALL, DAU_TU_CONG, LICHSU</t>
+          <t>BAO_HIEM, PTV-01, XD-01</t>
         </is>
       </c>
       <c r="M63" s="15" t="inlineStr"/>
       <c r="N63" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -4734,37 +4734,37 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Đầu tư công</t>
+          <t>Kiểm toán Độc lập</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>40/2020/NĐ-CP</t>
+          <t>67/2011/QH12</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết thi hành một số điều của Luật Đầu tư công</t>
+          <t>Luật Kiểm toán độc lập năm 2011</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>06/04/2020</t>
+          <t>29/03/2011</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>06/04/2020</t>
+          <t>01/01/2012</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
@@ -4779,18 +4779,18 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>Quy định trình tự, thủ tục lập và giao kế hoạch đầu tư công trung hạn và hàng năm</t>
+          <t>Căn cứ pháp lý then chốt cho gói TV-09 Kiểm toán độc lập quyết toán vốn đầu tư hoàn thành</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>ALL, DAU_TU_CONG, TV-01, TV-02, TV-03</t>
+          <t>KIEM_TOAN, TV-09</t>
         </is>
       </c>
       <c r="M64" s="8" t="inlineStr"/>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -4800,37 +4800,37 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>Quyết toán vốn</t>
+          <t>Kiểm toán Độc lập</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>99/2021/NĐ-CP</t>
+          <t>67/2015/TT-BTC</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>Quy định về quản lý, thanh toán, quyết toán dự án sử dụng vốn đầu tư công</t>
+          <t>Ban hành Chuẩn mực kiểm toán Việt Nam số 1000 - Kiểm toán báo cáo quyết toán dự án hoàn thành (VSA 1000)</t>
         </is>
       </c>
       <c r="F65" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Tài chính</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>11/11/2021</t>
+          <t>08/05/2015</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
@@ -4840,23 +4840,23 @@
       </c>
       <c r="J65" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 11/2020/NĐ-CP và Thông tư 10/2020/TT-BTC</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K65" s="10" t="inlineStr">
         <is>
-          <t>Nghị định xương sống về thẩm tra, phê duyệt quyết toán vốn đầu tư công dự án hoàn thành</t>
+          <t>Quy chuẩn phương pháp kiểm toán báo cáo quyết toán dự án hoàn thành gói TV-09</t>
         </is>
       </c>
       <c r="L65" s="10" t="inlineStr">
         <is>
-          <t>ALL, QUYET_TOAN, TAI_CHINH, TV-09, XD-01</t>
+          <t>KIEM_TOAN, TV-09</t>
         </is>
       </c>
       <c r="M65" s="15" t="inlineStr"/>
       <c r="N65" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -4866,37 +4866,37 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Quyết toán vốn</t>
+          <t>Đầu tư công</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>96/2021/TT-BTC</t>
+          <t>58/2024/QH15</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Quy định về hệ thống mẫu biểu hồ sơ quyết toán vốn đầu tư công dự án hoàn thành</t>
+          <t>Luật Đầu tư công năm 2024</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>Bộ Tài chính</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>11/11/2021</t>
+          <t>29/11/2024</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
@@ -4906,23 +4906,23 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>Được sửa đổi, bổ sung bởi Thông tư 24/2024/TT-BTC</t>
+          <t>Thay thế Luật Đầu tư công 39/2019/QH14</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>Ban hành toàn bộ mẫu biểu Báo cáo quyết toán A-B, Báo cáo quyết toán hoàn thành</t>
+          <t>Quy định thẩm quyền quyết định chủ trương đầu tư, phân cấp quản lý dự án sử dụng vốn ngân sách nhà nước</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>ALL, QUYET_TOAN, TAI_CHINH, TV-09, XD-01</t>
+          <t>ALL, DAU_TU_CONG, CHU_TRUONG, TV-01, TV-02, TV-03, TV-09</t>
         </is>
       </c>
       <c r="M66" s="8" t="inlineStr"/>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -4932,63 +4932,63 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Quyết toán vốn</t>
+          <t>Đầu tư công</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>24/2024/TT-BTC</t>
+          <t>39/2019/QH14</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 96/2021/TT-BTC quy định về hệ thống mẫu biểu hồ sơ quyết toán vốn đầu tư công dự án hoàn thành</t>
+          <t>Luật Đầu tư công năm 2019</t>
         </is>
       </c>
       <c r="F67" s="13" t="inlineStr">
         <is>
-          <t>Bộ Tài chính</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
         <is>
-          <t>19/04/2024</t>
+          <t>13/06/2019</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>05/06/2024</t>
-        </is>
-      </c>
-      <c r="I67" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>01/01/2020</t>
+        </is>
+      </c>
+      <c r="I67" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J67" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi Thông tư 96/2021/TT-BTC</t>
+          <t>Bị thay thế bởi Luật Đầu tư công 58/2024/QH15</t>
         </is>
       </c>
       <c r="K67" s="10" t="inlineStr">
         <is>
-          <t>Cập nhật quy trình kiểm toán độc lập và thẩm tra quyết toán vốn đầu tư công hiện hành</t>
+          <t>Hết hiệu lực từ 01/01/2025</t>
         </is>
       </c>
       <c r="L67" s="10" t="inlineStr">
         <is>
-          <t>ALL, QUYET_TOAN, TAI_CHINH, TV-09, XD-01</t>
+          <t>ALL, DAU_TU_CONG, LICHSU</t>
         </is>
       </c>
       <c r="M67" s="15" t="inlineStr"/>
       <c r="N67" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Phòng cháy chữa cháy</t>
+          <t>Đầu tư công</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>136/2020/NĐ-CP</t>
+          <t>40/2020/NĐ-CP</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Phòng cháy và chữa cháy và Luật sửa đổi, bổ sung một số điều của Luật Phòng cháy và chữa cháy</t>
+          <t>Quy định chi tiết thi hành một số điều của Luật Đầu tư công</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>24/11/2020</t>
+          <t>06/04/2020</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>10/01/2021</t>
+          <t>06/04/2020</t>
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr">
@@ -5038,23 +5038,23 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>Được sửa đổi, bổ sung bởi Nghị định 50/2024/NĐ-CP</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>Quy định danh mục công trình phải thẩm duyệt thiết kế PCCC và nghiệm thu PCCC trước khi đưa vào sử dụng</t>
+          <t>Quy định trình tự, thủ tục lập và giao kế hoạch đầu tư công trung hạn và hàng năm</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>PCCC, TV-02, TV-03, TV-04, TV-05, XD-01</t>
+          <t>ALL, DAU_TU_CONG, TV-01, TV-02, TV-03</t>
         </is>
       </c>
       <c r="M68" s="8" t="inlineStr"/>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>Phòng cháy chữa cháy</t>
+          <t>Quyết toán vốn</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
@@ -5074,12 +5074,12 @@
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>50/2024/NĐ-CP</t>
+          <t>254/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 136/2020/NĐ-CP và Nghị định số 83/2017/NĐ-CP</t>
+          <t>Quy định về quản lý, thanh toán, quyết toán dự án sử dụng vốn đầu tư công</t>
         </is>
       </c>
       <c r="F69" s="13" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
-          <t>10/05/2024</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>15/05/2024</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr">
@@ -5104,23 +5104,23 @@
       </c>
       <c r="J69" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi Nghị định 136/2020/NĐ-CP</t>
+          <t>Thay thế Nghị định 99/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="K69" s="10" t="inlineStr">
         <is>
-          <t>Phân cấp thẩm quyền thẩm duyệt PCCC và cắt giảm danh mục công trình phải thẩm duyệt</t>
+          <t>Nghị định xương sống hiện hành về thẩm tra, phê duyệt quyết toán vốn đầu tư công dự án hoàn thành</t>
         </is>
       </c>
       <c r="L69" s="10" t="inlineStr">
         <is>
-          <t>PCCC, TV-02, TV-03, TV-04, TV-05, XD-01</t>
+          <t>ALL, QUYET_TOAN, TAI_CHINH, TV-09, XD-01</t>
         </is>
       </c>
       <c r="M69" s="15" t="inlineStr"/>
       <c r="N69" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -5130,63 +5130,63 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Quy chuẩn PCCC</t>
+          <t>Quyết toán vốn</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Quy chuẩn</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>QCVN 06:2022/BXD</t>
+          <t>99/2021/NĐ-CP</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Quy chuẩn kỹ thuật quốc gia về An toàn cháy cho nhà và công trình (ban hành kèm Thông tư 06/2022/TT-BXD)</t>
+          <t>Quy định về quản lý, thanh toán, quyết toán dự án sử dụng vốn đầu tư công</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>Bộ Xây dựng</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>30/11/2022</t>
+          <t>11/11/2021</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>16/01/2023</t>
-        </is>
-      </c>
-      <c r="I70" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>01/01/2022</t>
+        </is>
+      </c>
+      <c r="I70" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>Được sửa đổi bởi Thông tư 09/2023/TT-BXD (Sửa đổi 1:2023 QCVN 06:2022/BXD)</t>
+          <t>Bị thay thế bởi Nghị định 254/2025/NĐ-CP từ ngày 26/09/2025</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>Quy chuẩn bắt buộc áp dụng khi lập hồ sơ thiết kế BVTC công trình (TV-04, TV-05, XD-01)</t>
+          <t>Đã bị thay thế phần lớn bởi NĐ 254/2025/NĐ-CP (chỉ còn áp dụng chuyển tiếp cho một số trường hợp cụ thể)</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>PCCC, TV-02, TV-03, TV-04, TV-05, XD-01</t>
+          <t>ALL, QUYET_TOAN, TAI_CHINH, LICHSU</t>
         </is>
       </c>
       <c r="M70" s="8" t="inlineStr"/>
       <c r="N70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -5196,32 +5196,32 @@
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>Bảo vệ Môi trường</t>
+          <t>Quyết toán vốn</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>72/2020/QH14</t>
+          <t>96/2021/TT-BTC</t>
         </is>
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>Luật Bảo vệ môi trường năm 2020</t>
+          <t>Quy định về hệ thống mẫu biểu hồ sơ quyết toán vốn đầu tư công dự án hoàn thành</t>
         </is>
       </c>
       <c r="F71" s="13" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Bộ Tài chính</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>17/11/2020</t>
+          <t>11/11/2021</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
@@ -5236,23 +5236,23 @@
       </c>
       <c r="J71" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Luật Bảo vệ môi trường 2014</t>
+          <t>Được sửa đổi, bổ sung bởi Thông tư 24/2024/TT-BTC</t>
         </is>
       </c>
       <c r="K71" s="10" t="inlineStr">
         <is>
-          <t>Luật nền tảng về Đánh giá tác động môi trường (ĐTM), Giấy phép môi trường và Đăng ký môi trường</t>
+          <t>Ban hành toàn bộ mẫu biểu Báo cáo quyết toán A-B, Báo cáo quyết toán hoàn thành</t>
         </is>
       </c>
       <c r="L71" s="10" t="inlineStr">
         <is>
-          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
+          <t>ALL, QUYET_TOAN, TAI_CHINH, TV-09, XD-01</t>
         </is>
       </c>
       <c r="M71" s="15" t="inlineStr"/>
       <c r="N71" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -5262,37 +5262,37 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Bảo vệ Môi trường</t>
+          <t>Quyết toán vốn</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>08/2022/NĐ-CP</t>
+          <t>24/2024/TT-BTC</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Bảo vệ môi trường</t>
+          <t>Sửa đổi, bổ sung một số điều của Thông tư số 96/2021/TT-BTC quy định về hệ thống mẫu biểu hồ sơ quyết toán vốn đầu tư công dự án hoàn thành</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Bộ Tài chính</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>10/01/2022</t>
+          <t>19/04/2024</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>10/01/2022</t>
+          <t>05/06/2024</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr">
@@ -5302,23 +5302,23 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>Được sửa đổi, bổ sung bởi Nghị định 05/2025/NĐ-CP và Nghị định 48/2026/NĐ-CP</t>
+          <t>Sửa đổi Thông tư 96/2021/TT-BTC</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>Quy định phân nhóm dự án đầu tư theo tiêu chí môi trường để lập ĐTM hoặc đăng ký môi trường</t>
+          <t>Cập nhật quy trình kiểm toán độc lập và thẩm tra quyết toán vốn đầu tư công hiện hành</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
+          <t>ALL, QUYET_TOAN, TAI_CHINH, TV-09, XD-01</t>
         </is>
       </c>
       <c r="M72" s="8" t="inlineStr"/>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>Bảo vệ Môi trường</t>
+          <t>Phòng cháy chữa cháy</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>05/2025/NĐ-CP</t>
+          <t>105/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP quy định chi tiết một số điều của Luật Bảo vệ môi trường</t>
+          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Phòng cháy, chữa cháy và cứu nạn, cứu hộ</t>
         </is>
       </c>
       <c r="F73" s="13" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>25/06/2025</t>
         </is>
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr">
@@ -5368,23 +5368,23 @@
       </c>
       <c r="J73" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi Nghị định 08/2022/NĐ-CP</t>
+          <t>Thay thế Nghị định 136/2020/NĐ-CP và Nghị định 50/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="K73" s="10" t="inlineStr">
         <is>
-          <t>Đơn giản hóa thủ tục cấp giấy phép môi trường và phân cấp thẩm quyền thẩm định ĐTM</t>
+          <t>Quy định chi tiết thủ tục thẩm duyệt, nghiệm thu PCCC và cứu nạn cứu hộ số hóa mới nhất</t>
         </is>
       </c>
       <c r="L73" s="10" t="inlineStr">
         <is>
-          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
+          <t>PCCC, TV-02, TV-03, TV-04, TV-05, XD-01</t>
         </is>
       </c>
       <c r="M73" s="15" t="inlineStr"/>
       <c r="N73" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Bảo vệ Môi trường</t>
+          <t>Phòng cháy chữa cháy</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -5404,12 +5404,12 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>48/2026/NĐ-CP</t>
+          <t>136/2020/NĐ-CP</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của các Nghị định quy định chi tiết Luật Bảo vệ môi trường</t>
+          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Phòng cháy và chữa cháy</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
@@ -5419,38 +5419,38 @@
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>24/11/2020</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
-        </is>
-      </c>
-      <c r="I74" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>10/01/2021</t>
+        </is>
+      </c>
+      <c r="I74" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi Nghị định 08/2022/NĐ-CP</t>
+          <t>Bị thay thế bởi Nghị định 105/2025/NĐ-CP từ ngày 01/07/2025</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>Bãi bỏ cấp đổi GPMT, cho phép lập ĐTM cuốn chiếu theo từng giai đoạn dự án</t>
+          <t>Hết hiệu lực từ 01/07/2025</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
+          <t>PCCC, LICHSU</t>
         </is>
       </c>
       <c r="M74" s="8" t="inlineStr"/>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -5460,22 +5460,22 @@
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>Bảo vệ Môi trường</t>
+          <t>Phòng cháy chữa cháy</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Nghị quyết</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>66.19/2026/NQ-CP</t>
+          <t>50/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>Nghị quyết về việc tháo gỡ khó khăn, vướng mắc trong thực hiện thủ tục môi trường cho các dự án đầu tư công</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 136/2020/NĐ-CP và Nghị định số 83/2017/NĐ-CP</t>
         </is>
       </c>
       <c r="F75" s="13" t="inlineStr">
@@ -5485,38 +5485,38 @@
       </c>
       <c r="G75" s="11" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>10/05/2024</t>
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="I75" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>15/05/2024</t>
+        </is>
+      </c>
+      <c r="I75" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J75" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bị thay thế bởi Nghị định 105/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="K75" s="10" t="inlineStr">
         <is>
-          <t>Cơ chế đặc thù tháo gỡ thủ tục đăng ký môi trường đối với dự án cải tạo, sửa chữa doanh trại</t>
+          <t>Hết hiệu lực từ 01/07/2025</t>
         </is>
       </c>
       <c r="L75" s="10" t="inlineStr">
         <is>
-          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
+          <t>PCCC, LICHSU</t>
         </is>
       </c>
       <c r="M75" s="15" t="inlineStr"/>
       <c r="N75" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -5526,37 +5526,37 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Chi thường xuyên &amp; Tài sản công</t>
+          <t>Quy chuẩn PCCC</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Quy chuẩn</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>15/2017/QH14</t>
+          <t>QCVN 06:2022/BXD</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Luật Quản lý, sử dụng tài sản công</t>
+          <t>Quy chuẩn kỹ thuật quốc gia về An toàn cháy cho nhà và công trình (ban hành kèm Thông tư 06/2022/TT-BXD)</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Bộ Xây dựng</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>21/06/2017</t>
+          <t>30/11/2022</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>16/01/2023</t>
         </is>
       </c>
       <c r="I76" s="7" t="inlineStr">
@@ -5566,23 +5566,23 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Luật Quản lý tài sản nhà nước 2008</t>
+          <t>Được sửa đổi bởi Thông tư 09/2023/TT-BXD (Sửa đổi 1:2023 QCVN 06:2022/BXD)</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>Chế độ quản lý, bảo dưỡng, nâng cấp và sử dụng tài sản công trong các cơ quan, đơn vị</t>
+          <t>Quy chuẩn bắt buộc áp dụng khi lập hồ sơ thiết kế BVTC công trình (TV-04, TV-05, XD-01)</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
+          <t>PCCC, TV-02, TV-03, TV-04, TV-05, XD-01</t>
         </is>
       </c>
       <c r="M76" s="8" t="inlineStr"/>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -5592,37 +5592,37 @@
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>Chi thường xuyên &amp; Tài sản công</t>
+          <t>Bảo vệ Môi trường</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>151/2017/NĐ-CP</t>
+          <t>72/2020/QH14</t>
         </is>
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
+          <t>Luật Bảo vệ môi trường năm 2020</t>
         </is>
       </c>
       <c r="F77" s="13" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
         <is>
-          <t>26/12/2017</t>
+          <t>17/11/2020</t>
         </is>
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="I77" s="7" t="inlineStr">
@@ -5632,23 +5632,23 @@
       </c>
       <c r="J77" s="10" t="inlineStr">
         <is>
-          <t>Được sửa đổi, bổ sung bởi Nghị định 114/2024/NĐ-CP và Nghị định 186/2025/NĐ-CP</t>
+          <t>Thay thế Luật Bảo vệ môi trường 2014</t>
         </is>
       </c>
       <c r="K77" s="10" t="inlineStr">
         <is>
-          <t>Quy trình sử dụng tài sản công, sửa chữa và bảo dưỡng tài sản</t>
+          <t>Luật nền tảng về Đánh giá tác động môi trường (ĐTM), Giấy phép môi trường và Đăng ký môi trường</t>
         </is>
       </c>
       <c r="L77" s="10" t="inlineStr">
         <is>
-          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
+          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
         </is>
       </c>
       <c r="M77" s="15" t="inlineStr"/>
       <c r="N77" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Chi thường xuyên &amp; Tài sản công</t>
+          <t>Bảo vệ Môi trường</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>114/2024/NĐ-CP</t>
+          <t>08/2022/NĐ-CP</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 151/2017/NĐ-CP quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
+          <t>Quy định chi tiết một số điều của Luật Bảo vệ môi trường</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>15/09/2024</t>
+          <t>10/01/2022</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>30/10/2024</t>
+          <t>10/01/2022</t>
         </is>
       </c>
       <c r="I78" s="7" t="inlineStr">
@@ -5698,23 +5698,23 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi Nghị định 151/2017/NĐ-CP</t>
+          <t>Được sửa đổi, bổ sung bởi Nghị định 05/2025/NĐ-CP và Nghị định 48/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>Phân cấp thẩm quyền bảo dưỡng, sửa chữa tài sản công trong các đơn vị dự toán</t>
+          <t>Quy định phân nhóm dự án đầu tư theo tiêu chí môi trường để lập ĐTM hoặc đăng ký môi trường</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
+          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
         </is>
       </c>
       <c r="M78" s="8" t="inlineStr"/>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>Chi thường xuyên &amp; Tài sản công</t>
+          <t>Bảo vệ Môi trường</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
@@ -5734,12 +5734,12 @@
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>186/2025/NĐ-CP</t>
+          <t>05/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="E79" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 151/2017/NĐ-CP về quản lý, sử dụng tài sản công</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP quy định chi tiết một số điều của Luật Bảo vệ môi trường</t>
         </is>
       </c>
       <c r="F79" s="13" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="G79" s="11" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>01/08/2025</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
@@ -5764,23 +5764,23 @@
       </c>
       <c r="J79" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi Nghị định 151/2017/NĐ-CP</t>
+          <t>Sửa đổi Nghị định 08/2022/NĐ-CP</t>
         </is>
       </c>
       <c r="K79" s="10" t="inlineStr">
         <is>
-          <t>Hướng dẫn cụ thể về trình tự phê duyệt dự toán sửa chữa, cải tạo tài sản công</t>
+          <t>Đơn giản hóa thủ tục cấp giấy phép môi trường và phân cấp thẩm quyền thẩm định ĐTM</t>
         </is>
       </c>
       <c r="L79" s="10" t="inlineStr">
         <is>
-          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
+          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
         </is>
       </c>
       <c r="M79" s="15" t="inlineStr"/>
       <c r="N79" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Chi thường xuyên &amp; Tài sản công</t>
+          <t>Bảo vệ Môi trường</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>138/2024/NĐ-CP</t>
+          <t>48/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Quy định việc sử dụng kinh phí chi thường xuyên ngân sách nhà nước để thực hiện mua sắm tài sản, trang thiết bị; cải tạo, nâng cấp, mở rộng, xây dựng mới hạng mục công trình trong các dự án đã đầu tư xây dựng</t>
+          <t>Sửa đổi, bổ sung một số điều của các Nghị định quy định chi tiết Luật Bảo vệ môi trường</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
@@ -5815,38 +5815,38 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>24/10/2024</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>24/10/2024</t>
-        </is>
-      </c>
-      <c r="I80" s="14" t="inlineStr">
-        <is>
-          <t>Hết hiệu lực</t>
+          <t>29/01/2026</t>
+        </is>
+      </c>
+      <c r="I80" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 98/2025/NĐ-CP và Nghị định 104/2026/NĐ-CP</t>
+          <t>Sửa đổi Nghị định 08/2022/NĐ-CP</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>Nghị định nền tảng cho phép dùng nguồn chi thường xuyên để sửa chữa, cải tạo công trình dưới 15 tỷ đồng</t>
+          <t>Bãi bỏ cấp đổi GPMT, cho phép lập ĐTM cuốn chiếu theo từng giai đoạn dự án</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01, LICHSU</t>
+          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
         </is>
       </c>
       <c r="M80" s="8" t="inlineStr"/>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -5856,22 +5856,22 @@
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>Chi thường xuyên &amp; Tài sản công</t>
+          <t>Bảo vệ Môi trường</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Nghị quyết</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>98/2025/NĐ-CP</t>
+          <t>66.19/2026/NQ-CP</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 138/2024/NĐ-CP về sử dụng kinh phí chi thường xuyên ngân sách nhà nước</t>
+          <t>Nghị quyết về việc tháo gỡ khó khăn, vướng mắc trong thực hiện thủ tục môi trường cho các dự án đầu tư công</t>
         </is>
       </c>
       <c r="F81" s="13" t="inlineStr">
@@ -5881,12 +5881,12 @@
       </c>
       <c r="G81" s="11" t="inlineStr">
         <is>
-          <t>12/05/2025</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="I81" s="7" t="inlineStr">
@@ -5896,23 +5896,23 @@
       </c>
       <c r="J81" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 138/2024/NĐ-CP</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K81" s="10" t="inlineStr">
         <is>
-          <t>Phân cấp thẩm quyền quyết định dự toán mua sắm, cải tạo tài sản cho Thủ trưởng đơn vị dự toán</t>
+          <t>Cơ chế đặc thù tháo gỡ thủ tục đăng ký môi trường đối với dự án cải tạo, sửa chữa doanh trại</t>
         </is>
       </c>
       <c r="L81" s="10" t="inlineStr">
         <is>
-          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
+          <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
         </is>
       </c>
       <c r="M81" s="15" t="inlineStr"/>
       <c r="N81" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -5927,32 +5927,32 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Nghị định</t>
+          <t>Luật</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>104/2026/NĐ-CP</t>
+          <t>15/2017/QH14</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 138/2024/NĐ-CP và Nghị định 98/2025/NĐ-CP về quản lý và thanh toán kinh phí chi thường xuyên sửa chữa cơ sở vật chất</t>
+          <t>Luật Quản lý, sử dụng tài sản công</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>Chính phủ</t>
+          <t>Quốc hội</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>21/06/2017</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="I82" s="7" t="inlineStr">
@@ -5962,12 +5962,12 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi Nghị định 98/2025/NĐ-CP</t>
+          <t>Thay thế Luật Quản lý tài sản nhà nước 2008</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>Quy định quy trình giải ngân kinh phí chi thường xuyên tại Kho bạc Nhà nước</t>
+          <t>Chế độ quản lý, bảo dưỡng, nâng cấp và sử dụng tài sản công trong các cơ quan, đơn vị</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
@@ -5978,7 +5978,7 @@
       <c r="M82" s="8" t="inlineStr"/>
       <c r="N82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Thông tư</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>65/2021/TT-BTC</t>
+          <t>151/2017/NĐ-CP</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>Quy định về lập dự toán, quản lý, sử dụng và quyết toán kinh phí bảo dưỡng, sửa chữa tài sản công</t>
+          <t>Quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
         </is>
       </c>
       <c r="F83" s="13" t="inlineStr">
         <is>
-          <t>Bộ Tài chính</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>29/07/2021</t>
+          <t>26/12/2017</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>15/09/2021</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="I83" s="7" t="inlineStr">
@@ -6028,12 +6028,12 @@
       </c>
       <c r="J83" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Thông tư 92/2017/TT-BTC</t>
+          <t>Được sửa đổi, bổ sung bởi Nghị định 114/2024/NĐ-CP và Nghị định 186/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="K83" s="10" t="inlineStr">
         <is>
-          <t>Hướng dẫn chi tiết định mức lập dự toán chi thường xuyên sửa chữa cơ sở vật chất, doanh trại</t>
+          <t>Quy trình sử dụng tài sản công, sửa chữa và bảo dưỡng tài sản</t>
         </is>
       </c>
       <c r="L83" s="10" t="inlineStr">
@@ -6044,7 +6044,7 @@
       <c r="M83" s="15" t="inlineStr"/>
       <c r="N83" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Thể thức Văn bản</t>
+          <t>Chi thường xuyên &amp; Tài sản công</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -6064,12 +6064,12 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>30/2020/NĐ-CP</t>
+          <t>114/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Về công tác văn thư</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 151/2017/NĐ-CP quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
@@ -6079,12 +6079,12 @@
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>05/03/2020</t>
+          <t>15/09/2024</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>05/03/2020</t>
+          <t>30/10/2024</t>
         </is>
       </c>
       <c r="I84" s="7" t="inlineStr">
@@ -6094,23 +6094,23 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 110/2004/NĐ-CP</t>
+          <t>Sửa đổi Nghị định 151/2017/NĐ-CP</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>Quy chuẩn thể thức văn bản hành chính (Tờ trình, Quyết định, Biên bản, font Times New Roman 13pt/14pt)</t>
+          <t>Phân cấp thẩm quyền bảo dưỡng, sửa chữa tài sản công trong các đơn vị dự toán</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>ALL, THE_THUC, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
+          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
         </is>
       </c>
       <c r="M84" s="8" t="inlineStr"/>
       <c r="N84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -6120,37 +6120,37 @@
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>Đối tác công tư</t>
+          <t>Chi thường xuyên &amp; Tài sản công</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>64/2020/QH14</t>
+          <t>186/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>Luật Đầu tư theo phương thức đối tác công tư (PPP)</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 151/2017/NĐ-CP về quản lý, sử dụng tài sản công</t>
         </is>
       </c>
       <c r="F85" s="13" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
-          <t>18/06/2020</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
+          <t>01/08/2025</t>
         </is>
       </c>
       <c r="I85" s="7" t="inlineStr">
@@ -6160,23 +6160,23 @@
       </c>
       <c r="J85" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Sửa đổi Nghị định 151/2017/NĐ-CP</t>
         </is>
       </c>
       <c r="K85" s="10" t="inlineStr">
         <is>
-          <t>Căn cứ pháp lý cho các dự án đầu tư theo hình thức đối tác công tư</t>
+          <t>Hướng dẫn cụ thể về trình tự phê duyệt dự toán sửa chữa, cải tạo tài sản công</t>
         </is>
       </c>
       <c r="L85" s="10" t="inlineStr">
         <is>
-          <t>PPP, DAU_TU_CONG</t>
+          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
         </is>
       </c>
       <c r="M85" s="15" t="inlineStr"/>
       <c r="N85" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Đối tác công tư</t>
+          <t>Chi thường xuyên &amp; Tài sản công</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>35/2021/NĐ-CP</t>
+          <t>104/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết và hướng dẫn thi hành Luật Đầu tư theo phương thức đối tác công tư</t>
+          <t>Quy định việc sử dụng kinh phí chi thường xuyên ngân sách nhà nước để thực hiện mua sắm tài sản, trang thiết bị; cải tạo, nâng cấp, mở rộng, xây dựng mới hạng mục công trình trong các dự án đã đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>29/03/2021</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>29/03/2021</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="I86" s="7" t="inlineStr">
@@ -6226,23 +6226,23 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Thay thế Nghị định 138/2024/NĐ-CP và Nghị định 98/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết quy trình lập dự án và lựa chọn nhà đầu tư PPP</t>
+          <t>Phân cấp thẩm quyền quyết định dự toán mua sắm, cải tạo tài sản cho Thủ trưởng đơn vị dự toán</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>PPP, DAU_TU_CONG</t>
+          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
         </is>
       </c>
       <c r="M86" s="8" t="inlineStr"/>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -6252,63 +6252,63 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>Đầu tư kinh doanh</t>
+          <t>Chi thường xuyên &amp; Tài sản công</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Luật</t>
+          <t>Nghị định</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>61/2020/QH14</t>
+          <t>138/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
-          <t>Luật Đầu tư năm 2020 (sửa đổi bởi Luật số 57/2024/QH15)</t>
+          <t>Quy định việc sử dụng kinh phí chi thường xuyên ngân sách nhà nước để thực hiện mua sắm tài sản, trang thiết bị; cải tạo, nâng cấp, mở rộng, xây dựng mới hạng mục công trình trong các dự án đã đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F87" s="13" t="inlineStr">
         <is>
-          <t>Quốc hội</t>
+          <t>Chính phủ</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr">
         <is>
-          <t>17/06/2020</t>
+          <t>24/10/2024</t>
         </is>
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
-        </is>
-      </c>
-      <c r="I87" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>24/10/2024</t>
+        </is>
+      </c>
+      <c r="I87" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J87" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Luật Đầu tư 2014</t>
+          <t>Bị thay thế bởi Nghị định 98/2025/NĐ-CP và Nghị định 104/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="K87" s="10" t="inlineStr">
         <is>
-          <t>Căn cứ pháp lý về thủ tục chấp thuận chủ trương đầu tư dự án</t>
+          <t>Đã hết hiệu lực</t>
         </is>
       </c>
       <c r="L87" s="10" t="inlineStr">
         <is>
-          <t>DAU_TU_KINH_DOANH</t>
+          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, LICHSU</t>
         </is>
       </c>
       <c r="M87" s="15" t="inlineStr"/>
       <c r="N87" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Đầu tư kinh doanh</t>
+          <t>Chi thường xuyên &amp; Tài sản công</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -6328,12 +6328,12 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>31/2021/NĐ-CP</t>
+          <t>98/2025/NĐ-CP</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết và hướng dẫn thi hành một số điều của Luật Đầu tư</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 138/2024/NĐ-CP về sử dụng kinh phí chi thường xuyên ngân sách nhà nước</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
@@ -6343,38 +6343,38 @@
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>26/03/2021</t>
+          <t>12/05/2025</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>26/03/2021</t>
-        </is>
-      </c>
-      <c r="I88" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+          <t>01/07/2025</t>
+        </is>
+      </c>
+      <c r="I88" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Bị thay thế bởi Nghị định 104/2026/NĐ-CP</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết trình tự, thủ tục đầu tư và ưu đãi đầu tư</t>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>DAU_TU_KINH_DOANH</t>
+          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, LICHSU</t>
         </is>
       </c>
       <c r="M88" s="8" t="inlineStr"/>
       <c r="N88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>
@@ -6384,37 +6384,37 @@
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>Quốc phòng &amp; Doanh trại</t>
+          <t>Chi thường xuyên &amp; Tài sản công</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Văn bản Hợp nhất</t>
+          <t>Thông tư</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>15/VBHN-BQP</t>
+          <t>65/2021/TT-BTC</t>
         </is>
       </c>
       <c r="E89" s="10" t="inlineStr">
         <is>
-          <t>Văn bản hợp nhất Thông tư quy định về phân cấp, ủy quyền quyết định chủ trương đầu tư và dự án đầu tư công trong Bộ Quốc phòng</t>
+          <t>Quy định về lập dự toán, quản lý, sử dụng và quyết toán kinh phí bảo dưỡng, sửa chữa tài sản công</t>
         </is>
       </c>
       <c r="F89" s="13" t="inlineStr">
         <is>
-          <t>Bộ Quốc phòng</t>
+          <t>Bộ Tài chính</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr">
         <is>
-          <t>15/03/2025</t>
+          <t>29/07/2021</t>
         </is>
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>15/03/2025</t>
+          <t>15/09/2021</t>
         </is>
       </c>
       <c r="I89" s="7" t="inlineStr">
@@ -6424,23 +6424,419 @@
       </c>
       <c r="J89" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Thay thế Thông tư 92/2017/TT-BTC</t>
         </is>
       </c>
       <c r="K89" s="10" t="inlineStr">
         <is>
-          <t>Văn bản hợp nhất hướng dẫn công tác quản lý dự án và phân cấp trong Bộ Quốc phòng</t>
+          <t>Hướng dẫn chi tiết định mức lập dự toán chi thường xuyên sửa chữa cơ sở vật chất, doanh trại</t>
         </is>
       </c>
       <c r="L89" s="10" t="inlineStr">
         <is>
-          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+          <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
         </is>
       </c>
       <c r="M89" s="15" t="inlineStr"/>
       <c r="N89" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:26</t>
+          <t>2026-08-21 17:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="26" customHeight="1">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Thể thức Văn bản</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>Nghị định</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>30/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>Về công tác văn thư</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>Chính phủ</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>05/03/2020</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>05/03/2020</t>
+        </is>
+      </c>
+      <c r="I90" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>Thay thế Nghị định 110/2004/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>Quy chuẩn thể thức văn bản hành chính (Tờ trình, Quyết định, Biên bản, font Times New Roman 13pt/14pt)</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>ALL, THE_THUC, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
+        </is>
+      </c>
+      <c r="M90" s="8" t="inlineStr"/>
+      <c r="N90" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21 17:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="26" customHeight="1">
+      <c r="A91" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>Đối tác công tư</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr">
+        <is>
+          <t>Luật</t>
+        </is>
+      </c>
+      <c r="D91" s="12" t="inlineStr">
+        <is>
+          <t>64/2020/QH14</t>
+        </is>
+      </c>
+      <c r="E91" s="10" t="inlineStr">
+        <is>
+          <t>Luật Đầu tư theo phương thức đối tác công tư (PPP)</t>
+        </is>
+      </c>
+      <c r="F91" s="13" t="inlineStr">
+        <is>
+          <t>Quốc hội</t>
+        </is>
+      </c>
+      <c r="G91" s="11" t="inlineStr">
+        <is>
+          <t>18/06/2020</t>
+        </is>
+      </c>
+      <c r="H91" s="11" t="inlineStr">
+        <is>
+          <t>01/01/2021</t>
+        </is>
+      </c>
+      <c r="I91" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
+        </is>
+      </c>
+      <c r="J91" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K91" s="10" t="inlineStr">
+        <is>
+          <t>Căn cứ pháp lý cho các dự án đầu tư theo hình thức đối tác công tư</t>
+        </is>
+      </c>
+      <c r="L91" s="10" t="inlineStr">
+        <is>
+          <t>PPP, DAU_TU_CONG</t>
+        </is>
+      </c>
+      <c r="M91" s="15" t="inlineStr"/>
+      <c r="N91" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-21 17:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="26" customHeight="1">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Đối tác công tư</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>Nghị định</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>35/2021/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>Quy định chi tiết và hướng dẫn thi hành Luật Đầu tư theo phương thức đối tác công tư</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>Chính phủ</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>29/03/2021</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>29/03/2021</t>
+        </is>
+      </c>
+      <c r="I92" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>Quy định chi tiết quy trình lập dự án và lựa chọn nhà đầu tư PPP</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>PPP, DAU_TU_CONG</t>
+        </is>
+      </c>
+      <c r="M92" s="8" t="inlineStr"/>
+      <c r="N92" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21 17:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="26" customHeight="1">
+      <c r="A93" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="10" t="inlineStr">
+        <is>
+          <t>Đầu tư kinh doanh</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>Luật</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>61/2020/QH14</t>
+        </is>
+      </c>
+      <c r="E93" s="10" t="inlineStr">
+        <is>
+          <t>Luật Đầu tư năm 2020 (sửa đổi bởi Luật số 57/2024/QH15)</t>
+        </is>
+      </c>
+      <c r="F93" s="13" t="inlineStr">
+        <is>
+          <t>Quốc hội</t>
+        </is>
+      </c>
+      <c r="G93" s="11" t="inlineStr">
+        <is>
+          <t>17/06/2020</t>
+        </is>
+      </c>
+      <c r="H93" s="11" t="inlineStr">
+        <is>
+          <t>01/01/2021</t>
+        </is>
+      </c>
+      <c r="I93" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
+        </is>
+      </c>
+      <c r="J93" s="10" t="inlineStr">
+        <is>
+          <t>Thay thế Luật Đầu tư 2014</t>
+        </is>
+      </c>
+      <c r="K93" s="10" t="inlineStr">
+        <is>
+          <t>Căn cứ pháp lý về thủ tục chấp thuận chủ trương đầu tư dự án</t>
+        </is>
+      </c>
+      <c r="L93" s="10" t="inlineStr">
+        <is>
+          <t>DAU_TU_KINH_DOANH</t>
+        </is>
+      </c>
+      <c r="M93" s="15" t="inlineStr"/>
+      <c r="N93" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-21 17:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="26" customHeight="1">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Đầu tư kinh doanh</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>Nghị định</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>31/2021/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>Quy định chi tiết và hướng dẫn thi hành một số điều của Luật Đầu tư</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>Chính phủ</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>26/03/2021</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>26/03/2021</t>
+        </is>
+      </c>
+      <c r="I94" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>Quy định chi tiết trình tự, thủ tục đầu tư và ưu đãi đầu tư</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>DAU_TU_KINH_DOANH</t>
+        </is>
+      </c>
+      <c r="M94" s="8" t="inlineStr"/>
+      <c r="N94" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21 17:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="26" customHeight="1">
+      <c r="A95" s="9" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="10" t="inlineStr">
+        <is>
+          <t>Quốc phòng &amp; Doanh trại</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="inlineStr">
+        <is>
+          <t>Văn bản Hợp nhất</t>
+        </is>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
+        <is>
+          <t>15/VBHN-BQP</t>
+        </is>
+      </c>
+      <c r="E95" s="10" t="inlineStr">
+        <is>
+          <t>Văn bản hợp nhất Thông tư quy định về phân cấp, ủy quyền quyết định chủ trương đầu tư và dự án đầu tư công trong Bộ Quốc phòng</t>
+        </is>
+      </c>
+      <c r="F95" s="13" t="inlineStr">
+        <is>
+          <t>Bộ Quốc phòng</t>
+        </is>
+      </c>
+      <c r="G95" s="11" t="inlineStr">
+        <is>
+          <t>15/03/2025</t>
+        </is>
+      </c>
+      <c r="H95" s="11" t="inlineStr">
+        <is>
+          <t>15/03/2025</t>
+        </is>
+      </c>
+      <c r="I95" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
+        </is>
+      </c>
+      <c r="J95" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K95" s="10" t="inlineStr">
+        <is>
+          <t>Văn bản hợp nhất hướng dẫn công tác quản lý dự án và phân cấp trong Bộ Quốc phòng</t>
+        </is>
+      </c>
+      <c r="L95" s="10" t="inlineStr">
+        <is>
+          <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
+        </is>
+      </c>
+      <c r="M95" s="15" t="inlineStr"/>
+      <c r="N95" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-21 17:02</t>
         </is>
       </c>
     </row>

--- a/Kho_Can_Cu_Phap_Ly.xlsx
+++ b/Kho_Can_Cu_Phap_Ly.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,6 +47,12 @@
       <b val="1"/>
       <color rgb="00065F46"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="002563EB"/>
+      <sz val="10"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -156,7 +162,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -174,10 +180,10 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -657,7 +663,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Luật Quy hoạch đô thị và nông thôn năm 2024</t>
+          <t>Luật Quy hoạch đô thị và nông thôn năm 2024 (Hợp nhất toàn diện)</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
@@ -687,7 +693,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Có hiệu lực từ 01/07/2025; hợp nhất quản lý quy hoạch đô thị và nông thôn, phân cấp mạnh cho địa phương</t>
+          <t>Có hiệu lực từ 01/07/2025; hợp nhất quy hoạch đô thị - nông thôn; bãi bỏ giấy phép quy hoạch; phân cấp duyệt Tổng mặt bằng 1/500 cho địa phương; căn cứ gói TV-01</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -695,10 +701,14 @@
           <t>ALL, QUY_HOACH, TV-01, TV-02, BQP</t>
         </is>
       </c>
-      <c r="M2" s="8" t="inlineStr"/>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=47/2024/QH15</t>
+        </is>
+      </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -723,7 +733,7 @@
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>Luật Quy hoạch đô thị năm 2009</t>
+          <t>Luật Quy hoạch đô thị năm 2009 (Hết hiệu lực từ 01/07/2025)</t>
         </is>
       </c>
       <c r="F3" s="13" t="inlineStr">
@@ -753,7 +763,7 @@
       </c>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <t>Hết hiệu lực từ ngày 01/07/2025</t>
+          <t>Hết hiệu lực từ 01/07/2025; đồ án đã duyệt trước 01/07/2025 tiếp tục thực hiện đến hết kỳ quy hoạch</t>
         </is>
       </c>
       <c r="L3" s="10" t="inlineStr">
@@ -761,10 +771,14 @@
           <t>ALL, QUY_HOACH, TV-01, TV-02, BQP, LICHSU</t>
         </is>
       </c>
-      <c r="M3" s="15" t="inlineStr"/>
+      <c r="M3" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=30/2009/QH12</t>
+        </is>
+      </c>
       <c r="N3" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -789,7 +803,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Quy hoạch đô thị và nông thôn</t>
+          <t>Quy định chi tiết một số điều của Luật Quy hoạch đô thị và nông thôn năm 2024</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -819,7 +833,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết trình tự lập, thẩm định và phê duyệt quy hoạch đô thị và nông thôn mới nhất</t>
+          <t>Có hiệu lực từ 01/07/2025; chuẩn hóa trình tự lập, thẩm định và phê duyệt bản vẽ Tổng mặt bằng tỷ lệ 1/500; căn cứ trực tiếp nghiệm thu gói TV-01</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -827,10 +841,14 @@
           <t>ALL, QUY_HOACH, TV-01, TV-02, QLDA</t>
         </is>
       </c>
-      <c r="M4" s="8" t="inlineStr"/>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=178/2025/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -855,7 +873,7 @@
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số nội dung về quy hoạch xây dựng</t>
+          <t>Quy định chi tiết một số nội dung về quy hoạch xây dựng (Đã hết hiệu lực)</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -885,7 +903,7 @@
       </c>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>Đã hết hiệu lực từ 01/07/2025 khi Luật Quy hoạch ĐT&amp;NT 47/2024 có hiệu lực</t>
+          <t>Đã hết hiệu lực từ 01/07/2025; đồ án quy hoạch đã phê duyệt trước 01/07/2025 tiếp tục có hiệu lực thi hành theo đồ án đã duyệt</t>
         </is>
       </c>
       <c r="L5" s="10" t="inlineStr">
@@ -893,10 +911,14 @@
           <t>ALL, QUY_HOACH, TV-01, TV-02, QLDA, LICHSU</t>
         </is>
       </c>
-      <c r="M5" s="15" t="inlineStr"/>
+      <c r="M5" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=44/2015/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N5" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -921,7 +943,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Quy định về hồ sơ nhiệm vụ và hồ sơ đồ án quy hoạch xây dựng vùng liên huyện, quy hoạch xây dựng vùng huyện, quy hoạch đô thị, quy hoạch xây dựng khu chức năng và quy hoạch nông thôn</t>
+          <t>Quy định về hồ sơ nhiệm vụ và đồ án quy hoạch xây dựng, quy hoạch đô thị và nông thôn</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -959,10 +981,14 @@
           <t>QUY_HOACH, TV-01, HO_SO_QUY_HOACH</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr"/>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=04/2022/TT-BXD</t>
+        </is>
+      </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -987,7 +1013,7 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>Hướng dẫn xác định, quản lý chi phí quy hoạch xây dựng và quy hoạch đô thị</t>
+          <t>Hướng dẫn xác định, quản lý chi phí quy hoạch xây dựng (Đã hết hiệu lực)</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -1017,7 +1043,7 @@
       </c>
       <c r="K7" s="10" t="inlineStr">
         <is>
-          <t>Đã hết hiệu lực</t>
+          <t>Hết hiệu lực từ 01/07/2025; hợp đồng tư vấn quy hoạch đã ký trước 01/07/2025 tiếp tục thực hiện theo giá hợp đồng đã ký</t>
         </is>
       </c>
       <c r="L7" s="10" t="inlineStr">
@@ -1025,10 +1051,14 @@
           <t>QUY_HOACH, CHI_PHI_QUY_HOACH, DU_TOAN, TV-01, LICHSU</t>
         </is>
       </c>
-      <c r="M7" s="15" t="inlineStr"/>
+      <c r="M7" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=20/2019/TT-BXD</t>
+        </is>
+      </c>
       <c r="N7" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -1091,10 +1121,14 @@
           <t>QCVN, QUY_HOACH, TV-01, TV-02, TV-04, XD-01</t>
         </is>
       </c>
-      <c r="M8" s="8" t="inlineStr"/>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=QCVN%2001%3A2021/BXD</t>
+        </is>
+      </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1178,7 @@
       </c>
       <c r="J9" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Văn bản gốc / Ban hành lần đầu</t>
         </is>
       </c>
       <c r="K9" s="10" t="inlineStr">
@@ -1157,10 +1191,14 @@
           <t>KHAO_SAT, DO_DAC, TV-01, TV-02, XD-01</t>
         </is>
       </c>
-      <c r="M9" s="15" t="inlineStr"/>
+      <c r="M9" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=27/2018/QH14</t>
+        </is>
+      </c>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -1223,10 +1261,14 @@
           <t>KHAO_SAT, DO_DAC, TV-01, TV-02, XD-01</t>
         </is>
       </c>
-      <c r="M10" s="8" t="inlineStr"/>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=27/2019/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1293,7 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>Luật Xây dựng năm 2025</t>
+          <t>Luật Xây dựng năm 2025 (Thay thế toàn diện Luật Xây dựng 2014 &amp; Luật 62/2020)</t>
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr">
@@ -1281,7 +1323,7 @@
       </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>Luật khung hiện hành chi phối toàn bộ hoạt động đầu tư xây dựng công trình, thẩm định và cấp phép</t>
+          <t>Có hiệu lực từ 01/07/2026. ĐỘT PHÁ: BÃI BỎ cơ quan chuyên môn thẩm định thiết kế sau TKCS; CĐT tự phê duyệt TKBVTC và dự toán qua tư vấn thẩm tra TV-05</t>
         </is>
       </c>
       <c r="L11" s="10" t="inlineStr">
@@ -1289,10 +1331,14 @@
           <t>ALL, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
-      <c r="M11" s="15" t="inlineStr"/>
+      <c r="M11" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=135/2025/QH15</t>
+        </is>
+      </c>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1363,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Luật Xây dựng năm 2014</t>
+          <t>Luật Xây dựng năm 2014 (Hết hiệu lực từ 01/07/2026)</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -1347,7 +1393,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Dự án đã phê duyệt trước 01/07/2026 thực hiện theo quy định chuyển tiếp của Luật 135/2025</t>
+          <t>Hết hiệu lực từ 01/07/2026; dự án đã duyệt trước 01/07/2026 không phải duyệt lại; nếu điều chỉnh sau 01/07/2026 thì thực hiện theo Luật 135/2025</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -1355,10 +1401,14 @@
           <t>ALL, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01, LICHSU</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr"/>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=50/2014/QH13</t>
+        </is>
+      </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1433,7 @@
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>Luật sửa đổi, bổ sung một số điều của Luật Xây dựng năm 2020</t>
+          <t>Luật sửa đổi, bổ sung một số điều của Luật Xây dựng năm 2020 (Hết hiệu lực 01/07/2026)</t>
         </is>
       </c>
       <c r="F13" s="13" t="inlineStr">
@@ -1413,7 +1463,7 @@
       </c>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t>Hết hiệu lực từ 01/07/2026</t>
+          <t>Hết hiệu lực từ 01/07/2026; cơ chế thẩm định thiết kế giai đoạn 2021-2026 chuyển giao sang Chủ đầu tư tự phê duyệt theo Luật 135/2025</t>
         </is>
       </c>
       <c r="L13" s="10" t="inlineStr">
@@ -1421,10 +1471,14 @@
           <t>ALL, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01, LICHSU</t>
         </is>
       </c>
-      <c r="M13" s="15" t="inlineStr"/>
+      <c r="M13" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=62/2020/QH14</t>
+        </is>
+      </c>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1533,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Nghị định xương sống hiện hành về thẩm tra, thẩm định thiết kế, dự toán và quản lý dự án xây dựng</t>
+          <t>Có hiệu lực từ 01/07/2026; hướng dẫn bãi bỏ thẩm định thiết kế sau TKCS của CQCM; CĐT tự duyệt TKBVTC qua tư vấn thẩm tra độc lập TV-05</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -1487,10 +1541,14 @@
           <t>ALL, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr"/>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=217/2026/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1573,7 @@
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 15/2021/NĐ-CP quy định chi tiết một số nội dung về quản lý dự án đầu tư xây dựng</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 15/2021/NĐ-CP về quản lý dự án ĐTXD (Đã hết hiệu lực)</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
@@ -1545,7 +1603,7 @@
       </c>
       <c r="K15" s="10" t="inlineStr">
         <is>
-          <t>Hết hiệu lực từ 01/07/2026</t>
+          <t>Hết hiệu lực từ 01/07/2026; kết quả thẩm định thiết kế đã có trước 01/07/2026 giữ nguyên giá trị pháp lý</t>
         </is>
       </c>
       <c r="L15" s="10" t="inlineStr">
@@ -1553,10 +1611,14 @@
           <t>ALL, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01, LICHSU</t>
         </is>
       </c>
-      <c r="M15" s="15" t="inlineStr"/>
+      <c r="M15" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=175/2024/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1643,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số nội dung về quản lý dự án đầu tư xây dựng</t>
+          <t>Quy định chi tiết một số nội dung về quản lý dự án đầu tư xây dựng (Đã hết hiệu lực)</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -1611,7 +1673,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Hết hiệu lực toàn bộ</t>
+          <t>Hết hiệu lực từ 01/07/2026; chứng chỉ hành nghề và chứng chỉ năng lực tổ chức đã cấp trước 01/07/2026 có giá trị đến khi hết hạn</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -1619,10 +1681,14 @@
           <t>ALL, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01, LICHSU</t>
         </is>
       </c>
-      <c r="M16" s="8" t="inlineStr"/>
+      <c r="M16" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=15/2021/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -1685,10 +1751,14 @@
           <t>ALL, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
-      <c r="M17" s="15" t="inlineStr"/>
+      <c r="M17" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=35/2023/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -1738,12 +1808,12 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Văn bản gốc / Ban hành lần đầu</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Quy định biện pháp an toàn lao động bắt buộc trong thi công xây dựng và giám sát công trường</t>
+          <t>Quy định biện pháp an toàn lao động bắt buộc trên công trường thi công xây dựng (XD-01) và giám sát (TV-08)</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -1751,10 +1821,14 @@
           <t>AN_TOAN_LAO_DONG, TV-08, XD-01</t>
         </is>
       </c>
-      <c r="M18" s="8" t="inlineStr"/>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=84/2015/QH13</t>
+        </is>
+      </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1883,7 @@
       </c>
       <c r="K19" s="10" t="inlineStr">
         <is>
-          <t>Luật đấu thầu nền tảng chi phối toàn bộ các gói thầu TV, XD, PTV của dự án</t>
+          <t>Luật đấu thầu nền tảng chi phối toàn bộ 11 gói thầu TV, XD, PTV của dự án trên Hệ thống mạng đấu thầu quốc gia</t>
         </is>
       </c>
       <c r="L19" s="10" t="inlineStr">
@@ -1817,10 +1891,14 @@
           <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
         </is>
       </c>
-      <c r="M19" s="15" t="inlineStr"/>
+      <c r="M19" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=22/2023/QH15</t>
+        </is>
+      </c>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1923,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Luật sửa đổi, bổ sung một số điều của Luật Quy hoạch, Luật Đầu tư, Luật Đầu tư theo phương thức đối tác công tư và Luật Đấu thầu</t>
+          <t>Luật sửa đổi, bổ sung một số điều của Luật Quy hoạch, Luật Đầu tư, Luật PPP và Luật Đấu thầu</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -1883,10 +1961,14 @@
           <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
         </is>
       </c>
-      <c r="M20" s="8" t="inlineStr"/>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=57/2024/QH15</t>
+        </is>
+      </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1993,7 @@
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>Luật sửa đổi, bổ sung một số điều của Luật Đấu thầu, Luật Đầu tư công, Luật Quản lý tài sản công</t>
+          <t>Luật sửa đổi, bổ sung một số điều của Luật Đấu thầu, Luật Đầu tư công, Luật Quản lý TSC</t>
         </is>
       </c>
       <c r="F21" s="13" t="inlineStr">
@@ -1941,7 +2023,7 @@
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
-          <t>Phân cấp triệt để thẩm quyền lựa chọn nhà thầu cho Chủ đầu tư và nâng hạn mức chỉ định thầu</t>
+          <t>Có hiệu lực từ 01/07/2025; nâng hạn mức chỉ định thầu rút gọn (500 triệu gói TV/PTV, 01 tỷ gói XD); phân cấp triệt để CĐT duyệt E-HSMT</t>
         </is>
       </c>
       <c r="L21" s="10" t="inlineStr">
@@ -1949,10 +2031,14 @@
           <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
         </is>
       </c>
-      <c r="M21" s="15" t="inlineStr"/>
+      <c r="M21" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=90/2025/QH15</t>
+        </is>
+      </c>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -1977,7 +2063,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Luật Đấu thầu năm 2013</t>
+          <t>Luật Đấu thầu năm 2013 (Đã hết hiệu lực từ 01/01/2024)</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -2007,7 +2093,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Hết hiệu lực từ 01/01/2024</t>
+          <t>Hết hiệu lực từ 01/01/2024; gói thầu phát hành HSMT trước 01/01/2024 tiếp tục thực hiện theo Luật 43/2013 đến khi quyết toán</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -2015,10 +2101,14 @@
           <t>ALL, DAU_THAU, LICHSU</t>
         </is>
       </c>
-      <c r="M22" s="8" t="inlineStr"/>
+      <c r="M22" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=43/2013/QH13</t>
+        </is>
+      </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2163,7 @@
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
-          <t>Nghị định xương sống hiện hành về quy trình chỉ định thầu rút gọn, đấu thầu rộng rãi qua mạng</t>
+          <t>Có hiệu lực từ 04/08/2025; nâng hạn mức chỉ định thầu rút gọn (xây lắp 2 tỷ, mua sắm 500tr); bãi bỏ thẩm định KHLCNT tổng thể</t>
         </is>
       </c>
       <c r="L23" s="10" t="inlineStr">
@@ -2081,10 +2171,14 @@
           <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
         </is>
       </c>
-      <c r="M23" s="15" t="inlineStr"/>
+      <c r="M23" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=214/2025/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2203,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Đấu thầu về lựa chọn nhà thầu</t>
+          <t>Quy định chi tiết thi hành Luật Đấu thầu về lựa chọn nhà thầu (Đã hết hiệu lực)</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -2139,7 +2233,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng chuyển tiếp cho các gói thầu phát hành E-HSMT trước 04/08/2025</t>
+          <t>Hết hiệu lực từ 04/08/2025; áp dụng chuyển tiếp cho các gói thầu đã phát hành E-HSMT trước 04/08/2025</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -2147,10 +2241,14 @@
           <t>ALL, DAU_THAU, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01, LICHSU</t>
         </is>
       </c>
-      <c r="M24" s="8" t="inlineStr"/>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=24/2024/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2273,7 @@
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết thi hành một số điều của Luật Đấu thầu về lựa chọn nhà thầu</t>
+          <t>Quy định chi tiết thi hành một số điều của Luật Đấu thầu (Đã hết hiệu lực)</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
@@ -2200,7 +2298,7 @@
       </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 24/2024/NĐ-CP, Bị thay thế bởi 24/2024/NĐ-CP</t>
+          <t>Bị thay thế bởi 24/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="K25" s="10" t="inlineStr">
@@ -2213,10 +2311,14 @@
           <t>ALL, DAU_THAU, LICHSU</t>
         </is>
       </c>
-      <c r="M25" s="15" t="inlineStr"/>
+      <c r="M25" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=63/2014/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2343,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Hướng dẫn việc cung cấp, đăng tải thông tin về đấu thầu và mẫu hồ sơ đấu thầu trên Hệ thống mạng đấu thầu quốc gia</t>
+          <t>Hướng dẫn việc cung cấp, đăng tải thông tin về đấu thầu và mẫu hồ sơ đấu thầu trên e-GP</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -2271,7 +2373,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>Ban hành toàn bộ biểu mẫu E-HSMT xây lắp, tư vấn, phi tư vấn, E-HSYC chỉ định thầu hiện hành</t>
+          <t>Có hiệu lực từ 04/08/2025; ban hành toàn bộ biểu mẫu E-HSMT xây lắp, tư vấn (TV-04, TV-06, XD-01) trên Hệ thống e-GP</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -2279,10 +2381,14 @@
           <t>ALL, DAU_THAU, E_HSMT, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, XD-01</t>
         </is>
       </c>
-      <c r="M26" s="8" t="inlineStr"/>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=79/2025/TT-BTC</t>
+        </is>
+      </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2413,7 @@
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>Hướng dẫn việc cung cấp, đăng tải thông tin về đấu thầu và mẫu hồ sơ đấu thầu trên Hệ thống mạng đấu thầu quốc gia</t>
+          <t>Hướng dẫn đăng tải thông tin và mẫu hồ sơ đấu thầu trên e-GP (Đã hết hiệu lực)</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
@@ -2345,10 +2451,14 @@
           <t>ALL, DAU_THAU, E_HSMT, LICHSU</t>
         </is>
       </c>
-      <c r="M27" s="15" t="inlineStr"/>
+      <c r="M27" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=06/2024/TT-BKH%C4%90T</t>
+        </is>
+      </c>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2513,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng lập HSYC và đánh giá hồ sơ đề xuất gói thầu mua sắm hàng hóa, doanh cụ</t>
+          <t>Có hiệu lực từ 08/08/2025; áp dụng lập HSYC và đánh giá hồ sơ đề xuất gói thầu mua sắm hàng hóa, doanh cụ</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -2411,10 +2521,14 @@
           <t>ALL, DAU_THAU, E_HSMT, TV-06, XD-01</t>
         </is>
       </c>
-      <c r="M28" s="8" t="inlineStr"/>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=80/2025/TT-BTC</t>
+        </is>
+      </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2583,7 @@
       </c>
       <c r="K29" s="10" t="inlineStr">
         <is>
-          <t>Quy định phương pháp lập và quản lý Tổng mức đầu tư, Dự toán xây dựng công trình hiện hành</t>
+          <t>Có hiệu lực từ 01/07/2026; chuẩn hóa 4 phương pháp lập TMĐT; trao quyền cho Chủ đầu tư tự phê duyệt dự toán chi phí chuẩn bị đầu tư và dự toán gói thầu</t>
         </is>
       </c>
       <c r="L29" s="10" t="inlineStr">
@@ -2477,10 +2591,14 @@
           <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
         </is>
       </c>
-      <c r="M29" s="15" t="inlineStr"/>
+      <c r="M29" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=206/2026/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N29" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2623,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Về quản lý chi phí đầu tư xây dựng</t>
+          <t>Về quản lý chi phí đầu tư xây dựng (Hết hiệu lực từ 01/07/2026)</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -2535,7 +2653,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>Dự án đã phê duyệt dự toán trước 01/07/2026 thực hiện theo điều khoản chuyển tiếp của NĐ 206</t>
+          <t>Hết hiệu lực từ 01/07/2026; dự án đã phê duyệt dự toán trước 01/07/2026 thực hiện theo điều khoản chuyển tiếp của NĐ 206</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -2543,10 +2661,14 @@
           <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01, LICHSU</t>
         </is>
       </c>
-      <c r="M30" s="8" t="inlineStr"/>
+      <c r="M30" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=10/2021/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2723,7 @@
       </c>
       <c r="K31" s="10" t="inlineStr">
         <is>
-          <t>Quy định cơ cấu chi phí xây dựng, chi phí gián tiếp, chi phí chung trong dự toán mới nhất</t>
+          <t>Có hiệu lực từ 01/07/2026; quy định cơ cấu chi phí xây dựng, phương pháp tính chi phí gián tiếp và chi phí chung trong dự toán mới nhất</t>
         </is>
       </c>
       <c r="L31" s="10" t="inlineStr">
@@ -2609,10 +2731,14 @@
           <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, TV-01, TV-02, TV-03, TV-04, TV-05, XD-01</t>
         </is>
       </c>
-      <c r="M31" s="15" t="inlineStr"/>
+      <c r="M31" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=36/2026/TT-BXD</t>
+        </is>
+      </c>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2793,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>Hệ thống định mức xây dựng và tỷ lệ % chi phí quản lý dự án, tư vấn thiết kế, giám sát mới nhất</t>
+          <t>Có hiệu lực từ 01/07/2026; ban hành hệ thống định mức dự toán mới và tỷ lệ % chi phí tư vấn lập BCNCKT (TV-03), TKBVTC (TV-04), thẩm tra (TV-05), giám sát (TV-08), kiểm toán (TV-09)</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -2675,10 +2801,14 @@
           <t>ALL, DINH_MUC, DU_TOAN, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-08, TV-09, XD-01</t>
         </is>
       </c>
-      <c r="M32" s="8" t="inlineStr"/>
+      <c r="M32" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=38/2026/TT-BXD</t>
+        </is>
+      </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2833,7 @@
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>Ban hành định mức xây dựng</t>
+          <t>Ban hành định mức xây dựng (Hết hiệu lực từ 01/07/2026)</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
@@ -2741,10 +2871,14 @@
           <t>ALL, DINH_MUC, DU_TOAN, LICHSU</t>
         </is>
       </c>
-      <c r="M33" s="15" t="inlineStr"/>
+      <c r="M33" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=12/2021/TT-BXD</t>
+        </is>
+      </c>
       <c r="N33" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2903,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số định mức xây dựng ban hành tại Thông tư số 12/2021/TT-BXD</t>
+          <t>Sửa đổi, bổ sung một số định mức xây dựng ban hành tại Thông tư số 12/2021/TT-BXD (Hết hiệu lực 01/07/2026)</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -2807,10 +2941,14 @@
           <t>ALL, DINH_MUC, DU_TOAN, LICHSU</t>
         </is>
       </c>
-      <c r="M34" s="8" t="inlineStr"/>
+      <c r="M34" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=09/2024/TT-BXD</t>
+        </is>
+      </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2973,7 @@
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 11/2021/TT-BXD hướng dẫn một số nội dung xác định và quản lý chi phí đầu tư xây dựng</t>
+          <t>Sửa đổi, bổ sung Thông tư 11/2021/TT-BXD về quản lý chi phí (Hết hiệu lực 01/07/2026)</t>
         </is>
       </c>
       <c r="F35" s="13" t="inlineStr">
@@ -2873,10 +3011,14 @@
           <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, LICHSU</t>
         </is>
       </c>
-      <c r="M35" s="15" t="inlineStr"/>
+      <c r="M35" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=01/2025/TT-BXD</t>
+        </is>
+      </c>
       <c r="N35" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -2901,7 +3043,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Hướng dẫn một số nội dung xác định và quản lý chi phí đầu tư xây dựng</t>
+          <t>Hướng dẫn xác định và quản lý chi phí đầu tư xây dựng (Hết hiệu lực từ 01/07/2026)</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -2939,10 +3081,14 @@
           <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, LICHSU</t>
         </is>
       </c>
-      <c r="M36" s="8" t="inlineStr"/>
+      <c r="M36" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=11/2021/TT-BXD</t>
+        </is>
+      </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -2967,7 +3113,7 @@
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 11/2021/TT-BXD hướng dẫn một số nội dung xác định và quản lý chi phí đầu tư xây dựng</t>
+          <t>Sửa đổi, bổ sung Thông tư số 11/2021/TT-BXD về quản lý chi phí (Hết hiệu lực 01/07/2026)</t>
         </is>
       </c>
       <c r="F37" s="13" t="inlineStr">
@@ -3005,10 +3151,14 @@
           <t>ALL, DU_TOAN, QUAN_LY_CHI_PHI, LICHSU</t>
         </is>
       </c>
-      <c r="M37" s="15" t="inlineStr"/>
+      <c r="M37" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=14/2023/TT-BXD</t>
+        </is>
+      </c>
       <c r="N37" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3208,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Văn bản gốc / Ban hành lần đầu</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
@@ -3071,10 +3221,14 @@
           <t>ALL, DU_TOAN, DO_BOC_KHOI_LUONG, TV-04, TV-05, XD-01</t>
         </is>
       </c>
-      <c r="M38" s="8" t="inlineStr"/>
+      <c r="M38" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=13/2021/TT-BXD</t>
+        </is>
+      </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3283,7 @@
       </c>
       <c r="K39" s="10" t="inlineStr">
         <is>
-          <t>Suất vốn đầu tư hiện hành phục vụ tính Tổng mức đầu tư BCNCKT (FS/BKTKT gói TV-02, TV-03)</t>
+          <t>Ban hành ngày 30/03/2026; căn cứ tính Tổng mức đầu tư Báo cáo NCKT (gói TV-02, TV-03)</t>
         </is>
       </c>
       <c r="L39" s="10" t="inlineStr">
@@ -3137,10 +3291,14 @@
           <t>SUAT_VON_DAU_TU, TMDT, TV-01, TV-02, TV-03, TV-04</t>
         </is>
       </c>
-      <c r="M39" s="15" t="inlineStr"/>
+      <c r="M39" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=425/Q%C4%90-BXD</t>
+        </is>
+      </c>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3323,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Công bố Suất vốn đầu tư xây dựng công trình và giá xây dựng tổng hợp bộ phận kết cấu công trình năm 2023</t>
+          <t>Công bố Suất vốn đầu tư xây dựng công trình và giá xây dựng tổng hợp năm 2023 (Hết hiệu lực)</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -3203,10 +3361,14 @@
           <t>SUAT_VON_DAU_TU, TMDT, LICHSU</t>
         </is>
       </c>
-      <c r="M40" s="8" t="inlineStr"/>
+      <c r="M40" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=510/Q%C4%90-BXD</t>
+        </is>
+      </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3393,7 @@
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết và biện pháp thực hiện một số nội dung Luật Xây dựng thuộc phạm vi quản lý của Bộ Quốc phòng</t>
+          <t>Quy định chi tiết và biện pháp thực hiện một số nội dung Luật Xây dựng thuộc phạm vi Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F41" s="13" t="inlineStr">
@@ -3256,12 +3418,12 @@
       </c>
       <c r="J41" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Thay thế Thông tư 106/2021/TT-BQP</t>
         </is>
       </c>
       <c r="K41" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng cho các dự án đầu tư xây dựng công trình trong toàn Bộ Quốc phòng</t>
+          <t>Có hiệu lực từ 09/07/2026; hướng dẫn chi tiết quy chuẩn xây dựng công trình quốc phòng, thẩm quyền kiểm tra nghiệm thu của Cục Doanh trại, kiểm tra trực tuyến và ứng dụng BIM</t>
         </is>
       </c>
       <c r="L41" s="10" t="inlineStr">
@@ -3269,10 +3431,14 @@
           <t>ALL, BQP, QLDA, XD-01, TOAN_QUAN</t>
         </is>
       </c>
-      <c r="M41" s="15" t="inlineStr"/>
+      <c r="M41" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=101/2026/TT-BQP</t>
+        </is>
+      </c>
       <c r="N41" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3463,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Quy định và hướng dẫn về lập, thẩm định, quyết định, phân cấp quyết định chủ trương đầu tư, dự án đầu tư trong Bộ Quốc phòng</t>
+          <t>Quy định về lập, thẩm định, quyết định, phân cấp quyết định chủ trương và dự án đầu tư trong BQP</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -3327,7 +3493,7 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>Văn bản xương sống về phân cấp, ủy quyền quyết định đầu tư và dự án đầu tư công mới nhất trong BQP</t>
+          <t>Có hiệu lực từ 17/07/2026; phân cấp toàn diện chủ trương đầu tư, thẩm định BCNCKT, phê duyệt KHLCNT và phê duyệt dự toán cho Tư lệnh/Chủ đầu tư theo từng hạn mức nhóm dự án</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -3335,10 +3501,14 @@
           <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
-      <c r="M42" s="8" t="inlineStr"/>
+      <c r="M42" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=102/2026/TT-BQP</t>
+        </is>
+      </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3533,7 @@
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>Quy định phân cấp, ủy quyền quyết định chủ trương đầu tư và dự án đầu tư công trong Bộ Quốc phòng</t>
+          <t>Quy định phân cấp, ủy quyền chủ trương và dự án đầu tư công trong BQP (Hết hiệu lực 17/07/2026)</t>
         </is>
       </c>
       <c r="F43" s="13" t="inlineStr">
@@ -3393,7 +3563,7 @@
       </c>
       <c r="K43" s="10" t="inlineStr">
         <is>
-          <t>Áp dụng phân cấp thẩm quyền đầu tư BQP giai đoạn 2021-2026</t>
+          <t>Hết hiệu lực từ 17/07/2026; dự án đã duyệt chủ trương hoặc đang thẩm định trước 17/07/2026 tiếp tục áp dụng TT 128</t>
         </is>
       </c>
       <c r="L43" s="10" t="inlineStr">
@@ -3401,10 +3571,14 @@
           <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01, LICHSU</t>
         </is>
       </c>
-      <c r="M43" s="15" t="inlineStr"/>
+      <c r="M43" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=128/2021/TT-BQP</t>
+        </is>
+      </c>
       <c r="N43" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -3429,7 +3603,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 128/2021/TT-BQP ngày 01/10/2021 về quy định phân cấp, ủy quyền quyết định chủ trương đầu tư và dự án đầu tư công trong BQP</t>
+          <t>Sửa đổi Thông tư 128/2021/TT-BQP về phân cấp đầu tư công BQP (Hết hiệu lực 17/07/2026)</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -3459,7 +3633,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>Cập nhật phân cấp đầu tư BQP giai đoạn 2023-2026</t>
+          <t>Hết hiệu lực từ 17/07/2026</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -3467,10 +3641,14 @@
           <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01, LICHSU</t>
         </is>
       </c>
-      <c r="M44" s="8" t="inlineStr"/>
+      <c r="M44" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=73/2023/TT-BQP</t>
+        </is>
+      </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3673,7 @@
       </c>
       <c r="E45" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 128/2021/TT-BQP về phân cấp quản lý và thực hiện dự án đầu tư công trong Bộ Quốc phòng</t>
+          <t>Sửa đổi Thông tư 128/2021/TT-BQP về phân cấp dự án đầu tư công BQP (Hết hiệu lực 17/07/2026)</t>
         </is>
       </c>
       <c r="F45" s="13" t="inlineStr">
@@ -3525,7 +3703,7 @@
       </c>
       <c r="K45" s="10" t="inlineStr">
         <is>
-          <t>Phân cấp phê duyệt thiết kế, dự toán BQP giai đoạn 2024-2026</t>
+          <t>Hết hiệu lực từ 17/07/2026</t>
         </is>
       </c>
       <c r="L45" s="10" t="inlineStr">
@@ -3533,10 +3711,14 @@
           <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01, LICHSU</t>
         </is>
       </c>
-      <c r="M45" s="15" t="inlineStr"/>
+      <c r="M45" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=120/2024/TT-BQP</t>
+        </is>
+      </c>
       <c r="N45" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3743,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Quy định về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng trong Bộ Quốc phòng</t>
+          <t>Quy định về quản lý chất lượng, thi công xây dựng và bảo trì công trình trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -3591,7 +3773,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>Quy chuẩn nghiệm thu và quản lý chất lượng công trình quân sự</t>
+          <t>Quy chuẩn nghiệm thu và quản lý chất lượng công trình quân sự (áp dụng song song phần sửa đổi của TT 24/2025)</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -3599,10 +3781,14 @@
           <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
         </is>
       </c>
-      <c r="M46" s="8" t="inlineStr"/>
+      <c r="M46" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=174/2021/TT-BQP</t>
+        </is>
+      </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3813,7 @@
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 174/2021/TT-BQP về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng trong Bộ Quốc phòng</t>
+          <t>Sửa đổi, bổ sung Thông tư số 174/2021/TT-BQP về quản lý chất lượng công trình trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F47" s="13" t="inlineStr">
@@ -3652,12 +3838,12 @@
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung Thông tư 174/2021/TT-BQP về quản lý chất lượng công trình BQP</t>
+          <t>Sửa đổi, bổ sung Thông tư 174/2021/TT-BQP</t>
         </is>
       </c>
       <c r="K47" s="10" t="inlineStr">
         <is>
-          <t>Quy chuẩn kiểm tra công tác nghiệm thu công trình quân sự đặc thù hiện hành</t>
+          <t>Có hiệu lực từ 20/06/2025; bãi bỏ Điều 4, 6, 7; thay thế các biểu mẫu nghiệm thu mới và phân loại công trình quốc phòng Loại A, Loại B</t>
         </is>
       </c>
       <c r="L47" s="10" t="inlineStr">
@@ -3665,10 +3851,14 @@
           <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
         </is>
       </c>
-      <c r="M47" s="15" t="inlineStr"/>
+      <c r="M47" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=24/2025/TT-BQP</t>
+        </is>
+      </c>
       <c r="N47" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3913,7 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>Điều lệ xương sống về quy hoạch tổng mặt bằng, bảo dưỡng, quản lý và sử dụng doanh trại</t>
+          <t>Có hiệu lực từ 13/07/2023; điều lệ 10 chương, 60 điều chi phối toàn diện quy hoạch tổng mặt bằng, bảo dưỡng, quản lý và sử dụng doanh trại</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -3731,10 +3921,14 @@
           <t>BQP, DOANH_TRAI, TV-01, TV-02, TV-04, XD-01</t>
         </is>
       </c>
-      <c r="M48" s="8" t="inlineStr"/>
+      <c r="M48" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=36/2023/TT-BQP</t>
+        </is>
+      </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3953,7 @@
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>Quy định về tiêu chuẩn, định mức sử dụng máy móc, thiết bị văn phòng phổ biến thuộc phạm vi quản lý của Bộ Quốc phòng</t>
+          <t>Quy định tiêu chuẩn, định mức sử dụng máy móc, thiết bị văn phòng trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F49" s="13" t="inlineStr">
@@ -3789,7 +3983,7 @@
       </c>
       <c r="K49" s="10" t="inlineStr">
         <is>
-          <t>Tiêu chuẩn định mức máy móc, thiết bị làm việc của cán bộ sĩ quan BQP (gói Doanh cụ XD-01)</t>
+          <t>Tiêu chuẩn định mức máy móc, thiết bị làm việc của cán bộ sĩ quan BQP (áp dụng trực tiếp cho gói Doanh cụ XD-01)</t>
         </is>
       </c>
       <c r="L49" s="10" t="inlineStr">
@@ -3797,10 +3991,14 @@
           <t>BQP, DOANH_TRAI, TV-01, TV-02, TV-04, XD-01</t>
         </is>
       </c>
-      <c r="M49" s="15" t="inlineStr"/>
+      <c r="M49" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=150/2018/TT-BQP</t>
+        </is>
+      </c>
       <c r="N49" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -3825,7 +4023,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều của Luật Nhà ở áp dụng trong Bộ Quốc phòng (Mẫu giấy tờ nhà ở công vụ và dự án nhà ở LLVT)</t>
+          <t>Quy định chi tiết một số điều của Luật Nhà ở áp dụng trong Bộ Quốc phòng</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -3850,12 +4048,12 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Văn bản gốc / Ban hành lần đầu</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>Áp dụng cho các dự án đầu tư xây dựng nhà ở cho lực lượng vũ trang thuộc BQP</t>
+          <t>Áp dụng cho các dự án đầu tư xây dựng nhà ở công vụ và nhà ở cho lực lượng vũ trang thuộc BQP</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
@@ -3863,10 +4061,14 @@
           <t>BQP, DOANH_TRAI, TV-01, TV-02, TV-04, XD-01</t>
         </is>
       </c>
-      <c r="M50" s="8" t="inlineStr"/>
+      <c r="M50" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=94/2024/TT-BQP</t>
+        </is>
+      </c>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -3916,7 +4118,7 @@
       </c>
       <c r="J51" s="10" t="inlineStr">
         <is>
-          <t>Quyết định số 12/QĐ-TTg</t>
+          <t>Thay thế Quyết định số 12/QĐ-TTg</t>
         </is>
       </c>
       <c r="K51" s="10" t="inlineStr">
@@ -3929,10 +4131,14 @@
           <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
-      <c r="M51" s="15" t="inlineStr"/>
+      <c r="M51" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=35/Q%C4%90-TTg</t>
+        </is>
+      </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -3957,7 +4163,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số nội dung về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng</t>
+          <t>Quy định chi tiết một số nội dung về quản lý chất lượng, thi công xây dựng và bảo trì công trình</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
@@ -3987,7 +4193,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>Nghị định hiện hành chi phối quản lý chất lượng, nhật ký điện tử và nghiệm thu công trình</t>
+          <t>Có hiệu lực từ 01/07/2026; bắt buộc áp dụng Nhật ký thi công điện tử, số hóa biên bản nghiệm thu; phân cấp kiểm tra công tác nghiệm thu đưa công trình vào sử dụng (TV-08, XD-01)</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -3995,10 +4201,14 @@
           <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
         </is>
       </c>
-      <c r="M52" s="8" t="inlineStr"/>
+      <c r="M52" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=207/2026/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4233,7 @@
       </c>
       <c r="E53" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số nội dung về quản lý chất lượng, thi công xây dựng và bảo trì công trình xây dựng</t>
+          <t>Quy định về quản lý chất lượng, thi công và bảo trì công trình (Hết hiệu lực 01/07/2026)</t>
         </is>
       </c>
       <c r="F53" s="13" t="inlineStr">
@@ -4053,7 +4263,7 @@
       </c>
       <c r="K53" s="10" t="inlineStr">
         <is>
-          <t>Hết hiệu lực từ 01/07/2026</t>
+          <t>Hết hiệu lực từ 01/07/2026; biên bản nghiệm thu đã lập theo NĐ 06/2021 trước 01/07/2026 giữ nguyên giá trị pháp lý</t>
         </is>
       </c>
       <c r="L53" s="10" t="inlineStr">
@@ -4061,10 +4271,14 @@
           <t>CHAT_LUONG, NGHIEM_THU, LICHSU</t>
         </is>
       </c>
-      <c r="M53" s="15" t="inlineStr"/>
+      <c r="M53" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=06/2021/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N53" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4328,7 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Văn bản gốc / Ban hành lần đầu</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
@@ -4127,10 +4341,14 @@
           <t>CHAT_LUONG, NGHIEM_THU, TV-01, TV-02, TV-04, TV-05, TV-07, TV-08, XD-01</t>
         </is>
       </c>
-      <c r="M54" s="8" t="inlineStr"/>
+      <c r="M54" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=10/2021/TT-BXD</t>
+        </is>
+      </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -4185,7 +4403,7 @@
       </c>
       <c r="K55" s="10" t="inlineStr">
         <is>
-          <t>Nghị định xương sống hiện hành về hợp đồng xây dựng, tạm ứng, điều chỉnh giá và thanh lý hợp đồng</t>
+          <t>Có hiệu lực từ 01/07/2026; tạm ứng tối thiểu 10% tối đa 50%; điều chỉnh giá hợp đồng trọn gói; giải quyết tranh chấp qua Ban xử lý tranh chấp và Hòa giải viên</t>
         </is>
       </c>
       <c r="L55" s="10" t="inlineStr">
@@ -4193,10 +4411,14 @@
           <t>ALL, HOP_DONG, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
         </is>
       </c>
-      <c r="M55" s="15" t="inlineStr"/>
+      <c r="M55" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=210/2026/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N55" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4443,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết về hợp đồng xây dựng</t>
+          <t>Quy định chi tiết về hợp đồng xây dựng (Hết hiệu lực từ 01/07/2026)</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -4251,7 +4473,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>Hết hiệu lực từ 01/07/2026; áp dụng chuyển tiếp cho các hợp đồng đã ký trước 01/07/2026</t>
+          <t>Hết hiệu lực từ 01/07/2026; hợp đồng đã ký trước 01/07/2026 tiếp tục thực hiện theo điều khoản hợp đồng đã ký</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
@@ -4259,10 +4481,14 @@
           <t>ALL, HOP_DONG, LICHSU</t>
         </is>
       </c>
-      <c r="M56" s="8" t="inlineStr"/>
+      <c r="M56" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=37/2015/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4513,7 @@
       </c>
       <c r="E57" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 37/2015/NĐ-CP quy định chi tiết về hợp đồng xây dựng</t>
+          <t>Sửa đổi, bổ sung Nghị định số 37/2015/NĐ-CP về hợp đồng xây dựng (Hết hiệu lực 01/07/2026)</t>
         </is>
       </c>
       <c r="F57" s="13" t="inlineStr">
@@ -4325,10 +4551,14 @@
           <t>ALL, HOP_DONG, LICHSU</t>
         </is>
       </c>
-      <c r="M57" s="15" t="inlineStr"/>
+      <c r="M57" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=50/2021/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N57" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4608,7 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Văn bản gốc / Ban hành lần đầu</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
@@ -4391,10 +4621,14 @@
           <t>ALL, HOP_DONG, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
         </is>
       </c>
-      <c r="M58" s="8" t="inlineStr"/>
+      <c r="M58" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=02/2023/TT-BXD</t>
+        </is>
+      </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -4457,10 +4691,14 @@
           <t>THI_NGHIEM_COC, TV-07, XD-01</t>
         </is>
       </c>
-      <c r="M59" s="15" t="inlineStr"/>
+      <c r="M59" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=TCVN%209393%3A2012</t>
+        </is>
+      </c>
       <c r="N59" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4748,7 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Văn bản gốc / Ban hành lần đầu</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
@@ -4523,10 +4761,14 @@
           <t>KHAO_SAT, TV-02</t>
         </is>
       </c>
-      <c r="M60" s="8" t="inlineStr"/>
+      <c r="M60" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=TCVN%209363%3A2012</t>
+        </is>
+      </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4818,7 @@
       </c>
       <c r="J61" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Văn bản gốc / Ban hành lần đầu</t>
         </is>
       </c>
       <c r="K61" s="10" t="inlineStr">
@@ -4589,10 +4831,14 @@
           <t>DO_DAC, TV-01</t>
         </is>
       </c>
-      <c r="M61" s="15" t="inlineStr"/>
+      <c r="M61" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=TCVN%209401%3A2012</t>
+        </is>
+      </c>
       <c r="N61" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -4655,10 +4901,14 @@
           <t>BAO_HIEM, PTV-01, XD-01</t>
         </is>
       </c>
-      <c r="M62" s="8" t="inlineStr"/>
+      <c r="M62" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=08/2022/QH15</t>
+        </is>
+      </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4933,7 @@
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>Quy định về bảo hiểm bắt buộc trách nhiệm dân sự của chủ xe cơ giới, bảo hiểm cháy, nổ bắt buộc, bảo hiểm bắt buộc trong hoạt động đầu tư xây dựng</t>
+          <t>Quy định về bảo hiểm bắt buộc trong hoạt động đầu tư xây dựng</t>
         </is>
       </c>
       <c r="F63" s="13" t="inlineStr">
@@ -4721,10 +4971,14 @@
           <t>BAO_HIEM, PTV-01, XD-01</t>
         </is>
       </c>
-      <c r="M63" s="15" t="inlineStr"/>
+      <c r="M63" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=67/2023/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N63" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -4774,7 +5028,7 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Văn bản gốc / Ban hành lần đầu</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
@@ -4787,10 +5041,14 @@
           <t>KIEM_TOAN, TV-09</t>
         </is>
       </c>
-      <c r="M64" s="8" t="inlineStr"/>
+      <c r="M64" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=67/2011/QH12</t>
+        </is>
+      </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -4815,7 +5073,7 @@
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>Ban hành Chuẩn mực kiểm toán Việt Nam số 1000 - Kiểm toán báo cáo quyết toán dự án hoàn thành (VSA 1000)</t>
+          <t>Ban hành Chuẩn mực kiểm toán Việt Nam số 1000 - Kiểm toán quyết toán dự án hoàn thành (VSA 1000)</t>
         </is>
       </c>
       <c r="F65" s="13" t="inlineStr">
@@ -4840,7 +5098,7 @@
       </c>
       <c r="J65" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Văn bản gốc / Ban hành lần đầu</t>
         </is>
       </c>
       <c r="K65" s="10" t="inlineStr">
@@ -4853,10 +5111,14 @@
           <t>KIEM_TOAN, TV-09</t>
         </is>
       </c>
-      <c r="M65" s="15" t="inlineStr"/>
+      <c r="M65" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=67/2015/TT-BTC</t>
+        </is>
+      </c>
       <c r="N65" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -4919,10 +5181,14 @@
           <t>ALL, DAU_TU_CONG, CHU_TRUONG, TV-01, TV-02, TV-03, TV-09</t>
         </is>
       </c>
-      <c r="M66" s="8" t="inlineStr"/>
+      <c r="M66" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=58/2024/QH15</t>
+        </is>
+      </c>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -4947,7 +5213,7 @@
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>Luật Đầu tư công năm 2019</t>
+          <t>Luật Đầu tư công năm 2019 (Đã hết hiệu lực từ 01/01/2025)</t>
         </is>
       </c>
       <c r="F67" s="13" t="inlineStr">
@@ -4985,10 +5251,14 @@
           <t>ALL, DAU_TU_CONG, LICHSU</t>
         </is>
       </c>
-      <c r="M67" s="15" t="inlineStr"/>
+      <c r="M67" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=39/2019/QH14</t>
+        </is>
+      </c>
       <c r="N67" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5308,7 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Văn bản gốc / Ban hành lần đầu</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
@@ -5051,10 +5321,14 @@
           <t>ALL, DAU_TU_CONG, TV-01, TV-02, TV-03</t>
         </is>
       </c>
-      <c r="M68" s="8" t="inlineStr"/>
+      <c r="M68" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=40/2020/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5383,7 @@
       </c>
       <c r="K69" s="10" t="inlineStr">
         <is>
-          <t>Nghị định xương sống hiện hành về thẩm tra, phê duyệt quyết toán vốn đầu tư công dự án hoàn thành</t>
+          <t>Có hiệu lực từ 26/09/2025; rút ngắn thời gian thanh toán KBNN còn 02 ngày làm việc; hạn lập hồ sơ quyết toán A-B không quá 06 tháng nhóm C (TV-09, XD-01)</t>
         </is>
       </c>
       <c r="L69" s="10" t="inlineStr">
@@ -5117,10 +5391,14 @@
           <t>ALL, QUYET_TOAN, TAI_CHINH, TV-09, XD-01</t>
         </is>
       </c>
-      <c r="M69" s="15" t="inlineStr"/>
+      <c r="M69" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=254/2025/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N69" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -5145,7 +5423,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Quy định về quản lý, thanh toán, quyết toán dự án sử dụng vốn đầu tư công</t>
+          <t>Quy định quản lý, thanh quyết toán vốn đầu tư công (Hết hiệu lực từ 26/09/2025)</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
@@ -5175,7 +5453,7 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>Đã bị thay thế phần lớn bởi NĐ 254/2025/NĐ-CP (chỉ còn áp dụng chuyển tiếp cho một số trường hợp cụ thể)</t>
+          <t>Hết hiệu lực từ 26/09/2025; hồ sơ quyết toán đã nộp trước 26/09/2025 tiếp tục thẩm tra theo NĐ 99/2021</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
@@ -5183,10 +5461,14 @@
           <t>ALL, QUYET_TOAN, TAI_CHINH, LICHSU</t>
         </is>
       </c>
-      <c r="M70" s="8" t="inlineStr"/>
+      <c r="M70" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=99/2021/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -5249,10 +5531,14 @@
           <t>ALL, QUYET_TOAN, TAI_CHINH, TV-09, XD-01</t>
         </is>
       </c>
-      <c r="M71" s="15" t="inlineStr"/>
+      <c r="M71" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=96/2021/TT-BTC</t>
+        </is>
+      </c>
       <c r="N71" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5563,7 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Thông tư số 96/2021/TT-BTC quy định về hệ thống mẫu biểu hồ sơ quyết toán vốn đầu tư công dự án hoàn thành</t>
+          <t>Sửa đổi, bổ sung Thông tư số 96/2021/TT-BTC về mẫu biểu quyết toán vốn đầu tư công</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -5315,10 +5601,14 @@
           <t>ALL, QUYET_TOAN, TAI_CHINH, TV-09, XD-01</t>
         </is>
       </c>
-      <c r="M72" s="8" t="inlineStr"/>
+      <c r="M72" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=24/2024/TT-BTC</t>
+        </is>
+      </c>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -5373,7 +5663,7 @@
       </c>
       <c r="K73" s="10" t="inlineStr">
         <is>
-          <t>Quy định chi tiết thủ tục thẩm duyệt, nghiệm thu PCCC và cứu nạn cứu hộ số hóa mới nhất</t>
+          <t>Có hiệu lực từ 01/07/2025; cắt giảm danh mục thẩm duyệt PCCC; phân cấp Công an huyện/tỉnh; nộp trực tuyến DVC (05-07 ngày làm việc)</t>
         </is>
       </c>
       <c r="L73" s="10" t="inlineStr">
@@ -5381,10 +5671,14 @@
           <t>PCCC, TV-02, TV-03, TV-04, TV-05, XD-01</t>
         </is>
       </c>
-      <c r="M73" s="15" t="inlineStr"/>
+      <c r="M73" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=105/2025/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N73" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5703,7 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Quy định chi tiết một số điều và biện pháp thi hành Luật Phòng cháy và chữa cháy</t>
+          <t>Quy định chi tiết thi hành Luật Phòng cháy và chữa cháy (Hết hiệu lực 01/07/2025)</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
@@ -5447,10 +5741,14 @@
           <t>PCCC, LICHSU</t>
         </is>
       </c>
-      <c r="M74" s="8" t="inlineStr"/>
+      <c r="M74" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=136/2020/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -5475,7 +5773,7 @@
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 136/2020/NĐ-CP và Nghị định số 83/2017/NĐ-CP</t>
+          <t>Sửa đổi, bổ sung Nghị định số 136/2020/NĐ-CP về PCCC (Hết hiệu lực 01/07/2025)</t>
         </is>
       </c>
       <c r="F75" s="13" t="inlineStr">
@@ -5513,10 +5811,14 @@
           <t>PCCC, LICHSU</t>
         </is>
       </c>
-      <c r="M75" s="15" t="inlineStr"/>
+      <c r="M75" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=50/2024/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N75" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -5579,10 +5881,14 @@
           <t>PCCC, TV-02, TV-03, TV-04, TV-05, XD-01</t>
         </is>
       </c>
-      <c r="M76" s="8" t="inlineStr"/>
+      <c r="M76" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=QCVN%2006%3A2022/BXD</t>
+        </is>
+      </c>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5943,7 @@
       </c>
       <c r="K77" s="10" t="inlineStr">
         <is>
-          <t>Luật nền tảng về Đánh giá tác động môi trường (ĐTM), Giấy phép môi trường và Đăng ký môi trường</t>
+          <t>Luật nền tảng về ĐTM, Giấy phép môi trường và Đăng ký môi trường dự án</t>
         </is>
       </c>
       <c r="L77" s="10" t="inlineStr">
@@ -5645,10 +5951,14 @@
           <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
         </is>
       </c>
-      <c r="M77" s="15" t="inlineStr"/>
+      <c r="M77" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=72/2020/QH14</t>
+        </is>
+      </c>
       <c r="N77" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -5711,10 +6021,14 @@
           <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
         </is>
       </c>
-      <c r="M78" s="8" t="inlineStr"/>
+      <c r="M78" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=08/2022/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -5739,7 +6053,7 @@
       </c>
       <c r="E79" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP quy định chi tiết một số điều của Luật Bảo vệ môi trường</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định số 08/2022/NĐ-CP về bảo vệ môi trường</t>
         </is>
       </c>
       <c r="F79" s="13" t="inlineStr">
@@ -5777,10 +6091,14 @@
           <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
         </is>
       </c>
-      <c r="M79" s="15" t="inlineStr"/>
+      <c r="M79" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=05/2025/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N79" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -5805,7 +6123,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của các Nghị định quy định chi tiết Luật Bảo vệ môi trường</t>
+          <t>Sửa đổi, bổ sung các Nghị định quy định chi tiết Luật Bảo vệ môi trường</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
@@ -5835,7 +6153,7 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>Bãi bỏ cấp đổi GPMT, cho phép lập ĐTM cuốn chiếu theo từng giai đoạn dự án</t>
+          <t>Có hiệu lực từ 29/01/2026; bãi bỏ cấp đổi GPMT phức tạp; phân cấp thẩm định ĐTM; cho phép làm thủ tục môi trường song song với thiết kế xây dựng</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
@@ -5843,10 +6161,14 @@
           <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
         </is>
       </c>
-      <c r="M80" s="8" t="inlineStr"/>
+      <c r="M80" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=48/2026/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -5871,7 +6193,7 @@
       </c>
       <c r="E81" s="10" t="inlineStr">
         <is>
-          <t>Nghị quyết về việc tháo gỡ khó khăn, vướng mắc trong thực hiện thủ tục môi trường cho các dự án đầu tư công</t>
+          <t>Nghị quyết tháo gỡ khó khăn trong thực hiện thủ tục môi trường cho dự án đầu tư công</t>
         </is>
       </c>
       <c r="F81" s="13" t="inlineStr">
@@ -5896,7 +6218,7 @@
       </c>
       <c r="J81" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Văn bản gốc / Ban hành lần đầu</t>
         </is>
       </c>
       <c r="K81" s="10" t="inlineStr">
@@ -5909,10 +6231,14 @@
           <t>MOI_TRUONG, TV-01, TV-02, TV-03, TV-04, XD-01</t>
         </is>
       </c>
-      <c r="M81" s="15" t="inlineStr"/>
+      <c r="M81" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=66.19/2026/NQ-CP</t>
+        </is>
+      </c>
       <c r="N81" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -5975,10 +6301,14 @@
           <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
         </is>
       </c>
-      <c r="M82" s="8" t="inlineStr"/>
+      <c r="M82" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=15/2017/QH14</t>
+        </is>
+      </c>
       <c r="N82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -6041,10 +6371,14 @@
           <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
         </is>
       </c>
-      <c r="M83" s="15" t="inlineStr"/>
+      <c r="M83" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=151/2017/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N83" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -6069,7 +6403,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 151/2017/NĐ-CP quy định chi tiết một số điều của Luật Quản lý, sử dụng tài sản công</t>
+          <t>Sửa đổi, bổ sung một số điều của Nghị định 151/2017/NĐ-CP về quản lý tài sản công</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
@@ -6107,10 +6441,14 @@
           <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
         </is>
       </c>
-      <c r="M84" s="8" t="inlineStr"/>
+      <c r="M84" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=114/2024/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6473,7 @@
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 151/2017/NĐ-CP về quản lý, sử dụng tài sản công</t>
+          <t>Sửa đổi, bổ sung Nghị định số 151/2017/NĐ-CP về quản lý, sử dụng tài sản công</t>
         </is>
       </c>
       <c r="F85" s="13" t="inlineStr">
@@ -6173,10 +6511,14 @@
           <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
         </is>
       </c>
-      <c r="M85" s="15" t="inlineStr"/>
+      <c r="M85" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=186/2025/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N85" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6543,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Quy định việc sử dụng kinh phí chi thường xuyên ngân sách nhà nước để thực hiện mua sắm tài sản, trang thiết bị; cải tạo, nâng cấp, mở rộng, xây dựng mới hạng mục công trình trong các dự án đã đầu tư xây dựng</t>
+          <t>Quy định việc sử dụng kinh phí chi thường xuyên NSNN để mua sắm, cải tạo, sửa chữa tài sản công</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
@@ -6231,7 +6573,7 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>Phân cấp thẩm quyền quyết định dự toán mua sắm, cải tạo tài sản cho Thủ trưởng đơn vị dự toán</t>
+          <t>Có hiệu lực từ 01/05/2026; phân cấp Thủ trưởng đơn vị dự toán BQP phê duyệt dự toán sửa chữa cơ sở vật chất, doanh trại dưới 15 tỷ đồng</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
@@ -6239,10 +6581,14 @@
           <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
         </is>
       </c>
-      <c r="M86" s="8" t="inlineStr"/>
+      <c r="M86" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=104/2026/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6613,7 @@
       </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
-          <t>Quy định việc sử dụng kinh phí chi thường xuyên ngân sách nhà nước để thực hiện mua sắm tài sản, trang thiết bị; cải tạo, nâng cấp, mở rộng, xây dựng mới hạng mục công trình trong các dự án đã đầu tư xây dựng</t>
+          <t>Quy định sử dụng kinh phí chi thường xuyên mua sắm, cải tạo tài sản công (Hết hiệu lực)</t>
         </is>
       </c>
       <c r="F87" s="13" t="inlineStr">
@@ -6305,10 +6651,14 @@
           <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, LICHSU</t>
         </is>
       </c>
-      <c r="M87" s="15" t="inlineStr"/>
+      <c r="M87" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=138/2024/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N87" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6683,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>Sửa đổi, bổ sung một số điều của Nghị định số 138/2024/NĐ-CP về sử dụng kinh phí chi thường xuyên ngân sách nhà nước</t>
+          <t>Sửa đổi Nghị định 138/2024/NĐ-CP về sử dụng kinh phí chi thường xuyên (Hết hiệu lực)</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
@@ -6371,10 +6721,14 @@
           <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, LICHSU</t>
         </is>
       </c>
-      <c r="M88" s="8" t="inlineStr"/>
+      <c r="M88" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=98/2025/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -6437,10 +6791,14 @@
           <t>CHI_THUONG_XUYEN, TAI_SAN_CONG, SUA_CHUA, TV-01, TV-02, XD-01</t>
         </is>
       </c>
-      <c r="M89" s="15" t="inlineStr"/>
+      <c r="M89" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=65/2021/TT-BTC</t>
+        </is>
+      </c>
       <c r="N89" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -6503,10 +6861,14 @@
           <t>ALL, THE_THUC, TV-01, TV-02, TV-03, TV-04, TV-05, TV-06, TV-07, TV-08, TV-09, PTV-01, XD-01</t>
         </is>
       </c>
-      <c r="M90" s="8" t="inlineStr"/>
+      <c r="M90" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=30/2020/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -6556,7 +6918,7 @@
       </c>
       <c r="J91" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Văn bản gốc / Ban hành lần đầu</t>
         </is>
       </c>
       <c r="K91" s="10" t="inlineStr">
@@ -6569,10 +6931,14 @@
           <t>PPP, DAU_TU_CONG</t>
         </is>
       </c>
-      <c r="M91" s="15" t="inlineStr"/>
+      <c r="M91" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=64/2020/QH14</t>
+        </is>
+      </c>
       <c r="N91" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6988,7 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Văn bản gốc / Ban hành lần đầu</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr">
@@ -6635,10 +7001,14 @@
           <t>PPP, DAU_TU_CONG</t>
         </is>
       </c>
-      <c r="M92" s="8" t="inlineStr"/>
+      <c r="M92" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=35/2021/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -6701,10 +7071,14 @@
           <t>DAU_TU_KINH_DOANH</t>
         </is>
       </c>
-      <c r="M93" s="15" t="inlineStr"/>
+      <c r="M93" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=61/2020/QH14</t>
+        </is>
+      </c>
       <c r="N93" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -6754,7 +7128,7 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Văn bản gốc / Ban hành lần đầu</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
@@ -6767,10 +7141,14 @@
           <t>DAU_TU_KINH_DOANH</t>
         </is>
       </c>
-      <c r="M94" s="8" t="inlineStr"/>
+      <c r="M94" s="8" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=31/2021/N%C4%90-CP</t>
+        </is>
+      </c>
       <c r="N94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>
@@ -6820,7 +7198,7 @@
       </c>
       <c r="J95" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Văn bản gốc / Ban hành lần đầu</t>
         </is>
       </c>
       <c r="K95" s="10" t="inlineStr">
@@ -6833,10 +7211,14 @@
           <t>ALL, BQP, PHAN_CAP, QLDA, TV-01, TV-02, TV-03, TV-04, TV-05, TV-08, XD-01</t>
         </is>
       </c>
-      <c r="M95" s="15" t="inlineStr"/>
+      <c r="M95" s="15" t="inlineStr">
+        <is>
+          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=15/VBHN-BQP</t>
+        </is>
+      </c>
       <c r="N95" s="11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:02</t>
+          <t>2026-08-22 07:11</t>
         </is>
       </c>
     </row>

--- a/Kho_Can_Cu_Phap_Ly.xlsx
+++ b/Kho_Can_Cu_Phap_Ly.xlsx
@@ -703,12 +703,12 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=47/2024/QH15</t>
+          <t>https://www.google.com/search?q=47/2024/QH15%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="M3" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=30/2009/QH12</t>
+          <t>https://www.google.com/search?q=30/2009/QH12%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N3" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=178/2025/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=178/2025/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="M5" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=44/2015/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=44/2015/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N5" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=04/2022/TT-BXD</t>
+          <t>https://www.google.com/search?q=04/2022/TT-BXD%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="M7" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=20/2019/TT-BXD</t>
+          <t>https://www.google.com/search?q=20/2019/TT-BXD%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N7" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=QCVN%2001%3A2021/BXD</t>
+          <t>https://www.google.com/search?q=QCVN%2001%3A2021/BXD%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="M9" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=27/2018/QH14</t>
+          <t>https://www.google.com/search?q=27/2018/QH14%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="M10" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=27/2019/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=27/2019/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="M11" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=135/2025/QH15</t>
+          <t>https://www.google.com/search?q=135/2025/QH15%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=50/2014/QH13</t>
+          <t>https://www.google.com/search?q=50/2014/QH13%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="M13" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=62/2020/QH14</t>
+          <t>https://www.google.com/search?q=62/2020/QH14%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=217/2026/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=217/2026/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="M15" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=175/2024/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=175/2024/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -1683,12 +1683,12 @@
       </c>
       <c r="M16" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=15/2021/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=15/2021/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="M17" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=35/2023/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=35/2023/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=84/2015/QH13</t>
+          <t>https://www.google.com/search?q=84/2015/QH13%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -1893,12 +1893,12 @@
       </c>
       <c r="M19" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=22/2023/QH15</t>
+          <t>https://www.google.com/search?q=22/2023/QH15%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -1963,12 +1963,12 @@
       </c>
       <c r="M20" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=57/2024/QH15</t>
+          <t>https://www.google.com/search?q=57/2024/QH15%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -2033,12 +2033,12 @@
       </c>
       <c r="M21" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=90/2025/QH15</t>
+          <t>https://www.google.com/search?q=90/2025/QH15%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=43/2013/QH13</t>
+          <t>https://www.google.com/search?q=43/2013/QH13%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="M23" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=214/2025/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=214/2025/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -2243,12 +2243,12 @@
       </c>
       <c r="M24" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=24/2024/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=24/2024/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi 24/2024/NĐ-CP</t>
+          <t>Bị thay thế bởi Nghị định 24/2024/NĐ-CP, Bị thay thế bởi 24/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="K25" s="10" t="inlineStr">
@@ -2313,12 +2313,12 @@
       </c>
       <c r="M25" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=63/2014/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=63/2014/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -2383,12 +2383,12 @@
       </c>
       <c r="M26" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=79/2025/TT-BTC</t>
+          <t>https://www.google.com/search?q=79/2025/TT-BTC%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -2453,12 +2453,12 @@
       </c>
       <c r="M27" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=06/2024/TT-BKH%C4%90T</t>
+          <t>https://www.google.com/search?q=06/2024/TT-BKH%C4%90T%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N27" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -2523,12 +2523,12 @@
       </c>
       <c r="M28" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=80/2025/TT-BTC</t>
+          <t>https://www.google.com/search?q=80/2025/TT-BTC%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -2593,12 +2593,12 @@
       </c>
       <c r="M29" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=206/2026/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=206/2026/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N29" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="M30" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=10/2021/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=10/2021/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="M31" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=36/2026/TT-BXD</t>
+          <t>https://www.google.com/search?q=36/2026/TT-BXD%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N31" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -2803,12 +2803,12 @@
       </c>
       <c r="M32" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=38/2026/TT-BXD</t>
+          <t>https://www.google.com/search?q=38/2026/TT-BXD%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -2873,12 +2873,12 @@
       </c>
       <c r="M33" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=12/2021/TT-BXD</t>
+          <t>https://www.google.com/search?q=12/2021/TT-BXD%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N33" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -2943,12 +2943,12 @@
       </c>
       <c r="M34" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=09/2024/TT-BXD</t>
+          <t>https://www.google.com/search?q=09/2024/TT-BXD%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="M35" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=01/2025/TT-BXD</t>
+          <t>https://www.google.com/search?q=01/2025/TT-BXD%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N35" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -3083,12 +3083,12 @@
       </c>
       <c r="M36" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=11/2021/TT-BXD</t>
+          <t>https://www.google.com/search?q=11/2021/TT-BXD%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -3153,12 +3153,12 @@
       </c>
       <c r="M37" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=14/2023/TT-BXD</t>
+          <t>https://www.google.com/search?q=14/2023/TT-BXD%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N37" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="M38" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=13/2021/TT-BXD</t>
+          <t>https://www.google.com/search?q=13/2021/TT-BXD%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -3293,12 +3293,12 @@
       </c>
       <c r="M39" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=425/Q%C4%90-BXD</t>
+          <t>https://www.google.com/search?q=425/Q%C4%90-BXD%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -3363,12 +3363,12 @@
       </c>
       <c r="M40" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=510/Q%C4%90-BXD</t>
+          <t>https://www.google.com/search?q=510/Q%C4%90-BXD%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -3433,12 +3433,12 @@
       </c>
       <c r="M41" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=101/2026/TT-BQP</t>
+          <t>https://www.google.com/search?q=101/2026/TT-BQP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N41" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -3503,12 +3503,12 @@
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=102/2026/TT-BQP</t>
+          <t>https://www.google.com/search?q=102/2026/TT-BQP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="M43" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=128/2021/TT-BQP</t>
+          <t>https://www.google.com/search?q=128/2021/TT-BQP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N43" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -3643,12 +3643,12 @@
       </c>
       <c r="M44" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=73/2023/TT-BQP</t>
+          <t>https://www.google.com/search?q=73/2023/TT-BQP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -3713,12 +3713,12 @@
       </c>
       <c r="M45" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=120/2024/TT-BQP</t>
+          <t>https://www.google.com/search?q=120/2024/TT-BQP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N45" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -3783,12 +3783,12 @@
       </c>
       <c r="M46" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=174/2021/TT-BQP</t>
+          <t>https://www.google.com/search?q=174/2021/TT-BQP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -3853,12 +3853,12 @@
       </c>
       <c r="M47" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=24/2025/TT-BQP</t>
+          <t>https://www.google.com/search?q=24/2025/TT-BQP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N47" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="M48" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=36/2023/TT-BQP</t>
+          <t>https://www.google.com/search?q=36/2023/TT-BQP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -3993,12 +3993,12 @@
       </c>
       <c r="M49" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=150/2018/TT-BQP</t>
+          <t>https://www.google.com/search?q=150/2018/TT-BQP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N49" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -4063,12 +4063,12 @@
       </c>
       <c r="M50" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=94/2024/TT-BQP</t>
+          <t>https://www.google.com/search?q=94/2024/TT-BQP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -4133,12 +4133,12 @@
       </c>
       <c r="M51" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=35/Q%C4%90-TTg</t>
+          <t>https://www.google.com/search?q=35/Q%C4%90-TTg%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="M52" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=207/2026/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=207/2026/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="M53" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=06/2021/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=06/2021/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N53" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -4343,12 +4343,12 @@
       </c>
       <c r="M54" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=10/2021/TT-BXD</t>
+          <t>https://www.google.com/search?q=10/2021/TT-BXD%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -4413,12 +4413,12 @@
       </c>
       <c r="M55" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=210/2026/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=210/2026/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N55" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="M56" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=37/2015/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=37/2015/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -4553,12 +4553,12 @@
       </c>
       <c r="M57" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=50/2021/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=50/2021/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N57" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -4623,12 +4623,12 @@
       </c>
       <c r="M58" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=02/2023/TT-BXD</t>
+          <t>https://www.google.com/search?q=02/2023/TT-BXD%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -4693,12 +4693,12 @@
       </c>
       <c r="M59" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=TCVN%209393%3A2012</t>
+          <t>https://www.google.com/search?q=TCVN%209393%3A2012%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N59" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -4763,12 +4763,12 @@
       </c>
       <c r="M60" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=TCVN%209363%3A2012</t>
+          <t>https://www.google.com/search?q=TCVN%209363%3A2012%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -4833,12 +4833,12 @@
       </c>
       <c r="M61" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=TCVN%209401%3A2012</t>
+          <t>https://www.google.com/search?q=TCVN%209401%3A2012%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N61" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -4903,12 +4903,12 @@
       </c>
       <c r="M62" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=08/2022/QH15</t>
+          <t>https://www.google.com/search?q=08/2022/QH15%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -4973,12 +4973,12 @@
       </c>
       <c r="M63" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=67/2023/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=67/2023/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N63" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -5043,12 +5043,12 @@
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=67/2011/QH12</t>
+          <t>https://www.google.com/search?q=67/2011/QH12%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -5113,12 +5113,12 @@
       </c>
       <c r="M65" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=67/2015/TT-BTC</t>
+          <t>https://www.google.com/search?q=67/2015/TT-BTC%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N65" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="M66" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=58/2024/QH15</t>
+          <t>https://www.google.com/search?q=58/2024/QH15%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -5253,12 +5253,12 @@
       </c>
       <c r="M67" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=39/2019/QH14</t>
+          <t>https://www.google.com/search?q=39/2019/QH14%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N67" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -5323,12 +5323,12 @@
       </c>
       <c r="M68" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=40/2020/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=40/2020/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="M69" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=254/2025/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=254/2025/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N69" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="M70" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=99/2021/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=99/2021/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -5533,12 +5533,12 @@
       </c>
       <c r="M71" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=96/2021/TT-BTC</t>
+          <t>https://www.google.com/search?q=96/2021/TT-BTC%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N71" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -5603,12 +5603,12 @@
       </c>
       <c r="M72" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=24/2024/TT-BTC</t>
+          <t>https://www.google.com/search?q=24/2024/TT-BTC%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -5673,12 +5673,12 @@
       </c>
       <c r="M73" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=105/2025/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=105/2025/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N73" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="M74" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=136/2020/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=136/2020/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -5813,12 +5813,12 @@
       </c>
       <c r="M75" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=50/2024/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=50/2024/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N75" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="M76" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=QCVN%2006%3A2022/BXD</t>
+          <t>https://www.google.com/search?q=QCVN%2006%3A2022/BXD%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -5953,12 +5953,12 @@
       </c>
       <c r="M77" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=72/2020/QH14</t>
+          <t>https://www.google.com/search?q=72/2020/QH14%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N77" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -6023,12 +6023,12 @@
       </c>
       <c r="M78" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=08/2022/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=08/2022/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -6093,12 +6093,12 @@
       </c>
       <c r="M79" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=05/2025/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=05/2025/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N79" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -6163,12 +6163,12 @@
       </c>
       <c r="M80" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=48/2026/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=48/2026/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -6233,12 +6233,12 @@
       </c>
       <c r="M81" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=66.19/2026/NQ-CP</t>
+          <t>https://www.google.com/search?q=19/2026/NQ-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N81" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -6303,12 +6303,12 @@
       </c>
       <c r="M82" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=15/2017/QH14</t>
+          <t>https://www.google.com/search?q=15/2017/QH14%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -6373,12 +6373,12 @@
       </c>
       <c r="M83" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=151/2017/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=151/2017/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N83" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -6443,12 +6443,12 @@
       </c>
       <c r="M84" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=114/2024/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=114/2024/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -6513,12 +6513,12 @@
       </c>
       <c r="M85" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=186/2025/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=186/2025/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N85" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="M86" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=104/2026/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=104/2026/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -6653,12 +6653,12 @@
       </c>
       <c r="M87" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=138/2024/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=138/2024/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N87" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -6723,12 +6723,12 @@
       </c>
       <c r="M88" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=98/2025/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=98/2025/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -6793,12 +6793,12 @@
       </c>
       <c r="M89" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=65/2021/TT-BTC</t>
+          <t>https://www.google.com/search?q=65/2021/TT-BTC%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N89" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -6863,12 +6863,12 @@
       </c>
       <c r="M90" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=30/2020/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=30/2020/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -6933,12 +6933,12 @@
       </c>
       <c r="M91" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=64/2020/QH14</t>
+          <t>https://www.google.com/search?q=64/2020/QH14%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N91" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -7003,12 +7003,12 @@
       </c>
       <c r="M92" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=35/2021/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=35/2021/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -7073,12 +7073,12 @@
       </c>
       <c r="M93" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=61/2020/QH14</t>
+          <t>https://www.google.com/search?q=61/2020/QH14%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N93" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -7143,12 +7143,12 @@
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=31/2021/N%C4%90-CP</t>
+          <t>https://www.google.com/search?q=31/2021/N%C4%90-CP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>
@@ -7213,12 +7213,12 @@
       </c>
       <c r="M95" s="15" t="inlineStr">
         <is>
-          <t>https://thuvienphapluat.vn/page/tim-van-ban.aspx?keyword=15/VBHN-BQP</t>
+          <t>https://www.google.com/search?q=15/VBHN-BQP%20thuvienphapluat</t>
         </is>
       </c>
       <c r="N95" s="11" t="inlineStr">
         <is>
-          <t>2026-08-22 07:11</t>
+          <t>2026-08-22 07:31</t>
         </is>
       </c>
     </row>

--- a/Kho_Can_Cu_Phap_Ly.xlsx
+++ b/Kho_Can_Cu_Phap_Ly.xlsx
@@ -2298,7 +2298,7 @@
       </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
-          <t>Bị thay thế bởi Nghị định 24/2024/NĐ-CP, Bị thay thế bởi 24/2024/NĐ-CP</t>
+          <t>Bị thay thế bởi 24/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="K25" s="10" t="inlineStr">

--- a/Kho_Can_Cu_Phap_Ly.xlsx
+++ b/Kho_Can_Cu_Phap_Ly.xlsx
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N95"/>
+  <dimension ref="A1:N96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2151,14 +2151,14 @@
           <t>04/08/2025</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>Đang có hiệu lực</t>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Hết hiệu lực</t>
         </is>
       </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 24/2024/NĐ-CP và Nghị định 63/2014/NĐ-CP</t>
+          <t>Thay thế Nghị định 24/2024/NĐ-CP và Nghị định 63/2014/NĐ-CP, Bị thay thế bởi 24/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="K23" s="10" t="inlineStr">
@@ -7219,6 +7219,76 @@
       <c r="N95" s="11" t="inlineStr">
         <is>
           <t>2026-08-22 07:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="26" customHeight="1">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Xây dựng &amp; Đấu thầu</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>Nghị định</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>42/2026/QĐ-TTg</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>Quyết định 42/2026/QĐ-TTg Ban hành Danh mục lĩnh vực, cơ sở phát thải khí nhà kính phải thực hiện kiểm kê khí nhà kính (cập nhật)</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>Thủ tướng Chính phủ</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="I96" s="7" t="inlineStr">
+        <is>
+          <t>Đang có hiệu lực</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>Áp dụng theo quy định ban hành mới</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>Quyết định 42/2026/QĐ-TTg Ban hành Danh mục lĩnh vực, cơ sở phát thải khí nhà kính phải thực hiện kiểm kê khí nhà kính (cập nhật) Quy định danh mục các lĩnh vực sản xuất, công trìn</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>#Xây_dựng, #Đấu_thầu, #Dự_án</t>
+        </is>
+      </c>
+      <c r="M96" s="8" t="inlineStr">
+        <is>
+          <t>https://telegra.ph/BÁO-CÁO-PHÂN-TÍCH-Quyết-định-422026QĐ-TTg-Ban-hành-Danh-mục-lĩnh-vực-cơ-sở-phát-thải-khí-nhà-kín-08-22</t>
+        </is>
+      </c>
+      <c r="N96" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-22 07:46</t>
         </is>
       </c>
     </row>

--- a/Kho_Can_Cu_Phap_Ly.xlsx
+++ b/Kho_Can_Cu_Phap_Ly.xlsx
@@ -2158,7 +2158,7 @@
       </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
-          <t>Thay thế Nghị định 24/2024/NĐ-CP và Nghị định 63/2014/NĐ-CP, Bị thay thế bởi 24/2024/NĐ-CP</t>
+          <t>Bị thay thế bởi 24/2024/NĐ-CP</t>
         </is>
       </c>
       <c r="K23" s="10" t="inlineStr">
